--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\0 -docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\Mermisi-main\Journals\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
   <si>
     <t>რიცხვი</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>`</t>
+  </si>
+  <si>
+    <t>18,09,2026</t>
   </si>
 </sst>
 </file>
@@ -488,7 +491,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -541,98 +544,94 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -878,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DU31"/>
+  <dimension ref="A1:BX31"/>
   <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="2"/>
@@ -887,33 +886,38 @@
     <col min="5" max="5" width="14.5703125" style="1" customWidth="1"/>
     <col min="6" max="36" width="3.5703125" style="1"/>
     <col min="37" max="37" width="3.5703125" style="1" customWidth="1"/>
-    <col min="38" max="101" width="3.5703125" style="1"/>
-    <col min="102" max="102" width="3.28515625" style="1" customWidth="1"/>
-    <col min="103" max="103" width="3" style="1" customWidth="1"/>
-    <col min="104" max="124" width="3.5703125" style="1"/>
-    <col min="125" max="125" width="5.140625" style="1" customWidth="1"/>
-    <col min="126" max="16384" width="3.5703125" style="1"/>
+    <col min="38" max="75" width="3.5703125" style="1"/>
+    <col min="76" max="76" width="5.140625" style="1" customWidth="1"/>
+    <col min="77" max="16384" width="3.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="46"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
       <c r="F1" s="25">
         <v>3</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="24">
+        <v>1</v>
+      </c>
+      <c r="J1" s="25">
+        <v>2</v>
+      </c>
+      <c r="K1" s="26"/>
+      <c r="L1" s="25">
+        <v>2</v>
+      </c>
+      <c r="M1" s="26"/>
+      <c r="N1" s="25">
+        <v>2</v>
+      </c>
+      <c r="O1" s="26"/>
       <c r="P1" s="23"/>
       <c r="Q1" s="23"/>
       <c r="R1" s="23"/>
@@ -974,1346 +978,821 @@
       <c r="BU1" s="23"/>
       <c r="BV1" s="23"/>
       <c r="BW1" s="23"/>
-      <c r="BX1" s="23"/>
-      <c r="BY1" s="23"/>
-      <c r="BZ1" s="23"/>
-      <c r="CA1" s="23"/>
-      <c r="CB1" s="23"/>
-      <c r="CC1" s="23"/>
-      <c r="CD1" s="23"/>
-      <c r="CE1" s="23"/>
-      <c r="CF1" s="23"/>
-      <c r="CG1" s="23"/>
-      <c r="CH1" s="23"/>
-      <c r="CI1" s="23"/>
-      <c r="CJ1" s="23"/>
-      <c r="CK1" s="23"/>
-      <c r="CL1" s="23"/>
-      <c r="CM1" s="23"/>
-      <c r="CN1" s="23"/>
-      <c r="CO1" s="23"/>
-      <c r="CP1" s="23"/>
-      <c r="CQ1" s="23"/>
-      <c r="CR1" s="23"/>
-      <c r="CS1" s="23"/>
-      <c r="CT1" s="23"/>
-      <c r="CU1" s="23"/>
-      <c r="CV1" s="23"/>
-      <c r="CW1" s="23"/>
-      <c r="CX1" s="23"/>
-      <c r="CY1" s="23"/>
-      <c r="CZ1" s="23"/>
-      <c r="DA1" s="23"/>
-      <c r="DB1" s="23"/>
-      <c r="DC1" s="23"/>
-      <c r="DD1" s="23"/>
-      <c r="DE1" s="23"/>
-      <c r="DF1" s="23"/>
-      <c r="DG1" s="23"/>
-      <c r="DH1" s="23"/>
-      <c r="DI1" s="24"/>
-      <c r="DJ1" s="24"/>
-      <c r="DK1" s="24"/>
-      <c r="DL1" s="24"/>
-      <c r="DM1" s="24"/>
-      <c r="DN1" s="24"/>
-      <c r="DO1" s="24"/>
-      <c r="DP1" s="24"/>
-      <c r="DQ1" s="24"/>
-      <c r="DR1" s="24"/>
-      <c r="DS1" s="24"/>
-      <c r="DT1" s="24"/>
-      <c r="DU1" s="1">
-        <f>SUM(F1:DT1)</f>
+      <c r="BX1" s="2">
+        <f>SUM(F1:BW1)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="29">
+        <v>46274</v>
+      </c>
+      <c r="G2" s="29">
+        <v>46274</v>
+      </c>
+      <c r="H2" s="29">
+        <v>46274</v>
+      </c>
+      <c r="I2" s="29">
+        <v>46276</v>
+      </c>
+      <c r="J2" s="29">
+        <v>46279</v>
+      </c>
+      <c r="K2" s="29">
+        <v>46279</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="29">
+        <v>46286</v>
+      </c>
+      <c r="O2" s="29">
+        <v>46286</v>
+      </c>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+      <c r="AT2" s="29"/>
+      <c r="AU2" s="29"/>
+      <c r="AV2" s="29"/>
+      <c r="AW2" s="29"/>
+      <c r="AX2" s="29"/>
+      <c r="AY2" s="29"/>
+      <c r="AZ2" s="29"/>
+      <c r="BA2" s="29"/>
+      <c r="BB2" s="29"/>
+      <c r="BC2" s="29"/>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="29"/>
+      <c r="BG2" s="29"/>
+      <c r="BH2" s="29"/>
+      <c r="BI2" s="29"/>
+      <c r="BJ2" s="29"/>
+      <c r="BK2" s="29"/>
+      <c r="BL2" s="29"/>
+      <c r="BM2" s="29"/>
+      <c r="BN2" s="29"/>
+      <c r="BO2" s="29"/>
+      <c r="BP2" s="29"/>
+      <c r="BQ2" s="29"/>
+      <c r="BR2" s="29"/>
+      <c r="BS2" s="29"/>
+      <c r="BT2" s="29"/>
+      <c r="BU2" s="29"/>
+      <c r="BV2" s="29"/>
+      <c r="BW2" s="29"/>
+    </row>
+    <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="29"/>
+      <c r="AC3" s="29"/>
+      <c r="AD3" s="29"/>
+      <c r="AE3" s="29"/>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="29"/>
+      <c r="AH3" s="29"/>
+      <c r="AI3" s="29"/>
+      <c r="AJ3" s="29"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="29"/>
+      <c r="AN3" s="29"/>
+      <c r="AO3" s="29"/>
+      <c r="AP3" s="29"/>
+      <c r="AQ3" s="29"/>
+      <c r="AR3" s="29"/>
+      <c r="AS3" s="29"/>
+      <c r="AT3" s="29"/>
+      <c r="AU3" s="29"/>
+      <c r="AV3" s="29"/>
+      <c r="AW3" s="29"/>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+      <c r="AZ3" s="29"/>
+      <c r="BA3" s="29"/>
+      <c r="BB3" s="29"/>
+      <c r="BC3" s="29"/>
+      <c r="BD3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="29"/>
+      <c r="BG3" s="29"/>
+      <c r="BH3" s="29"/>
+      <c r="BI3" s="29"/>
+      <c r="BJ3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="29"/>
+      <c r="BO3" s="29"/>
+      <c r="BP3" s="29"/>
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="29"/>
+      <c r="BS3" s="29"/>
+      <c r="BT3" s="29"/>
+      <c r="BU3" s="29"/>
+      <c r="BV3" s="29"/>
+      <c r="BW3" s="29"/>
+    </row>
+    <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="29"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="29"/>
+      <c r="AX4" s="29"/>
+      <c r="AY4" s="29"/>
+      <c r="AZ4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+      <c r="BC4" s="29"/>
+      <c r="BD4" s="29"/>
+      <c r="BE4" s="29"/>
+      <c r="BF4" s="29"/>
+      <c r="BG4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="29"/>
+      <c r="BJ4" s="29"/>
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="29"/>
+      <c r="BM4" s="29"/>
+      <c r="BN4" s="29"/>
+      <c r="BO4" s="29"/>
+      <c r="BP4" s="29"/>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="29"/>
+      <c r="BS4" s="29"/>
+      <c r="BT4" s="29"/>
+      <c r="BU4" s="29"/>
+      <c r="BV4" s="29"/>
+      <c r="BW4" s="29"/>
+    </row>
+    <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="48" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:125" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="30">
-        <v>46274</v>
-      </c>
-      <c r="G2" s="30">
-        <v>46274</v>
-      </c>
-      <c r="H2" s="30">
-        <v>46274</v>
-      </c>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="30"/>
-      <c r="AI2" s="30"/>
-      <c r="AJ2" s="30"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="30"/>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-      <c r="AT2" s="30"/>
-      <c r="AU2" s="30"/>
-      <c r="AV2" s="30"/>
-      <c r="AW2" s="30"/>
-      <c r="AX2" s="30"/>
-      <c r="AY2" s="30"/>
-      <c r="AZ2" s="30"/>
-      <c r="BA2" s="30"/>
-      <c r="BB2" s="30"/>
-      <c r="BC2" s="30"/>
-      <c r="BD2" s="30"/>
-      <c r="BE2" s="30"/>
-      <c r="BF2" s="30"/>
-      <c r="BG2" s="30"/>
-      <c r="BH2" s="30"/>
-      <c r="BI2" s="30"/>
-      <c r="BJ2" s="30"/>
-      <c r="BK2" s="30"/>
-      <c r="BL2" s="30"/>
-      <c r="BM2" s="30"/>
-      <c r="BN2" s="30"/>
-      <c r="BO2" s="30"/>
-      <c r="BP2" s="30"/>
-      <c r="BQ2" s="30"/>
-      <c r="BR2" s="30"/>
-      <c r="BS2" s="30"/>
-      <c r="BT2" s="30"/>
-      <c r="BU2" s="30"/>
-      <c r="BV2" s="30"/>
-      <c r="BW2" s="30"/>
-      <c r="BX2" s="30"/>
-      <c r="BY2" s="30"/>
-      <c r="BZ2" s="30"/>
-      <c r="CA2" s="30"/>
-      <c r="CB2" s="30"/>
-      <c r="CC2" s="30"/>
-      <c r="CD2" s="30"/>
-      <c r="CE2" s="30"/>
-      <c r="CF2" s="30"/>
-      <c r="CG2" s="30"/>
-      <c r="CH2" s="30"/>
-      <c r="CI2" s="30"/>
-      <c r="CJ2" s="30"/>
-      <c r="CK2" s="30"/>
-      <c r="CL2" s="30"/>
-      <c r="CM2" s="30"/>
-      <c r="CN2" s="30"/>
-      <c r="CO2" s="30"/>
-      <c r="CP2" s="30"/>
-      <c r="CQ2" s="30"/>
-      <c r="CR2" s="30"/>
-      <c r="CS2" s="30"/>
-      <c r="CT2" s="30"/>
-      <c r="CU2" s="30"/>
-      <c r="CV2" s="30"/>
-      <c r="CW2" s="30"/>
-      <c r="CX2" s="30"/>
-      <c r="CY2" s="30"/>
-      <c r="CZ2" s="30"/>
-      <c r="DA2" s="30"/>
-      <c r="DB2" s="30"/>
-      <c r="DC2" s="30"/>
-      <c r="DD2" s="30"/>
-      <c r="DE2" s="30"/>
-      <c r="DF2" s="30"/>
-      <c r="DG2" s="30"/>
-      <c r="DH2" s="30"/>
-      <c r="DI2" s="30"/>
-      <c r="DJ2" s="30"/>
-      <c r="DK2" s="30"/>
-      <c r="DL2" s="30"/>
-      <c r="DM2" s="30"/>
-      <c r="DN2" s="30"/>
-      <c r="DO2" s="30"/>
-      <c r="DP2" s="30"/>
-      <c r="DQ2" s="30"/>
-      <c r="DR2" s="30"/>
-      <c r="DS2" s="30"/>
-      <c r="DT2" s="30"/>
-    </row>
-    <row r="3" spans="1:125" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30"/>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="30"/>
-      <c r="BH3" s="30"/>
-      <c r="BI3" s="30"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="30"/>
-      <c r="BL3" s="30"/>
-      <c r="BM3" s="30"/>
-      <c r="BN3" s="30"/>
-      <c r="BO3" s="30"/>
-      <c r="BP3" s="30"/>
-      <c r="BQ3" s="30"/>
-      <c r="BR3" s="30"/>
-      <c r="BS3" s="30"/>
-      <c r="BT3" s="30"/>
-      <c r="BU3" s="30"/>
-      <c r="BV3" s="30"/>
-      <c r="BW3" s="30"/>
-      <c r="BX3" s="30"/>
-      <c r="BY3" s="30"/>
-      <c r="BZ3" s="30"/>
-      <c r="CA3" s="30"/>
-      <c r="CB3" s="30"/>
-      <c r="CC3" s="30"/>
-      <c r="CD3" s="30"/>
-      <c r="CE3" s="30"/>
-      <c r="CF3" s="30"/>
-      <c r="CG3" s="30"/>
-      <c r="CH3" s="30"/>
-      <c r="CI3" s="30"/>
-      <c r="CJ3" s="30"/>
-      <c r="CK3" s="30"/>
-      <c r="CL3" s="30"/>
-      <c r="CM3" s="30"/>
-      <c r="CN3" s="30"/>
-      <c r="CO3" s="30"/>
-      <c r="CP3" s="30"/>
-      <c r="CQ3" s="30"/>
-      <c r="CR3" s="30"/>
-      <c r="CS3" s="30"/>
-      <c r="CT3" s="30"/>
-      <c r="CU3" s="30"/>
-      <c r="CV3" s="30"/>
-      <c r="CW3" s="30"/>
-      <c r="CX3" s="30"/>
-      <c r="CY3" s="30"/>
-      <c r="CZ3" s="30"/>
-      <c r="DA3" s="30"/>
-      <c r="DB3" s="30"/>
-      <c r="DC3" s="30"/>
-      <c r="DD3" s="30"/>
-      <c r="DE3" s="30"/>
-      <c r="DF3" s="30"/>
-      <c r="DG3" s="30"/>
-      <c r="DH3" s="30"/>
-      <c r="DI3" s="30"/>
-      <c r="DJ3" s="30"/>
-      <c r="DK3" s="30"/>
-      <c r="DL3" s="30"/>
-      <c r="DM3" s="30"/>
-      <c r="DN3" s="30"/>
-      <c r="DO3" s="30"/>
-      <c r="DP3" s="30"/>
-      <c r="DQ3" s="30"/>
-      <c r="DR3" s="30"/>
-      <c r="DS3" s="30"/>
-      <c r="DT3" s="30"/>
-    </row>
-    <row r="4" spans="1:125" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="30"/>
-      <c r="AI4" s="30"/>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="30"/>
-      <c r="AL4" s="30"/>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="30"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="30"/>
-      <c r="AU4" s="30"/>
-      <c r="AV4" s="30"/>
-      <c r="AW4" s="30"/>
-      <c r="AX4" s="30"/>
-      <c r="AY4" s="30"/>
-      <c r="AZ4" s="30"/>
-      <c r="BA4" s="30"/>
-      <c r="BB4" s="30"/>
-      <c r="BC4" s="30"/>
-      <c r="BD4" s="30"/>
-      <c r="BE4" s="30"/>
-      <c r="BF4" s="30"/>
-      <c r="BG4" s="30"/>
-      <c r="BH4" s="30"/>
-      <c r="BI4" s="30"/>
-      <c r="BJ4" s="30"/>
-      <c r="BK4" s="30"/>
-      <c r="BL4" s="30"/>
-      <c r="BM4" s="30"/>
-      <c r="BN4" s="30"/>
-      <c r="BO4" s="30"/>
-      <c r="BP4" s="30"/>
-      <c r="BQ4" s="30"/>
-      <c r="BR4" s="30"/>
-      <c r="BS4" s="30"/>
-      <c r="BT4" s="30"/>
-      <c r="BU4" s="30"/>
-      <c r="BV4" s="30"/>
-      <c r="BW4" s="30"/>
-      <c r="BX4" s="30"/>
-      <c r="BY4" s="30"/>
-      <c r="BZ4" s="30"/>
-      <c r="CA4" s="30"/>
-      <c r="CB4" s="30"/>
-      <c r="CC4" s="30"/>
-      <c r="CD4" s="30"/>
-      <c r="CE4" s="30"/>
-      <c r="CF4" s="30"/>
-      <c r="CG4" s="30"/>
-      <c r="CH4" s="30"/>
-      <c r="CI4" s="30"/>
-      <c r="CJ4" s="30"/>
-      <c r="CK4" s="30"/>
-      <c r="CL4" s="30"/>
-      <c r="CM4" s="30"/>
-      <c r="CN4" s="30"/>
-      <c r="CO4" s="30"/>
-      <c r="CP4" s="30"/>
-      <c r="CQ4" s="30"/>
-      <c r="CR4" s="30"/>
-      <c r="CS4" s="30"/>
-      <c r="CT4" s="30"/>
-      <c r="CU4" s="30"/>
-      <c r="CV4" s="30"/>
-      <c r="CW4" s="30"/>
-      <c r="CX4" s="30"/>
-      <c r="CY4" s="30"/>
-      <c r="CZ4" s="30"/>
-      <c r="DA4" s="30"/>
-      <c r="DB4" s="30"/>
-      <c r="DC4" s="30"/>
-      <c r="DD4" s="30"/>
-      <c r="DE4" s="30"/>
-      <c r="DF4" s="30"/>
-      <c r="DG4" s="30"/>
-      <c r="DH4" s="30"/>
-      <c r="DI4" s="30"/>
-      <c r="DJ4" s="30"/>
-      <c r="DK4" s="30"/>
-      <c r="DL4" s="30"/>
-      <c r="DM4" s="30"/>
-      <c r="DN4" s="30"/>
-      <c r="DO4" s="30"/>
-      <c r="DP4" s="30"/>
-      <c r="DQ4" s="30"/>
-      <c r="DR4" s="30"/>
-      <c r="DS4" s="30"/>
-      <c r="DT4" s="30"/>
-    </row>
-    <row r="5" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
         <v>60</v>
       </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="30"/>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="30"/>
-      <c r="AG5" s="30"/>
-      <c r="AH5" s="30"/>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="30"/>
-      <c r="AK5" s="30"/>
-      <c r="AL5" s="30"/>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-      <c r="AT5" s="30"/>
-      <c r="AU5" s="30"/>
-      <c r="AV5" s="30"/>
-      <c r="AW5" s="30"/>
-      <c r="AX5" s="30"/>
-      <c r="AY5" s="30"/>
-      <c r="AZ5" s="30"/>
-      <c r="BA5" s="30"/>
-      <c r="BB5" s="30"/>
-      <c r="BC5" s="30"/>
-      <c r="BD5" s="30"/>
-      <c r="BE5" s="30"/>
-      <c r="BF5" s="30"/>
-      <c r="BG5" s="30"/>
-      <c r="BH5" s="30"/>
-      <c r="BI5" s="30"/>
-      <c r="BJ5" s="30"/>
-      <c r="BK5" s="30"/>
-      <c r="BL5" s="30"/>
-      <c r="BM5" s="30"/>
-      <c r="BN5" s="30"/>
-      <c r="BO5" s="30"/>
-      <c r="BP5" s="30"/>
-      <c r="BQ5" s="30"/>
-      <c r="BR5" s="30"/>
-      <c r="BS5" s="30"/>
-      <c r="BT5" s="30"/>
-      <c r="BU5" s="30"/>
-      <c r="BV5" s="30"/>
-      <c r="BW5" s="30"/>
-      <c r="BX5" s="30"/>
-      <c r="BY5" s="30"/>
-      <c r="BZ5" s="30"/>
-      <c r="CA5" s="30"/>
-      <c r="CB5" s="30"/>
-      <c r="CC5" s="30"/>
-      <c r="CD5" s="30"/>
-      <c r="CE5" s="30"/>
-      <c r="CF5" s="30"/>
-      <c r="CG5" s="30"/>
-      <c r="CH5" s="30"/>
-      <c r="CI5" s="30"/>
-      <c r="CJ5" s="30"/>
-      <c r="CK5" s="30"/>
-      <c r="CL5" s="30"/>
-      <c r="CM5" s="30"/>
-      <c r="CN5" s="30"/>
-      <c r="CO5" s="30"/>
-      <c r="CP5" s="30"/>
-      <c r="CQ5" s="30"/>
-      <c r="CR5" s="30"/>
-      <c r="CS5" s="30"/>
-      <c r="CT5" s="30"/>
-      <c r="CU5" s="30"/>
-      <c r="CV5" s="30"/>
-      <c r="CW5" s="30"/>
-      <c r="CX5" s="30"/>
-      <c r="CY5" s="30"/>
-      <c r="CZ5" s="30"/>
-      <c r="DA5" s="30"/>
-      <c r="DB5" s="30"/>
-      <c r="DC5" s="30"/>
-      <c r="DD5" s="30"/>
-      <c r="DE5" s="30"/>
-      <c r="DF5" s="30"/>
-      <c r="DG5" s="30"/>
-      <c r="DH5" s="30"/>
-      <c r="DI5" s="30"/>
-      <c r="DJ5" s="30"/>
-      <c r="DK5" s="30"/>
-      <c r="DL5" s="30"/>
-      <c r="DM5" s="30"/>
-      <c r="DN5" s="30"/>
-      <c r="DO5" s="30"/>
-      <c r="DP5" s="30"/>
-      <c r="DQ5" s="30"/>
-      <c r="DR5" s="30"/>
-      <c r="DS5" s="30"/>
-      <c r="DT5" s="30"/>
-    </row>
-    <row r="6" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="D5" s="50"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="29"/>
+      <c r="BS5" s="29"/>
+      <c r="BT5" s="29"/>
+      <c r="BU5" s="29"/>
+      <c r="BV5" s="29"/>
+      <c r="BW5" s="29"/>
+    </row>
+    <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
         <v>4</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="30"/>
-      <c r="AO6" s="30"/>
-      <c r="AP6" s="30"/>
-      <c r="AQ6" s="30"/>
-      <c r="AR6" s="30"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="30"/>
-      <c r="AU6" s="30"/>
-      <c r="AV6" s="30"/>
-      <c r="AW6" s="30"/>
-      <c r="AX6" s="30"/>
-      <c r="AY6" s="30"/>
-      <c r="AZ6" s="30"/>
-      <c r="BA6" s="30"/>
-      <c r="BB6" s="30"/>
-      <c r="BC6" s="30"/>
-      <c r="BD6" s="30"/>
-      <c r="BE6" s="30"/>
-      <c r="BF6" s="30"/>
-      <c r="BG6" s="30"/>
-      <c r="BH6" s="30"/>
-      <c r="BI6" s="30"/>
-      <c r="BJ6" s="30"/>
-      <c r="BK6" s="30"/>
-      <c r="BL6" s="30"/>
-      <c r="BM6" s="30"/>
-      <c r="BN6" s="30"/>
-      <c r="BO6" s="30"/>
-      <c r="BP6" s="30"/>
-      <c r="BQ6" s="30"/>
-      <c r="BR6" s="30"/>
-      <c r="BS6" s="30"/>
-      <c r="BT6" s="30"/>
-      <c r="BU6" s="30"/>
-      <c r="BV6" s="30"/>
-      <c r="BW6" s="30"/>
-      <c r="BX6" s="30"/>
-      <c r="BY6" s="30"/>
-      <c r="BZ6" s="30"/>
-      <c r="CA6" s="30"/>
-      <c r="CB6" s="30"/>
-      <c r="CC6" s="30"/>
-      <c r="CD6" s="30"/>
-      <c r="CE6" s="30"/>
-      <c r="CF6" s="30"/>
-      <c r="CG6" s="30"/>
-      <c r="CH6" s="30"/>
-      <c r="CI6" s="30"/>
-      <c r="CJ6" s="30"/>
-      <c r="CK6" s="30"/>
-      <c r="CL6" s="30"/>
-      <c r="CM6" s="30"/>
-      <c r="CN6" s="30"/>
-      <c r="CO6" s="30"/>
-      <c r="CP6" s="30"/>
-      <c r="CQ6" s="30"/>
-      <c r="CR6" s="30"/>
-      <c r="CS6" s="30"/>
-      <c r="CT6" s="30"/>
-      <c r="CU6" s="30"/>
-      <c r="CV6" s="30"/>
-      <c r="CW6" s="30"/>
-      <c r="CX6" s="30"/>
-      <c r="CY6" s="30"/>
-      <c r="CZ6" s="30"/>
-      <c r="DA6" s="30"/>
-      <c r="DB6" s="30"/>
-      <c r="DC6" s="30"/>
-      <c r="DD6" s="30"/>
-      <c r="DE6" s="30"/>
-      <c r="DF6" s="30"/>
-      <c r="DG6" s="30"/>
-      <c r="DH6" s="30"/>
-      <c r="DI6" s="30"/>
-      <c r="DJ6" s="30"/>
-      <c r="DK6" s="30"/>
-      <c r="DL6" s="30"/>
-      <c r="DM6" s="30"/>
-      <c r="DN6" s="30"/>
-      <c r="DO6" s="30"/>
-      <c r="DP6" s="30"/>
-      <c r="DQ6" s="30"/>
-      <c r="DR6" s="30"/>
-      <c r="DS6" s="30"/>
-      <c r="DT6" s="30"/>
-    </row>
-    <row r="7" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="D6" s="50"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="29"/>
+      <c r="BD6" s="29"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BG6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="29"/>
+      <c r="BJ6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="29"/>
+      <c r="BM6" s="29"/>
+      <c r="BN6" s="29"/>
+      <c r="BO6" s="29"/>
+      <c r="BP6" s="29"/>
+      <c r="BQ6" s="29"/>
+      <c r="BR6" s="29"/>
+      <c r="BS6" s="29"/>
+      <c r="BT6" s="29"/>
+      <c r="BU6" s="29"/>
+      <c r="BV6" s="29"/>
+      <c r="BW6" s="29"/>
+    </row>
+    <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="41">
+      <c r="B7" s="51"/>
+      <c r="C7" s="49">
         <v>11</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="31"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="31"/>
-      <c r="AC7" s="31"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="31"/>
-      <c r="AF7" s="31"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="31"/>
-      <c r="AI7" s="31"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="31"/>
-      <c r="AL7" s="31"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="31"/>
-      <c r="AO7" s="31"/>
-      <c r="AP7" s="31"/>
-      <c r="AQ7" s="31"/>
-      <c r="AR7" s="31"/>
-      <c r="AS7" s="31"/>
-      <c r="AT7" s="31"/>
-      <c r="AU7" s="31"/>
-      <c r="AV7" s="31"/>
-      <c r="AW7" s="31"/>
-      <c r="AX7" s="31"/>
-      <c r="AY7" s="31"/>
-      <c r="AZ7" s="31"/>
-      <c r="BA7" s="31"/>
-      <c r="BB7" s="31"/>
-      <c r="BC7" s="31"/>
-      <c r="BD7" s="31"/>
-      <c r="BE7" s="31"/>
-      <c r="BF7" s="31"/>
-      <c r="BG7" s="31"/>
-      <c r="BH7" s="31"/>
-      <c r="BI7" s="31"/>
-      <c r="BJ7" s="31"/>
-      <c r="BK7" s="31"/>
-      <c r="BL7" s="31"/>
-      <c r="BM7" s="31"/>
-      <c r="BN7" s="31"/>
-      <c r="BO7" s="31"/>
-      <c r="BP7" s="31"/>
-      <c r="BQ7" s="31"/>
-      <c r="BR7" s="31"/>
-      <c r="BS7" s="31"/>
-      <c r="BT7" s="31"/>
-      <c r="BU7" s="31"/>
-      <c r="BV7" s="31"/>
-      <c r="BW7" s="31"/>
-      <c r="BX7" s="31"/>
-      <c r="BY7" s="31"/>
-      <c r="BZ7" s="31"/>
-      <c r="CA7" s="31"/>
-      <c r="CB7" s="31"/>
-      <c r="CC7" s="31"/>
-      <c r="CD7" s="31"/>
-      <c r="CE7" s="31"/>
-      <c r="CF7" s="31"/>
-      <c r="CG7" s="31"/>
-      <c r="CH7" s="31"/>
-      <c r="CI7" s="31"/>
-      <c r="CJ7" s="31"/>
-      <c r="CK7" s="31"/>
-      <c r="CL7" s="31"/>
-      <c r="CM7" s="31"/>
-      <c r="CN7" s="31"/>
-      <c r="CO7" s="31"/>
-      <c r="CP7" s="31"/>
-      <c r="CQ7" s="31"/>
-      <c r="CR7" s="31"/>
-      <c r="CS7" s="31"/>
-      <c r="CT7" s="31"/>
-      <c r="CU7" s="31"/>
-      <c r="CV7" s="31"/>
-      <c r="CW7" s="31"/>
-      <c r="CX7" s="31"/>
-      <c r="CY7" s="31"/>
-      <c r="CZ7" s="31"/>
-      <c r="DA7" s="31"/>
-      <c r="DB7" s="31"/>
-      <c r="DC7" s="31"/>
-      <c r="DD7" s="31"/>
-      <c r="DE7" s="31"/>
-      <c r="DF7" s="31"/>
-      <c r="DG7" s="31"/>
-      <c r="DH7" s="31"/>
-      <c r="DI7" s="31"/>
-      <c r="DJ7" s="31"/>
-      <c r="DK7" s="31"/>
-      <c r="DL7" s="31"/>
-      <c r="DM7" s="31"/>
-      <c r="DN7" s="31"/>
-      <c r="DO7" s="31"/>
-      <c r="DP7" s="31"/>
-      <c r="DQ7" s="31"/>
-      <c r="DR7" s="31"/>
-      <c r="DS7" s="31"/>
-      <c r="DT7" s="31"/>
-    </row>
-    <row r="8" spans="1:125" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
+      <c r="D7" s="50"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="30"/>
+      <c r="AU7" s="30"/>
+      <c r="AV7" s="30"/>
+      <c r="AW7" s="30"/>
+      <c r="AX7" s="30"/>
+      <c r="AY7" s="30"/>
+      <c r="AZ7" s="30"/>
+      <c r="BA7" s="30"/>
+      <c r="BB7" s="30"/>
+      <c r="BC7" s="30"/>
+      <c r="BD7" s="30"/>
+      <c r="BE7" s="30"/>
+      <c r="BF7" s="30"/>
+      <c r="BG7" s="30"/>
+      <c r="BH7" s="30"/>
+      <c r="BI7" s="30"/>
+      <c r="BJ7" s="30"/>
+      <c r="BK7" s="30"/>
+      <c r="BL7" s="30"/>
+      <c r="BM7" s="30"/>
+      <c r="BN7" s="30"/>
+      <c r="BO7" s="30"/>
+      <c r="BP7" s="30"/>
+      <c r="BQ7" s="30"/>
+      <c r="BR7" s="30"/>
+      <c r="BS7" s="30"/>
+      <c r="BT7" s="30"/>
+      <c r="BU7" s="30"/>
+      <c r="BV7" s="30"/>
+      <c r="BW7" s="30"/>
+    </row>
+    <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="32">
+      <c r="B8" s="33"/>
+      <c r="C8" s="31">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="28">
-        <v>1</v>
-      </c>
-      <c r="G8" s="28">
+      <c r="F8" s="27">
+        <v>1</v>
+      </c>
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <v>3</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="27">
         <v>5</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="27">
         <v>7</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="27">
         <v>8</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="27">
         <v>9</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="27">
         <v>10</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="27">
         <v>11</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="27">
         <v>12</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="27">
         <v>13</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="27">
         <v>14</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="27">
         <v>15</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="27">
         <v>16</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="27">
         <v>17</v>
       </c>
-      <c r="W8" s="28">
+      <c r="W8" s="27">
         <v>18</v>
       </c>
-      <c r="X8" s="28">
+      <c r="X8" s="27">
         <v>19</v>
       </c>
-      <c r="Y8" s="28">
+      <c r="Y8" s="27">
         <v>20</v>
       </c>
-      <c r="Z8" s="28">
+      <c r="Z8" s="27">
         <v>21</v>
       </c>
-      <c r="AA8" s="28">
+      <c r="AA8" s="27">
         <v>22</v>
       </c>
-      <c r="AB8" s="28">
+      <c r="AB8" s="27">
         <v>23</v>
       </c>
-      <c r="AC8" s="28">
+      <c r="AC8" s="27">
         <v>24</v>
       </c>
-      <c r="AD8" s="28">
+      <c r="AD8" s="27">
         <v>25</v>
       </c>
-      <c r="AE8" s="28">
+      <c r="AE8" s="27">
         <v>26</v>
       </c>
-      <c r="AF8" s="28">
+      <c r="AF8" s="27">
         <v>27</v>
       </c>
-      <c r="AG8" s="28">
+      <c r="AG8" s="27">
         <v>28</v>
       </c>
-      <c r="AH8" s="28">
+      <c r="AH8" s="27">
         <v>29</v>
       </c>
-      <c r="AI8" s="28">
+      <c r="AI8" s="27">
         <v>30</v>
       </c>
-      <c r="AJ8" s="28">
+      <c r="AJ8" s="27">
         <v>31</v>
       </c>
-      <c r="AK8" s="28">
+      <c r="AK8" s="27">
         <v>32</v>
       </c>
-      <c r="AL8" s="28">
+      <c r="AL8" s="27">
         <v>33</v>
       </c>
-      <c r="AM8" s="28">
+      <c r="AM8" s="27">
         <v>34</v>
       </c>
-      <c r="AN8" s="28">
+      <c r="AN8" s="27">
         <v>35</v>
       </c>
-      <c r="AO8" s="28">
+      <c r="AO8" s="27">
         <v>36</v>
       </c>
-      <c r="AP8" s="28">
+      <c r="AP8" s="27">
         <v>37</v>
       </c>
-      <c r="AQ8" s="28">
+      <c r="AQ8" s="27">
         <v>38</v>
       </c>
-      <c r="AR8" s="28">
+      <c r="AR8" s="27">
         <v>39</v>
       </c>
-      <c r="AS8" s="28">
+      <c r="AS8" s="27">
         <v>40</v>
       </c>
-      <c r="AT8" s="28">
+      <c r="AT8" s="27">
         <v>41</v>
       </c>
-      <c r="AU8" s="28">
+      <c r="AU8" s="27">
         <v>42</v>
       </c>
-      <c r="AV8" s="28">
+      <c r="AV8" s="27">
         <v>43</v>
       </c>
-      <c r="AW8" s="28">
+      <c r="AW8" s="27">
         <v>44</v>
       </c>
-      <c r="AX8" s="28">
+      <c r="AX8" s="27">
         <v>45</v>
       </c>
-      <c r="AY8" s="28">
+      <c r="AY8" s="27">
         <v>46</v>
       </c>
-      <c r="AZ8" s="28">
+      <c r="AZ8" s="27">
         <v>47</v>
       </c>
-      <c r="BA8" s="28">
+      <c r="BA8" s="27">
         <v>48</v>
       </c>
-      <c r="BB8" s="28">
+      <c r="BB8" s="27">
         <v>49</v>
       </c>
-      <c r="BC8" s="28">
+      <c r="BC8" s="27">
         <v>50</v>
       </c>
-      <c r="BD8" s="28">
+      <c r="BD8" s="27">
         <v>51</v>
       </c>
-      <c r="BE8" s="28">
+      <c r="BE8" s="27">
         <v>52</v>
       </c>
-      <c r="BF8" s="28">
+      <c r="BF8" s="27">
         <v>53</v>
       </c>
-      <c r="BG8" s="28">
+      <c r="BG8" s="27">
         <v>54</v>
       </c>
-      <c r="BH8" s="28">
+      <c r="BH8" s="27">
         <v>55</v>
       </c>
-      <c r="BI8" s="28">
+      <c r="BI8" s="27">
         <v>56</v>
       </c>
-      <c r="BJ8" s="28">
+      <c r="BJ8" s="27">
         <v>57</v>
       </c>
-      <c r="BK8" s="28">
+      <c r="BK8" s="27">
         <v>58</v>
       </c>
-      <c r="BL8" s="28">
+      <c r="BL8" s="27">
         <v>59</v>
       </c>
-      <c r="BM8" s="28">
+      <c r="BM8" s="27">
         <v>60</v>
       </c>
-      <c r="BN8" s="28">
+      <c r="BN8" s="27">
         <v>61</v>
       </c>
-      <c r="BO8" s="28">
+      <c r="BO8" s="27">
         <v>62</v>
       </c>
-      <c r="BP8" s="28">
+      <c r="BP8" s="27">
         <v>63</v>
       </c>
-      <c r="BQ8" s="28">
+      <c r="BQ8" s="27">
         <v>64</v>
       </c>
-      <c r="BR8" s="28">
+      <c r="BR8" s="27">
         <v>65</v>
       </c>
-      <c r="BS8" s="28">
+      <c r="BS8" s="27">
         <v>66</v>
       </c>
-      <c r="BT8" s="28">
+      <c r="BT8" s="27">
         <v>67</v>
       </c>
-      <c r="BU8" s="28">
+      <c r="BU8" s="27">
         <v>68</v>
       </c>
-      <c r="BV8" s="28">
+      <c r="BV8" s="27">
         <v>69</v>
       </c>
-      <c r="BW8" s="28">
+      <c r="BW8" s="27">
         <v>70</v>
       </c>
-      <c r="BX8" s="28">
-        <v>71</v>
-      </c>
-      <c r="BY8" s="28">
-        <v>72</v>
-      </c>
-      <c r="BZ8" s="28">
-        <v>73</v>
-      </c>
-      <c r="CA8" s="28">
-        <v>74</v>
-      </c>
-      <c r="CB8" s="28">
-        <v>75</v>
-      </c>
-      <c r="CC8" s="28">
-        <v>76</v>
-      </c>
-      <c r="CD8" s="28">
-        <v>77</v>
-      </c>
-      <c r="CE8" s="28">
-        <v>78</v>
-      </c>
-      <c r="CF8" s="28">
-        <v>79</v>
-      </c>
-      <c r="CG8" s="28">
-        <v>80</v>
-      </c>
-      <c r="CH8" s="28">
-        <v>81</v>
-      </c>
-      <c r="CI8" s="28">
-        <v>82</v>
-      </c>
-      <c r="CJ8" s="28">
-        <v>83</v>
-      </c>
-      <c r="CK8" s="28">
-        <v>84</v>
-      </c>
-      <c r="CL8" s="28">
-        <v>85</v>
-      </c>
-      <c r="CM8" s="28">
-        <v>86</v>
-      </c>
-      <c r="CN8" s="28">
-        <v>87</v>
-      </c>
-      <c r="CO8" s="28">
-        <v>88</v>
-      </c>
-      <c r="CP8" s="28">
-        <v>89</v>
-      </c>
-      <c r="CQ8" s="28">
-        <v>90</v>
-      </c>
-      <c r="CR8" s="28">
-        <v>91</v>
-      </c>
-      <c r="CS8" s="28">
-        <v>92</v>
-      </c>
-      <c r="CT8" s="28">
-        <v>93</v>
-      </c>
-      <c r="CU8" s="28">
-        <v>94</v>
-      </c>
-      <c r="CV8" s="28">
-        <v>95</v>
-      </c>
-      <c r="CW8" s="28">
-        <v>96</v>
-      </c>
-      <c r="CX8" s="28">
-        <v>97</v>
-      </c>
-      <c r="CY8" s="28">
-        <v>98</v>
-      </c>
-      <c r="CZ8" s="28">
-        <v>99</v>
-      </c>
-      <c r="DA8" s="28">
-        <v>100</v>
-      </c>
-      <c r="DB8" s="28">
-        <v>101</v>
-      </c>
-      <c r="DC8" s="28">
-        <v>102</v>
-      </c>
-      <c r="DD8" s="28">
-        <v>103</v>
-      </c>
-      <c r="DE8" s="28">
-        <v>104</v>
-      </c>
-      <c r="DF8" s="28">
-        <v>105</v>
-      </c>
-      <c r="DG8" s="28">
-        <v>106</v>
-      </c>
-      <c r="DH8" s="28">
-        <v>107</v>
-      </c>
-      <c r="DI8" s="28">
-        <v>108</v>
-      </c>
-      <c r="DJ8" s="28">
-        <v>109</v>
-      </c>
-      <c r="DK8" s="28">
-        <v>110</v>
-      </c>
-      <c r="DL8" s="28">
-        <v>111</v>
-      </c>
-      <c r="DM8" s="28">
-        <v>112</v>
-      </c>
-      <c r="DN8" s="28">
-        <v>113</v>
-      </c>
-      <c r="DO8" s="28">
-        <v>114</v>
-      </c>
-      <c r="DP8" s="28">
-        <v>115</v>
-      </c>
-      <c r="DQ8" s="28">
-        <v>116</v>
-      </c>
-      <c r="DR8" s="28">
-        <v>117</v>
-      </c>
-      <c r="DS8" s="28">
-        <v>118</v>
-      </c>
-      <c r="DT8" s="28">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+    </row>
+    <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="37"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="29"/>
-      <c r="AP9" s="29"/>
-      <c r="AQ9" s="29"/>
-      <c r="AR9" s="29"/>
-      <c r="AS9" s="29"/>
-      <c r="AT9" s="29"/>
-      <c r="AU9" s="29"/>
-      <c r="AV9" s="29"/>
-      <c r="AW9" s="29"/>
-      <c r="AX9" s="29"/>
-      <c r="AY9" s="29"/>
-      <c r="AZ9" s="29"/>
-      <c r="BA9" s="29"/>
-      <c r="BB9" s="29"/>
-      <c r="BC9" s="29"/>
-      <c r="BD9" s="29"/>
-      <c r="BE9" s="29"/>
-      <c r="BF9" s="29"/>
-      <c r="BG9" s="29"/>
-      <c r="BH9" s="29"/>
-      <c r="BI9" s="29"/>
-      <c r="BJ9" s="29"/>
-      <c r="BK9" s="29"/>
-      <c r="BL9" s="29"/>
-      <c r="BM9" s="29"/>
-      <c r="BN9" s="29"/>
-      <c r="BO9" s="29"/>
-      <c r="BP9" s="29"/>
-      <c r="BQ9" s="29"/>
-      <c r="BR9" s="29"/>
-      <c r="BS9" s="29"/>
-      <c r="BT9" s="29"/>
-      <c r="BU9" s="29"/>
-      <c r="BV9" s="29"/>
-      <c r="BW9" s="29"/>
-      <c r="BX9" s="29"/>
-      <c r="BY9" s="29"/>
-      <c r="BZ9" s="29"/>
-      <c r="CA9" s="29"/>
-      <c r="CB9" s="29"/>
-      <c r="CC9" s="29"/>
-      <c r="CD9" s="29"/>
-      <c r="CE9" s="29"/>
-      <c r="CF9" s="29"/>
-      <c r="CG9" s="29"/>
-      <c r="CH9" s="29"/>
-      <c r="CI9" s="29"/>
-      <c r="CJ9" s="29"/>
-      <c r="CK9" s="29"/>
-      <c r="CL9" s="29"/>
-      <c r="CM9" s="29"/>
-      <c r="CN9" s="29"/>
-      <c r="CO9" s="29"/>
-      <c r="CP9" s="29"/>
-      <c r="CQ9" s="29"/>
-      <c r="CR9" s="29"/>
-      <c r="CS9" s="29"/>
-      <c r="CT9" s="29"/>
-      <c r="CU9" s="29"/>
-      <c r="CV9" s="29"/>
-      <c r="CW9" s="29"/>
-      <c r="CX9" s="29"/>
-      <c r="CY9" s="29"/>
-      <c r="CZ9" s="29"/>
-      <c r="DA9" s="29"/>
-      <c r="DB9" s="29"/>
-      <c r="DC9" s="29"/>
-      <c r="DD9" s="29"/>
-      <c r="DE9" s="29"/>
-      <c r="DF9" s="29"/>
-      <c r="DG9" s="29"/>
-      <c r="DH9" s="29"/>
-      <c r="DI9" s="29"/>
-      <c r="DJ9" s="29"/>
-      <c r="DK9" s="29"/>
-      <c r="DL9" s="29"/>
-      <c r="DM9" s="29"/>
-      <c r="DN9" s="29"/>
-      <c r="DO9" s="29"/>
-      <c r="DP9" s="29"/>
-      <c r="DQ9" s="29"/>
-      <c r="DR9" s="29"/>
-      <c r="DS9" s="29"/>
-      <c r="DT9" s="29"/>
-    </row>
-    <row r="10" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
+    </row>
+    <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2531,155 +2010,8 @@
       <c r="BW10" s="8">
         <v>1</v>
       </c>
-      <c r="BX10" s="8">
-        <v>1</v>
-      </c>
-      <c r="BY10" s="8">
-        <v>1</v>
-      </c>
-      <c r="BZ10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CA10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CB10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CC10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CD10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CE10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CF10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CG10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CH10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CI10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CJ10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CK10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CL10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CM10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CN10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CO10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CP10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CQ10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CR10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CS10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CT10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CU10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CV10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CW10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CX10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CY10" s="8">
-        <v>1</v>
-      </c>
-      <c r="CZ10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DA10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DB10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DC10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DD10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DE10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DF10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DG10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DH10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DI10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DJ10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DK10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DL10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DM10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DN10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DO10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DP10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DQ10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DR10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DS10" s="8">
-        <v>1</v>
-      </c>
-      <c r="DT10" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>1</v>
       </c>
@@ -2690,12 +2022,12 @@
         <v>13</v>
       </c>
       <c r="D11" s="11">
-        <f t="shared" ref="D11:D26" si="0">COUNT(F11:DT11)</f>
-        <v>0</v>
+        <f t="shared" ref="D11:D26" si="0">COUNT(F11:BW11)</f>
+        <v>4</v>
       </c>
       <c r="E11" s="15">
         <f>D11/C5</f>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -2703,12 +2035,20 @@
         <v>44</v>
       </c>
       <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
       <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -2769,57 +2109,8 @@
       <c r="BU11" s="3"/>
       <c r="BV11" s="3"/>
       <c r="BW11" s="3"/>
-      <c r="BX11" s="3"/>
-      <c r="BY11" s="3"/>
-      <c r="BZ11" s="3"/>
-      <c r="CA11" s="3"/>
-      <c r="CB11" s="3"/>
-      <c r="CC11" s="3"/>
-      <c r="CD11" s="3"/>
-      <c r="CE11" s="3"/>
-      <c r="CF11" s="3"/>
-      <c r="CG11" s="3"/>
-      <c r="CH11" s="3"/>
-      <c r="CI11" s="3"/>
-      <c r="CJ11" s="3"/>
-      <c r="CK11" s="3"/>
-      <c r="CL11" s="3"/>
-      <c r="CM11" s="3"/>
-      <c r="CN11" s="3"/>
-      <c r="CO11" s="3"/>
-      <c r="CP11" s="3"/>
-      <c r="CQ11" s="3"/>
-      <c r="CR11" s="3"/>
-      <c r="CS11" s="3"/>
-      <c r="CT11" s="3"/>
-      <c r="CU11" s="3"/>
-      <c r="CV11" s="3"/>
-      <c r="CW11" s="3"/>
-      <c r="CX11" s="3"/>
-      <c r="CY11" s="3"/>
-      <c r="CZ11" s="3"/>
-      <c r="DA11" s="3"/>
-      <c r="DB11" s="3"/>
-      <c r="DC11" s="3"/>
-      <c r="DD11" s="3"/>
-      <c r="DE11" s="3"/>
-      <c r="DF11" s="3"/>
-      <c r="DG11" s="3"/>
-      <c r="DH11" s="3"/>
-      <c r="DI11" s="3"/>
-      <c r="DJ11" s="3"/>
-      <c r="DK11" s="3"/>
-      <c r="DL11" s="3"/>
-      <c r="DM11" s="3"/>
-      <c r="DN11" s="3"/>
-      <c r="DO11" s="3"/>
-      <c r="DP11" s="3"/>
-      <c r="DQ11" s="3"/>
-      <c r="DR11" s="3"/>
-      <c r="DS11" s="3"/>
-      <c r="DT11" s="3"/>
-    </row>
-    <row r="12" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>3</v>
       </c>
@@ -2831,11 +2122,11 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" s="15">
         <f>D12/C5</f>
-        <v>0.05</v>
+        <v>0.11666666666666667</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -2847,12 +2138,20 @@
         <v>0</v>
       </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
       <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -2913,57 +2212,8 @@
       <c r="BU12" s="3"/>
       <c r="BV12" s="3"/>
       <c r="BW12" s="3"/>
-      <c r="BX12" s="3"/>
-      <c r="BY12" s="3"/>
-      <c r="BZ12" s="3"/>
-      <c r="CA12" s="3"/>
-      <c r="CB12" s="3"/>
-      <c r="CC12" s="3"/>
-      <c r="CD12" s="3"/>
-      <c r="CE12" s="3"/>
-      <c r="CF12" s="3"/>
-      <c r="CG12" s="3"/>
-      <c r="CH12" s="3"/>
-      <c r="CI12" s="3"/>
-      <c r="CJ12" s="3"/>
-      <c r="CK12" s="3"/>
-      <c r="CL12" s="3"/>
-      <c r="CM12" s="3"/>
-      <c r="CN12" s="3"/>
-      <c r="CO12" s="3"/>
-      <c r="CP12" s="3"/>
-      <c r="CQ12" s="3"/>
-      <c r="CR12" s="3"/>
-      <c r="CS12" s="3"/>
-      <c r="CT12" s="3"/>
-      <c r="CU12" s="3"/>
-      <c r="CV12" s="3"/>
-      <c r="CW12" s="3"/>
-      <c r="CX12" s="3"/>
-      <c r="CY12" s="3"/>
-      <c r="CZ12" s="3"/>
-      <c r="DA12" s="3"/>
-      <c r="DB12" s="3"/>
-      <c r="DC12" s="3"/>
-      <c r="DD12" s="3"/>
-      <c r="DE12" s="3"/>
-      <c r="DF12" s="3"/>
-      <c r="DG12" s="3"/>
-      <c r="DH12" s="3"/>
-      <c r="DI12" s="3"/>
-      <c r="DJ12" s="3"/>
-      <c r="DK12" s="3"/>
-      <c r="DL12" s="3"/>
-      <c r="DM12" s="3"/>
-      <c r="DN12" s="3"/>
-      <c r="DO12" s="3"/>
-      <c r="DP12" s="3"/>
-      <c r="DQ12" s="3"/>
-      <c r="DR12" s="3"/>
-      <c r="DS12" s="3"/>
-      <c r="DT12" s="3"/>
-    </row>
-    <row r="13" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>4</v>
       </c>
@@ -2975,11 +2225,11 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" s="15">
         <f>D13/C5</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -2993,10 +2243,16 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
       <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
@@ -3057,57 +2313,8 @@
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
       <c r="BW13" s="3"/>
-      <c r="BX13" s="3"/>
-      <c r="BY13" s="3"/>
-      <c r="BZ13" s="3"/>
-      <c r="CA13" s="3"/>
-      <c r="CB13" s="3"/>
-      <c r="CC13" s="3"/>
-      <c r="CD13" s="3"/>
-      <c r="CE13" s="3"/>
-      <c r="CF13" s="3"/>
-      <c r="CG13" s="3"/>
-      <c r="CH13" s="3"/>
-      <c r="CI13" s="3"/>
-      <c r="CJ13" s="3"/>
-      <c r="CK13" s="3"/>
-      <c r="CL13" s="3"/>
-      <c r="CM13" s="3"/>
-      <c r="CN13" s="3"/>
-      <c r="CO13" s="3"/>
-      <c r="CP13" s="3"/>
-      <c r="CQ13" s="3"/>
-      <c r="CR13" s="3"/>
-      <c r="CS13" s="3"/>
-      <c r="CT13" s="3"/>
-      <c r="CU13" s="3"/>
-      <c r="CV13" s="3"/>
-      <c r="CW13" s="3"/>
-      <c r="CX13" s="3"/>
-      <c r="CY13" s="3"/>
-      <c r="CZ13" s="3"/>
-      <c r="DA13" s="3"/>
-      <c r="DB13" s="3"/>
-      <c r="DC13" s="3"/>
-      <c r="DD13" s="3"/>
-      <c r="DE13" s="3"/>
-      <c r="DF13" s="3"/>
-      <c r="DG13" s="3"/>
-      <c r="DH13" s="3"/>
-      <c r="DI13" s="3"/>
-      <c r="DJ13" s="3"/>
-      <c r="DK13" s="3"/>
-      <c r="DL13" s="3"/>
-      <c r="DM13" s="3"/>
-      <c r="DN13" s="3"/>
-      <c r="DO13" s="3"/>
-      <c r="DP13" s="3"/>
-      <c r="DQ13" s="3"/>
-      <c r="DR13" s="3"/>
-      <c r="DS13" s="3"/>
-      <c r="DT13" s="3"/>
-    </row>
-    <row r="14" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>6</v>
       </c>
@@ -3119,11 +2326,11 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E14" s="15">
         <f>D14/C5</f>
-        <v>0.05</v>
+        <v>0.11666666666666667</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -3135,12 +2342,20 @@
         <v>0</v>
       </c>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
       <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -3201,57 +2416,8 @@
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
       <c r="BW14" s="3"/>
-      <c r="BX14" s="3"/>
-      <c r="BY14" s="3"/>
-      <c r="BZ14" s="3"/>
-      <c r="CA14" s="3"/>
-      <c r="CB14" s="3"/>
-      <c r="CC14" s="3"/>
-      <c r="CD14" s="3"/>
-      <c r="CE14" s="3"/>
-      <c r="CF14" s="3"/>
-      <c r="CG14" s="3"/>
-      <c r="CH14" s="3"/>
-      <c r="CI14" s="3"/>
-      <c r="CJ14" s="3"/>
-      <c r="CK14" s="3"/>
-      <c r="CL14" s="3"/>
-      <c r="CM14" s="3"/>
-      <c r="CN14" s="3"/>
-      <c r="CO14" s="3"/>
-      <c r="CP14" s="3"/>
-      <c r="CQ14" s="3"/>
-      <c r="CR14" s="3"/>
-      <c r="CS14" s="3"/>
-      <c r="CT14" s="3"/>
-      <c r="CU14" s="3"/>
-      <c r="CV14" s="3"/>
-      <c r="CW14" s="3"/>
-      <c r="CX14" s="3"/>
-      <c r="CY14" s="3"/>
-      <c r="CZ14" s="3"/>
-      <c r="DA14" s="3"/>
-      <c r="DB14" s="3"/>
-      <c r="DC14" s="3"/>
-      <c r="DD14" s="3"/>
-      <c r="DE14" s="3"/>
-      <c r="DF14" s="3"/>
-      <c r="DG14" s="3"/>
-      <c r="DH14" s="3"/>
-      <c r="DI14" s="3"/>
-      <c r="DJ14" s="3"/>
-      <c r="DK14" s="3"/>
-      <c r="DL14" s="3"/>
-      <c r="DM14" s="3"/>
-      <c r="DN14" s="3"/>
-      <c r="DO14" s="3"/>
-      <c r="DP14" s="3"/>
-      <c r="DQ14" s="3"/>
-      <c r="DR14" s="3"/>
-      <c r="DS14" s="3"/>
-      <c r="DT14" s="3"/>
-    </row>
-    <row r="15" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>7</v>
       </c>
@@ -3262,12 +2428,12 @@
         <v>25</v>
       </c>
       <c r="D15" s="11">
-        <f>COUNT(F15:DT15)</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="E15" s="15">
         <f>D15/C5</f>
-        <v>0.05</v>
+        <v>0.11666666666666667</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -3279,12 +2445,20 @@
         <v>0</v>
       </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
       <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -3345,57 +2519,8 @@
       <c r="BU15" s="3"/>
       <c r="BV15" s="3"/>
       <c r="BW15" s="3"/>
-      <c r="BX15" s="3"/>
-      <c r="BY15" s="3"/>
-      <c r="BZ15" s="3"/>
-      <c r="CA15" s="3"/>
-      <c r="CB15" s="3"/>
-      <c r="CC15" s="3"/>
-      <c r="CD15" s="3"/>
-      <c r="CE15" s="3"/>
-      <c r="CF15" s="3"/>
-      <c r="CG15" s="3"/>
-      <c r="CH15" s="3"/>
-      <c r="CI15" s="3"/>
-      <c r="CJ15" s="3"/>
-      <c r="CK15" s="3"/>
-      <c r="CL15" s="3"/>
-      <c r="CM15" s="3"/>
-      <c r="CN15" s="3"/>
-      <c r="CO15" s="3"/>
-      <c r="CP15" s="3"/>
-      <c r="CQ15" s="3"/>
-      <c r="CR15" s="3"/>
-      <c r="CS15" s="3"/>
-      <c r="CT15" s="3"/>
-      <c r="CU15" s="3"/>
-      <c r="CV15" s="3"/>
-      <c r="CW15" s="3"/>
-      <c r="CX15" s="3"/>
-      <c r="CY15" s="3"/>
-      <c r="CZ15" s="3"/>
-      <c r="DA15" s="3"/>
-      <c r="DB15" s="3"/>
-      <c r="DC15" s="3"/>
-      <c r="DD15" s="3"/>
-      <c r="DE15" s="3"/>
-      <c r="DF15" s="3"/>
-      <c r="DG15" s="3"/>
-      <c r="DH15" s="3"/>
-      <c r="DI15" s="3"/>
-      <c r="DJ15" s="3"/>
-      <c r="DK15" s="3"/>
-      <c r="DL15" s="3"/>
-      <c r="DM15" s="3"/>
-      <c r="DN15" s="3"/>
-      <c r="DO15" s="3"/>
-      <c r="DP15" s="3"/>
-      <c r="DQ15" s="3"/>
-      <c r="DR15" s="3"/>
-      <c r="DS15" s="3"/>
-      <c r="DT15" s="3"/>
-    </row>
-    <row r="16" spans="1:125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>8</v>
       </c>
@@ -3407,19 +2532,23 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <f>D16/C5</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -3483,57 +2612,8 @@
       <c r="BU16" s="3"/>
       <c r="BV16" s="3"/>
       <c r="BW16" s="3"/>
-      <c r="BX16" s="3"/>
-      <c r="BY16" s="3"/>
-      <c r="BZ16" s="3"/>
-      <c r="CA16" s="3"/>
-      <c r="CB16" s="3"/>
-      <c r="CC16" s="3"/>
-      <c r="CD16" s="3"/>
-      <c r="CE16" s="3"/>
-      <c r="CF16" s="3"/>
-      <c r="CG16" s="3"/>
-      <c r="CH16" s="3"/>
-      <c r="CI16" s="3"/>
-      <c r="CJ16" s="3"/>
-      <c r="CK16" s="3"/>
-      <c r="CL16" s="3"/>
-      <c r="CM16" s="3"/>
-      <c r="CN16" s="3"/>
-      <c r="CO16" s="3"/>
-      <c r="CP16" s="3"/>
-      <c r="CQ16" s="3"/>
-      <c r="CR16" s="3"/>
-      <c r="CS16" s="3"/>
-      <c r="CT16" s="3"/>
-      <c r="CU16" s="3"/>
-      <c r="CV16" s="3"/>
-      <c r="CW16" s="3"/>
-      <c r="CX16" s="3"/>
-      <c r="CY16" s="3"/>
-      <c r="CZ16" s="3"/>
-      <c r="DA16" s="3"/>
-      <c r="DB16" s="3"/>
-      <c r="DC16" s="3"/>
-      <c r="DD16" s="3"/>
-      <c r="DE16" s="3"/>
-      <c r="DF16" s="3"/>
-      <c r="DG16" s="3"/>
-      <c r="DH16" s="3"/>
-      <c r="DI16" s="3"/>
-      <c r="DJ16" s="3"/>
-      <c r="DK16" s="3"/>
-      <c r="DL16" s="3"/>
-      <c r="DM16" s="3"/>
-      <c r="DN16" s="3"/>
-      <c r="DO16" s="3"/>
-      <c r="DP16" s="3"/>
-      <c r="DQ16" s="3"/>
-      <c r="DR16" s="3"/>
-      <c r="DS16" s="3"/>
-      <c r="DT16" s="3"/>
-    </row>
-    <row r="17" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>10</v>
       </c>
@@ -3545,22 +2625,28 @@
       </c>
       <c r="D17" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
         <f>D17/C5</f>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -3621,57 +2707,8 @@
       <c r="BU17" s="3"/>
       <c r="BV17" s="3"/>
       <c r="BW17" s="3"/>
-      <c r="BX17" s="3"/>
-      <c r="BY17" s="3"/>
-      <c r="BZ17" s="3"/>
-      <c r="CA17" s="3"/>
-      <c r="CB17" s="3"/>
-      <c r="CC17" s="3"/>
-      <c r="CD17" s="3"/>
-      <c r="CE17" s="3"/>
-      <c r="CF17" s="3"/>
-      <c r="CG17" s="3"/>
-      <c r="CH17" s="3"/>
-      <c r="CI17" s="3"/>
-      <c r="CJ17" s="3"/>
-      <c r="CK17" s="3"/>
-      <c r="CL17" s="3"/>
-      <c r="CM17" s="3"/>
-      <c r="CN17" s="3"/>
-      <c r="CO17" s="3"/>
-      <c r="CP17" s="3"/>
-      <c r="CQ17" s="3"/>
-      <c r="CR17" s="3"/>
-      <c r="CS17" s="3"/>
-      <c r="CT17" s="3"/>
-      <c r="CU17" s="3"/>
-      <c r="CV17" s="3"/>
-      <c r="CW17" s="3"/>
-      <c r="CX17" s="3"/>
-      <c r="CY17" s="3"/>
-      <c r="CZ17" s="3"/>
-      <c r="DA17" s="3"/>
-      <c r="DB17" s="3"/>
-      <c r="DC17" s="3"/>
-      <c r="DD17" s="3"/>
-      <c r="DE17" s="3"/>
-      <c r="DF17" s="3"/>
-      <c r="DG17" s="3"/>
-      <c r="DH17" s="3"/>
-      <c r="DI17" s="3"/>
-      <c r="DJ17" s="3"/>
-      <c r="DK17" s="3"/>
-      <c r="DL17" s="3"/>
-      <c r="DM17" s="3"/>
-      <c r="DN17" s="3"/>
-      <c r="DO17" s="3"/>
-      <c r="DP17" s="3"/>
-      <c r="DQ17" s="3"/>
-      <c r="DR17" s="3"/>
-      <c r="DS17" s="3"/>
-      <c r="DT17" s="3"/>
-    </row>
-    <row r="18" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>11</v>
       </c>
@@ -3683,22 +2720,32 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
         <f>D18/C5</f>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
       <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
       <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -3759,57 +2806,8 @@
       <c r="BU18" s="3"/>
       <c r="BV18" s="3"/>
       <c r="BW18" s="3"/>
-      <c r="BX18" s="3"/>
-      <c r="BY18" s="3"/>
-      <c r="BZ18" s="3"/>
-      <c r="CA18" s="3"/>
-      <c r="CB18" s="3"/>
-      <c r="CC18" s="3"/>
-      <c r="CD18" s="3"/>
-      <c r="CE18" s="3"/>
-      <c r="CF18" s="3"/>
-      <c r="CG18" s="3"/>
-      <c r="CH18" s="3"/>
-      <c r="CI18" s="3"/>
-      <c r="CJ18" s="3"/>
-      <c r="CK18" s="3"/>
-      <c r="CL18" s="3"/>
-      <c r="CM18" s="3"/>
-      <c r="CN18" s="3"/>
-      <c r="CO18" s="3"/>
-      <c r="CP18" s="3"/>
-      <c r="CQ18" s="3"/>
-      <c r="CR18" s="3"/>
-      <c r="CS18" s="3"/>
-      <c r="CT18" s="3"/>
-      <c r="CU18" s="3"/>
-      <c r="CV18" s="3"/>
-      <c r="CW18" s="3"/>
-      <c r="CX18" s="3"/>
-      <c r="CY18" s="3"/>
-      <c r="CZ18" s="3"/>
-      <c r="DA18" s="3"/>
-      <c r="DB18" s="3"/>
-      <c r="DC18" s="3"/>
-      <c r="DD18" s="3"/>
-      <c r="DE18" s="3"/>
-      <c r="DF18" s="3"/>
-      <c r="DG18" s="3"/>
-      <c r="DH18" s="3"/>
-      <c r="DI18" s="3"/>
-      <c r="DJ18" s="3"/>
-      <c r="DK18" s="3"/>
-      <c r="DL18" s="3"/>
-      <c r="DM18" s="3"/>
-      <c r="DN18" s="3"/>
-      <c r="DO18" s="3"/>
-      <c r="DP18" s="3"/>
-      <c r="DQ18" s="3"/>
-      <c r="DR18" s="3"/>
-      <c r="DS18" s="3"/>
-      <c r="DT18" s="3"/>
-    </row>
-    <row r="19" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>11</v>
       </c>
@@ -3890,57 +2888,8 @@
       <c r="BU19" s="3"/>
       <c r="BV19" s="3"/>
       <c r="BW19" s="3"/>
-      <c r="BX19" s="3"/>
-      <c r="BY19" s="3"/>
-      <c r="BZ19" s="3"/>
-      <c r="CA19" s="3"/>
-      <c r="CB19" s="3"/>
-      <c r="CC19" s="3"/>
-      <c r="CD19" s="3"/>
-      <c r="CE19" s="3"/>
-      <c r="CF19" s="3"/>
-      <c r="CG19" s="3"/>
-      <c r="CH19" s="3"/>
-      <c r="CI19" s="3"/>
-      <c r="CJ19" s="3"/>
-      <c r="CK19" s="3"/>
-      <c r="CL19" s="3"/>
-      <c r="CM19" s="3"/>
-      <c r="CN19" s="3"/>
-      <c r="CO19" s="3"/>
-      <c r="CP19" s="3"/>
-      <c r="CQ19" s="3"/>
-      <c r="CR19" s="3"/>
-      <c r="CS19" s="3"/>
-      <c r="CT19" s="3"/>
-      <c r="CU19" s="3"/>
-      <c r="CV19" s="3"/>
-      <c r="CW19" s="3"/>
-      <c r="CX19" s="3"/>
-      <c r="CY19" s="3"/>
-      <c r="CZ19" s="3"/>
-      <c r="DA19" s="3"/>
-      <c r="DB19" s="3"/>
-      <c r="DC19" s="3"/>
-      <c r="DD19" s="3"/>
-      <c r="DE19" s="3"/>
-      <c r="DF19" s="3"/>
-      <c r="DG19" s="3"/>
-      <c r="DH19" s="3"/>
-      <c r="DI19" s="3"/>
-      <c r="DJ19" s="3"/>
-      <c r="DK19" s="3"/>
-      <c r="DL19" s="3"/>
-      <c r="DM19" s="3"/>
-      <c r="DN19" s="3"/>
-      <c r="DO19" s="3"/>
-      <c r="DP19" s="3"/>
-      <c r="DQ19" s="3"/>
-      <c r="DR19" s="3"/>
-      <c r="DS19" s="3"/>
-      <c r="DT19" s="3"/>
-    </row>
-    <row r="20" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>12</v>
       </c>
@@ -4021,57 +2970,8 @@
       <c r="BU20" s="3"/>
       <c r="BV20" s="3"/>
       <c r="BW20" s="3"/>
-      <c r="BX20" s="3"/>
-      <c r="BY20" s="3"/>
-      <c r="BZ20" s="3"/>
-      <c r="CA20" s="3"/>
-      <c r="CB20" s="3"/>
-      <c r="CC20" s="3"/>
-      <c r="CD20" s="3"/>
-      <c r="CE20" s="3"/>
-      <c r="CF20" s="3"/>
-      <c r="CG20" s="3"/>
-      <c r="CH20" s="3"/>
-      <c r="CI20" s="3"/>
-      <c r="CJ20" s="3"/>
-      <c r="CK20" s="3"/>
-      <c r="CL20" s="3"/>
-      <c r="CM20" s="3"/>
-      <c r="CN20" s="3"/>
-      <c r="CO20" s="3"/>
-      <c r="CP20" s="3"/>
-      <c r="CQ20" s="3"/>
-      <c r="CR20" s="3"/>
-      <c r="CS20" s="3"/>
-      <c r="CT20" s="3"/>
-      <c r="CU20" s="3"/>
-      <c r="CV20" s="3"/>
-      <c r="CW20" s="3"/>
-      <c r="CX20" s="3"/>
-      <c r="CY20" s="3"/>
-      <c r="CZ20" s="3"/>
-      <c r="DA20" s="3"/>
-      <c r="DB20" s="3"/>
-      <c r="DC20" s="3"/>
-      <c r="DD20" s="3"/>
-      <c r="DE20" s="3"/>
-      <c r="DF20" s="3"/>
-      <c r="DG20" s="3"/>
-      <c r="DH20" s="3"/>
-      <c r="DI20" s="3"/>
-      <c r="DJ20" s="3"/>
-      <c r="DK20" s="3"/>
-      <c r="DL20" s="3"/>
-      <c r="DM20" s="3"/>
-      <c r="DN20" s="3"/>
-      <c r="DO20" s="3"/>
-      <c r="DP20" s="3"/>
-      <c r="DQ20" s="3"/>
-      <c r="DR20" s="3"/>
-      <c r="DS20" s="3"/>
-      <c r="DT20" s="3"/>
-    </row>
-    <row r="21" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>13</v>
       </c>
@@ -4152,57 +3052,8 @@
       <c r="BU21" s="3"/>
       <c r="BV21" s="3"/>
       <c r="BW21" s="3"/>
-      <c r="BX21" s="3"/>
-      <c r="BY21" s="3"/>
-      <c r="BZ21" s="3"/>
-      <c r="CA21" s="3"/>
-      <c r="CB21" s="3"/>
-      <c r="CC21" s="3"/>
-      <c r="CD21" s="3"/>
-      <c r="CE21" s="3"/>
-      <c r="CF21" s="3"/>
-      <c r="CG21" s="3"/>
-      <c r="CH21" s="3"/>
-      <c r="CI21" s="3"/>
-      <c r="CJ21" s="3"/>
-      <c r="CK21" s="3"/>
-      <c r="CL21" s="3"/>
-      <c r="CM21" s="3"/>
-      <c r="CN21" s="3"/>
-      <c r="CO21" s="3"/>
-      <c r="CP21" s="3"/>
-      <c r="CQ21" s="3"/>
-      <c r="CR21" s="3"/>
-      <c r="CS21" s="3"/>
-      <c r="CT21" s="3"/>
-      <c r="CU21" s="3"/>
-      <c r="CV21" s="3"/>
-      <c r="CW21" s="3"/>
-      <c r="CX21" s="3"/>
-      <c r="CY21" s="3"/>
-      <c r="CZ21" s="3"/>
-      <c r="DA21" s="3"/>
-      <c r="DB21" s="3"/>
-      <c r="DC21" s="3"/>
-      <c r="DD21" s="3"/>
-      <c r="DE21" s="3"/>
-      <c r="DF21" s="3"/>
-      <c r="DG21" s="3"/>
-      <c r="DH21" s="3"/>
-      <c r="DI21" s="3"/>
-      <c r="DJ21" s="3"/>
-      <c r="DK21" s="3"/>
-      <c r="DL21" s="3"/>
-      <c r="DM21" s="3"/>
-      <c r="DN21" s="3"/>
-      <c r="DO21" s="3"/>
-      <c r="DP21" s="3"/>
-      <c r="DQ21" s="3"/>
-      <c r="DR21" s="3"/>
-      <c r="DS21" s="3"/>
-      <c r="DT21" s="3"/>
-    </row>
-    <row r="22" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>14</v>
       </c>
@@ -4283,57 +3134,8 @@
       <c r="BU22" s="3"/>
       <c r="BV22" s="3"/>
       <c r="BW22" s="3"/>
-      <c r="BX22" s="3"/>
-      <c r="BY22" s="3"/>
-      <c r="BZ22" s="3"/>
-      <c r="CA22" s="3"/>
-      <c r="CB22" s="3"/>
-      <c r="CC22" s="3"/>
-      <c r="CD22" s="3"/>
-      <c r="CE22" s="3"/>
-      <c r="CF22" s="3"/>
-      <c r="CG22" s="3"/>
-      <c r="CH22" s="3"/>
-      <c r="CI22" s="3"/>
-      <c r="CJ22" s="3"/>
-      <c r="CK22" s="3"/>
-      <c r="CL22" s="3"/>
-      <c r="CM22" s="3"/>
-      <c r="CN22" s="3"/>
-      <c r="CO22" s="3"/>
-      <c r="CP22" s="3"/>
-      <c r="CQ22" s="3"/>
-      <c r="CR22" s="3"/>
-      <c r="CS22" s="3"/>
-      <c r="CT22" s="3"/>
-      <c r="CU22" s="3"/>
-      <c r="CV22" s="3"/>
-      <c r="CW22" s="3"/>
-      <c r="CX22" s="3"/>
-      <c r="CY22" s="3"/>
-      <c r="CZ22" s="3"/>
-      <c r="DA22" s="3"/>
-      <c r="DB22" s="3"/>
-      <c r="DC22" s="3"/>
-      <c r="DD22" s="3"/>
-      <c r="DE22" s="3"/>
-      <c r="DF22" s="3"/>
-      <c r="DG22" s="3"/>
-      <c r="DH22" s="3"/>
-      <c r="DI22" s="3"/>
-      <c r="DJ22" s="3"/>
-      <c r="DK22" s="3"/>
-      <c r="DL22" s="3"/>
-      <c r="DM22" s="3"/>
-      <c r="DN22" s="3"/>
-      <c r="DO22" s="3"/>
-      <c r="DP22" s="3"/>
-      <c r="DQ22" s="3"/>
-      <c r="DR22" s="3"/>
-      <c r="DS22" s="3"/>
-      <c r="DT22" s="3"/>
-    </row>
-    <row r="23" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>15</v>
       </c>
@@ -4414,57 +3216,8 @@
       <c r="BU23" s="3"/>
       <c r="BV23" s="3"/>
       <c r="BW23" s="3"/>
-      <c r="BX23" s="3"/>
-      <c r="BY23" s="3"/>
-      <c r="BZ23" s="3"/>
-      <c r="CA23" s="3"/>
-      <c r="CB23" s="3"/>
-      <c r="CC23" s="3"/>
-      <c r="CD23" s="3"/>
-      <c r="CE23" s="3"/>
-      <c r="CF23" s="3"/>
-      <c r="CG23" s="3"/>
-      <c r="CH23" s="3"/>
-      <c r="CI23" s="3"/>
-      <c r="CJ23" s="3"/>
-      <c r="CK23" s="3"/>
-      <c r="CL23" s="3"/>
-      <c r="CM23" s="3"/>
-      <c r="CN23" s="3"/>
-      <c r="CO23" s="3"/>
-      <c r="CP23" s="3"/>
-      <c r="CQ23" s="3"/>
-      <c r="CR23" s="3"/>
-      <c r="CS23" s="3"/>
-      <c r="CT23" s="3"/>
-      <c r="CU23" s="3"/>
-      <c r="CV23" s="3"/>
-      <c r="CW23" s="3"/>
-      <c r="CX23" s="3"/>
-      <c r="CY23" s="3"/>
-      <c r="CZ23" s="3"/>
-      <c r="DA23" s="3"/>
-      <c r="DB23" s="3"/>
-      <c r="DC23" s="3"/>
-      <c r="DD23" s="3"/>
-      <c r="DE23" s="3"/>
-      <c r="DF23" s="3"/>
-      <c r="DG23" s="3"/>
-      <c r="DH23" s="3"/>
-      <c r="DI23" s="3"/>
-      <c r="DJ23" s="3"/>
-      <c r="DK23" s="3"/>
-      <c r="DL23" s="3"/>
-      <c r="DM23" s="3"/>
-      <c r="DN23" s="3"/>
-      <c r="DO23" s="3"/>
-      <c r="DP23" s="3"/>
-      <c r="DQ23" s="3"/>
-      <c r="DR23" s="3"/>
-      <c r="DS23" s="3"/>
-      <c r="DT23" s="3"/>
-    </row>
-    <row r="24" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>16</v>
       </c>
@@ -4545,57 +3298,8 @@
       <c r="BU24" s="3"/>
       <c r="BV24" s="3"/>
       <c r="BW24" s="3"/>
-      <c r="BX24" s="3"/>
-      <c r="BY24" s="3"/>
-      <c r="BZ24" s="3"/>
-      <c r="CA24" s="3"/>
-      <c r="CB24" s="3"/>
-      <c r="CC24" s="3"/>
-      <c r="CD24" s="3"/>
-      <c r="CE24" s="3"/>
-      <c r="CF24" s="3"/>
-      <c r="CG24" s="3"/>
-      <c r="CH24" s="3"/>
-      <c r="CI24" s="3"/>
-      <c r="CJ24" s="3"/>
-      <c r="CK24" s="3"/>
-      <c r="CL24" s="3"/>
-      <c r="CM24" s="3"/>
-      <c r="CN24" s="3"/>
-      <c r="CO24" s="3"/>
-      <c r="CP24" s="3"/>
-      <c r="CQ24" s="3"/>
-      <c r="CR24" s="3"/>
-      <c r="CS24" s="3"/>
-      <c r="CT24" s="3"/>
-      <c r="CU24" s="3"/>
-      <c r="CV24" s="3"/>
-      <c r="CW24" s="3"/>
-      <c r="CX24" s="3"/>
-      <c r="CY24" s="3"/>
-      <c r="CZ24" s="3"/>
-      <c r="DA24" s="3"/>
-      <c r="DB24" s="3"/>
-      <c r="DC24" s="3"/>
-      <c r="DD24" s="3"/>
-      <c r="DE24" s="3"/>
-      <c r="DF24" s="3"/>
-      <c r="DG24" s="3"/>
-      <c r="DH24" s="3"/>
-      <c r="DI24" s="3"/>
-      <c r="DJ24" s="3"/>
-      <c r="DK24" s="3"/>
-      <c r="DL24" s="3"/>
-      <c r="DM24" s="3"/>
-      <c r="DN24" s="3"/>
-      <c r="DO24" s="3"/>
-      <c r="DP24" s="3"/>
-      <c r="DQ24" s="3"/>
-      <c r="DR24" s="3"/>
-      <c r="DS24" s="3"/>
-      <c r="DT24" s="3"/>
-    </row>
-    <row r="25" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>17</v>
       </c>
@@ -4676,57 +3380,8 @@
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
       <c r="BW25" s="3"/>
-      <c r="BX25" s="3"/>
-      <c r="BY25" s="3"/>
-      <c r="BZ25" s="3"/>
-      <c r="CA25" s="3"/>
-      <c r="CB25" s="3"/>
-      <c r="CC25" s="3"/>
-      <c r="CD25" s="3"/>
-      <c r="CE25" s="3"/>
-      <c r="CF25" s="3"/>
-      <c r="CG25" s="3"/>
-      <c r="CH25" s="3"/>
-      <c r="CI25" s="3"/>
-      <c r="CJ25" s="3"/>
-      <c r="CK25" s="3"/>
-      <c r="CL25" s="3"/>
-      <c r="CM25" s="3"/>
-      <c r="CN25" s="3"/>
-      <c r="CO25" s="3"/>
-      <c r="CP25" s="3"/>
-      <c r="CQ25" s="3"/>
-      <c r="CR25" s="3"/>
-      <c r="CS25" s="3"/>
-      <c r="CT25" s="3"/>
-      <c r="CU25" s="3"/>
-      <c r="CV25" s="3"/>
-      <c r="CW25" s="3"/>
-      <c r="CX25" s="3"/>
-      <c r="CY25" s="3"/>
-      <c r="CZ25" s="3"/>
-      <c r="DA25" s="3"/>
-      <c r="DB25" s="3"/>
-      <c r="DC25" s="3"/>
-      <c r="DD25" s="3"/>
-      <c r="DE25" s="3"/>
-      <c r="DF25" s="3"/>
-      <c r="DG25" s="3"/>
-      <c r="DH25" s="3"/>
-      <c r="DI25" s="3"/>
-      <c r="DJ25" s="3"/>
-      <c r="DK25" s="3"/>
-      <c r="DL25" s="3"/>
-      <c r="DM25" s="3"/>
-      <c r="DN25" s="3"/>
-      <c r="DO25" s="3"/>
-      <c r="DP25" s="3"/>
-      <c r="DQ25" s="3"/>
-      <c r="DR25" s="3"/>
-      <c r="DS25" s="3"/>
-      <c r="DT25" s="3"/>
-    </row>
-    <row r="26" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>18</v>
       </c>
@@ -4736,128 +3391,79 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
-      <c r="Y26" s="33"/>
-      <c r="Z26" s="33"/>
-      <c r="AA26" s="33"/>
-      <c r="AB26" s="33"/>
-      <c r="AC26" s="33"/>
-      <c r="AD26" s="33"/>
-      <c r="AE26" s="33"/>
-      <c r="AF26" s="33"/>
-      <c r="AG26" s="33"/>
-      <c r="AH26" s="33"/>
-      <c r="AI26" s="33"/>
-      <c r="AJ26" s="33"/>
-      <c r="AK26" s="33"/>
-      <c r="AL26" s="33"/>
-      <c r="AM26" s="33"/>
-      <c r="AN26" s="33"/>
-      <c r="AO26" s="33"/>
-      <c r="AP26" s="33"/>
-      <c r="AQ26" s="33"/>
-      <c r="AR26" s="33"/>
-      <c r="AS26" s="33"/>
-      <c r="AT26" s="33"/>
-      <c r="AU26" s="33"/>
-      <c r="AV26" s="33"/>
-      <c r="AW26" s="33"/>
-      <c r="AX26" s="33"/>
-      <c r="AY26" s="33"/>
-      <c r="AZ26" s="33"/>
-      <c r="BA26" s="33"/>
-      <c r="BB26" s="33"/>
-      <c r="BC26" s="33"/>
-      <c r="BD26" s="33"/>
-      <c r="BE26" s="33"/>
-      <c r="BF26" s="33"/>
-      <c r="BG26" s="33"/>
-      <c r="BH26" s="33"/>
-      <c r="BI26" s="33"/>
-      <c r="BJ26" s="33"/>
-      <c r="BK26" s="33"/>
-      <c r="BL26" s="33"/>
-      <c r="BM26" s="33"/>
-      <c r="BN26" s="33"/>
-      <c r="BO26" s="33"/>
-      <c r="BP26" s="33"/>
-      <c r="BQ26" s="33"/>
-      <c r="BR26" s="33"/>
-      <c r="BS26" s="33"/>
-      <c r="BT26" s="33"/>
-      <c r="BU26" s="33"/>
-      <c r="BV26" s="33"/>
-      <c r="BW26" s="33"/>
-      <c r="BX26" s="33"/>
-      <c r="BY26" s="33"/>
-      <c r="BZ26" s="33"/>
-      <c r="CA26" s="33"/>
-      <c r="CB26" s="33"/>
-      <c r="CC26" s="33"/>
-      <c r="CD26" s="33"/>
-      <c r="CE26" s="33"/>
-      <c r="CF26" s="33"/>
-      <c r="CG26" s="33"/>
-      <c r="CH26" s="33"/>
-      <c r="CI26" s="33"/>
-      <c r="CJ26" s="33"/>
-      <c r="CK26" s="33"/>
-      <c r="CL26" s="33"/>
-      <c r="CM26" s="33"/>
-      <c r="CN26" s="33"/>
-      <c r="CO26" s="33"/>
-      <c r="CP26" s="33"/>
-      <c r="CQ26" s="33"/>
-      <c r="CR26" s="33"/>
-      <c r="CS26" s="33"/>
-      <c r="CT26" s="33"/>
-      <c r="CU26" s="33"/>
-      <c r="CV26" s="33"/>
-      <c r="CW26" s="33"/>
-      <c r="CX26" s="33"/>
-      <c r="CY26" s="33"/>
-      <c r="CZ26" s="33"/>
-      <c r="DA26" s="33"/>
-      <c r="DB26" s="33"/>
-      <c r="DC26" s="33"/>
-      <c r="DD26" s="33"/>
-      <c r="DE26" s="33"/>
-      <c r="DF26" s="33"/>
-      <c r="DG26" s="33"/>
-      <c r="DH26" s="33"/>
-      <c r="DI26" s="33"/>
-      <c r="DJ26" s="33"/>
-      <c r="DK26" s="33"/>
-      <c r="DL26" s="33"/>
-      <c r="DM26" s="33"/>
-      <c r="DN26" s="33"/>
-      <c r="DO26" s="33"/>
-      <c r="DP26" s="33"/>
-      <c r="DQ26" s="33"/>
-      <c r="DR26" s="33"/>
-      <c r="DS26" s="33"/>
-      <c r="DT26" s="33"/>
-    </row>
-    <row r="27" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="32"/>
+      <c r="AN26" s="32"/>
+      <c r="AO26" s="32"/>
+      <c r="AP26" s="32"/>
+      <c r="AQ26" s="32"/>
+      <c r="AR26" s="32"/>
+      <c r="AS26" s="32"/>
+      <c r="AT26" s="32"/>
+      <c r="AU26" s="32"/>
+      <c r="AV26" s="32"/>
+      <c r="AW26" s="32"/>
+      <c r="AX26" s="32"/>
+      <c r="AY26" s="32"/>
+      <c r="AZ26" s="32"/>
+      <c r="BA26" s="32"/>
+      <c r="BB26" s="32"/>
+      <c r="BC26" s="32"/>
+      <c r="BD26" s="32"/>
+      <c r="BE26" s="32"/>
+      <c r="BF26" s="32"/>
+      <c r="BG26" s="32"/>
+      <c r="BH26" s="32"/>
+      <c r="BI26" s="32"/>
+      <c r="BJ26" s="32"/>
+      <c r="BK26" s="32"/>
+      <c r="BL26" s="32"/>
+      <c r="BM26" s="32"/>
+      <c r="BN26" s="32"/>
+      <c r="BO26" s="32"/>
+      <c r="BP26" s="32"/>
+      <c r="BQ26" s="32"/>
+      <c r="BR26" s="32"/>
+      <c r="BS26" s="32"/>
+      <c r="BT26" s="32"/>
+      <c r="BU26" s="32"/>
+      <c r="BV26" s="32"/>
+      <c r="BW26" s="32"/>
+    </row>
+    <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F27" s="53"/>
       <c r="G27" s="53"/>
       <c r="H27" s="53"/>
@@ -4928,132 +3534,40 @@
       <c r="BU27" s="53"/>
       <c r="BV27" s="53"/>
       <c r="BW27" s="53"/>
-      <c r="BX27" s="53"/>
-      <c r="BY27" s="53"/>
-      <c r="BZ27" s="53"/>
-      <c r="CA27" s="53"/>
-      <c r="CB27" s="53"/>
-      <c r="CC27" s="53"/>
-      <c r="CD27" s="53"/>
-      <c r="CE27" s="54"/>
-      <c r="CF27" s="55"/>
-      <c r="CG27" s="55"/>
-      <c r="CH27" s="55"/>
-      <c r="CI27" s="55"/>
-      <c r="CJ27" s="55"/>
-      <c r="CK27" s="55"/>
-      <c r="CL27" s="55"/>
-      <c r="CM27" s="55"/>
-      <c r="CN27" s="55"/>
-      <c r="CO27" s="55"/>
-      <c r="CP27" s="55"/>
-      <c r="CQ27" s="55"/>
-      <c r="CR27" s="55"/>
-      <c r="CS27" s="55"/>
-      <c r="CT27" s="55"/>
-      <c r="CU27" s="55"/>
-      <c r="CV27" s="55"/>
-      <c r="CW27" s="55"/>
-      <c r="CX27" s="55"/>
-      <c r="CY27" s="55"/>
-      <c r="CZ27" s="55"/>
-      <c r="DA27" s="55"/>
-      <c r="DB27" s="55"/>
-      <c r="DC27" s="55"/>
-      <c r="DD27" s="55"/>
-      <c r="DE27" s="55"/>
-      <c r="DF27" s="55"/>
-      <c r="DG27" s="55"/>
-      <c r="DH27" s="55"/>
-      <c r="DI27" s="55"/>
-      <c r="DJ27" s="55"/>
-      <c r="DK27" s="55"/>
-      <c r="DL27" s="55"/>
-      <c r="DM27" s="55"/>
-      <c r="DN27" s="55"/>
-      <c r="DO27" s="55"/>
-      <c r="DP27" s="55"/>
-      <c r="DQ27" s="55"/>
-      <c r="DR27" s="55"/>
-      <c r="DS27" s="55"/>
-      <c r="DT27" s="55"/>
-    </row>
-    <row r="29" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="22">
         <f>SUM(E11:E18)/8</f>
-        <v>2.5000000000000001E-2</v>
+        <v>8.5416666666666682E-2</v>
       </c>
       <c r="AJ29" s="16"/>
       <c r="AK29" s="17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AJ30" s="18"/>
       <c r="AK30" s="17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AJ31" s="21"/>
       <c r="AK31" s="1" t="s">
         <v>42</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="260">
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
+  <mergeCells count="164">
     <mergeCell ref="F27:S27"/>
     <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:DT27"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="AX27:BW27"/>
     <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DF2:DF7"/>
     <mergeCell ref="BD2:BD7"/>
     <mergeCell ref="BE2:BE7"/>
     <mergeCell ref="BF2:BF7"/>
@@ -5062,11 +3576,7 @@
     <mergeCell ref="BN2:BN7"/>
     <mergeCell ref="BO2:BO7"/>
     <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
     <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
     <mergeCell ref="BH2:BH7"/>
     <mergeCell ref="BI2:BI7"/>
     <mergeCell ref="BJ2:BJ7"/>
@@ -5078,45 +3588,6 @@
     <mergeCell ref="AP2:AP7"/>
     <mergeCell ref="AQ2:AQ7"/>
     <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="Y2:Y7"/>
     <mergeCell ref="Z2:Z7"/>
     <mergeCell ref="AA2:AA7"/>
     <mergeCell ref="AB2:AB7"/>
@@ -5126,11 +3597,21 @@
     <mergeCell ref="AH2:AH7"/>
     <mergeCell ref="AI2:AI7"/>
     <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="E2:E7"/>
     <mergeCell ref="F2:F7"/>
@@ -5149,6 +3630,11 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="F8:F9"/>
@@ -5161,92 +3647,18 @@
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="E26:DT26"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="E26:BW26"/>
     <mergeCell ref="BU8:BU9"/>
     <mergeCell ref="BV8:BV9"/>
     <mergeCell ref="BW8:BW9"/>
     <mergeCell ref="BF8:BF9"/>
     <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
     <mergeCell ref="AW8:AW9"/>
     <mergeCell ref="AX8:AX9"/>
     <mergeCell ref="AY8:AY9"/>
     <mergeCell ref="AZ8:AZ9"/>
     <mergeCell ref="BA8:BA9"/>
     <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
     <mergeCell ref="BH8:BH9"/>
     <mergeCell ref="BI8:BI9"/>
     <mergeCell ref="BJ8:BJ9"/>
@@ -5259,9 +3671,63 @@
     <mergeCell ref="AN8:AN9"/>
     <mergeCell ref="AO8:AO9"/>
     <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="N1:O1"/>
     <mergeCell ref="AQ8:AQ9"/>
     <mergeCell ref="AR8:AR9"/>
     <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5283,49 +3749,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="57" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="63" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="57" t="s">
+      <c r="H3" s="55" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="57"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="55"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -5343,7 +3809,7 @@
       </c>
       <c r="E5" s="19">
         <f>COUNTIF(cms!H11:Y11,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5" s="19">
         <f>COUNTIF(cms!Z11:AY11,0)</f>
@@ -5399,7 +3865,7 @@
       </c>
       <c r="E7" s="19">
         <f>COUNTIF(cms!H12:Y12,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7" s="19">
         <f>COUNTIF(cms!Z12:AY12,0)</f>
@@ -5427,7 +3893,7 @@
       </c>
       <c r="E8" s="19">
         <f>COUNTIF(cms!H13:Y13,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" s="19">
         <f>COUNTIF(cms!Z13:AY13,0)</f>
@@ -5483,7 +3949,7 @@
       </c>
       <c r="E10" s="19">
         <f>COUNTIF(cms!H14:Y14,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10" s="19">
         <f>COUNTIF(cms!Z14:AY14,0)</f>
@@ -5511,7 +3977,7 @@
       </c>
       <c r="E11" s="19">
         <f>COUNTIF(cms!H15:Y15,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11" s="19">
         <f>COUNTIF(cms!Z15:AY15,0)</f>
@@ -5539,7 +4005,7 @@
       </c>
       <c r="E12" s="19">
         <f>COUNTIF(cms!H16:Y16,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="19">
         <f>COUNTIF(cms!Z16:AY16,0)</f>
@@ -5595,7 +4061,7 @@
       </c>
       <c r="E14" s="19">
         <f>COUNTIF(cms!H17:Y17,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" s="19">
         <f>COUNTIF(cms!Z17:AY17,0)</f>
@@ -5623,7 +4089,7 @@
       </c>
       <c r="E15" s="19">
         <f>COUNTIF(cms!H18:Y18,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F15" s="19">
         <f>COUNTIF(cms!Z18:AY18,0)</f>

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t>რიცხვი</t>
   </si>
@@ -64,12 +64,6 @@
     <t>ცოტნე</t>
   </si>
   <si>
-    <t>ბუზალაძე</t>
-  </si>
-  <si>
-    <t>ანანო</t>
-  </si>
-  <si>
     <t>გოგონაძე</t>
   </si>
   <si>
@@ -80,12 +74,6 @@
   </si>
   <si>
     <t>ქრისტინე</t>
-  </si>
-  <si>
-    <t>კენჭიაშვილი</t>
-  </si>
-  <si>
-    <t>ბექა</t>
   </si>
   <si>
     <t>კოტოიანი</t>
@@ -113,12 +101,6 @@
   </si>
   <si>
     <t>წიგნაძე</t>
-  </si>
-  <si>
-    <t>საკნელაშვილი</t>
-  </si>
-  <si>
-    <t>თამარ</t>
   </si>
   <si>
     <t>ვებტექნოლოგიები,  ჯგუფი: 12-2024</t>
@@ -491,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -526,9 +508,6 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -547,92 +526,92 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -892,907 +871,913 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40"/>
-      <c r="F1" s="25">
+      <c r="A1" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="31"/>
+      <c r="F1" s="46">
         <v>3</v>
       </c>
-      <c r="G1" s="52"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="24">
-        <v>1</v>
-      </c>
-      <c r="J1" s="25">
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="23">
+        <v>1</v>
+      </c>
+      <c r="J1" s="46">
         <v>2</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="25">
+      <c r="K1" s="48"/>
+      <c r="L1" s="46">
         <v>2</v>
       </c>
-      <c r="M1" s="26"/>
-      <c r="N1" s="25">
+      <c r="M1" s="48"/>
+      <c r="N1" s="46">
         <v>2</v>
       </c>
-      <c r="O1" s="26"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23"/>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="23"/>
-      <c r="AJ1" s="23"/>
-      <c r="AK1" s="23"/>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="23"/>
-      <c r="AO1" s="23"/>
-      <c r="AP1" s="23"/>
-      <c r="AQ1" s="23"/>
-      <c r="AR1" s="23"/>
-      <c r="AS1" s="23"/>
-      <c r="AT1" s="23"/>
-      <c r="AU1" s="23"/>
-      <c r="AV1" s="23"/>
-      <c r="AW1" s="23"/>
-      <c r="AX1" s="23"/>
-      <c r="AY1" s="23"/>
-      <c r="AZ1" s="23"/>
-      <c r="BA1" s="23"/>
-      <c r="BB1" s="23"/>
-      <c r="BC1" s="23"/>
-      <c r="BD1" s="23"/>
-      <c r="BE1" s="23"/>
-      <c r="BF1" s="23"/>
-      <c r="BG1" s="23"/>
-      <c r="BH1" s="23"/>
-      <c r="BI1" s="23"/>
-      <c r="BJ1" s="23"/>
-      <c r="BK1" s="23"/>
-      <c r="BL1" s="23"/>
-      <c r="BM1" s="23"/>
-      <c r="BN1" s="23"/>
-      <c r="BO1" s="23"/>
-      <c r="BP1" s="23"/>
-      <c r="BQ1" s="23"/>
-      <c r="BR1" s="23"/>
-      <c r="BS1" s="23"/>
-      <c r="BT1" s="23"/>
-      <c r="BU1" s="23"/>
-      <c r="BV1" s="23"/>
-      <c r="BW1" s="23"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="46">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="22"/>
+      <c r="AO1" s="22"/>
+      <c r="AP1" s="22"/>
+      <c r="AQ1" s="22"/>
+      <c r="AR1" s="22"/>
+      <c r="AS1" s="22"/>
+      <c r="AT1" s="22"/>
+      <c r="AU1" s="22"/>
+      <c r="AV1" s="22"/>
+      <c r="AW1" s="22"/>
+      <c r="AX1" s="22"/>
+      <c r="AY1" s="22"/>
+      <c r="AZ1" s="22"/>
+      <c r="BA1" s="22"/>
+      <c r="BB1" s="22"/>
+      <c r="BC1" s="22"/>
+      <c r="BD1" s="22"/>
+      <c r="BE1" s="22"/>
+      <c r="BF1" s="22"/>
+      <c r="BG1" s="22"/>
+      <c r="BH1" s="22"/>
+      <c r="BI1" s="22"/>
+      <c r="BJ1" s="22"/>
+      <c r="BK1" s="22"/>
+      <c r="BL1" s="22"/>
+      <c r="BM1" s="22"/>
+      <c r="BN1" s="22"/>
+      <c r="BO1" s="22"/>
+      <c r="BP1" s="22"/>
+      <c r="BQ1" s="22"/>
+      <c r="BR1" s="22"/>
+      <c r="BS1" s="22"/>
+      <c r="BT1" s="22"/>
+      <c r="BU1" s="22"/>
+      <c r="BV1" s="22"/>
+      <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="29">
+      <c r="A2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="27">
         <v>46274</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="27">
         <v>46274</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="27">
         <v>46274</v>
       </c>
-      <c r="I2" s="29">
+      <c r="I2" s="27">
         <v>46276</v>
       </c>
-      <c r="J2" s="29">
+      <c r="J2" s="27">
         <v>46279</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="27">
         <v>46279</v>
       </c>
-      <c r="L2" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="M2" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="29">
+      <c r="L2" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="27">
         <v>46286</v>
       </c>
-      <c r="O2" s="29">
+      <c r="O2" s="27">
         <v>46286</v>
       </c>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
-      <c r="BJ2" s="29"/>
-      <c r="BK2" s="29"/>
-      <c r="BL2" s="29"/>
-      <c r="BM2" s="29"/>
-      <c r="BN2" s="29"/>
-      <c r="BO2" s="29"/>
-      <c r="BP2" s="29"/>
-      <c r="BQ2" s="29"/>
-      <c r="BR2" s="29"/>
-      <c r="BS2" s="29"/>
-      <c r="BT2" s="29"/>
-      <c r="BU2" s="29"/>
-      <c r="BV2" s="29"/>
-      <c r="BW2" s="29"/>
+      <c r="P2" s="27">
+        <v>46290</v>
+      </c>
+      <c r="Q2" s="27">
+        <v>46290</v>
+      </c>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="27"/>
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="27"/>
+      <c r="AU2" s="27"/>
+      <c r="AV2" s="27"/>
+      <c r="AW2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="27"/>
+      <c r="AZ2" s="27"/>
+      <c r="BA2" s="27"/>
+      <c r="BB2" s="27"/>
+      <c r="BC2" s="27"/>
+      <c r="BD2" s="27"/>
+      <c r="BE2" s="27"/>
+      <c r="BF2" s="27"/>
+      <c r="BG2" s="27"/>
+      <c r="BH2" s="27"/>
+      <c r="BI2" s="27"/>
+      <c r="BJ2" s="27"/>
+      <c r="BK2" s="27"/>
+      <c r="BL2" s="27"/>
+      <c r="BM2" s="27"/>
+      <c r="BN2" s="27"/>
+      <c r="BO2" s="27"/>
+      <c r="BP2" s="27"/>
+      <c r="BQ2" s="27"/>
+      <c r="BR2" s="27"/>
+      <c r="BS2" s="27"/>
+      <c r="BT2" s="27"/>
+      <c r="BU2" s="27"/>
+      <c r="BV2" s="27"/>
+      <c r="BW2" s="27"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="29"/>
-      <c r="BJ3" s="29"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="29"/>
-      <c r="BM3" s="29"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="29"/>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="29"/>
-      <c r="BT3" s="29"/>
-      <c r="BU3" s="29"/>
-      <c r="BV3" s="29"/>
-      <c r="BW3" s="29"/>
+      <c r="A3" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27"/>
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="27"/>
+      <c r="AS3" s="27"/>
+      <c r="AT3" s="27"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="27"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27"/>
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="27"/>
+      <c r="BB3" s="27"/>
+      <c r="BC3" s="27"/>
+      <c r="BD3" s="27"/>
+      <c r="BE3" s="27"/>
+      <c r="BF3" s="27"/>
+      <c r="BG3" s="27"/>
+      <c r="BH3" s="27"/>
+      <c r="BI3" s="27"/>
+      <c r="BJ3" s="27"/>
+      <c r="BK3" s="27"/>
+      <c r="BL3" s="27"/>
+      <c r="BM3" s="27"/>
+      <c r="BN3" s="27"/>
+      <c r="BO3" s="27"/>
+      <c r="BP3" s="27"/>
+      <c r="BQ3" s="27"/>
+      <c r="BR3" s="27"/>
+      <c r="BS3" s="27"/>
+      <c r="BT3" s="27"/>
+      <c r="BU3" s="27"/>
+      <c r="BV3" s="27"/>
+      <c r="BW3" s="27"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="32" t="s">
+      <c r="A4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29"/>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="29"/>
-      <c r="AS4" s="29"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="29"/>
-      <c r="AV4" s="29"/>
-      <c r="AW4" s="29"/>
-      <c r="AX4" s="29"/>
-      <c r="AY4" s="29"/>
-      <c r="AZ4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="29"/>
-      <c r="BJ4" s="29"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="29"/>
-      <c r="BT4" s="29"/>
-      <c r="BU4" s="29"/>
-      <c r="BV4" s="29"/>
-      <c r="BW4" s="29"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="27"/>
+      <c r="AW4" s="27"/>
+      <c r="AX4" s="27"/>
+      <c r="AY4" s="27"/>
+      <c r="AZ4" s="27"/>
+      <c r="BA4" s="27"/>
+      <c r="BB4" s="27"/>
+      <c r="BC4" s="27"/>
+      <c r="BD4" s="27"/>
+      <c r="BE4" s="27"/>
+      <c r="BF4" s="27"/>
+      <c r="BG4" s="27"/>
+      <c r="BH4" s="27"/>
+      <c r="BI4" s="27"/>
+      <c r="BJ4" s="27"/>
+      <c r="BK4" s="27"/>
+      <c r="BL4" s="27"/>
+      <c r="BM4" s="27"/>
+      <c r="BN4" s="27"/>
+      <c r="BO4" s="27"/>
+      <c r="BP4" s="27"/>
+      <c r="BQ4" s="27"/>
+      <c r="BR4" s="27"/>
+      <c r="BS4" s="27"/>
+      <c r="BT4" s="27"/>
+      <c r="BU4" s="27"/>
+      <c r="BV4" s="27"/>
+      <c r="BW4" s="27"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="42"/>
+      <c r="C5" s="43">
         <v>60</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
-      <c r="BJ5" s="29"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="29"/>
-      <c r="BM5" s="29"/>
-      <c r="BN5" s="29"/>
-      <c r="BO5" s="29"/>
-      <c r="BP5" s="29"/>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="29"/>
-      <c r="BS5" s="29"/>
-      <c r="BT5" s="29"/>
-      <c r="BU5" s="29"/>
-      <c r="BV5" s="29"/>
-      <c r="BW5" s="29"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="27"/>
+      <c r="AK5" s="27"/>
+      <c r="AL5" s="27"/>
+      <c r="AM5" s="27"/>
+      <c r="AN5" s="27"/>
+      <c r="AO5" s="27"/>
+      <c r="AP5" s="27"/>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="27"/>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="27"/>
+      <c r="AW5" s="27"/>
+      <c r="AX5" s="27"/>
+      <c r="AY5" s="27"/>
+      <c r="AZ5" s="27"/>
+      <c r="BA5" s="27"/>
+      <c r="BB5" s="27"/>
+      <c r="BC5" s="27"/>
+      <c r="BD5" s="27"/>
+      <c r="BE5" s="27"/>
+      <c r="BF5" s="27"/>
+      <c r="BG5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="27"/>
+      <c r="BJ5" s="27"/>
+      <c r="BK5" s="27"/>
+      <c r="BL5" s="27"/>
+      <c r="BM5" s="27"/>
+      <c r="BN5" s="27"/>
+      <c r="BO5" s="27"/>
+      <c r="BP5" s="27"/>
+      <c r="BQ5" s="27"/>
+      <c r="BR5" s="27"/>
+      <c r="BS5" s="27"/>
+      <c r="BT5" s="27"/>
+      <c r="BU5" s="27"/>
+      <c r="BV5" s="27"/>
+      <c r="BW5" s="27"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43">
         <v>4</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
-      <c r="AI6" s="29"/>
-      <c r="AJ6" s="29"/>
-      <c r="AK6" s="29"/>
-      <c r="AL6" s="29"/>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
-      <c r="AO6" s="29"/>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="29"/>
-      <c r="AS6" s="29"/>
-      <c r="AT6" s="29"/>
-      <c r="AU6" s="29"/>
-      <c r="AV6" s="29"/>
-      <c r="AW6" s="29"/>
-      <c r="AX6" s="29"/>
-      <c r="AY6" s="29"/>
-      <c r="AZ6" s="29"/>
-      <c r="BA6" s="29"/>
-      <c r="BB6" s="29"/>
-      <c r="BC6" s="29"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="29"/>
-      <c r="BG6" s="29"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="29"/>
-      <c r="BJ6" s="29"/>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="29"/>
-      <c r="BM6" s="29"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="29"/>
-      <c r="BP6" s="29"/>
-      <c r="BQ6" s="29"/>
-      <c r="BR6" s="29"/>
-      <c r="BS6" s="29"/>
-      <c r="BT6" s="29"/>
-      <c r="BU6" s="29"/>
-      <c r="BV6" s="29"/>
-      <c r="BW6" s="29"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="27"/>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="27"/>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="27"/>
+      <c r="AG6" s="27"/>
+      <c r="AH6" s="27"/>
+      <c r="AI6" s="27"/>
+      <c r="AJ6" s="27"/>
+      <c r="AK6" s="27"/>
+      <c r="AL6" s="27"/>
+      <c r="AM6" s="27"/>
+      <c r="AN6" s="27"/>
+      <c r="AO6" s="27"/>
+      <c r="AP6" s="27"/>
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="27"/>
+      <c r="AS6" s="27"/>
+      <c r="AT6" s="27"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="27"/>
+      <c r="AW6" s="27"/>
+      <c r="AX6" s="27"/>
+      <c r="AY6" s="27"/>
+      <c r="AZ6" s="27"/>
+      <c r="BA6" s="27"/>
+      <c r="BB6" s="27"/>
+      <c r="BC6" s="27"/>
+      <c r="BD6" s="27"/>
+      <c r="BE6" s="27"/>
+      <c r="BF6" s="27"/>
+      <c r="BG6" s="27"/>
+      <c r="BH6" s="27"/>
+      <c r="BI6" s="27"/>
+      <c r="BJ6" s="27"/>
+      <c r="BK6" s="27"/>
+      <c r="BL6" s="27"/>
+      <c r="BM6" s="27"/>
+      <c r="BN6" s="27"/>
+      <c r="BO6" s="27"/>
+      <c r="BP6" s="27"/>
+      <c r="BQ6" s="27"/>
+      <c r="BR6" s="27"/>
+      <c r="BS6" s="27"/>
+      <c r="BT6" s="27"/>
+      <c r="BU6" s="27"/>
+      <c r="BV6" s="27"/>
+      <c r="BW6" s="27"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="49">
+      <c r="B7" s="45"/>
+      <c r="C7" s="43">
         <v>11</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="30"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="30"/>
-      <c r="AN7" s="30"/>
-      <c r="AO7" s="30"/>
-      <c r="AP7" s="30"/>
-      <c r="AQ7" s="30"/>
-      <c r="AR7" s="30"/>
-      <c r="AS7" s="30"/>
-      <c r="AT7" s="30"/>
-      <c r="AU7" s="30"/>
-      <c r="AV7" s="30"/>
-      <c r="AW7" s="30"/>
-      <c r="AX7" s="30"/>
-      <c r="AY7" s="30"/>
-      <c r="AZ7" s="30"/>
-      <c r="BA7" s="30"/>
-      <c r="BB7" s="30"/>
-      <c r="BC7" s="30"/>
-      <c r="BD7" s="30"/>
-      <c r="BE7" s="30"/>
-      <c r="BF7" s="30"/>
-      <c r="BG7" s="30"/>
-      <c r="BH7" s="30"/>
-      <c r="BI7" s="30"/>
-      <c r="BJ7" s="30"/>
-      <c r="BK7" s="30"/>
-      <c r="BL7" s="30"/>
-      <c r="BM7" s="30"/>
-      <c r="BN7" s="30"/>
-      <c r="BO7" s="30"/>
-      <c r="BP7" s="30"/>
-      <c r="BQ7" s="30"/>
-      <c r="BR7" s="30"/>
-      <c r="BS7" s="30"/>
-      <c r="BT7" s="30"/>
-      <c r="BU7" s="30"/>
-      <c r="BV7" s="30"/>
-      <c r="BW7" s="30"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="28"/>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="28"/>
+      <c r="AH7" s="28"/>
+      <c r="AI7" s="28"/>
+      <c r="AJ7" s="28"/>
+      <c r="AK7" s="28"/>
+      <c r="AL7" s="28"/>
+      <c r="AM7" s="28"/>
+      <c r="AN7" s="28"/>
+      <c r="AO7" s="28"/>
+      <c r="AP7" s="28"/>
+      <c r="AQ7" s="28"/>
+      <c r="AR7" s="28"/>
+      <c r="AS7" s="28"/>
+      <c r="AT7" s="28"/>
+      <c r="AU7" s="28"/>
+      <c r="AV7" s="28"/>
+      <c r="AW7" s="28"/>
+      <c r="AX7" s="28"/>
+      <c r="AY7" s="28"/>
+      <c r="AZ7" s="28"/>
+      <c r="BA7" s="28"/>
+      <c r="BB7" s="28"/>
+      <c r="BC7" s="28"/>
+      <c r="BD7" s="28"/>
+      <c r="BE7" s="28"/>
+      <c r="BF7" s="28"/>
+      <c r="BG7" s="28"/>
+      <c r="BH7" s="28"/>
+      <c r="BI7" s="28"/>
+      <c r="BJ7" s="28"/>
+      <c r="BK7" s="28"/>
+      <c r="BL7" s="28"/>
+      <c r="BM7" s="28"/>
+      <c r="BN7" s="28"/>
+      <c r="BO7" s="28"/>
+      <c r="BP7" s="28"/>
+      <c r="BQ7" s="28"/>
+      <c r="BR7" s="28"/>
+      <c r="BS7" s="28"/>
+      <c r="BT7" s="28"/>
+      <c r="BU7" s="28"/>
+      <c r="BV7" s="28"/>
+      <c r="BW7" s="28"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="31">
+      <c r="B8" s="49"/>
+      <c r="C8" s="50">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="27">
-        <v>1</v>
-      </c>
-      <c r="G8" s="27">
+      <c r="F8" s="25">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25">
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="25">
         <v>3</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="25">
         <v>4</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="25">
         <v>5</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="25">
         <v>6</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="25">
         <v>7</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="25">
         <v>8</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="25">
         <v>9</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="25">
         <v>10</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="25">
         <v>11</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="25">
         <v>12</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="25">
         <v>13</v>
       </c>
-      <c r="S8" s="27">
+      <c r="S8" s="25">
         <v>14</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="25">
         <v>15</v>
       </c>
-      <c r="U8" s="27">
+      <c r="U8" s="25">
         <v>16</v>
       </c>
-      <c r="V8" s="27">
+      <c r="V8" s="25">
         <v>17</v>
       </c>
-      <c r="W8" s="27">
+      <c r="W8" s="25">
         <v>18</v>
       </c>
-      <c r="X8" s="27">
+      <c r="X8" s="25">
         <v>19</v>
       </c>
-      <c r="Y8" s="27">
+      <c r="Y8" s="25">
         <v>20</v>
       </c>
-      <c r="Z8" s="27">
+      <c r="Z8" s="25">
         <v>21</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AA8" s="25">
         <v>22</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="25">
         <v>23</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AC8" s="25">
         <v>24</v>
       </c>
-      <c r="AD8" s="27">
+      <c r="AD8" s="25">
         <v>25</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AE8" s="25">
         <v>26</v>
       </c>
-      <c r="AF8" s="27">
+      <c r="AF8" s="25">
         <v>27</v>
       </c>
-      <c r="AG8" s="27">
+      <c r="AG8" s="25">
         <v>28</v>
       </c>
-      <c r="AH8" s="27">
+      <c r="AH8" s="25">
         <v>29</v>
       </c>
-      <c r="AI8" s="27">
+      <c r="AI8" s="25">
         <v>30</v>
       </c>
-      <c r="AJ8" s="27">
+      <c r="AJ8" s="25">
         <v>31</v>
       </c>
-      <c r="AK8" s="27">
+      <c r="AK8" s="25">
         <v>32</v>
       </c>
-      <c r="AL8" s="27">
+      <c r="AL8" s="25">
         <v>33</v>
       </c>
-      <c r="AM8" s="27">
+      <c r="AM8" s="25">
         <v>34</v>
       </c>
-      <c r="AN8" s="27">
+      <c r="AN8" s="25">
         <v>35</v>
       </c>
-      <c r="AO8" s="27">
+      <c r="AO8" s="25">
         <v>36</v>
       </c>
-      <c r="AP8" s="27">
+      <c r="AP8" s="25">
         <v>37</v>
       </c>
-      <c r="AQ8" s="27">
+      <c r="AQ8" s="25">
         <v>38</v>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="25">
         <v>39</v>
       </c>
-      <c r="AS8" s="27">
+      <c r="AS8" s="25">
         <v>40</v>
       </c>
-      <c r="AT8" s="27">
+      <c r="AT8" s="25">
         <v>41</v>
       </c>
-      <c r="AU8" s="27">
+      <c r="AU8" s="25">
         <v>42</v>
       </c>
-      <c r="AV8" s="27">
+      <c r="AV8" s="25">
         <v>43</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="AW8" s="25">
         <v>44</v>
       </c>
-      <c r="AX8" s="27">
+      <c r="AX8" s="25">
         <v>45</v>
       </c>
-      <c r="AY8" s="27">
+      <c r="AY8" s="25">
         <v>46</v>
       </c>
-      <c r="AZ8" s="27">
+      <c r="AZ8" s="25">
         <v>47</v>
       </c>
-      <c r="BA8" s="27">
+      <c r="BA8" s="25">
         <v>48</v>
       </c>
-      <c r="BB8" s="27">
+      <c r="BB8" s="25">
         <v>49</v>
       </c>
-      <c r="BC8" s="27">
+      <c r="BC8" s="25">
         <v>50</v>
       </c>
-      <c r="BD8" s="27">
+      <c r="BD8" s="25">
         <v>51</v>
       </c>
-      <c r="BE8" s="27">
+      <c r="BE8" s="25">
         <v>52</v>
       </c>
-      <c r="BF8" s="27">
+      <c r="BF8" s="25">
         <v>53</v>
       </c>
-      <c r="BG8" s="27">
+      <c r="BG8" s="25">
         <v>54</v>
       </c>
-      <c r="BH8" s="27">
+      <c r="BH8" s="25">
         <v>55</v>
       </c>
-      <c r="BI8" s="27">
+      <c r="BI8" s="25">
         <v>56</v>
       </c>
-      <c r="BJ8" s="27">
+      <c r="BJ8" s="25">
         <v>57</v>
       </c>
-      <c r="BK8" s="27">
+      <c r="BK8" s="25">
         <v>58</v>
       </c>
-      <c r="BL8" s="27">
+      <c r="BL8" s="25">
         <v>59</v>
       </c>
-      <c r="BM8" s="27">
+      <c r="BM8" s="25">
         <v>60</v>
       </c>
-      <c r="BN8" s="27">
+      <c r="BN8" s="25">
         <v>61</v>
       </c>
-      <c r="BO8" s="27">
+      <c r="BO8" s="25">
         <v>62</v>
       </c>
-      <c r="BP8" s="27">
+      <c r="BP8" s="25">
         <v>63</v>
       </c>
-      <c r="BQ8" s="27">
+      <c r="BQ8" s="25">
         <v>64</v>
       </c>
-      <c r="BR8" s="27">
+      <c r="BR8" s="25">
         <v>65</v>
       </c>
-      <c r="BS8" s="27">
+      <c r="BS8" s="25">
         <v>66</v>
       </c>
-      <c r="BT8" s="27">
+      <c r="BT8" s="25">
         <v>67</v>
       </c>
-      <c r="BU8" s="27">
+      <c r="BU8" s="25">
         <v>68</v>
       </c>
-      <c r="BV8" s="27">
+      <c r="BV8" s="25">
         <v>69</v>
       </c>
-      <c r="BW8" s="27">
+      <c r="BW8" s="25">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="28"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
-      <c r="AU9" s="28"/>
-      <c r="AV9" s="28"/>
-      <c r="AW9" s="28"/>
-      <c r="AX9" s="28"/>
-      <c r="AY9" s="28"/>
-      <c r="AZ9" s="28"/>
-      <c r="BA9" s="28"/>
-      <c r="BB9" s="28"/>
-      <c r="BC9" s="28"/>
-      <c r="BD9" s="28"/>
-      <c r="BE9" s="28"/>
-      <c r="BF9" s="28"/>
-      <c r="BG9" s="28"/>
-      <c r="BH9" s="28"/>
-      <c r="BI9" s="28"/>
-      <c r="BJ9" s="28"/>
-      <c r="BK9" s="28"/>
-      <c r="BL9" s="28"/>
-      <c r="BM9" s="28"/>
-      <c r="BN9" s="28"/>
-      <c r="BO9" s="28"/>
-      <c r="BP9" s="28"/>
-      <c r="BQ9" s="28"/>
-      <c r="BR9" s="28"/>
-      <c r="BS9" s="28"/>
-      <c r="BT9" s="28"/>
-      <c r="BU9" s="28"/>
-      <c r="BV9" s="28"/>
-      <c r="BW9" s="28"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="26"/>
+      <c r="AA9" s="26"/>
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26"/>
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26"/>
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="26"/>
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="26"/>
+      <c r="AN9" s="26"/>
+      <c r="AO9" s="26"/>
+      <c r="AP9" s="26"/>
+      <c r="AQ9" s="26"/>
+      <c r="AR9" s="26"/>
+      <c r="AS9" s="26"/>
+      <c r="AT9" s="26"/>
+      <c r="AU9" s="26"/>
+      <c r="AV9" s="26"/>
+      <c r="AW9" s="26"/>
+      <c r="AX9" s="26"/>
+      <c r="AY9" s="26"/>
+      <c r="AZ9" s="26"/>
+      <c r="BA9" s="26"/>
+      <c r="BB9" s="26"/>
+      <c r="BC9" s="26"/>
+      <c r="BD9" s="26"/>
+      <c r="BE9" s="26"/>
+      <c r="BF9" s="26"/>
+      <c r="BG9" s="26"/>
+      <c r="BH9" s="26"/>
+      <c r="BI9" s="26"/>
+      <c r="BJ9" s="26"/>
+      <c r="BK9" s="26"/>
+      <c r="BL9" s="26"/>
+      <c r="BM9" s="26"/>
+      <c r="BN9" s="26"/>
+      <c r="BO9" s="26"/>
+      <c r="BP9" s="26"/>
+      <c r="BQ9" s="26"/>
+      <c r="BR9" s="26"/>
+      <c r="BS9" s="26"/>
+      <c r="BT9" s="26"/>
+      <c r="BU9" s="26"/>
+      <c r="BV9" s="26"/>
+      <c r="BW9" s="26"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2025,14 +2010,14 @@
         <f t="shared" ref="D11:D26" si="0">COUNT(F11:BW11)</f>
         <v>4</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="14">
         <f>D11/C5</f>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
@@ -2115,16 +2100,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <f>D12/C5</f>
         <v>0.11666666666666667</v>
       </c>
@@ -2218,16 +2203,16 @@
         <v>4</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <f>D13/C5</f>
         <v>0.1</v>
       </c>
@@ -2319,16 +2304,16 @@
         <v>6</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f>D14/C5</f>
         <v>0.11666666666666667</v>
       </c>
@@ -2422,16 +2407,16 @@
         <v>7</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <f>D15/C5</f>
         <v>0.11666666666666667</v>
       </c>
@@ -2525,16 +2510,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <f>D16/C5</f>
         <v>3.3333333333333333E-2</v>
       </c>
@@ -2618,16 +2603,16 @@
         <v>10</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D17" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <f>D17/C5</f>
         <v>0.05</v>
       </c>
@@ -2713,16 +2698,16 @@
         <v>11</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <f>D18/C5</f>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -3391,149 +3376,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
-      <c r="S26" s="32"/>
-      <c r="T26" s="32"/>
-      <c r="U26" s="32"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="32"/>
-      <c r="X26" s="32"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="32"/>
-      <c r="AA26" s="32"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="32"/>
-      <c r="AG26" s="32"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="32"/>
-      <c r="AJ26" s="32"/>
-      <c r="AK26" s="32"/>
-      <c r="AL26" s="32"/>
-      <c r="AM26" s="32"/>
-      <c r="AN26" s="32"/>
-      <c r="AO26" s="32"/>
-      <c r="AP26" s="32"/>
-      <c r="AQ26" s="32"/>
-      <c r="AR26" s="32"/>
-      <c r="AS26" s="32"/>
-      <c r="AT26" s="32"/>
-      <c r="AU26" s="32"/>
-      <c r="AV26" s="32"/>
-      <c r="AW26" s="32"/>
-      <c r="AX26" s="32"/>
-      <c r="AY26" s="32"/>
-      <c r="AZ26" s="32"/>
-      <c r="BA26" s="32"/>
-      <c r="BB26" s="32"/>
-      <c r="BC26" s="32"/>
-      <c r="BD26" s="32"/>
-      <c r="BE26" s="32"/>
-      <c r="BF26" s="32"/>
-      <c r="BG26" s="32"/>
-      <c r="BH26" s="32"/>
-      <c r="BI26" s="32"/>
-      <c r="BJ26" s="32"/>
-      <c r="BK26" s="32"/>
-      <c r="BL26" s="32"/>
-      <c r="BM26" s="32"/>
-      <c r="BN26" s="32"/>
-      <c r="BO26" s="32"/>
-      <c r="BP26" s="32"/>
-      <c r="BQ26" s="32"/>
-      <c r="BR26" s="32"/>
-      <c r="BS26" s="32"/>
-      <c r="BT26" s="32"/>
-      <c r="BU26" s="32"/>
-      <c r="BV26" s="32"/>
-      <c r="BW26" s="32"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="40"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+      <c r="V26" s="40"/>
+      <c r="W26" s="40"/>
+      <c r="X26" s="40"/>
+      <c r="Y26" s="40"/>
+      <c r="Z26" s="40"/>
+      <c r="AA26" s="40"/>
+      <c r="AB26" s="40"/>
+      <c r="AC26" s="40"/>
+      <c r="AD26" s="40"/>
+      <c r="AE26" s="40"/>
+      <c r="AF26" s="40"/>
+      <c r="AG26" s="40"/>
+      <c r="AH26" s="40"/>
+      <c r="AI26" s="40"/>
+      <c r="AJ26" s="40"/>
+      <c r="AK26" s="40"/>
+      <c r="AL26" s="40"/>
+      <c r="AM26" s="40"/>
+      <c r="AN26" s="40"/>
+      <c r="AO26" s="40"/>
+      <c r="AP26" s="40"/>
+      <c r="AQ26" s="40"/>
+      <c r="AR26" s="40"/>
+      <c r="AS26" s="40"/>
+      <c r="AT26" s="40"/>
+      <c r="AU26" s="40"/>
+      <c r="AV26" s="40"/>
+      <c r="AW26" s="40"/>
+      <c r="AX26" s="40"/>
+      <c r="AY26" s="40"/>
+      <c r="AZ26" s="40"/>
+      <c r="BA26" s="40"/>
+      <c r="BB26" s="40"/>
+      <c r="BC26" s="40"/>
+      <c r="BD26" s="40"/>
+      <c r="BE26" s="40"/>
+      <c r="BF26" s="40"/>
+      <c r="BG26" s="40"/>
+      <c r="BH26" s="40"/>
+      <c r="BI26" s="40"/>
+      <c r="BJ26" s="40"/>
+      <c r="BK26" s="40"/>
+      <c r="BL26" s="40"/>
+      <c r="BM26" s="40"/>
+      <c r="BN26" s="40"/>
+      <c r="BO26" s="40"/>
+      <c r="BP26" s="40"/>
+      <c r="BQ26" s="40"/>
+      <c r="BR26" s="40"/>
+      <c r="BS26" s="40"/>
+      <c r="BT26" s="40"/>
+      <c r="BU26" s="40"/>
+      <c r="BV26" s="40"/>
+      <c r="BW26" s="40"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="53"/>
-      <c r="V27" s="53"/>
-      <c r="W27" s="53"/>
-      <c r="X27" s="53"/>
-      <c r="Y27" s="53"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="53"/>
-      <c r="AB27" s="53"/>
-      <c r="AC27" s="53"/>
-      <c r="AD27" s="53"/>
-      <c r="AE27" s="53"/>
-      <c r="AF27" s="53"/>
-      <c r="AG27" s="53"/>
-      <c r="AH27" s="53"/>
-      <c r="AI27" s="53"/>
-      <c r="AJ27" s="53"/>
-      <c r="AK27" s="53"/>
-      <c r="AL27" s="53"/>
-      <c r="AM27" s="53"/>
-      <c r="AN27" s="53"/>
-      <c r="AO27" s="53"/>
-      <c r="AP27" s="53"/>
-      <c r="AQ27" s="53"/>
-      <c r="AR27" s="53"/>
-      <c r="AS27" s="53"/>
-      <c r="AT27" s="53"/>
-      <c r="AU27" s="53"/>
-      <c r="AV27" s="53"/>
-      <c r="AW27" s="53"/>
-      <c r="AX27" s="53"/>
-      <c r="AY27" s="53"/>
-      <c r="AZ27" s="53"/>
-      <c r="BA27" s="53"/>
-      <c r="BB27" s="53"/>
-      <c r="BC27" s="53"/>
-      <c r="BD27" s="53"/>
-      <c r="BE27" s="53"/>
-      <c r="BF27" s="53"/>
-      <c r="BG27" s="53"/>
-      <c r="BH27" s="53"/>
-      <c r="BI27" s="53"/>
-      <c r="BJ27" s="53"/>
-      <c r="BK27" s="53"/>
-      <c r="BL27" s="53"/>
-      <c r="BM27" s="53"/>
-      <c r="BN27" s="53"/>
-      <c r="BO27" s="53"/>
-      <c r="BP27" s="53"/>
-      <c r="BQ27" s="53"/>
-      <c r="BR27" s="53"/>
-      <c r="BS27" s="53"/>
-      <c r="BT27" s="53"/>
-      <c r="BU27" s="53"/>
-      <c r="BV27" s="53"/>
-      <c r="BW27" s="53"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="24"/>
+      <c r="T27" s="24"/>
+      <c r="U27" s="24"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="24"/>
+      <c r="X27" s="24"/>
+      <c r="Y27" s="24"/>
+      <c r="Z27" s="24"/>
+      <c r="AA27" s="24"/>
+      <c r="AB27" s="24"/>
+      <c r="AC27" s="24"/>
+      <c r="AD27" s="24"/>
+      <c r="AE27" s="24"/>
+      <c r="AF27" s="24"/>
+      <c r="AG27" s="24"/>
+      <c r="AH27" s="24"/>
+      <c r="AI27" s="24"/>
+      <c r="AJ27" s="24"/>
+      <c r="AK27" s="24"/>
+      <c r="AL27" s="24"/>
+      <c r="AM27" s="24"/>
+      <c r="AN27" s="24"/>
+      <c r="AO27" s="24"/>
+      <c r="AP27" s="24"/>
+      <c r="AQ27" s="24"/>
+      <c r="AR27" s="24"/>
+      <c r="AS27" s="24"/>
+      <c r="AT27" s="24"/>
+      <c r="AU27" s="24"/>
+      <c r="AV27" s="24"/>
+      <c r="AW27" s="24"/>
+      <c r="AX27" s="24"/>
+      <c r="AY27" s="24"/>
+      <c r="AZ27" s="24"/>
+      <c r="BA27" s="24"/>
+      <c r="BB27" s="24"/>
+      <c r="BC27" s="24"/>
+      <c r="BD27" s="24"/>
+      <c r="BE27" s="24"/>
+      <c r="BF27" s="24"/>
+      <c r="BG27" s="24"/>
+      <c r="BH27" s="24"/>
+      <c r="BI27" s="24"/>
+      <c r="BJ27" s="24"/>
+      <c r="BK27" s="24"/>
+      <c r="BL27" s="24"/>
+      <c r="BM27" s="24"/>
+      <c r="BN27" s="24"/>
+      <c r="BO27" s="24"/>
+      <c r="BP27" s="24"/>
+      <c r="BQ27" s="24"/>
+      <c r="BR27" s="24"/>
+      <c r="BS27" s="24"/>
+      <c r="BT27" s="24"/>
+      <c r="BU27" s="24"/>
+      <c r="BV27" s="24"/>
+      <c r="BW27" s="24"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3541,29 +3526,170 @@
       </c>
     </row>
     <row r="29" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="22">
+      <c r="E29" s="21">
         <f>SUM(E11:E18)/8</f>
         <v>8.5416666666666682E-2</v>
       </c>
-      <c r="AJ29" s="16"/>
-      <c r="AK29" s="17" t="s">
-        <v>34</v>
+      <c r="AJ29" s="15"/>
+      <c r="AK29" s="16" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AJ30" s="18"/>
-      <c r="AK30" s="17" t="s">
-        <v>35</v>
+      <c r="AJ30" s="17"/>
+      <c r="AK30" s="16" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AJ31" s="21"/>
+      <c r="AJ31" s="20"/>
       <c r="AK31" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="165">
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="E26:BW26"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
     <mergeCell ref="F27:S27"/>
     <mergeCell ref="T27:AW27"/>
     <mergeCell ref="AX27:BW27"/>
@@ -3588,146 +3714,6 @@
     <mergeCell ref="AP2:AP7"/>
     <mergeCell ref="AQ2:AQ7"/>
     <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E26:BW26"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3736,7 +3722,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H23"/>
+  <dimension ref="A2:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.7109375" customWidth="1"/>
@@ -3749,49 +3735,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="55" t="s">
-        <v>39</v>
+      <c r="C3" s="57"/>
+      <c r="D3" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="54" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="55"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="54"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -3803,27 +3789,27 @@
       <c r="C5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="18">
         <f>COUNTIF(cms!F11:G11,0)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <f>COUNTIF(cms!H11:Y11,0)</f>
         <v>4</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="18">
         <f>COUNTIF(cms!Z11:AY11,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="18">
         <f>COUNTIF(cms!AZ11:BU11,0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="20"/>
-    </row>
-    <row r="6" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>14</v>
@@ -3831,27 +3817,27 @@
       <c r="C6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E6" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F6" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G6" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H6" s="20"/>
-    </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="18">
+        <f>COUNTIF(cms!F12:G12,0)</f>
+        <v>2</v>
+      </c>
+      <c r="E6" s="18">
+        <f>COUNTIF(cms!H12:Y12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F6" s="18">
+        <f>COUNTIF(cms!Z12:AY12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="18">
+        <f>COUNTIF(cms!AZ12:BU12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>16</v>
@@ -3859,27 +3845,27 @@
       <c r="C7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="19">
-        <f>COUNTIF(cms!F12:G12,0)</f>
+      <c r="D7" s="18">
+        <f>COUNTIF(cms!F13:G13,0)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="19">
-        <f>COUNTIF(cms!H12:Y12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="F7" s="19">
-        <f>COUNTIF(cms!Z12:AY12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="19">
-        <f>COUNTIF(cms!AZ12:BU12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="20"/>
-    </row>
-    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="18">
+        <f>COUNTIF(cms!H13:Y13,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F7" s="18">
+        <f>COUNTIF(cms!Z13:AY13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="18">
+        <f>COUNTIF(cms!AZ13:BU13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>18</v>
@@ -3887,55 +3873,55 @@
       <c r="C8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="19">
-        <f>COUNTIF(cms!F13:G13,0)</f>
+      <c r="D8" s="18">
+        <f>COUNTIF(cms!F14:G14,0)</f>
         <v>2</v>
       </c>
-      <c r="E8" s="19">
-        <f>COUNTIF(cms!H13:Y13,0)</f>
-        <v>4</v>
-      </c>
-      <c r="F8" s="19">
-        <f>COUNTIF(cms!Z13:AY13,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="19">
-        <f>COUNTIF(cms!AZ13:BU13,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="20"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="18">
+        <f>COUNTIF(cms!H14:Y14,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F8" s="18">
+        <f>COUNTIF(cms!Z14:AY14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
+        <f>COUNTIF(cms!AZ14:BU14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="18">
+        <f>COUNTIF(cms!F15:G15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="E9" s="18">
+        <f>COUNTIF(cms!H15:Y15,0)</f>
         <v>5</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E9" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F9" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G9" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H9" s="20"/>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="18">
+        <f>COUNTIF(cms!Z15:AY15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="18">
+        <f>COUNTIF(cms!AZ15:BU15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>22</v>
@@ -3943,27 +3929,27 @@
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="19">
-        <f>COUNTIF(cms!F14:G14,0)</f>
+      <c r="D10" s="18">
+        <f>COUNTIF(cms!F16:G16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="18">
+        <f>COUNTIF(cms!H16:Y16,0)</f>
         <v>2</v>
       </c>
-      <c r="E10" s="19">
-        <f>COUNTIF(cms!H14:Y14,0)</f>
-        <v>5</v>
-      </c>
-      <c r="F10" s="19">
-        <f>COUNTIF(cms!Z14:AY14,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="19">
-        <f>COUNTIF(cms!AZ14:BU14,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="20"/>
-    </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="18">
+        <f>COUNTIF(cms!Z16:AY16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <f>COUNTIF(cms!AZ16:BU16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="19"/>
+    </row>
+    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>24</v>
@@ -3971,231 +3957,147 @@
       <c r="C11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="19">
-        <f>COUNTIF(cms!F15:G15,0)</f>
-        <v>2</v>
-      </c>
-      <c r="E11" s="19">
-        <f>COUNTIF(cms!H15:Y15,0)</f>
-        <v>5</v>
-      </c>
-      <c r="F11" s="19">
-        <f>COUNTIF(cms!Z15:AY15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="19">
-        <f>COUNTIF(cms!AZ15:BU15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="18">
+        <f>COUNTIF(cms!F17:G17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="18">
+        <f>COUNTIF(cms!H17:Y17,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F11" s="18">
+        <f>COUNTIF(cms!Z17:AY17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <f>COUNTIF(cms!AZ17:BU17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="19">
-        <f>COUNTIF(cms!F16:G16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="19">
-        <f>COUNTIF(cms!H16:Y16,0)</f>
-        <v>2</v>
-      </c>
-      <c r="F12" s="19">
-        <f>COUNTIF(cms!Z16:AY16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="19">
-        <f>COUNTIF(cms!AZ16:BU16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="20"/>
-    </row>
-    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="D12" s="18">
+        <f>COUNTIF(cms!F18:G18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="18">
+        <f>COUNTIF(cms!H18:Y18,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F12" s="18">
+        <f>COUNTIF(cms!Z18:AY18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <f>COUNTIF(cms!AZ18:BU18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="19"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
-        <v>9</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E13" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F13" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G13" s="19" t="e">
-        <f>COUNTIF(cms!#REF!,0)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H13" s="20"/>
-    </row>
-    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="19">
-        <f>COUNTIF(cms!F17:G17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="19">
-        <f>COUNTIF(cms!H17:Y17,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F14" s="19">
-        <f>COUNTIF(cms!Z17:AY17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="19">
-        <f>COUNTIF(cms!AZ17:BU17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>11</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="19">
-        <f>COUNTIF(cms!F18:G18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="19">
-        <f>COUNTIF(cms!H18:Y18,0)</f>
-        <v>5</v>
-      </c>
-      <c r="F15" s="19">
-        <f>COUNTIF(cms!Z18:AY18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="19">
-        <f>COUNTIF(cms!AZ18:BU18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="20"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <v>12</v>
-      </c>
-      <c r="B17" s="13"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>16</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
-        <v>17</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
-        <v>18</v>
-      </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -526,92 +526,92 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -871,38 +871,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="31"/>
-      <c r="F1" s="46">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
+      <c r="F1" s="24">
         <v>3</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="25"/>
       <c r="I1" s="23">
         <v>1</v>
       </c>
-      <c r="J1" s="46">
+      <c r="J1" s="24">
         <v>2</v>
       </c>
-      <c r="K1" s="48"/>
-      <c r="L1" s="46">
+      <c r="K1" s="25"/>
+      <c r="L1" s="24">
         <v>2</v>
       </c>
-      <c r="M1" s="48"/>
-      <c r="N1" s="46">
+      <c r="M1" s="25"/>
+      <c r="N1" s="24">
         <v>2</v>
       </c>
-      <c r="O1" s="48"/>
-      <c r="P1" s="46">
+      <c r="O1" s="25"/>
+      <c r="P1" s="24">
         <v>2</v>
       </c>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="24">
+        <v>2</v>
+      </c>
+      <c r="S1" s="25"/>
       <c r="T1" s="22"/>
       <c r="U1" s="22"/>
       <c r="V1" s="22"/>
@@ -961,823 +963,827 @@
       <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="27">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="28">
         <v>46274</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="28">
         <v>46274</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="28">
         <v>46274</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="28">
         <v>46276</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="28">
         <v>46279</v>
       </c>
-      <c r="K2" s="27">
+      <c r="K2" s="28">
         <v>46279</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="27">
+      <c r="N2" s="28">
         <v>46286</v>
       </c>
-      <c r="O2" s="27">
+      <c r="O2" s="28">
         <v>46286</v>
       </c>
-      <c r="P2" s="27">
+      <c r="P2" s="28">
         <v>46290</v>
       </c>
-      <c r="Q2" s="27">
+      <c r="Q2" s="28">
         <v>46290</v>
       </c>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="27"/>
-      <c r="AJ2" s="27"/>
-      <c r="AK2" s="27"/>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="27"/>
-      <c r="AO2" s="27"/>
-      <c r="AP2" s="27"/>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="27"/>
-      <c r="AS2" s="27"/>
-      <c r="AT2" s="27"/>
-      <c r="AU2" s="27"/>
-      <c r="AV2" s="27"/>
-      <c r="AW2" s="27"/>
-      <c r="AX2" s="27"/>
-      <c r="AY2" s="27"/>
-      <c r="AZ2" s="27"/>
-      <c r="BA2" s="27"/>
-      <c r="BB2" s="27"/>
-      <c r="BC2" s="27"/>
-      <c r="BD2" s="27"/>
-      <c r="BE2" s="27"/>
-      <c r="BF2" s="27"/>
-      <c r="BG2" s="27"/>
-      <c r="BH2" s="27"/>
-      <c r="BI2" s="27"/>
-      <c r="BJ2" s="27"/>
-      <c r="BK2" s="27"/>
-      <c r="BL2" s="27"/>
-      <c r="BM2" s="27"/>
-      <c r="BN2" s="27"/>
-      <c r="BO2" s="27"/>
-      <c r="BP2" s="27"/>
-      <c r="BQ2" s="27"/>
-      <c r="BR2" s="27"/>
-      <c r="BS2" s="27"/>
-      <c r="BT2" s="27"/>
-      <c r="BU2" s="27"/>
-      <c r="BV2" s="27"/>
-      <c r="BW2" s="27"/>
+      <c r="R2" s="28">
+        <v>46293</v>
+      </c>
+      <c r="S2" s="28">
+        <v>46293</v>
+      </c>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="27"/>
-      <c r="AN3" s="27"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="27"/>
-      <c r="AS3" s="27"/>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27"/>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="27"/>
-      <c r="BF3" s="27"/>
-      <c r="BG3" s="27"/>
-      <c r="BH3" s="27"/>
-      <c r="BI3" s="27"/>
-      <c r="BJ3" s="27"/>
-      <c r="BK3" s="27"/>
-      <c r="BL3" s="27"/>
-      <c r="BM3" s="27"/>
-      <c r="BN3" s="27"/>
-      <c r="BO3" s="27"/>
-      <c r="BP3" s="27"/>
-      <c r="BQ3" s="27"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40" t="s">
+      <c r="A4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="27"/>
-      <c r="AH4" s="27"/>
-      <c r="AI4" s="27"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="27"/>
-      <c r="AL4" s="27"/>
-      <c r="AM4" s="27"/>
-      <c r="AN4" s="27"/>
-      <c r="AO4" s="27"/>
-      <c r="AP4" s="27"/>
-      <c r="AQ4" s="27"/>
-      <c r="AR4" s="27"/>
-      <c r="AS4" s="27"/>
-      <c r="AT4" s="27"/>
-      <c r="AU4" s="27"/>
-      <c r="AV4" s="27"/>
-      <c r="AW4" s="27"/>
-      <c r="AX4" s="27"/>
-      <c r="AY4" s="27"/>
-      <c r="AZ4" s="27"/>
-      <c r="BA4" s="27"/>
-      <c r="BB4" s="27"/>
-      <c r="BC4" s="27"/>
-      <c r="BD4" s="27"/>
-      <c r="BE4" s="27"/>
-      <c r="BF4" s="27"/>
-      <c r="BG4" s="27"/>
-      <c r="BH4" s="27"/>
-      <c r="BI4" s="27"/>
-      <c r="BJ4" s="27"/>
-      <c r="BK4" s="27"/>
-      <c r="BL4" s="27"/>
-      <c r="BM4" s="27"/>
-      <c r="BN4" s="27"/>
-      <c r="BO4" s="27"/>
-      <c r="BP4" s="27"/>
-      <c r="BQ4" s="27"/>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="27"/>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="27"/>
-      <c r="BV4" s="27"/>
-      <c r="BW4" s="27"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="43">
+      <c r="B5" s="47"/>
+      <c r="C5" s="48">
         <v>60</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="27"/>
-      <c r="AC5" s="27"/>
-      <c r="AD5" s="27"/>
-      <c r="AE5" s="27"/>
-      <c r="AF5" s="27"/>
-      <c r="AG5" s="27"/>
-      <c r="AH5" s="27"/>
-      <c r="AI5" s="27"/>
-      <c r="AJ5" s="27"/>
-      <c r="AK5" s="27"/>
-      <c r="AL5" s="27"/>
-      <c r="AM5" s="27"/>
-      <c r="AN5" s="27"/>
-      <c r="AO5" s="27"/>
-      <c r="AP5" s="27"/>
-      <c r="AQ5" s="27"/>
-      <c r="AR5" s="27"/>
-      <c r="AS5" s="27"/>
-      <c r="AT5" s="27"/>
-      <c r="AU5" s="27"/>
-      <c r="AV5" s="27"/>
-      <c r="AW5" s="27"/>
-      <c r="AX5" s="27"/>
-      <c r="AY5" s="27"/>
-      <c r="AZ5" s="27"/>
-      <c r="BA5" s="27"/>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="27"/>
-      <c r="BD5" s="27"/>
-      <c r="BE5" s="27"/>
-      <c r="BF5" s="27"/>
-      <c r="BG5" s="27"/>
-      <c r="BH5" s="27"/>
-      <c r="BI5" s="27"/>
-      <c r="BJ5" s="27"/>
-      <c r="BK5" s="27"/>
-      <c r="BL5" s="27"/>
-      <c r="BM5" s="27"/>
-      <c r="BN5" s="27"/>
-      <c r="BO5" s="27"/>
-      <c r="BP5" s="27"/>
-      <c r="BQ5" s="27"/>
-      <c r="BR5" s="27"/>
-      <c r="BS5" s="27"/>
-      <c r="BT5" s="27"/>
-      <c r="BU5" s="27"/>
-      <c r="BV5" s="27"/>
-      <c r="BW5" s="27"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48">
         <v>4</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="27"/>
-      <c r="AC6" s="27"/>
-      <c r="AD6" s="27"/>
-      <c r="AE6" s="27"/>
-      <c r="AF6" s="27"/>
-      <c r="AG6" s="27"/>
-      <c r="AH6" s="27"/>
-      <c r="AI6" s="27"/>
-      <c r="AJ6" s="27"/>
-      <c r="AK6" s="27"/>
-      <c r="AL6" s="27"/>
-      <c r="AM6" s="27"/>
-      <c r="AN6" s="27"/>
-      <c r="AO6" s="27"/>
-      <c r="AP6" s="27"/>
-      <c r="AQ6" s="27"/>
-      <c r="AR6" s="27"/>
-      <c r="AS6" s="27"/>
-      <c r="AT6" s="27"/>
-      <c r="AU6" s="27"/>
-      <c r="AV6" s="27"/>
-      <c r="AW6" s="27"/>
-      <c r="AX6" s="27"/>
-      <c r="AY6" s="27"/>
-      <c r="AZ6" s="27"/>
-      <c r="BA6" s="27"/>
-      <c r="BB6" s="27"/>
-      <c r="BC6" s="27"/>
-      <c r="BD6" s="27"/>
-      <c r="BE6" s="27"/>
-      <c r="BF6" s="27"/>
-      <c r="BG6" s="27"/>
-      <c r="BH6" s="27"/>
-      <c r="BI6" s="27"/>
-      <c r="BJ6" s="27"/>
-      <c r="BK6" s="27"/>
-      <c r="BL6" s="27"/>
-      <c r="BM6" s="27"/>
-      <c r="BN6" s="27"/>
-      <c r="BO6" s="27"/>
-      <c r="BP6" s="27"/>
-      <c r="BQ6" s="27"/>
-      <c r="BR6" s="27"/>
-      <c r="BS6" s="27"/>
-      <c r="BT6" s="27"/>
-      <c r="BU6" s="27"/>
-      <c r="BV6" s="27"/>
-      <c r="BW6" s="27"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
+      <c r="BM6" s="28"/>
+      <c r="BN6" s="28"/>
+      <c r="BO6" s="28"/>
+      <c r="BP6" s="28"/>
+      <c r="BQ6" s="28"/>
+      <c r="BR6" s="28"/>
+      <c r="BS6" s="28"/>
+      <c r="BT6" s="28"/>
+      <c r="BU6" s="28"/>
+      <c r="BV6" s="28"/>
+      <c r="BW6" s="28"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="43">
+      <c r="B7" s="50"/>
+      <c r="C7" s="48">
         <v>11</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="28"/>
-      <c r="AH7" s="28"/>
-      <c r="AI7" s="28"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="28"/>
-      <c r="AL7" s="28"/>
-      <c r="AM7" s="28"/>
-      <c r="AN7" s="28"/>
-      <c r="AO7" s="28"/>
-      <c r="AP7" s="28"/>
-      <c r="AQ7" s="28"/>
-      <c r="AR7" s="28"/>
-      <c r="AS7" s="28"/>
-      <c r="AT7" s="28"/>
-      <c r="AU7" s="28"/>
-      <c r="AV7" s="28"/>
-      <c r="AW7" s="28"/>
-      <c r="AX7" s="28"/>
-      <c r="AY7" s="28"/>
-      <c r="AZ7" s="28"/>
-      <c r="BA7" s="28"/>
-      <c r="BB7" s="28"/>
-      <c r="BC7" s="28"/>
-      <c r="BD7" s="28"/>
-      <c r="BE7" s="28"/>
-      <c r="BF7" s="28"/>
-      <c r="BG7" s="28"/>
-      <c r="BH7" s="28"/>
-      <c r="BI7" s="28"/>
-      <c r="BJ7" s="28"/>
-      <c r="BK7" s="28"/>
-      <c r="BL7" s="28"/>
-      <c r="BM7" s="28"/>
-      <c r="BN7" s="28"/>
-      <c r="BO7" s="28"/>
-      <c r="BP7" s="28"/>
-      <c r="BQ7" s="28"/>
-      <c r="BR7" s="28"/>
-      <c r="BS7" s="28"/>
-      <c r="BT7" s="28"/>
-      <c r="BU7" s="28"/>
-      <c r="BV7" s="28"/>
-      <c r="BW7" s="28"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50">
+      <c r="B8" s="32"/>
+      <c r="C8" s="30">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="41"/>
+      <c r="D8" s="33"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="25">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25">
+      <c r="F8" s="26">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26">
         <v>2</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <v>3</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="26">
         <v>4</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="26">
         <v>5</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="26">
         <v>6</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="26">
         <v>7</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="26">
         <v>8</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="26">
         <v>9</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="26">
         <v>10</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="26">
         <v>11</v>
       </c>
-      <c r="Q8" s="25">
+      <c r="Q8" s="26">
         <v>12</v>
       </c>
-      <c r="R8" s="25">
+      <c r="R8" s="26">
         <v>13</v>
       </c>
-      <c r="S8" s="25">
+      <c r="S8" s="26">
         <v>14</v>
       </c>
-      <c r="T8" s="25">
+      <c r="T8" s="26">
         <v>15</v>
       </c>
-      <c r="U8" s="25">
+      <c r="U8" s="26">
         <v>16</v>
       </c>
-      <c r="V8" s="25">
+      <c r="V8" s="26">
         <v>17</v>
       </c>
-      <c r="W8" s="25">
+      <c r="W8" s="26">
         <v>18</v>
       </c>
-      <c r="X8" s="25">
+      <c r="X8" s="26">
         <v>19</v>
       </c>
-      <c r="Y8" s="25">
+      <c r="Y8" s="26">
         <v>20</v>
       </c>
-      <c r="Z8" s="25">
+      <c r="Z8" s="26">
         <v>21</v>
       </c>
-      <c r="AA8" s="25">
+      <c r="AA8" s="26">
         <v>22</v>
       </c>
-      <c r="AB8" s="25">
+      <c r="AB8" s="26">
         <v>23</v>
       </c>
-      <c r="AC8" s="25">
+      <c r="AC8" s="26">
         <v>24</v>
       </c>
-      <c r="AD8" s="25">
+      <c r="AD8" s="26">
         <v>25</v>
       </c>
-      <c r="AE8" s="25">
+      <c r="AE8" s="26">
         <v>26</v>
       </c>
-      <c r="AF8" s="25">
+      <c r="AF8" s="26">
         <v>27</v>
       </c>
-      <c r="AG8" s="25">
+      <c r="AG8" s="26">
         <v>28</v>
       </c>
-      <c r="AH8" s="25">
+      <c r="AH8" s="26">
         <v>29</v>
       </c>
-      <c r="AI8" s="25">
+      <c r="AI8" s="26">
         <v>30</v>
       </c>
-      <c r="AJ8" s="25">
+      <c r="AJ8" s="26">
         <v>31</v>
       </c>
-      <c r="AK8" s="25">
+      <c r="AK8" s="26">
         <v>32</v>
       </c>
-      <c r="AL8" s="25">
+      <c r="AL8" s="26">
         <v>33</v>
       </c>
-      <c r="AM8" s="25">
+      <c r="AM8" s="26">
         <v>34</v>
       </c>
-      <c r="AN8" s="25">
+      <c r="AN8" s="26">
         <v>35</v>
       </c>
-      <c r="AO8" s="25">
+      <c r="AO8" s="26">
         <v>36</v>
       </c>
-      <c r="AP8" s="25">
+      <c r="AP8" s="26">
         <v>37</v>
       </c>
-      <c r="AQ8" s="25">
+      <c r="AQ8" s="26">
         <v>38</v>
       </c>
-      <c r="AR8" s="25">
+      <c r="AR8" s="26">
         <v>39</v>
       </c>
-      <c r="AS8" s="25">
+      <c r="AS8" s="26">
         <v>40</v>
       </c>
-      <c r="AT8" s="25">
+      <c r="AT8" s="26">
         <v>41</v>
       </c>
-      <c r="AU8" s="25">
+      <c r="AU8" s="26">
         <v>42</v>
       </c>
-      <c r="AV8" s="25">
+      <c r="AV8" s="26">
         <v>43</v>
       </c>
-      <c r="AW8" s="25">
+      <c r="AW8" s="26">
         <v>44</v>
       </c>
-      <c r="AX8" s="25">
+      <c r="AX8" s="26">
         <v>45</v>
       </c>
-      <c r="AY8" s="25">
+      <c r="AY8" s="26">
         <v>46</v>
       </c>
-      <c r="AZ8" s="25">
+      <c r="AZ8" s="26">
         <v>47</v>
       </c>
-      <c r="BA8" s="25">
+      <c r="BA8" s="26">
         <v>48</v>
       </c>
-      <c r="BB8" s="25">
+      <c r="BB8" s="26">
         <v>49</v>
       </c>
-      <c r="BC8" s="25">
+      <c r="BC8" s="26">
         <v>50</v>
       </c>
-      <c r="BD8" s="25">
+      <c r="BD8" s="26">
         <v>51</v>
       </c>
-      <c r="BE8" s="25">
+      <c r="BE8" s="26">
         <v>52</v>
       </c>
-      <c r="BF8" s="25">
+      <c r="BF8" s="26">
         <v>53</v>
       </c>
-      <c r="BG8" s="25">
+      <c r="BG8" s="26">
         <v>54</v>
       </c>
-      <c r="BH8" s="25">
+      <c r="BH8" s="26">
         <v>55</v>
       </c>
-      <c r="BI8" s="25">
+      <c r="BI8" s="26">
         <v>56</v>
       </c>
-      <c r="BJ8" s="25">
+      <c r="BJ8" s="26">
         <v>57</v>
       </c>
-      <c r="BK8" s="25">
+      <c r="BK8" s="26">
         <v>58</v>
       </c>
-      <c r="BL8" s="25">
+      <c r="BL8" s="26">
         <v>59</v>
       </c>
-      <c r="BM8" s="25">
+      <c r="BM8" s="26">
         <v>60</v>
       </c>
-      <c r="BN8" s="25">
+      <c r="BN8" s="26">
         <v>61</v>
       </c>
-      <c r="BO8" s="25">
+      <c r="BO8" s="26">
         <v>62</v>
       </c>
-      <c r="BP8" s="25">
+      <c r="BP8" s="26">
         <v>63</v>
       </c>
-      <c r="BQ8" s="25">
+      <c r="BQ8" s="26">
         <v>64</v>
       </c>
-      <c r="BR8" s="25">
+      <c r="BR8" s="26">
         <v>65</v>
       </c>
-      <c r="BS8" s="25">
+      <c r="BS8" s="26">
         <v>66</v>
       </c>
-      <c r="BT8" s="25">
+      <c r="BT8" s="26">
         <v>67</v>
       </c>
-      <c r="BU8" s="25">
+      <c r="BU8" s="26">
         <v>68</v>
       </c>
-      <c r="BV8" s="25">
+      <c r="BV8" s="26">
         <v>69</v>
       </c>
-      <c r="BW8" s="25">
+      <c r="BW8" s="26">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="26"/>
-      <c r="AD9" s="26"/>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="26"/>
-      <c r="AK9" s="26"/>
-      <c r="AL9" s="26"/>
-      <c r="AM9" s="26"/>
-      <c r="AN9" s="26"/>
-      <c r="AO9" s="26"/>
-      <c r="AP9" s="26"/>
-      <c r="AQ9" s="26"/>
-      <c r="AR9" s="26"/>
-      <c r="AS9" s="26"/>
-      <c r="AT9" s="26"/>
-      <c r="AU9" s="26"/>
-      <c r="AV9" s="26"/>
-      <c r="AW9" s="26"/>
-      <c r="AX9" s="26"/>
-      <c r="AY9" s="26"/>
-      <c r="AZ9" s="26"/>
-      <c r="BA9" s="26"/>
-      <c r="BB9" s="26"/>
-      <c r="BC9" s="26"/>
-      <c r="BD9" s="26"/>
-      <c r="BE9" s="26"/>
-      <c r="BF9" s="26"/>
-      <c r="BG9" s="26"/>
-      <c r="BH9" s="26"/>
-      <c r="BI9" s="26"/>
-      <c r="BJ9" s="26"/>
-      <c r="BK9" s="26"/>
-      <c r="BL9" s="26"/>
-      <c r="BM9" s="26"/>
-      <c r="BN9" s="26"/>
-      <c r="BO9" s="26"/>
-      <c r="BP9" s="26"/>
-      <c r="BQ9" s="26"/>
-      <c r="BR9" s="26"/>
-      <c r="BS9" s="26"/>
-      <c r="BT9" s="26"/>
-      <c r="BU9" s="26"/>
-      <c r="BV9" s="26"/>
-      <c r="BW9" s="26"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="27"/>
+      <c r="X9" s="27"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27"/>
+      <c r="AB9" s="27"/>
+      <c r="AC9" s="27"/>
+      <c r="AD9" s="27"/>
+      <c r="AE9" s="27"/>
+      <c r="AF9" s="27"/>
+      <c r="AG9" s="27"/>
+      <c r="AH9" s="27"/>
+      <c r="AI9" s="27"/>
+      <c r="AJ9" s="27"/>
+      <c r="AK9" s="27"/>
+      <c r="AL9" s="27"/>
+      <c r="AM9" s="27"/>
+      <c r="AN9" s="27"/>
+      <c r="AO9" s="27"/>
+      <c r="AP9" s="27"/>
+      <c r="AQ9" s="27"/>
+      <c r="AR9" s="27"/>
+      <c r="AS9" s="27"/>
+      <c r="AT9" s="27"/>
+      <c r="AU9" s="27"/>
+      <c r="AV9" s="27"/>
+      <c r="AW9" s="27"/>
+      <c r="AX9" s="27"/>
+      <c r="AY9" s="27"/>
+      <c r="AZ9" s="27"/>
+      <c r="BA9" s="27"/>
+      <c r="BB9" s="27"/>
+      <c r="BC9" s="27"/>
+      <c r="BD9" s="27"/>
+      <c r="BE9" s="27"/>
+      <c r="BF9" s="27"/>
+      <c r="BG9" s="27"/>
+      <c r="BH9" s="27"/>
+      <c r="BI9" s="27"/>
+      <c r="BJ9" s="27"/>
+      <c r="BK9" s="27"/>
+      <c r="BL9" s="27"/>
+      <c r="BM9" s="27"/>
+      <c r="BN9" s="27"/>
+      <c r="BO9" s="27"/>
+      <c r="BP9" s="27"/>
+      <c r="BQ9" s="27"/>
+      <c r="BR9" s="27"/>
+      <c r="BS9" s="27"/>
+      <c r="BT9" s="27"/>
+      <c r="BU9" s="27"/>
+      <c r="BV9" s="27"/>
+      <c r="BW9" s="27"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38"/>
-      <c r="B10" s="51"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2008,11 +2014,11 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" ref="D11:D26" si="0">COUNT(F11:BW11)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" s="14">
         <f>D11/C5</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -2036,8 +2042,12 @@
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
@@ -2107,11 +2117,11 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" s="14">
         <f>D12/C5</f>
-        <v>0.11666666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -2139,8 +2149,12 @@
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
@@ -2210,11 +2224,11 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" s="14">
         <f>D13/C5</f>
-        <v>0.1</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -2240,8 +2254,12 @@
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -2311,11 +2329,11 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" s="14">
         <f>D14/C5</f>
-        <v>0.11666666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -2343,8 +2361,12 @@
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
@@ -2414,11 +2436,11 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" s="14">
         <f>D15/C5</f>
-        <v>0.11666666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -2446,8 +2468,12 @@
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
@@ -2517,11 +2543,11 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
         <f>D16/C5</f>
-        <v>3.3333333333333333E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -2539,8 +2565,12 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
+      <c r="R16" s="3">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3">
+        <v>0</v>
+      </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -2705,11 +2735,11 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14">
         <f>D18/C5</f>
-        <v>8.3333333333333329E-2</v>
+        <v>0.11666666666666667</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -2733,8 +2763,12 @@
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -3376,149 +3410,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="50"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="40"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="40"/>
-      <c r="U26" s="40"/>
-      <c r="V26" s="40"/>
-      <c r="W26" s="40"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
-      <c r="AD26" s="40"/>
-      <c r="AE26" s="40"/>
-      <c r="AF26" s="40"/>
-      <c r="AG26" s="40"/>
-      <c r="AH26" s="40"/>
-      <c r="AI26" s="40"/>
-      <c r="AJ26" s="40"/>
-      <c r="AK26" s="40"/>
-      <c r="AL26" s="40"/>
-      <c r="AM26" s="40"/>
-      <c r="AN26" s="40"/>
-      <c r="AO26" s="40"/>
-      <c r="AP26" s="40"/>
-      <c r="AQ26" s="40"/>
-      <c r="AR26" s="40"/>
-      <c r="AS26" s="40"/>
-      <c r="AT26" s="40"/>
-      <c r="AU26" s="40"/>
-      <c r="AV26" s="40"/>
-      <c r="AW26" s="40"/>
-      <c r="AX26" s="40"/>
-      <c r="AY26" s="40"/>
-      <c r="AZ26" s="40"/>
-      <c r="BA26" s="40"/>
-      <c r="BB26" s="40"/>
-      <c r="BC26" s="40"/>
-      <c r="BD26" s="40"/>
-      <c r="BE26" s="40"/>
-      <c r="BF26" s="40"/>
-      <c r="BG26" s="40"/>
-      <c r="BH26" s="40"/>
-      <c r="BI26" s="40"/>
-      <c r="BJ26" s="40"/>
-      <c r="BK26" s="40"/>
-      <c r="BL26" s="40"/>
-      <c r="BM26" s="40"/>
-      <c r="BN26" s="40"/>
-      <c r="BO26" s="40"/>
-      <c r="BP26" s="40"/>
-      <c r="BQ26" s="40"/>
-      <c r="BR26" s="40"/>
-      <c r="BS26" s="40"/>
-      <c r="BT26" s="40"/>
-      <c r="BU26" s="40"/>
-      <c r="BV26" s="40"/>
-      <c r="BW26" s="40"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="31"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="31"/>
+      <c r="AL26" s="31"/>
+      <c r="AM26" s="31"/>
+      <c r="AN26" s="31"/>
+      <c r="AO26" s="31"/>
+      <c r="AP26" s="31"/>
+      <c r="AQ26" s="31"/>
+      <c r="AR26" s="31"/>
+      <c r="AS26" s="31"/>
+      <c r="AT26" s="31"/>
+      <c r="AU26" s="31"/>
+      <c r="AV26" s="31"/>
+      <c r="AW26" s="31"/>
+      <c r="AX26" s="31"/>
+      <c r="AY26" s="31"/>
+      <c r="AZ26" s="31"/>
+      <c r="BA26" s="31"/>
+      <c r="BB26" s="31"/>
+      <c r="BC26" s="31"/>
+      <c r="BD26" s="31"/>
+      <c r="BE26" s="31"/>
+      <c r="BF26" s="31"/>
+      <c r="BG26" s="31"/>
+      <c r="BH26" s="31"/>
+      <c r="BI26" s="31"/>
+      <c r="BJ26" s="31"/>
+      <c r="BK26" s="31"/>
+      <c r="BL26" s="31"/>
+      <c r="BM26" s="31"/>
+      <c r="BN26" s="31"/>
+      <c r="BO26" s="31"/>
+      <c r="BP26" s="31"/>
+      <c r="BQ26" s="31"/>
+      <c r="BR26" s="31"/>
+      <c r="BS26" s="31"/>
+      <c r="BT26" s="31"/>
+      <c r="BU26" s="31"/>
+      <c r="BV26" s="31"/>
+      <c r="BW26" s="31"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
-      <c r="R27" s="24"/>
-      <c r="S27" s="24"/>
-      <c r="T27" s="24"/>
-      <c r="U27" s="24"/>
-      <c r="V27" s="24"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-      <c r="AA27" s="24"/>
-      <c r="AB27" s="24"/>
-      <c r="AC27" s="24"/>
-      <c r="AD27" s="24"/>
-      <c r="AE27" s="24"/>
-      <c r="AF27" s="24"/>
-      <c r="AG27" s="24"/>
-      <c r="AH27" s="24"/>
-      <c r="AI27" s="24"/>
-      <c r="AJ27" s="24"/>
-      <c r="AK27" s="24"/>
-      <c r="AL27" s="24"/>
-      <c r="AM27" s="24"/>
-      <c r="AN27" s="24"/>
-      <c r="AO27" s="24"/>
-      <c r="AP27" s="24"/>
-      <c r="AQ27" s="24"/>
-      <c r="AR27" s="24"/>
-      <c r="AS27" s="24"/>
-      <c r="AT27" s="24"/>
-      <c r="AU27" s="24"/>
-      <c r="AV27" s="24"/>
-      <c r="AW27" s="24"/>
-      <c r="AX27" s="24"/>
-      <c r="AY27" s="24"/>
-      <c r="AZ27" s="24"/>
-      <c r="BA27" s="24"/>
-      <c r="BB27" s="24"/>
-      <c r="BC27" s="24"/>
-      <c r="BD27" s="24"/>
-      <c r="BE27" s="24"/>
-      <c r="BF27" s="24"/>
-      <c r="BG27" s="24"/>
-      <c r="BH27" s="24"/>
-      <c r="BI27" s="24"/>
-      <c r="BJ27" s="24"/>
-      <c r="BK27" s="24"/>
-      <c r="BL27" s="24"/>
-      <c r="BM27" s="24"/>
-      <c r="BN27" s="24"/>
-      <c r="BO27" s="24"/>
-      <c r="BP27" s="24"/>
-      <c r="BQ27" s="24"/>
-      <c r="BR27" s="24"/>
-      <c r="BS27" s="24"/>
-      <c r="BT27" s="24"/>
-      <c r="BU27" s="24"/>
-      <c r="BV27" s="24"/>
-      <c r="BW27" s="24"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="52"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="52"/>
+      <c r="T27" s="52"/>
+      <c r="U27" s="52"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="52"/>
+      <c r="X27" s="52"/>
+      <c r="Y27" s="52"/>
+      <c r="Z27" s="52"/>
+      <c r="AA27" s="52"/>
+      <c r="AB27" s="52"/>
+      <c r="AC27" s="52"/>
+      <c r="AD27" s="52"/>
+      <c r="AE27" s="52"/>
+      <c r="AF27" s="52"/>
+      <c r="AG27" s="52"/>
+      <c r="AH27" s="52"/>
+      <c r="AI27" s="52"/>
+      <c r="AJ27" s="52"/>
+      <c r="AK27" s="52"/>
+      <c r="AL27" s="52"/>
+      <c r="AM27" s="52"/>
+      <c r="AN27" s="52"/>
+      <c r="AO27" s="52"/>
+      <c r="AP27" s="52"/>
+      <c r="AQ27" s="52"/>
+      <c r="AR27" s="52"/>
+      <c r="AS27" s="52"/>
+      <c r="AT27" s="52"/>
+      <c r="AU27" s="52"/>
+      <c r="AV27" s="52"/>
+      <c r="AW27" s="52"/>
+      <c r="AX27" s="52"/>
+      <c r="AY27" s="52"/>
+      <c r="AZ27" s="52"/>
+      <c r="BA27" s="52"/>
+      <c r="BB27" s="52"/>
+      <c r="BC27" s="52"/>
+      <c r="BD27" s="52"/>
+      <c r="BE27" s="52"/>
+      <c r="BF27" s="52"/>
+      <c r="BG27" s="52"/>
+      <c r="BH27" s="52"/>
+      <c r="BI27" s="52"/>
+      <c r="BJ27" s="52"/>
+      <c r="BK27" s="52"/>
+      <c r="BL27" s="52"/>
+      <c r="BM27" s="52"/>
+      <c r="BN27" s="52"/>
+      <c r="BO27" s="52"/>
+      <c r="BP27" s="52"/>
+      <c r="BQ27" s="52"/>
+      <c r="BR27" s="52"/>
+      <c r="BS27" s="52"/>
+      <c r="BT27" s="52"/>
+      <c r="BU27" s="52"/>
+      <c r="BV27" s="52"/>
+      <c r="BW27" s="52"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3528,7 +3562,7 @@
     <row r="29" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="21">
         <f>SUM(E11:E18)/8</f>
-        <v>8.5416666666666682E-2</v>
+        <v>0.11458333333333334</v>
       </c>
       <c r="AJ29" s="15"/>
       <c r="AK29" s="16" t="s">
@@ -3548,65 +3582,90 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="165">
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
+  <mergeCells count="166">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:BW27"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E26:BW26"/>
     <mergeCell ref="BU8:BU9"/>
     <mergeCell ref="BV8:BV9"/>
@@ -3631,89 +3690,65 @@
     <mergeCell ref="AN8:AN9"/>
     <mergeCell ref="AO8:AO9"/>
     <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
     <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:BW27"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3746,7 +3781,7 @@
       <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="34" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="56" t="s">
@@ -3770,7 +3805,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="38"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="58"/>
       <c r="C4" s="59"/>
       <c r="D4" s="61"/>
@@ -3795,7 +3830,7 @@
       </c>
       <c r="E5" s="18">
         <f>COUNTIF(cms!H11:Y11,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" s="18">
         <f>COUNTIF(cms!Z11:AY11,0)</f>
@@ -3823,7 +3858,7 @@
       </c>
       <c r="E6" s="18">
         <f>COUNTIF(cms!H12:Y12,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" s="18">
         <f>COUNTIF(cms!Z12:AY12,0)</f>
@@ -3851,7 +3886,7 @@
       </c>
       <c r="E7" s="18">
         <f>COUNTIF(cms!H13:Y13,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" s="18">
         <f>COUNTIF(cms!Z13:AY13,0)</f>
@@ -3879,7 +3914,7 @@
       </c>
       <c r="E8" s="18">
         <f>COUNTIF(cms!H14:Y14,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="18">
         <f>COUNTIF(cms!Z14:AY14,0)</f>
@@ -3907,7 +3942,7 @@
       </c>
       <c r="E9" s="18">
         <f>COUNTIF(cms!H15:Y15,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" s="18">
         <f>COUNTIF(cms!Z15:AY15,0)</f>
@@ -3935,7 +3970,7 @@
       </c>
       <c r="E10" s="18">
         <f>COUNTIF(cms!H16:Y16,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="18">
         <f>COUNTIF(cms!Z16:AY16,0)</f>
@@ -3991,7 +4026,7 @@
       </c>
       <c r="E12" s="18">
         <f>COUNTIF(cms!H18:Y18,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="18">
         <f>COUNTIF(cms!Z18:AY18,0)</f>

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -532,6 +532,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -544,74 +547,71 @@
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -871,16 +871,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="F1" s="24">
         <v>3</v>
       </c>
-      <c r="G1" s="51"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="25"/>
       <c r="I1" s="23">
         <v>1</v>
@@ -905,8 +905,10 @@
         <v>2</v>
       </c>
       <c r="S1" s="25"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
+      <c r="T1" s="24">
+        <v>2</v>
+      </c>
+      <c r="U1" s="25"/>
       <c r="V1" s="22"/>
       <c r="W1" s="22"/>
       <c r="X1" s="22"/>
@@ -963,827 +965,831 @@
       <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="28">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="29">
         <v>46274</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="29">
         <v>46274</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="29">
         <v>46274</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="29">
         <v>46276</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="29">
         <v>46279</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="29">
         <v>46279</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="29">
         <v>46286</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="29">
         <v>46286</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="29">
         <v>46290</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="29">
         <v>46290</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="29">
         <v>46293</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="29">
         <v>46293</v>
       </c>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
+      <c r="T2" s="29">
+        <v>46297</v>
+      </c>
+      <c r="U2" s="29">
+        <v>46297</v>
+      </c>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+      <c r="AT2" s="29"/>
+      <c r="AU2" s="29"/>
+      <c r="AV2" s="29"/>
+      <c r="AW2" s="29"/>
+      <c r="AX2" s="29"/>
+      <c r="AY2" s="29"/>
+      <c r="AZ2" s="29"/>
+      <c r="BA2" s="29"/>
+      <c r="BB2" s="29"/>
+      <c r="BC2" s="29"/>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="29"/>
+      <c r="BG2" s="29"/>
+      <c r="BH2" s="29"/>
+      <c r="BI2" s="29"/>
+      <c r="BJ2" s="29"/>
+      <c r="BK2" s="29"/>
+      <c r="BL2" s="29"/>
+      <c r="BM2" s="29"/>
+      <c r="BN2" s="29"/>
+      <c r="BO2" s="29"/>
+      <c r="BP2" s="29"/>
+      <c r="BQ2" s="29"/>
+      <c r="BR2" s="29"/>
+      <c r="BS2" s="29"/>
+      <c r="BT2" s="29"/>
+      <c r="BU2" s="29"/>
+      <c r="BV2" s="29"/>
+      <c r="BW2" s="29"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="28"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="28"/>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="28"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="28"/>
-      <c r="AZ3" s="28"/>
-      <c r="BA3" s="28"/>
-      <c r="BB3" s="28"/>
-      <c r="BC3" s="28"/>
-      <c r="BD3" s="28"/>
-      <c r="BE3" s="28"/>
-      <c r="BF3" s="28"/>
-      <c r="BG3" s="28"/>
-      <c r="BH3" s="28"/>
-      <c r="BI3" s="28"/>
-      <c r="BJ3" s="28"/>
-      <c r="BK3" s="28"/>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="28"/>
-      <c r="BN3" s="28"/>
-      <c r="BO3" s="28"/>
-      <c r="BP3" s="28"/>
-      <c r="BQ3" s="28"/>
-      <c r="BR3" s="28"/>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="28"/>
-      <c r="BU3" s="28"/>
-      <c r="BV3" s="28"/>
-      <c r="BW3" s="28"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="29"/>
+      <c r="AC3" s="29"/>
+      <c r="AD3" s="29"/>
+      <c r="AE3" s="29"/>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="29"/>
+      <c r="AH3" s="29"/>
+      <c r="AI3" s="29"/>
+      <c r="AJ3" s="29"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="29"/>
+      <c r="AN3" s="29"/>
+      <c r="AO3" s="29"/>
+      <c r="AP3" s="29"/>
+      <c r="AQ3" s="29"/>
+      <c r="AR3" s="29"/>
+      <c r="AS3" s="29"/>
+      <c r="AT3" s="29"/>
+      <c r="AU3" s="29"/>
+      <c r="AV3" s="29"/>
+      <c r="AW3" s="29"/>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+      <c r="AZ3" s="29"/>
+      <c r="BA3" s="29"/>
+      <c r="BB3" s="29"/>
+      <c r="BC3" s="29"/>
+      <c r="BD3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="29"/>
+      <c r="BG3" s="29"/>
+      <c r="BH3" s="29"/>
+      <c r="BI3" s="29"/>
+      <c r="BJ3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="29"/>
+      <c r="BO3" s="29"/>
+      <c r="BP3" s="29"/>
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="29"/>
+      <c r="BS3" s="29"/>
+      <c r="BT3" s="29"/>
+      <c r="BU3" s="29"/>
+      <c r="BV3" s="29"/>
+      <c r="BW3" s="29"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="31" t="s">
+      <c r="A4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
-      <c r="BJ4" s="28"/>
-      <c r="BK4" s="28"/>
-      <c r="BL4" s="28"/>
-      <c r="BM4" s="28"/>
-      <c r="BN4" s="28"/>
-      <c r="BO4" s="28"/>
-      <c r="BP4" s="28"/>
-      <c r="BQ4" s="28"/>
-      <c r="BR4" s="28"/>
-      <c r="BS4" s="28"/>
-      <c r="BT4" s="28"/>
-      <c r="BU4" s="28"/>
-      <c r="BV4" s="28"/>
-      <c r="BW4" s="28"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="29"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="29"/>
+      <c r="AX4" s="29"/>
+      <c r="AY4" s="29"/>
+      <c r="AZ4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+      <c r="BC4" s="29"/>
+      <c r="BD4" s="29"/>
+      <c r="BE4" s="29"/>
+      <c r="BF4" s="29"/>
+      <c r="BG4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="29"/>
+      <c r="BJ4" s="29"/>
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="29"/>
+      <c r="BM4" s="29"/>
+      <c r="BN4" s="29"/>
+      <c r="BO4" s="29"/>
+      <c r="BP4" s="29"/>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="29"/>
+      <c r="BS4" s="29"/>
+      <c r="BT4" s="29"/>
+      <c r="BU4" s="29"/>
+      <c r="BV4" s="29"/>
+      <c r="BW4" s="29"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45">
         <v>60</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="28"/>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="28"/>
-      <c r="BP5" s="28"/>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="28"/>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="28"/>
-      <c r="BU5" s="28"/>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="28"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="29"/>
+      <c r="BS5" s="29"/>
+      <c r="BT5" s="29"/>
+      <c r="BU5" s="29"/>
+      <c r="BV5" s="29"/>
+      <c r="BW5" s="29"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45">
         <v>4</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="28"/>
-      <c r="AH6" s="28"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="28"/>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
-      <c r="BJ6" s="28"/>
-      <c r="BK6" s="28"/>
-      <c r="BL6" s="28"/>
-      <c r="BM6" s="28"/>
-      <c r="BN6" s="28"/>
-      <c r="BO6" s="28"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="28"/>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="28"/>
-      <c r="BU6" s="28"/>
-      <c r="BV6" s="28"/>
-      <c r="BW6" s="28"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="29"/>
+      <c r="BD6" s="29"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BG6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="29"/>
+      <c r="BJ6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="29"/>
+      <c r="BM6" s="29"/>
+      <c r="BN6" s="29"/>
+      <c r="BO6" s="29"/>
+      <c r="BP6" s="29"/>
+      <c r="BQ6" s="29"/>
+      <c r="BR6" s="29"/>
+      <c r="BS6" s="29"/>
+      <c r="BT6" s="29"/>
+      <c r="BU6" s="29"/>
+      <c r="BV6" s="29"/>
+      <c r="BW6" s="29"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="48">
+      <c r="B7" s="47"/>
+      <c r="C7" s="45">
         <v>11</v>
       </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="29"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
-      <c r="AV7" s="29"/>
-      <c r="AW7" s="29"/>
-      <c r="AX7" s="29"/>
-      <c r="AY7" s="29"/>
-      <c r="AZ7" s="29"/>
-      <c r="BA7" s="29"/>
-      <c r="BB7" s="29"/>
-      <c r="BC7" s="29"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="29"/>
-      <c r="BG7" s="29"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="29"/>
-      <c r="BJ7" s="29"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="29"/>
-      <c r="BM7" s="29"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="29"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="29"/>
-      <c r="BS7" s="29"/>
-      <c r="BT7" s="29"/>
-      <c r="BU7" s="29"/>
-      <c r="BV7" s="29"/>
-      <c r="BW7" s="29"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="30"/>
+      <c r="AU7" s="30"/>
+      <c r="AV7" s="30"/>
+      <c r="AW7" s="30"/>
+      <c r="AX7" s="30"/>
+      <c r="AY7" s="30"/>
+      <c r="AZ7" s="30"/>
+      <c r="BA7" s="30"/>
+      <c r="BB7" s="30"/>
+      <c r="BC7" s="30"/>
+      <c r="BD7" s="30"/>
+      <c r="BE7" s="30"/>
+      <c r="BF7" s="30"/>
+      <c r="BG7" s="30"/>
+      <c r="BH7" s="30"/>
+      <c r="BI7" s="30"/>
+      <c r="BJ7" s="30"/>
+      <c r="BK7" s="30"/>
+      <c r="BL7" s="30"/>
+      <c r="BM7" s="30"/>
+      <c r="BN7" s="30"/>
+      <c r="BO7" s="30"/>
+      <c r="BP7" s="30"/>
+      <c r="BQ7" s="30"/>
+      <c r="BR7" s="30"/>
+      <c r="BS7" s="30"/>
+      <c r="BT7" s="30"/>
+      <c r="BU7" s="30"/>
+      <c r="BV7" s="30"/>
+      <c r="BW7" s="30"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="30">
+      <c r="B8" s="49"/>
+      <c r="C8" s="50">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="26">
-        <v>1</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="F8" s="27">
+        <v>1</v>
+      </c>
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <v>3</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <v>5</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="27">
         <v>7</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="27">
         <v>8</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="27">
         <v>9</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="27">
         <v>10</v>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="27">
         <v>11</v>
       </c>
-      <c r="Q8" s="26">
+      <c r="Q8" s="27">
         <v>12</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="27">
         <v>13</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="27">
         <v>14</v>
       </c>
-      <c r="T8" s="26">
+      <c r="T8" s="27">
         <v>15</v>
       </c>
-      <c r="U8" s="26">
+      <c r="U8" s="27">
         <v>16</v>
       </c>
-      <c r="V8" s="26">
+      <c r="V8" s="27">
         <v>17</v>
       </c>
-      <c r="W8" s="26">
+      <c r="W8" s="27">
         <v>18</v>
       </c>
-      <c r="X8" s="26">
+      <c r="X8" s="27">
         <v>19</v>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="27">
         <v>20</v>
       </c>
-      <c r="Z8" s="26">
+      <c r="Z8" s="27">
         <v>21</v>
       </c>
-      <c r="AA8" s="26">
+      <c r="AA8" s="27">
         <v>22</v>
       </c>
-      <c r="AB8" s="26">
+      <c r="AB8" s="27">
         <v>23</v>
       </c>
-      <c r="AC8" s="26">
+      <c r="AC8" s="27">
         <v>24</v>
       </c>
-      <c r="AD8" s="26">
+      <c r="AD8" s="27">
         <v>25</v>
       </c>
-      <c r="AE8" s="26">
+      <c r="AE8" s="27">
         <v>26</v>
       </c>
-      <c r="AF8" s="26">
+      <c r="AF8" s="27">
         <v>27</v>
       </c>
-      <c r="AG8" s="26">
+      <c r="AG8" s="27">
         <v>28</v>
       </c>
-      <c r="AH8" s="26">
+      <c r="AH8" s="27">
         <v>29</v>
       </c>
-      <c r="AI8" s="26">
+      <c r="AI8" s="27">
         <v>30</v>
       </c>
-      <c r="AJ8" s="26">
+      <c r="AJ8" s="27">
         <v>31</v>
       </c>
-      <c r="AK8" s="26">
+      <c r="AK8" s="27">
         <v>32</v>
       </c>
-      <c r="AL8" s="26">
+      <c r="AL8" s="27">
         <v>33</v>
       </c>
-      <c r="AM8" s="26">
+      <c r="AM8" s="27">
         <v>34</v>
       </c>
-      <c r="AN8" s="26">
+      <c r="AN8" s="27">
         <v>35</v>
       </c>
-      <c r="AO8" s="26">
+      <c r="AO8" s="27">
         <v>36</v>
       </c>
-      <c r="AP8" s="26">
+      <c r="AP8" s="27">
         <v>37</v>
       </c>
-      <c r="AQ8" s="26">
+      <c r="AQ8" s="27">
         <v>38</v>
       </c>
-      <c r="AR8" s="26">
+      <c r="AR8" s="27">
         <v>39</v>
       </c>
-      <c r="AS8" s="26">
+      <c r="AS8" s="27">
         <v>40</v>
       </c>
-      <c r="AT8" s="26">
+      <c r="AT8" s="27">
         <v>41</v>
       </c>
-      <c r="AU8" s="26">
+      <c r="AU8" s="27">
         <v>42</v>
       </c>
-      <c r="AV8" s="26">
+      <c r="AV8" s="27">
         <v>43</v>
       </c>
-      <c r="AW8" s="26">
+      <c r="AW8" s="27">
         <v>44</v>
       </c>
-      <c r="AX8" s="26">
+      <c r="AX8" s="27">
         <v>45</v>
       </c>
-      <c r="AY8" s="26">
+      <c r="AY8" s="27">
         <v>46</v>
       </c>
-      <c r="AZ8" s="26">
+      <c r="AZ8" s="27">
         <v>47</v>
       </c>
-      <c r="BA8" s="26">
+      <c r="BA8" s="27">
         <v>48</v>
       </c>
-      <c r="BB8" s="26">
+      <c r="BB8" s="27">
         <v>49</v>
       </c>
-      <c r="BC8" s="26">
+      <c r="BC8" s="27">
         <v>50</v>
       </c>
-      <c r="BD8" s="26">
+      <c r="BD8" s="27">
         <v>51</v>
       </c>
-      <c r="BE8" s="26">
+      <c r="BE8" s="27">
         <v>52</v>
       </c>
-      <c r="BF8" s="26">
+      <c r="BF8" s="27">
         <v>53</v>
       </c>
-      <c r="BG8" s="26">
+      <c r="BG8" s="27">
         <v>54</v>
       </c>
-      <c r="BH8" s="26">
+      <c r="BH8" s="27">
         <v>55</v>
       </c>
-      <c r="BI8" s="26">
+      <c r="BI8" s="27">
         <v>56</v>
       </c>
-      <c r="BJ8" s="26">
+      <c r="BJ8" s="27">
         <v>57</v>
       </c>
-      <c r="BK8" s="26">
+      <c r="BK8" s="27">
         <v>58</v>
       </c>
-      <c r="BL8" s="26">
+      <c r="BL8" s="27">
         <v>59</v>
       </c>
-      <c r="BM8" s="26">
+      <c r="BM8" s="27">
         <v>60</v>
       </c>
-      <c r="BN8" s="26">
+      <c r="BN8" s="27">
         <v>61</v>
       </c>
-      <c r="BO8" s="26">
+      <c r="BO8" s="27">
         <v>62</v>
       </c>
-      <c r="BP8" s="26">
+      <c r="BP8" s="27">
         <v>63</v>
       </c>
-      <c r="BQ8" s="26">
+      <c r="BQ8" s="27">
         <v>64</v>
       </c>
-      <c r="BR8" s="26">
+      <c r="BR8" s="27">
         <v>65</v>
       </c>
-      <c r="BS8" s="26">
+      <c r="BS8" s="27">
         <v>66</v>
       </c>
-      <c r="BT8" s="26">
+      <c r="BT8" s="27">
         <v>67</v>
       </c>
-      <c r="BU8" s="26">
+      <c r="BU8" s="27">
         <v>68</v>
       </c>
-      <c r="BV8" s="26">
+      <c r="BV8" s="27">
         <v>69</v>
       </c>
-      <c r="BW8" s="26">
+      <c r="BW8" s="27">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="27"/>
-      <c r="AC9" s="27"/>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27"/>
-      <c r="AF9" s="27"/>
-      <c r="AG9" s="27"/>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27"/>
-      <c r="AJ9" s="27"/>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="27"/>
-      <c r="AN9" s="27"/>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="27"/>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="27"/>
-      <c r="AT9" s="27"/>
-      <c r="AU9" s="27"/>
-      <c r="AV9" s="27"/>
-      <c r="AW9" s="27"/>
-      <c r="AX9" s="27"/>
-      <c r="AY9" s="27"/>
-      <c r="AZ9" s="27"/>
-      <c r="BA9" s="27"/>
-      <c r="BB9" s="27"/>
-      <c r="BC9" s="27"/>
-      <c r="BD9" s="27"/>
-      <c r="BE9" s="27"/>
-      <c r="BF9" s="27"/>
-      <c r="BG9" s="27"/>
-      <c r="BH9" s="27"/>
-      <c r="BI9" s="27"/>
-      <c r="BJ9" s="27"/>
-      <c r="BK9" s="27"/>
-      <c r="BL9" s="27"/>
-      <c r="BM9" s="27"/>
-      <c r="BN9" s="27"/>
-      <c r="BO9" s="27"/>
-      <c r="BP9" s="27"/>
-      <c r="BQ9" s="27"/>
-      <c r="BR9" s="27"/>
-      <c r="BS9" s="27"/>
-      <c r="BT9" s="27"/>
-      <c r="BU9" s="27"/>
-      <c r="BV9" s="27"/>
-      <c r="BW9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
+      <c r="A10" s="40"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2014,11 +2020,11 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" ref="D11:D26" si="0">COUNT(F11:BW11)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" s="14">
         <f>D11/C5</f>
-        <v>0.1</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -2048,8 +2054,12 @@
       <c r="S11" s="3">
         <v>0</v>
       </c>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
+      <c r="T11" s="3">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
@@ -2117,11 +2127,11 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="14">
         <f>D12/C5</f>
-        <v>0.15</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -2155,8 +2165,12 @@
       <c r="S12" s="3">
         <v>0</v>
       </c>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
@@ -2224,11 +2238,11 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E13" s="14">
         <f>D13/C5</f>
-        <v>0.13333333333333333</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -2260,8 +2274,12 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
@@ -2329,11 +2347,11 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="14">
         <f>D14/C5</f>
-        <v>0.15</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -2367,8 +2385,12 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
@@ -2436,11 +2458,11 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" s="14">
         <f>D15/C5</f>
-        <v>0.15</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -2474,8 +2496,12 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
@@ -2543,11 +2569,11 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
         <f>D16/C5</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -2571,8 +2597,12 @@
       <c r="S16" s="3">
         <v>0</v>
       </c>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
+      <c r="T16" s="3">
+        <v>0</v>
+      </c>
+      <c r="U16" s="3">
+        <v>0</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
@@ -2735,11 +2765,11 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" s="14">
         <f>D18/C5</f>
-        <v>0.11666666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -2769,8 +2799,12 @@
       <c r="S18" s="3">
         <v>0</v>
       </c>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
@@ -3410,149 +3444,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="31"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
-      <c r="AL26" s="31"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="31"/>
-      <c r="AO26" s="31"/>
-      <c r="AP26" s="31"/>
-      <c r="AQ26" s="31"/>
-      <c r="AR26" s="31"/>
-      <c r="AS26" s="31"/>
-      <c r="AT26" s="31"/>
-      <c r="AU26" s="31"/>
-      <c r="AV26" s="31"/>
-      <c r="AW26" s="31"/>
-      <c r="AX26" s="31"/>
-      <c r="AY26" s="31"/>
-      <c r="AZ26" s="31"/>
-      <c r="BA26" s="31"/>
-      <c r="BB26" s="31"/>
-      <c r="BC26" s="31"/>
-      <c r="BD26" s="31"/>
-      <c r="BE26" s="31"/>
-      <c r="BF26" s="31"/>
-      <c r="BG26" s="31"/>
-      <c r="BH26" s="31"/>
-      <c r="BI26" s="31"/>
-      <c r="BJ26" s="31"/>
-      <c r="BK26" s="31"/>
-      <c r="BL26" s="31"/>
-      <c r="BM26" s="31"/>
-      <c r="BN26" s="31"/>
-      <c r="BO26" s="31"/>
-      <c r="BP26" s="31"/>
-      <c r="BQ26" s="31"/>
-      <c r="BR26" s="31"/>
-      <c r="BS26" s="31"/>
-      <c r="BT26" s="31"/>
-      <c r="BU26" s="31"/>
-      <c r="BV26" s="31"/>
-      <c r="BW26" s="31"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="42"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="42"/>
+      <c r="V26" s="42"/>
+      <c r="W26" s="42"/>
+      <c r="X26" s="42"/>
+      <c r="Y26" s="42"/>
+      <c r="Z26" s="42"/>
+      <c r="AA26" s="42"/>
+      <c r="AB26" s="42"/>
+      <c r="AC26" s="42"/>
+      <c r="AD26" s="42"/>
+      <c r="AE26" s="42"/>
+      <c r="AF26" s="42"/>
+      <c r="AG26" s="42"/>
+      <c r="AH26" s="42"/>
+      <c r="AI26" s="42"/>
+      <c r="AJ26" s="42"/>
+      <c r="AK26" s="42"/>
+      <c r="AL26" s="42"/>
+      <c r="AM26" s="42"/>
+      <c r="AN26" s="42"/>
+      <c r="AO26" s="42"/>
+      <c r="AP26" s="42"/>
+      <c r="AQ26" s="42"/>
+      <c r="AR26" s="42"/>
+      <c r="AS26" s="42"/>
+      <c r="AT26" s="42"/>
+      <c r="AU26" s="42"/>
+      <c r="AV26" s="42"/>
+      <c r="AW26" s="42"/>
+      <c r="AX26" s="42"/>
+      <c r="AY26" s="42"/>
+      <c r="AZ26" s="42"/>
+      <c r="BA26" s="42"/>
+      <c r="BB26" s="42"/>
+      <c r="BC26" s="42"/>
+      <c r="BD26" s="42"/>
+      <c r="BE26" s="42"/>
+      <c r="BF26" s="42"/>
+      <c r="BG26" s="42"/>
+      <c r="BH26" s="42"/>
+      <c r="BI26" s="42"/>
+      <c r="BJ26" s="42"/>
+      <c r="BK26" s="42"/>
+      <c r="BL26" s="42"/>
+      <c r="BM26" s="42"/>
+      <c r="BN26" s="42"/>
+      <c r="BO26" s="42"/>
+      <c r="BP26" s="42"/>
+      <c r="BQ26" s="42"/>
+      <c r="BR26" s="42"/>
+      <c r="BS26" s="42"/>
+      <c r="BT26" s="42"/>
+      <c r="BU26" s="42"/>
+      <c r="BV26" s="42"/>
+      <c r="BW26" s="42"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="52"/>
-      <c r="O27" s="52"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="52"/>
-      <c r="R27" s="52"/>
-      <c r="S27" s="52"/>
-      <c r="T27" s="52"/>
-      <c r="U27" s="52"/>
-      <c r="V27" s="52"/>
-      <c r="W27" s="52"/>
-      <c r="X27" s="52"/>
-      <c r="Y27" s="52"/>
-      <c r="Z27" s="52"/>
-      <c r="AA27" s="52"/>
-      <c r="AB27" s="52"/>
-      <c r="AC27" s="52"/>
-      <c r="AD27" s="52"/>
-      <c r="AE27" s="52"/>
-      <c r="AF27" s="52"/>
-      <c r="AG27" s="52"/>
-      <c r="AH27" s="52"/>
-      <c r="AI27" s="52"/>
-      <c r="AJ27" s="52"/>
-      <c r="AK27" s="52"/>
-      <c r="AL27" s="52"/>
-      <c r="AM27" s="52"/>
-      <c r="AN27" s="52"/>
-      <c r="AO27" s="52"/>
-      <c r="AP27" s="52"/>
-      <c r="AQ27" s="52"/>
-      <c r="AR27" s="52"/>
-      <c r="AS27" s="52"/>
-      <c r="AT27" s="52"/>
-      <c r="AU27" s="52"/>
-      <c r="AV27" s="52"/>
-      <c r="AW27" s="52"/>
-      <c r="AX27" s="52"/>
-      <c r="AY27" s="52"/>
-      <c r="AZ27" s="52"/>
-      <c r="BA27" s="52"/>
-      <c r="BB27" s="52"/>
-      <c r="BC27" s="52"/>
-      <c r="BD27" s="52"/>
-      <c r="BE27" s="52"/>
-      <c r="BF27" s="52"/>
-      <c r="BG27" s="52"/>
-      <c r="BH27" s="52"/>
-      <c r="BI27" s="52"/>
-      <c r="BJ27" s="52"/>
-      <c r="BK27" s="52"/>
-      <c r="BL27" s="52"/>
-      <c r="BM27" s="52"/>
-      <c r="BN27" s="52"/>
-      <c r="BO27" s="52"/>
-      <c r="BP27" s="52"/>
-      <c r="BQ27" s="52"/>
-      <c r="BR27" s="52"/>
-      <c r="BS27" s="52"/>
-      <c r="BT27" s="52"/>
-      <c r="BU27" s="52"/>
-      <c r="BV27" s="52"/>
-      <c r="BW27" s="52"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="26"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="26"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="26"/>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="26"/>
+      <c r="AC27" s="26"/>
+      <c r="AD27" s="26"/>
+      <c r="AE27" s="26"/>
+      <c r="AF27" s="26"/>
+      <c r="AG27" s="26"/>
+      <c r="AH27" s="26"/>
+      <c r="AI27" s="26"/>
+      <c r="AJ27" s="26"/>
+      <c r="AK27" s="26"/>
+      <c r="AL27" s="26"/>
+      <c r="AM27" s="26"/>
+      <c r="AN27" s="26"/>
+      <c r="AO27" s="26"/>
+      <c r="AP27" s="26"/>
+      <c r="AQ27" s="26"/>
+      <c r="AR27" s="26"/>
+      <c r="AS27" s="26"/>
+      <c r="AT27" s="26"/>
+      <c r="AU27" s="26"/>
+      <c r="AV27" s="26"/>
+      <c r="AW27" s="26"/>
+      <c r="AX27" s="26"/>
+      <c r="AY27" s="26"/>
+      <c r="AZ27" s="26"/>
+      <c r="BA27" s="26"/>
+      <c r="BB27" s="26"/>
+      <c r="BC27" s="26"/>
+      <c r="BD27" s="26"/>
+      <c r="BE27" s="26"/>
+      <c r="BF27" s="26"/>
+      <c r="BG27" s="26"/>
+      <c r="BH27" s="26"/>
+      <c r="BI27" s="26"/>
+      <c r="BJ27" s="26"/>
+      <c r="BK27" s="26"/>
+      <c r="BL27" s="26"/>
+      <c r="BM27" s="26"/>
+      <c r="BN27" s="26"/>
+      <c r="BO27" s="26"/>
+      <c r="BP27" s="26"/>
+      <c r="BQ27" s="26"/>
+      <c r="BR27" s="26"/>
+      <c r="BS27" s="26"/>
+      <c r="BT27" s="26"/>
+      <c r="BU27" s="26"/>
+      <c r="BV27" s="26"/>
+      <c r="BW27" s="26"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3562,7 +3596,7 @@
     <row r="29" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="21">
         <f>SUM(E11:E18)/8</f>
-        <v>0.11458333333333334</v>
+        <v>0.14374999999999999</v>
       </c>
       <c r="AJ29" s="15"/>
       <c r="AK29" s="16" t="s">
@@ -3582,7 +3616,150 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="166">
+  <mergeCells count="167">
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="E26:BW26"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="F27:S27"/>
     <mergeCell ref="T27:AW27"/>
@@ -3607,148 +3784,6 @@
     <mergeCell ref="BC2:BC7"/>
     <mergeCell ref="AP2:AP7"/>
     <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E26:BW26"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="S8:S9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3781,7 +3816,7 @@
       <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="40" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="56" t="s">
@@ -3805,7 +3840,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="58"/>
       <c r="C4" s="59"/>
       <c r="D4" s="61"/>
@@ -3830,7 +3865,7 @@
       </c>
       <c r="E5" s="18">
         <f>COUNTIF(cms!H11:Y11,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" s="18">
         <f>COUNTIF(cms!Z11:AY11,0)</f>
@@ -3858,7 +3893,7 @@
       </c>
       <c r="E6" s="18">
         <f>COUNTIF(cms!H12:Y12,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" s="18">
         <f>COUNTIF(cms!Z12:AY12,0)</f>
@@ -3886,7 +3921,7 @@
       </c>
       <c r="E7" s="18">
         <f>COUNTIF(cms!H13:Y13,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" s="18">
         <f>COUNTIF(cms!Z13:AY13,0)</f>
@@ -3914,7 +3949,7 @@
       </c>
       <c r="E8" s="18">
         <f>COUNTIF(cms!H14:Y14,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" s="18">
         <f>COUNTIF(cms!Z14:AY14,0)</f>
@@ -3942,7 +3977,7 @@
       </c>
       <c r="E9" s="18">
         <f>COUNTIF(cms!H15:Y15,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" s="18">
         <f>COUNTIF(cms!Z15:AY15,0)</f>
@@ -3970,7 +4005,7 @@
       </c>
       <c r="E10" s="18">
         <f>COUNTIF(cms!H16:Y16,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" s="18">
         <f>COUNTIF(cms!Z16:AY16,0)</f>
@@ -4026,7 +4061,7 @@
       </c>
       <c r="E12" s="18">
         <f>COUNTIF(cms!H18:Y18,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" s="18">
         <f>COUNTIF(cms!Z18:AY18,0)</f>

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -473,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -526,93 +526,93 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -639,6 +639,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -871,46 +877,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="33"/>
-      <c r="F1" s="24">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
+      <c r="F1" s="26">
         <v>3</v>
       </c>
-      <c r="G1" s="48"/>
-      <c r="H1" s="25"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="27"/>
       <c r="I1" s="23">
         <v>1</v>
       </c>
-      <c r="J1" s="24">
+      <c r="J1" s="26">
         <v>2</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="24">
+      <c r="K1" s="27"/>
+      <c r="L1" s="26">
         <v>2</v>
       </c>
-      <c r="M1" s="25"/>
-      <c r="N1" s="24">
+      <c r="M1" s="27"/>
+      <c r="N1" s="26">
         <v>2</v>
       </c>
-      <c r="O1" s="25"/>
-      <c r="P1" s="24">
+      <c r="O1" s="27"/>
+      <c r="P1" s="26">
         <v>2</v>
       </c>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="24">
+      <c r="Q1" s="27"/>
+      <c r="R1" s="26">
         <v>2</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="24">
+      <c r="S1" s="27"/>
+      <c r="T1" s="26">
         <v>2</v>
       </c>
-      <c r="U1" s="25"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="26">
+        <v>2</v>
+      </c>
+      <c r="W1" s="27"/>
       <c r="X1" s="22"/>
       <c r="Y1" s="22"/>
       <c r="Z1" s="22"/>
@@ -965,831 +973,835 @@
       <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="29">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="28">
         <v>46274</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="28">
         <v>46274</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="28">
         <v>46274</v>
       </c>
-      <c r="I2" s="29">
+      <c r="I2" s="28">
         <v>46276</v>
       </c>
-      <c r="J2" s="29">
+      <c r="J2" s="28">
         <v>46279</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="28">
         <v>46279</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="28">
         <v>46286</v>
       </c>
-      <c r="O2" s="29">
+      <c r="O2" s="28">
         <v>46286</v>
       </c>
-      <c r="P2" s="29">
+      <c r="P2" s="28">
         <v>46290</v>
       </c>
-      <c r="Q2" s="29">
+      <c r="Q2" s="28">
         <v>46290</v>
       </c>
-      <c r="R2" s="29">
+      <c r="R2" s="28">
         <v>46293</v>
       </c>
-      <c r="S2" s="29">
+      <c r="S2" s="28">
         <v>46293</v>
       </c>
-      <c r="T2" s="29">
+      <c r="T2" s="28">
         <v>46297</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="28">
         <v>46297</v>
       </c>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
-      <c r="BJ2" s="29"/>
-      <c r="BK2" s="29"/>
-      <c r="BL2" s="29"/>
-      <c r="BM2" s="29"/>
-      <c r="BN2" s="29"/>
-      <c r="BO2" s="29"/>
-      <c r="BP2" s="29"/>
-      <c r="BQ2" s="29"/>
-      <c r="BR2" s="29"/>
-      <c r="BS2" s="29"/>
-      <c r="BT2" s="29"/>
-      <c r="BU2" s="29"/>
-      <c r="BV2" s="29"/>
-      <c r="BW2" s="29"/>
+      <c r="V2" s="62">
+        <v>46300</v>
+      </c>
+      <c r="W2" s="62">
+        <v>46300</v>
+      </c>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="29"/>
-      <c r="BJ3" s="29"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="29"/>
-      <c r="BM3" s="29"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="29"/>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="29"/>
-      <c r="BT3" s="29"/>
-      <c r="BU3" s="29"/>
-      <c r="BV3" s="29"/>
-      <c r="BW3" s="29"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="42" t="s">
+      <c r="A4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29"/>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="29"/>
-      <c r="AS4" s="29"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="29"/>
-      <c r="AV4" s="29"/>
-      <c r="AW4" s="29"/>
-      <c r="AX4" s="29"/>
-      <c r="AY4" s="29"/>
-      <c r="AZ4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="29"/>
-      <c r="BJ4" s="29"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="29"/>
-      <c r="BT4" s="29"/>
-      <c r="BU4" s="29"/>
-      <c r="BV4" s="29"/>
-      <c r="BW4" s="29"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45">
+      <c r="B5" s="47"/>
+      <c r="C5" s="48">
         <v>60</v>
       </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
-      <c r="BJ5" s="29"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="29"/>
-      <c r="BM5" s="29"/>
-      <c r="BN5" s="29"/>
-      <c r="BO5" s="29"/>
-      <c r="BP5" s="29"/>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="29"/>
-      <c r="BS5" s="29"/>
-      <c r="BT5" s="29"/>
-      <c r="BU5" s="29"/>
-      <c r="BV5" s="29"/>
-      <c r="BW5" s="29"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48">
         <v>4</v>
       </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
-      <c r="AI6" s="29"/>
-      <c r="AJ6" s="29"/>
-      <c r="AK6" s="29"/>
-      <c r="AL6" s="29"/>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
-      <c r="AO6" s="29"/>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="29"/>
-      <c r="AS6" s="29"/>
-      <c r="AT6" s="29"/>
-      <c r="AU6" s="29"/>
-      <c r="AV6" s="29"/>
-      <c r="AW6" s="29"/>
-      <c r="AX6" s="29"/>
-      <c r="AY6" s="29"/>
-      <c r="AZ6" s="29"/>
-      <c r="BA6" s="29"/>
-      <c r="BB6" s="29"/>
-      <c r="BC6" s="29"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="29"/>
-      <c r="BG6" s="29"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="29"/>
-      <c r="BJ6" s="29"/>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="29"/>
-      <c r="BM6" s="29"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="29"/>
-      <c r="BP6" s="29"/>
-      <c r="BQ6" s="29"/>
-      <c r="BR6" s="29"/>
-      <c r="BS6" s="29"/>
-      <c r="BT6" s="29"/>
-      <c r="BU6" s="29"/>
-      <c r="BV6" s="29"/>
-      <c r="BW6" s="29"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
+      <c r="BM6" s="28"/>
+      <c r="BN6" s="28"/>
+      <c r="BO6" s="28"/>
+      <c r="BP6" s="28"/>
+      <c r="BQ6" s="28"/>
+      <c r="BR6" s="28"/>
+      <c r="BS6" s="28"/>
+      <c r="BT6" s="28"/>
+      <c r="BU6" s="28"/>
+      <c r="BV6" s="28"/>
+      <c r="BW6" s="28"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="45">
+      <c r="B7" s="50"/>
+      <c r="C7" s="48">
         <v>11</v>
       </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="30"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="30"/>
-      <c r="AN7" s="30"/>
-      <c r="AO7" s="30"/>
-      <c r="AP7" s="30"/>
-      <c r="AQ7" s="30"/>
-      <c r="AR7" s="30"/>
-      <c r="AS7" s="30"/>
-      <c r="AT7" s="30"/>
-      <c r="AU7" s="30"/>
-      <c r="AV7" s="30"/>
-      <c r="AW7" s="30"/>
-      <c r="AX7" s="30"/>
-      <c r="AY7" s="30"/>
-      <c r="AZ7" s="30"/>
-      <c r="BA7" s="30"/>
-      <c r="BB7" s="30"/>
-      <c r="BC7" s="30"/>
-      <c r="BD7" s="30"/>
-      <c r="BE7" s="30"/>
-      <c r="BF7" s="30"/>
-      <c r="BG7" s="30"/>
-      <c r="BH7" s="30"/>
-      <c r="BI7" s="30"/>
-      <c r="BJ7" s="30"/>
-      <c r="BK7" s="30"/>
-      <c r="BL7" s="30"/>
-      <c r="BM7" s="30"/>
-      <c r="BN7" s="30"/>
-      <c r="BO7" s="30"/>
-      <c r="BP7" s="30"/>
-      <c r="BQ7" s="30"/>
-      <c r="BR7" s="30"/>
-      <c r="BS7" s="30"/>
-      <c r="BT7" s="30"/>
-      <c r="BU7" s="30"/>
-      <c r="BV7" s="30"/>
-      <c r="BW7" s="30"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="63"/>
+      <c r="W7" s="63"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50">
+      <c r="B8" s="32"/>
+      <c r="C8" s="30">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="43"/>
+      <c r="D8" s="33"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="27">
-        <v>1</v>
-      </c>
-      <c r="G8" s="27">
+      <c r="F8" s="24">
+        <v>1</v>
+      </c>
+      <c r="G8" s="24">
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="24">
         <v>3</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="24">
         <v>4</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="24">
         <v>5</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="24">
         <v>6</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="24">
         <v>7</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="24">
         <v>8</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="24">
         <v>9</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="24">
         <v>10</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="24">
         <v>11</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="24">
         <v>12</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="24">
         <v>13</v>
       </c>
-      <c r="S8" s="27">
+      <c r="S8" s="24">
         <v>14</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="24">
         <v>15</v>
       </c>
-      <c r="U8" s="27">
+      <c r="U8" s="24">
         <v>16</v>
       </c>
-      <c r="V8" s="27">
+      <c r="V8" s="24">
         <v>17</v>
       </c>
-      <c r="W8" s="27">
+      <c r="W8" s="24">
         <v>18</v>
       </c>
-      <c r="X8" s="27">
+      <c r="X8" s="24">
         <v>19</v>
       </c>
-      <c r="Y8" s="27">
+      <c r="Y8" s="24">
         <v>20</v>
       </c>
-      <c r="Z8" s="27">
+      <c r="Z8" s="24">
         <v>21</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AA8" s="24">
         <v>22</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="24">
         <v>23</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AC8" s="24">
         <v>24</v>
       </c>
-      <c r="AD8" s="27">
+      <c r="AD8" s="24">
         <v>25</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AE8" s="24">
         <v>26</v>
       </c>
-      <c r="AF8" s="27">
+      <c r="AF8" s="24">
         <v>27</v>
       </c>
-      <c r="AG8" s="27">
+      <c r="AG8" s="24">
         <v>28</v>
       </c>
-      <c r="AH8" s="27">
+      <c r="AH8" s="24">
         <v>29</v>
       </c>
-      <c r="AI8" s="27">
+      <c r="AI8" s="24">
         <v>30</v>
       </c>
-      <c r="AJ8" s="27">
+      <c r="AJ8" s="24">
         <v>31</v>
       </c>
-      <c r="AK8" s="27">
+      <c r="AK8" s="24">
         <v>32</v>
       </c>
-      <c r="AL8" s="27">
+      <c r="AL8" s="24">
         <v>33</v>
       </c>
-      <c r="AM8" s="27">
+      <c r="AM8" s="24">
         <v>34</v>
       </c>
-      <c r="AN8" s="27">
+      <c r="AN8" s="24">
         <v>35</v>
       </c>
-      <c r="AO8" s="27">
+      <c r="AO8" s="24">
         <v>36</v>
       </c>
-      <c r="AP8" s="27">
+      <c r="AP8" s="24">
         <v>37</v>
       </c>
-      <c r="AQ8" s="27">
+      <c r="AQ8" s="24">
         <v>38</v>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="24">
         <v>39</v>
       </c>
-      <c r="AS8" s="27">
+      <c r="AS8" s="24">
         <v>40</v>
       </c>
-      <c r="AT8" s="27">
+      <c r="AT8" s="24">
         <v>41</v>
       </c>
-      <c r="AU8" s="27">
+      <c r="AU8" s="24">
         <v>42</v>
       </c>
-      <c r="AV8" s="27">
+      <c r="AV8" s="24">
         <v>43</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="AW8" s="24">
         <v>44</v>
       </c>
-      <c r="AX8" s="27">
+      <c r="AX8" s="24">
         <v>45</v>
       </c>
-      <c r="AY8" s="27">
+      <c r="AY8" s="24">
         <v>46</v>
       </c>
-      <c r="AZ8" s="27">
+      <c r="AZ8" s="24">
         <v>47</v>
       </c>
-      <c r="BA8" s="27">
+      <c r="BA8" s="24">
         <v>48</v>
       </c>
-      <c r="BB8" s="27">
+      <c r="BB8" s="24">
         <v>49</v>
       </c>
-      <c r="BC8" s="27">
+      <c r="BC8" s="24">
         <v>50</v>
       </c>
-      <c r="BD8" s="27">
+      <c r="BD8" s="24">
         <v>51</v>
       </c>
-      <c r="BE8" s="27">
+      <c r="BE8" s="24">
         <v>52</v>
       </c>
-      <c r="BF8" s="27">
+      <c r="BF8" s="24">
         <v>53</v>
       </c>
-      <c r="BG8" s="27">
+      <c r="BG8" s="24">
         <v>54</v>
       </c>
-      <c r="BH8" s="27">
+      <c r="BH8" s="24">
         <v>55</v>
       </c>
-      <c r="BI8" s="27">
+      <c r="BI8" s="24">
         <v>56</v>
       </c>
-      <c r="BJ8" s="27">
+      <c r="BJ8" s="24">
         <v>57</v>
       </c>
-      <c r="BK8" s="27">
+      <c r="BK8" s="24">
         <v>58</v>
       </c>
-      <c r="BL8" s="27">
+      <c r="BL8" s="24">
         <v>59</v>
       </c>
-      <c r="BM8" s="27">
+      <c r="BM8" s="24">
         <v>60</v>
       </c>
-      <c r="BN8" s="27">
+      <c r="BN8" s="24">
         <v>61</v>
       </c>
-      <c r="BO8" s="27">
+      <c r="BO8" s="24">
         <v>62</v>
       </c>
-      <c r="BP8" s="27">
+      <c r="BP8" s="24">
         <v>63</v>
       </c>
-      <c r="BQ8" s="27">
+      <c r="BQ8" s="24">
         <v>64</v>
       </c>
-      <c r="BR8" s="27">
+      <c r="BR8" s="24">
         <v>65</v>
       </c>
-      <c r="BS8" s="27">
+      <c r="BS8" s="24">
         <v>66</v>
       </c>
-      <c r="BT8" s="27">
+      <c r="BT8" s="24">
         <v>67</v>
       </c>
-      <c r="BU8" s="27">
+      <c r="BU8" s="24">
         <v>68</v>
       </c>
-      <c r="BV8" s="27">
+      <c r="BV8" s="24">
         <v>69</v>
       </c>
-      <c r="BW8" s="27">
+      <c r="BW8" s="24">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="28"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
-      <c r="AU9" s="28"/>
-      <c r="AV9" s="28"/>
-      <c r="AW9" s="28"/>
-      <c r="AX9" s="28"/>
-      <c r="AY9" s="28"/>
-      <c r="AZ9" s="28"/>
-      <c r="BA9" s="28"/>
-      <c r="BB9" s="28"/>
-      <c r="BC9" s="28"/>
-      <c r="BD9" s="28"/>
-      <c r="BE9" s="28"/>
-      <c r="BF9" s="28"/>
-      <c r="BG9" s="28"/>
-      <c r="BH9" s="28"/>
-      <c r="BI9" s="28"/>
-      <c r="BJ9" s="28"/>
-      <c r="BK9" s="28"/>
-      <c r="BL9" s="28"/>
-      <c r="BM9" s="28"/>
-      <c r="BN9" s="28"/>
-      <c r="BO9" s="28"/>
-      <c r="BP9" s="28"/>
-      <c r="BQ9" s="28"/>
-      <c r="BR9" s="28"/>
-      <c r="BS9" s="28"/>
-      <c r="BT9" s="28"/>
-      <c r="BU9" s="28"/>
-      <c r="BV9" s="28"/>
-      <c r="BW9" s="28"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="25"/>
+      <c r="AK9" s="25"/>
+      <c r="AL9" s="25"/>
+      <c r="AM9" s="25"/>
+      <c r="AN9" s="25"/>
+      <c r="AO9" s="25"/>
+      <c r="AP9" s="25"/>
+      <c r="AQ9" s="25"/>
+      <c r="AR9" s="25"/>
+      <c r="AS9" s="25"/>
+      <c r="AT9" s="25"/>
+      <c r="AU9" s="25"/>
+      <c r="AV9" s="25"/>
+      <c r="AW9" s="25"/>
+      <c r="AX9" s="25"/>
+      <c r="AY9" s="25"/>
+      <c r="AZ9" s="25"/>
+      <c r="BA9" s="25"/>
+      <c r="BB9" s="25"/>
+      <c r="BC9" s="25"/>
+      <c r="BD9" s="25"/>
+      <c r="BE9" s="25"/>
+      <c r="BF9" s="25"/>
+      <c r="BG9" s="25"/>
+      <c r="BH9" s="25"/>
+      <c r="BI9" s="25"/>
+      <c r="BJ9" s="25"/>
+      <c r="BK9" s="25"/>
+      <c r="BL9" s="25"/>
+      <c r="BM9" s="25"/>
+      <c r="BN9" s="25"/>
+      <c r="BO9" s="25"/>
+      <c r="BP9" s="25"/>
+      <c r="BQ9" s="25"/>
+      <c r="BR9" s="25"/>
+      <c r="BS9" s="25"/>
+      <c r="BT9" s="25"/>
+      <c r="BU9" s="25"/>
+      <c r="BV9" s="25"/>
+      <c r="BW9" s="25"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="40"/>
-      <c r="B10" s="51"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2127,11 +2139,11 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" s="14">
         <f>D12/C5</f>
-        <v>0.18333333333333332</v>
+        <v>0.21666666666666667</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -2171,8 +2183,12 @@
       <c r="U12" s="3">
         <v>0</v>
       </c>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
@@ -2238,11 +2254,11 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E13" s="14">
         <f>D13/C5</f>
-        <v>0.16666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -2280,8 +2296,12 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -2347,11 +2367,11 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E14" s="14">
         <f>D14/C5</f>
-        <v>0.18333333333333332</v>
+        <v>0.21666666666666667</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -2391,8 +2411,12 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
@@ -2458,11 +2482,11 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E15" s="14">
         <f>D15/C5</f>
-        <v>0.18333333333333332</v>
+        <v>0.21666666666666667</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -2502,8 +2526,12 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -2569,11 +2597,11 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="14">
         <f>D16/C5</f>
-        <v>0.1</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -2603,8 +2631,12 @@
       <c r="U16" s="3">
         <v>0</v>
       </c>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
+      <c r="V16" s="3">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0</v>
+      </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -2765,11 +2797,11 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14">
         <f>D18/C5</f>
-        <v>0.15</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -2805,8 +2837,12 @@
       <c r="U18" s="3">
         <v>0</v>
       </c>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
@@ -3444,149 +3480,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="50"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="42"/>
-      <c r="U26" s="42"/>
-      <c r="V26" s="42"/>
-      <c r="W26" s="42"/>
-      <c r="X26" s="42"/>
-      <c r="Y26" s="42"/>
-      <c r="Z26" s="42"/>
-      <c r="AA26" s="42"/>
-      <c r="AB26" s="42"/>
-      <c r="AC26" s="42"/>
-      <c r="AD26" s="42"/>
-      <c r="AE26" s="42"/>
-      <c r="AF26" s="42"/>
-      <c r="AG26" s="42"/>
-      <c r="AH26" s="42"/>
-      <c r="AI26" s="42"/>
-      <c r="AJ26" s="42"/>
-      <c r="AK26" s="42"/>
-      <c r="AL26" s="42"/>
-      <c r="AM26" s="42"/>
-      <c r="AN26" s="42"/>
-      <c r="AO26" s="42"/>
-      <c r="AP26" s="42"/>
-      <c r="AQ26" s="42"/>
-      <c r="AR26" s="42"/>
-      <c r="AS26" s="42"/>
-      <c r="AT26" s="42"/>
-      <c r="AU26" s="42"/>
-      <c r="AV26" s="42"/>
-      <c r="AW26" s="42"/>
-      <c r="AX26" s="42"/>
-      <c r="AY26" s="42"/>
-      <c r="AZ26" s="42"/>
-      <c r="BA26" s="42"/>
-      <c r="BB26" s="42"/>
-      <c r="BC26" s="42"/>
-      <c r="BD26" s="42"/>
-      <c r="BE26" s="42"/>
-      <c r="BF26" s="42"/>
-      <c r="BG26" s="42"/>
-      <c r="BH26" s="42"/>
-      <c r="BI26" s="42"/>
-      <c r="BJ26" s="42"/>
-      <c r="BK26" s="42"/>
-      <c r="BL26" s="42"/>
-      <c r="BM26" s="42"/>
-      <c r="BN26" s="42"/>
-      <c r="BO26" s="42"/>
-      <c r="BP26" s="42"/>
-      <c r="BQ26" s="42"/>
-      <c r="BR26" s="42"/>
-      <c r="BS26" s="42"/>
-      <c r="BT26" s="42"/>
-      <c r="BU26" s="42"/>
-      <c r="BV26" s="42"/>
-      <c r="BW26" s="42"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="31"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="31"/>
+      <c r="AL26" s="31"/>
+      <c r="AM26" s="31"/>
+      <c r="AN26" s="31"/>
+      <c r="AO26" s="31"/>
+      <c r="AP26" s="31"/>
+      <c r="AQ26" s="31"/>
+      <c r="AR26" s="31"/>
+      <c r="AS26" s="31"/>
+      <c r="AT26" s="31"/>
+      <c r="AU26" s="31"/>
+      <c r="AV26" s="31"/>
+      <c r="AW26" s="31"/>
+      <c r="AX26" s="31"/>
+      <c r="AY26" s="31"/>
+      <c r="AZ26" s="31"/>
+      <c r="BA26" s="31"/>
+      <c r="BB26" s="31"/>
+      <c r="BC26" s="31"/>
+      <c r="BD26" s="31"/>
+      <c r="BE26" s="31"/>
+      <c r="BF26" s="31"/>
+      <c r="BG26" s="31"/>
+      <c r="BH26" s="31"/>
+      <c r="BI26" s="31"/>
+      <c r="BJ26" s="31"/>
+      <c r="BK26" s="31"/>
+      <c r="BL26" s="31"/>
+      <c r="BM26" s="31"/>
+      <c r="BN26" s="31"/>
+      <c r="BO26" s="31"/>
+      <c r="BP26" s="31"/>
+      <c r="BQ26" s="31"/>
+      <c r="BR26" s="31"/>
+      <c r="BS26" s="31"/>
+      <c r="BT26" s="31"/>
+      <c r="BU26" s="31"/>
+      <c r="BV26" s="31"/>
+      <c r="BW26" s="31"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="26"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="26"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
-      <c r="AC27" s="26"/>
-      <c r="AD27" s="26"/>
-      <c r="AE27" s="26"/>
-      <c r="AF27" s="26"/>
-      <c r="AG27" s="26"/>
-      <c r="AH27" s="26"/>
-      <c r="AI27" s="26"/>
-      <c r="AJ27" s="26"/>
-      <c r="AK27" s="26"/>
-      <c r="AL27" s="26"/>
-      <c r="AM27" s="26"/>
-      <c r="AN27" s="26"/>
-      <c r="AO27" s="26"/>
-      <c r="AP27" s="26"/>
-      <c r="AQ27" s="26"/>
-      <c r="AR27" s="26"/>
-      <c r="AS27" s="26"/>
-      <c r="AT27" s="26"/>
-      <c r="AU27" s="26"/>
-      <c r="AV27" s="26"/>
-      <c r="AW27" s="26"/>
-      <c r="AX27" s="26"/>
-      <c r="AY27" s="26"/>
-      <c r="AZ27" s="26"/>
-      <c r="BA27" s="26"/>
-      <c r="BB27" s="26"/>
-      <c r="BC27" s="26"/>
-      <c r="BD27" s="26"/>
-      <c r="BE27" s="26"/>
-      <c r="BF27" s="26"/>
-      <c r="BG27" s="26"/>
-      <c r="BH27" s="26"/>
-      <c r="BI27" s="26"/>
-      <c r="BJ27" s="26"/>
-      <c r="BK27" s="26"/>
-      <c r="BL27" s="26"/>
-      <c r="BM27" s="26"/>
-      <c r="BN27" s="26"/>
-      <c r="BO27" s="26"/>
-      <c r="BP27" s="26"/>
-      <c r="BQ27" s="26"/>
-      <c r="BR27" s="26"/>
-      <c r="BS27" s="26"/>
-      <c r="BT27" s="26"/>
-      <c r="BU27" s="26"/>
-      <c r="BV27" s="26"/>
-      <c r="BW27" s="26"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="52"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="52"/>
+      <c r="T27" s="52"/>
+      <c r="U27" s="52"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="52"/>
+      <c r="X27" s="52"/>
+      <c r="Y27" s="52"/>
+      <c r="Z27" s="52"/>
+      <c r="AA27" s="52"/>
+      <c r="AB27" s="52"/>
+      <c r="AC27" s="52"/>
+      <c r="AD27" s="52"/>
+      <c r="AE27" s="52"/>
+      <c r="AF27" s="52"/>
+      <c r="AG27" s="52"/>
+      <c r="AH27" s="52"/>
+      <c r="AI27" s="52"/>
+      <c r="AJ27" s="52"/>
+      <c r="AK27" s="52"/>
+      <c r="AL27" s="52"/>
+      <c r="AM27" s="52"/>
+      <c r="AN27" s="52"/>
+      <c r="AO27" s="52"/>
+      <c r="AP27" s="52"/>
+      <c r="AQ27" s="52"/>
+      <c r="AR27" s="52"/>
+      <c r="AS27" s="52"/>
+      <c r="AT27" s="52"/>
+      <c r="AU27" s="52"/>
+      <c r="AV27" s="52"/>
+      <c r="AW27" s="52"/>
+      <c r="AX27" s="52"/>
+      <c r="AY27" s="52"/>
+      <c r="AZ27" s="52"/>
+      <c r="BA27" s="52"/>
+      <c r="BB27" s="52"/>
+      <c r="BC27" s="52"/>
+      <c r="BD27" s="52"/>
+      <c r="BE27" s="52"/>
+      <c r="BF27" s="52"/>
+      <c r="BG27" s="52"/>
+      <c r="BH27" s="52"/>
+      <c r="BI27" s="52"/>
+      <c r="BJ27" s="52"/>
+      <c r="BK27" s="52"/>
+      <c r="BL27" s="52"/>
+      <c r="BM27" s="52"/>
+      <c r="BN27" s="52"/>
+      <c r="BO27" s="52"/>
+      <c r="BP27" s="52"/>
+      <c r="BQ27" s="52"/>
+      <c r="BR27" s="52"/>
+      <c r="BS27" s="52"/>
+      <c r="BT27" s="52"/>
+      <c r="BU27" s="52"/>
+      <c r="BV27" s="52"/>
+      <c r="BW27" s="52"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3596,7 +3632,7 @@
     <row r="29" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="21">
         <f>SUM(E11:E18)/8</f>
-        <v>0.14374999999999999</v>
+        <v>0.16875000000000001</v>
       </c>
       <c r="AJ29" s="15"/>
       <c r="AK29" s="16" t="s">
@@ -3616,7 +3652,151 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="167">
+  <mergeCells count="168">
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:BW27"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="E26:BW26"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AR2:AR7"/>
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="N1:O1"/>
@@ -3641,149 +3821,6 @@
     <mergeCell ref="AM8:AM9"/>
     <mergeCell ref="S8:S9"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="E26:BW26"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:BW27"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3816,7 +3853,7 @@
       <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="34" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="56" t="s">
@@ -3840,7 +3877,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="58"/>
       <c r="C4" s="59"/>
       <c r="D4" s="61"/>
@@ -3893,7 +3930,7 @@
       </c>
       <c r="E6" s="18">
         <f>COUNTIF(cms!H12:Y12,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" s="18">
         <f>COUNTIF(cms!Z12:AY12,0)</f>
@@ -3921,7 +3958,7 @@
       </c>
       <c r="E7" s="18">
         <f>COUNTIF(cms!H13:Y13,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" s="18">
         <f>COUNTIF(cms!Z13:AY13,0)</f>
@@ -3949,7 +3986,7 @@
       </c>
       <c r="E8" s="18">
         <f>COUNTIF(cms!H14:Y14,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" s="18">
         <f>COUNTIF(cms!Z14:AY14,0)</f>
@@ -3977,7 +4014,7 @@
       </c>
       <c r="E9" s="18">
         <f>COUNTIF(cms!H15:Y15,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" s="18">
         <f>COUNTIF(cms!Z15:AY15,0)</f>
@@ -4005,7 +4042,7 @@
       </c>
       <c r="E10" s="18">
         <f>COUNTIF(cms!H16:Y16,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" s="18">
         <f>COUNTIF(cms!Z16:AY16,0)</f>
@@ -4061,7 +4098,7 @@
       </c>
       <c r="E12" s="18">
         <f>COUNTIF(cms!H18:Y18,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F12" s="18">
         <f>COUNTIF(cms!Z18:AY18,0)</f>

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -526,93 +526,99 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -639,12 +645,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -877,50 +877,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="39"/>
-      <c r="F1" s="26">
-        <v>3</v>
-      </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="35"/>
+      <c r="F1" s="24">
+        <v>7</v>
+      </c>
+      <c r="G1" s="50"/>
+      <c r="H1" s="25"/>
       <c r="I1" s="23">
         <v>1</v>
       </c>
-      <c r="J1" s="26">
+      <c r="J1" s="24">
         <v>2</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="26">
+      <c r="K1" s="25"/>
+      <c r="L1" s="24">
         <v>2</v>
       </c>
-      <c r="M1" s="27"/>
-      <c r="N1" s="26">
+      <c r="M1" s="25"/>
+      <c r="N1" s="24">
         <v>2</v>
       </c>
-      <c r="O1" s="27"/>
-      <c r="P1" s="26">
+      <c r="O1" s="25"/>
+      <c r="P1" s="24">
         <v>2</v>
       </c>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="26">
+      <c r="Q1" s="25"/>
+      <c r="R1" s="24">
         <v>2</v>
       </c>
-      <c r="S1" s="27"/>
-      <c r="T1" s="26">
+      <c r="S1" s="25"/>
+      <c r="T1" s="24">
         <v>2</v>
       </c>
-      <c r="U1" s="27"/>
-      <c r="V1" s="26">
+      <c r="U1" s="25"/>
+      <c r="V1" s="24">
         <v>2</v>
       </c>
-      <c r="W1" s="27"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="24">
+        <v>2</v>
+      </c>
+      <c r="Y1" s="25"/>
       <c r="Z1" s="22"/>
       <c r="AA1" s="22"/>
       <c r="AB1" s="22"/>
@@ -973,835 +975,839 @@
       <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="28">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="29">
         <v>46274</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="29">
         <v>46274</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="29">
         <v>46274</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="29">
         <v>46276</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="29">
         <v>46279</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="29">
         <v>46279</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="29">
         <v>46286</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="29">
         <v>46286</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="29">
         <v>46290</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="29">
         <v>46290</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="29">
         <v>46293</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="29">
         <v>46293</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="29">
         <v>46297</v>
       </c>
-      <c r="U2" s="28">
+      <c r="U2" s="29">
         <v>46297</v>
       </c>
-      <c r="V2" s="62">
+      <c r="V2" s="31">
         <v>46300</v>
       </c>
-      <c r="W2" s="62">
+      <c r="W2" s="31">
         <v>46300</v>
       </c>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
+      <c r="X2" s="29">
+        <v>46304</v>
+      </c>
+      <c r="Y2" s="29">
+        <v>46304</v>
+      </c>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+      <c r="AT2" s="29"/>
+      <c r="AU2" s="29"/>
+      <c r="AV2" s="29"/>
+      <c r="AW2" s="29"/>
+      <c r="AX2" s="29"/>
+      <c r="AY2" s="29"/>
+      <c r="AZ2" s="29"/>
+      <c r="BA2" s="29"/>
+      <c r="BB2" s="29"/>
+      <c r="BC2" s="29"/>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="29"/>
+      <c r="BG2" s="29"/>
+      <c r="BH2" s="29"/>
+      <c r="BI2" s="29"/>
+      <c r="BJ2" s="29"/>
+      <c r="BK2" s="29"/>
+      <c r="BL2" s="29"/>
+      <c r="BM2" s="29"/>
+      <c r="BN2" s="29"/>
+      <c r="BO2" s="29"/>
+      <c r="BP2" s="29"/>
+      <c r="BQ2" s="29"/>
+      <c r="BR2" s="29"/>
+      <c r="BS2" s="29"/>
+      <c r="BT2" s="29"/>
+      <c r="BU2" s="29"/>
+      <c r="BV2" s="29"/>
+      <c r="BW2" s="29"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="28"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="28"/>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="28"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="28"/>
-      <c r="AZ3" s="28"/>
-      <c r="BA3" s="28"/>
-      <c r="BB3" s="28"/>
-      <c r="BC3" s="28"/>
-      <c r="BD3" s="28"/>
-      <c r="BE3" s="28"/>
-      <c r="BF3" s="28"/>
-      <c r="BG3" s="28"/>
-      <c r="BH3" s="28"/>
-      <c r="BI3" s="28"/>
-      <c r="BJ3" s="28"/>
-      <c r="BK3" s="28"/>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="28"/>
-      <c r="BN3" s="28"/>
-      <c r="BO3" s="28"/>
-      <c r="BP3" s="28"/>
-      <c r="BQ3" s="28"/>
-      <c r="BR3" s="28"/>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="28"/>
-      <c r="BU3" s="28"/>
-      <c r="BV3" s="28"/>
-      <c r="BW3" s="28"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="29"/>
+      <c r="AC3" s="29"/>
+      <c r="AD3" s="29"/>
+      <c r="AE3" s="29"/>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="29"/>
+      <c r="AH3" s="29"/>
+      <c r="AI3" s="29"/>
+      <c r="AJ3" s="29"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="29"/>
+      <c r="AN3" s="29"/>
+      <c r="AO3" s="29"/>
+      <c r="AP3" s="29"/>
+      <c r="AQ3" s="29"/>
+      <c r="AR3" s="29"/>
+      <c r="AS3" s="29"/>
+      <c r="AT3" s="29"/>
+      <c r="AU3" s="29"/>
+      <c r="AV3" s="29"/>
+      <c r="AW3" s="29"/>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+      <c r="AZ3" s="29"/>
+      <c r="BA3" s="29"/>
+      <c r="BB3" s="29"/>
+      <c r="BC3" s="29"/>
+      <c r="BD3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="29"/>
+      <c r="BG3" s="29"/>
+      <c r="BH3" s="29"/>
+      <c r="BI3" s="29"/>
+      <c r="BJ3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="29"/>
+      <c r="BO3" s="29"/>
+      <c r="BP3" s="29"/>
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="29"/>
+      <c r="BS3" s="29"/>
+      <c r="BT3" s="29"/>
+      <c r="BU3" s="29"/>
+      <c r="BV3" s="29"/>
+      <c r="BW3" s="29"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="31" t="s">
+      <c r="A4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
-      <c r="BJ4" s="28"/>
-      <c r="BK4" s="28"/>
-      <c r="BL4" s="28"/>
-      <c r="BM4" s="28"/>
-      <c r="BN4" s="28"/>
-      <c r="BO4" s="28"/>
-      <c r="BP4" s="28"/>
-      <c r="BQ4" s="28"/>
-      <c r="BR4" s="28"/>
-      <c r="BS4" s="28"/>
-      <c r="BT4" s="28"/>
-      <c r="BU4" s="28"/>
-      <c r="BV4" s="28"/>
-      <c r="BW4" s="28"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="29"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="29"/>
+      <c r="AX4" s="29"/>
+      <c r="AY4" s="29"/>
+      <c r="AZ4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+      <c r="BC4" s="29"/>
+      <c r="BD4" s="29"/>
+      <c r="BE4" s="29"/>
+      <c r="BF4" s="29"/>
+      <c r="BG4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="29"/>
+      <c r="BJ4" s="29"/>
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="29"/>
+      <c r="BM4" s="29"/>
+      <c r="BN4" s="29"/>
+      <c r="BO4" s="29"/>
+      <c r="BP4" s="29"/>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="29"/>
+      <c r="BS4" s="29"/>
+      <c r="BT4" s="29"/>
+      <c r="BU4" s="29"/>
+      <c r="BV4" s="29"/>
+      <c r="BW4" s="29"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48">
+      <c r="B5" s="46"/>
+      <c r="C5" s="47">
         <v>60</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="28"/>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="28"/>
-      <c r="BP5" s="28"/>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="28"/>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="28"/>
-      <c r="BU5" s="28"/>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="28"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="29"/>
+      <c r="BS5" s="29"/>
+      <c r="BT5" s="29"/>
+      <c r="BU5" s="29"/>
+      <c r="BV5" s="29"/>
+      <c r="BW5" s="29"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47">
         <v>4</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="28"/>
-      <c r="AH6" s="28"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="28"/>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
-      <c r="BJ6" s="28"/>
-      <c r="BK6" s="28"/>
-      <c r="BL6" s="28"/>
-      <c r="BM6" s="28"/>
-      <c r="BN6" s="28"/>
-      <c r="BO6" s="28"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="28"/>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="28"/>
-      <c r="BU6" s="28"/>
-      <c r="BV6" s="28"/>
-      <c r="BW6" s="28"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="29"/>
+      <c r="BD6" s="29"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BG6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="29"/>
+      <c r="BJ6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="29"/>
+      <c r="BM6" s="29"/>
+      <c r="BN6" s="29"/>
+      <c r="BO6" s="29"/>
+      <c r="BP6" s="29"/>
+      <c r="BQ6" s="29"/>
+      <c r="BR6" s="29"/>
+      <c r="BS6" s="29"/>
+      <c r="BT6" s="29"/>
+      <c r="BU6" s="29"/>
+      <c r="BV6" s="29"/>
+      <c r="BW6" s="29"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="48">
+      <c r="B7" s="49"/>
+      <c r="C7" s="47">
         <v>11</v>
       </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="63"/>
-      <c r="W7" s="63"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
-      <c r="AV7" s="29"/>
-      <c r="AW7" s="29"/>
-      <c r="AX7" s="29"/>
-      <c r="AY7" s="29"/>
-      <c r="AZ7" s="29"/>
-      <c r="BA7" s="29"/>
-      <c r="BB7" s="29"/>
-      <c r="BC7" s="29"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="29"/>
-      <c r="BG7" s="29"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="29"/>
-      <c r="BJ7" s="29"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="29"/>
-      <c r="BM7" s="29"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="29"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="29"/>
-      <c r="BS7" s="29"/>
-      <c r="BT7" s="29"/>
-      <c r="BU7" s="29"/>
-      <c r="BV7" s="29"/>
-      <c r="BW7" s="29"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="32"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="30"/>
+      <c r="AU7" s="30"/>
+      <c r="AV7" s="30"/>
+      <c r="AW7" s="30"/>
+      <c r="AX7" s="30"/>
+      <c r="AY7" s="30"/>
+      <c r="AZ7" s="30"/>
+      <c r="BA7" s="30"/>
+      <c r="BB7" s="30"/>
+      <c r="BC7" s="30"/>
+      <c r="BD7" s="30"/>
+      <c r="BE7" s="30"/>
+      <c r="BF7" s="30"/>
+      <c r="BG7" s="30"/>
+      <c r="BH7" s="30"/>
+      <c r="BI7" s="30"/>
+      <c r="BJ7" s="30"/>
+      <c r="BK7" s="30"/>
+      <c r="BL7" s="30"/>
+      <c r="BM7" s="30"/>
+      <c r="BN7" s="30"/>
+      <c r="BO7" s="30"/>
+      <c r="BP7" s="30"/>
+      <c r="BQ7" s="30"/>
+      <c r="BR7" s="30"/>
+      <c r="BS7" s="30"/>
+      <c r="BT7" s="30"/>
+      <c r="BU7" s="30"/>
+      <c r="BV7" s="30"/>
+      <c r="BW7" s="30"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="30">
+      <c r="B8" s="51"/>
+      <c r="C8" s="52">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="45"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="24">
-        <v>1</v>
-      </c>
-      <c r="G8" s="24">
+      <c r="F8" s="27">
+        <v>1</v>
+      </c>
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="27">
         <v>3</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="27">
         <v>5</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="27">
         <v>7</v>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="27">
         <v>8</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="27">
         <v>9</v>
       </c>
-      <c r="O8" s="24">
+      <c r="O8" s="27">
         <v>10</v>
       </c>
-      <c r="P8" s="24">
+      <c r="P8" s="27">
         <v>11</v>
       </c>
-      <c r="Q8" s="24">
+      <c r="Q8" s="27">
         <v>12</v>
       </c>
-      <c r="R8" s="24">
+      <c r="R8" s="27">
         <v>13</v>
       </c>
-      <c r="S8" s="24">
+      <c r="S8" s="27">
         <v>14</v>
       </c>
-      <c r="T8" s="24">
+      <c r="T8" s="27">
         <v>15</v>
       </c>
-      <c r="U8" s="24">
+      <c r="U8" s="27">
         <v>16</v>
       </c>
-      <c r="V8" s="24">
+      <c r="V8" s="27">
         <v>17</v>
       </c>
-      <c r="W8" s="24">
+      <c r="W8" s="27">
         <v>18</v>
       </c>
-      <c r="X8" s="24">
+      <c r="X8" s="27">
         <v>19</v>
       </c>
-      <c r="Y8" s="24">
+      <c r="Y8" s="27">
         <v>20</v>
       </c>
-      <c r="Z8" s="24">
+      <c r="Z8" s="27">
         <v>21</v>
       </c>
-      <c r="AA8" s="24">
+      <c r="AA8" s="27">
         <v>22</v>
       </c>
-      <c r="AB8" s="24">
+      <c r="AB8" s="27">
         <v>23</v>
       </c>
-      <c r="AC8" s="24">
+      <c r="AC8" s="27">
         <v>24</v>
       </c>
-      <c r="AD8" s="24">
+      <c r="AD8" s="27">
         <v>25</v>
       </c>
-      <c r="AE8" s="24">
+      <c r="AE8" s="27">
         <v>26</v>
       </c>
-      <c r="AF8" s="24">
+      <c r="AF8" s="27">
         <v>27</v>
       </c>
-      <c r="AG8" s="24">
+      <c r="AG8" s="27">
         <v>28</v>
       </c>
-      <c r="AH8" s="24">
+      <c r="AH8" s="27">
         <v>29</v>
       </c>
-      <c r="AI8" s="24">
+      <c r="AI8" s="27">
         <v>30</v>
       </c>
-      <c r="AJ8" s="24">
+      <c r="AJ8" s="27">
         <v>31</v>
       </c>
-      <c r="AK8" s="24">
+      <c r="AK8" s="27">
         <v>32</v>
       </c>
-      <c r="AL8" s="24">
+      <c r="AL8" s="27">
         <v>33</v>
       </c>
-      <c r="AM8" s="24">
+      <c r="AM8" s="27">
         <v>34</v>
       </c>
-      <c r="AN8" s="24">
+      <c r="AN8" s="27">
         <v>35</v>
       </c>
-      <c r="AO8" s="24">
+      <c r="AO8" s="27">
         <v>36</v>
       </c>
-      <c r="AP8" s="24">
+      <c r="AP8" s="27">
         <v>37</v>
       </c>
-      <c r="AQ8" s="24">
+      <c r="AQ8" s="27">
         <v>38</v>
       </c>
-      <c r="AR8" s="24">
+      <c r="AR8" s="27">
         <v>39</v>
       </c>
-      <c r="AS8" s="24">
+      <c r="AS8" s="27">
         <v>40</v>
       </c>
-      <c r="AT8" s="24">
+      <c r="AT8" s="27">
         <v>41</v>
       </c>
-      <c r="AU8" s="24">
+      <c r="AU8" s="27">
         <v>42</v>
       </c>
-      <c r="AV8" s="24">
+      <c r="AV8" s="27">
         <v>43</v>
       </c>
-      <c r="AW8" s="24">
+      <c r="AW8" s="27">
         <v>44</v>
       </c>
-      <c r="AX8" s="24">
+      <c r="AX8" s="27">
         <v>45</v>
       </c>
-      <c r="AY8" s="24">
+      <c r="AY8" s="27">
         <v>46</v>
       </c>
-      <c r="AZ8" s="24">
+      <c r="AZ8" s="27">
         <v>47</v>
       </c>
-      <c r="BA8" s="24">
+      <c r="BA8" s="27">
         <v>48</v>
       </c>
-      <c r="BB8" s="24">
+      <c r="BB8" s="27">
         <v>49</v>
       </c>
-      <c r="BC8" s="24">
+      <c r="BC8" s="27">
         <v>50</v>
       </c>
-      <c r="BD8" s="24">
+      <c r="BD8" s="27">
         <v>51</v>
       </c>
-      <c r="BE8" s="24">
+      <c r="BE8" s="27">
         <v>52</v>
       </c>
-      <c r="BF8" s="24">
+      <c r="BF8" s="27">
         <v>53</v>
       </c>
-      <c r="BG8" s="24">
+      <c r="BG8" s="27">
         <v>54</v>
       </c>
-      <c r="BH8" s="24">
+      <c r="BH8" s="27">
         <v>55</v>
       </c>
-      <c r="BI8" s="24">
+      <c r="BI8" s="27">
         <v>56</v>
       </c>
-      <c r="BJ8" s="24">
+      <c r="BJ8" s="27">
         <v>57</v>
       </c>
-      <c r="BK8" s="24">
+      <c r="BK8" s="27">
         <v>58</v>
       </c>
-      <c r="BL8" s="24">
+      <c r="BL8" s="27">
         <v>59</v>
       </c>
-      <c r="BM8" s="24">
+      <c r="BM8" s="27">
         <v>60</v>
       </c>
-      <c r="BN8" s="24">
+      <c r="BN8" s="27">
         <v>61</v>
       </c>
-      <c r="BO8" s="24">
+      <c r="BO8" s="27">
         <v>62</v>
       </c>
-      <c r="BP8" s="24">
+      <c r="BP8" s="27">
         <v>63</v>
       </c>
-      <c r="BQ8" s="24">
+      <c r="BQ8" s="27">
         <v>64</v>
       </c>
-      <c r="BR8" s="24">
+      <c r="BR8" s="27">
         <v>65</v>
       </c>
-      <c r="BS8" s="24">
+      <c r="BS8" s="27">
         <v>66</v>
       </c>
-      <c r="BT8" s="24">
+      <c r="BT8" s="27">
         <v>67</v>
       </c>
-      <c r="BU8" s="24">
+      <c r="BU8" s="27">
         <v>68</v>
       </c>
-      <c r="BV8" s="24">
+      <c r="BV8" s="27">
         <v>69</v>
       </c>
-      <c r="BW8" s="24">
+      <c r="BW8" s="27">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
-      <c r="AE9" s="25"/>
-      <c r="AF9" s="25"/>
-      <c r="AG9" s="25"/>
-      <c r="AH9" s="25"/>
-      <c r="AI9" s="25"/>
-      <c r="AJ9" s="25"/>
-      <c r="AK9" s="25"/>
-      <c r="AL9" s="25"/>
-      <c r="AM9" s="25"/>
-      <c r="AN9" s="25"/>
-      <c r="AO9" s="25"/>
-      <c r="AP9" s="25"/>
-      <c r="AQ9" s="25"/>
-      <c r="AR9" s="25"/>
-      <c r="AS9" s="25"/>
-      <c r="AT9" s="25"/>
-      <c r="AU9" s="25"/>
-      <c r="AV9" s="25"/>
-      <c r="AW9" s="25"/>
-      <c r="AX9" s="25"/>
-      <c r="AY9" s="25"/>
-      <c r="AZ9" s="25"/>
-      <c r="BA9" s="25"/>
-      <c r="BB9" s="25"/>
-      <c r="BC9" s="25"/>
-      <c r="BD9" s="25"/>
-      <c r="BE9" s="25"/>
-      <c r="BF9" s="25"/>
-      <c r="BG9" s="25"/>
-      <c r="BH9" s="25"/>
-      <c r="BI9" s="25"/>
-      <c r="BJ9" s="25"/>
-      <c r="BK9" s="25"/>
-      <c r="BL9" s="25"/>
-      <c r="BM9" s="25"/>
-      <c r="BN9" s="25"/>
-      <c r="BO9" s="25"/>
-      <c r="BP9" s="25"/>
-      <c r="BQ9" s="25"/>
-      <c r="BR9" s="25"/>
-      <c r="BS9" s="25"/>
-      <c r="BT9" s="25"/>
-      <c r="BU9" s="25"/>
-      <c r="BV9" s="25"/>
-      <c r="BW9" s="25"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
+      <c r="A10" s="42"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2139,11 +2145,11 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" s="14">
         <f>D12/C5</f>
-        <v>0.21666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -2189,8 +2195,12 @@
       <c r="W12" s="3">
         <v>0</v>
       </c>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>0</v>
+      </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
@@ -2254,11 +2264,11 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="14">
         <f>D13/C5</f>
-        <v>0.2</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -2302,8 +2312,12 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
@@ -2367,11 +2381,11 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" s="14">
         <f>D14/C5</f>
-        <v>0.21666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -2417,8 +2431,12 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
@@ -2482,11 +2500,11 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" s="14">
         <f>D15/C5</f>
-        <v>0.21666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -2532,8 +2550,12 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
@@ -2597,11 +2619,11 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" s="14">
         <f>D16/C5</f>
-        <v>0.13333333333333333</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -2637,8 +2659,12 @@
       <c r="W16" s="3">
         <v>0</v>
       </c>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
+      <c r="X16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>0</v>
+      </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
@@ -2702,11 +2728,11 @@
       </c>
       <c r="D17" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
         <f>D17/C5</f>
-        <v>0.05</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -2732,8 +2758,12 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
@@ -2797,11 +2827,11 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E18" s="14">
         <f>D18/C5</f>
-        <v>0.18333333333333332</v>
+        <v>0.21666666666666667</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -2843,8 +2873,12 @@
       <c r="W18" s="3">
         <v>0</v>
       </c>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
@@ -3480,149 +3514,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="31"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
-      <c r="AL26" s="31"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="31"/>
-      <c r="AO26" s="31"/>
-      <c r="AP26" s="31"/>
-      <c r="AQ26" s="31"/>
-      <c r="AR26" s="31"/>
-      <c r="AS26" s="31"/>
-      <c r="AT26" s="31"/>
-      <c r="AU26" s="31"/>
-      <c r="AV26" s="31"/>
-      <c r="AW26" s="31"/>
-      <c r="AX26" s="31"/>
-      <c r="AY26" s="31"/>
-      <c r="AZ26" s="31"/>
-      <c r="BA26" s="31"/>
-      <c r="BB26" s="31"/>
-      <c r="BC26" s="31"/>
-      <c r="BD26" s="31"/>
-      <c r="BE26" s="31"/>
-      <c r="BF26" s="31"/>
-      <c r="BG26" s="31"/>
-      <c r="BH26" s="31"/>
-      <c r="BI26" s="31"/>
-      <c r="BJ26" s="31"/>
-      <c r="BK26" s="31"/>
-      <c r="BL26" s="31"/>
-      <c r="BM26" s="31"/>
-      <c r="BN26" s="31"/>
-      <c r="BO26" s="31"/>
-      <c r="BP26" s="31"/>
-      <c r="BQ26" s="31"/>
-      <c r="BR26" s="31"/>
-      <c r="BS26" s="31"/>
-      <c r="BT26" s="31"/>
-      <c r="BU26" s="31"/>
-      <c r="BV26" s="31"/>
-      <c r="BW26" s="31"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="44"/>
+      <c r="X26" s="44"/>
+      <c r="Y26" s="44"/>
+      <c r="Z26" s="44"/>
+      <c r="AA26" s="44"/>
+      <c r="AB26" s="44"/>
+      <c r="AC26" s="44"/>
+      <c r="AD26" s="44"/>
+      <c r="AE26" s="44"/>
+      <c r="AF26" s="44"/>
+      <c r="AG26" s="44"/>
+      <c r="AH26" s="44"/>
+      <c r="AI26" s="44"/>
+      <c r="AJ26" s="44"/>
+      <c r="AK26" s="44"/>
+      <c r="AL26" s="44"/>
+      <c r="AM26" s="44"/>
+      <c r="AN26" s="44"/>
+      <c r="AO26" s="44"/>
+      <c r="AP26" s="44"/>
+      <c r="AQ26" s="44"/>
+      <c r="AR26" s="44"/>
+      <c r="AS26" s="44"/>
+      <c r="AT26" s="44"/>
+      <c r="AU26" s="44"/>
+      <c r="AV26" s="44"/>
+      <c r="AW26" s="44"/>
+      <c r="AX26" s="44"/>
+      <c r="AY26" s="44"/>
+      <c r="AZ26" s="44"/>
+      <c r="BA26" s="44"/>
+      <c r="BB26" s="44"/>
+      <c r="BC26" s="44"/>
+      <c r="BD26" s="44"/>
+      <c r="BE26" s="44"/>
+      <c r="BF26" s="44"/>
+      <c r="BG26" s="44"/>
+      <c r="BH26" s="44"/>
+      <c r="BI26" s="44"/>
+      <c r="BJ26" s="44"/>
+      <c r="BK26" s="44"/>
+      <c r="BL26" s="44"/>
+      <c r="BM26" s="44"/>
+      <c r="BN26" s="44"/>
+      <c r="BO26" s="44"/>
+      <c r="BP26" s="44"/>
+      <c r="BQ26" s="44"/>
+      <c r="BR26" s="44"/>
+      <c r="BS26" s="44"/>
+      <c r="BT26" s="44"/>
+      <c r="BU26" s="44"/>
+      <c r="BV26" s="44"/>
+      <c r="BW26" s="44"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="52"/>
-      <c r="O27" s="52"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="52"/>
-      <c r="R27" s="52"/>
-      <c r="S27" s="52"/>
-      <c r="T27" s="52"/>
-      <c r="U27" s="52"/>
-      <c r="V27" s="52"/>
-      <c r="W27" s="52"/>
-      <c r="X27" s="52"/>
-      <c r="Y27" s="52"/>
-      <c r="Z27" s="52"/>
-      <c r="AA27" s="52"/>
-      <c r="AB27" s="52"/>
-      <c r="AC27" s="52"/>
-      <c r="AD27" s="52"/>
-      <c r="AE27" s="52"/>
-      <c r="AF27" s="52"/>
-      <c r="AG27" s="52"/>
-      <c r="AH27" s="52"/>
-      <c r="AI27" s="52"/>
-      <c r="AJ27" s="52"/>
-      <c r="AK27" s="52"/>
-      <c r="AL27" s="52"/>
-      <c r="AM27" s="52"/>
-      <c r="AN27" s="52"/>
-      <c r="AO27" s="52"/>
-      <c r="AP27" s="52"/>
-      <c r="AQ27" s="52"/>
-      <c r="AR27" s="52"/>
-      <c r="AS27" s="52"/>
-      <c r="AT27" s="52"/>
-      <c r="AU27" s="52"/>
-      <c r="AV27" s="52"/>
-      <c r="AW27" s="52"/>
-      <c r="AX27" s="52"/>
-      <c r="AY27" s="52"/>
-      <c r="AZ27" s="52"/>
-      <c r="BA27" s="52"/>
-      <c r="BB27" s="52"/>
-      <c r="BC27" s="52"/>
-      <c r="BD27" s="52"/>
-      <c r="BE27" s="52"/>
-      <c r="BF27" s="52"/>
-      <c r="BG27" s="52"/>
-      <c r="BH27" s="52"/>
-      <c r="BI27" s="52"/>
-      <c r="BJ27" s="52"/>
-      <c r="BK27" s="52"/>
-      <c r="BL27" s="52"/>
-      <c r="BM27" s="52"/>
-      <c r="BN27" s="52"/>
-      <c r="BO27" s="52"/>
-      <c r="BP27" s="52"/>
-      <c r="BQ27" s="52"/>
-      <c r="BR27" s="52"/>
-      <c r="BS27" s="52"/>
-      <c r="BT27" s="52"/>
-      <c r="BU27" s="52"/>
-      <c r="BV27" s="52"/>
-      <c r="BW27" s="52"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="26"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="26"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="26"/>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="26"/>
+      <c r="AC27" s="26"/>
+      <c r="AD27" s="26"/>
+      <c r="AE27" s="26"/>
+      <c r="AF27" s="26"/>
+      <c r="AG27" s="26"/>
+      <c r="AH27" s="26"/>
+      <c r="AI27" s="26"/>
+      <c r="AJ27" s="26"/>
+      <c r="AK27" s="26"/>
+      <c r="AL27" s="26"/>
+      <c r="AM27" s="26"/>
+      <c r="AN27" s="26"/>
+      <c r="AO27" s="26"/>
+      <c r="AP27" s="26"/>
+      <c r="AQ27" s="26"/>
+      <c r="AR27" s="26"/>
+      <c r="AS27" s="26"/>
+      <c r="AT27" s="26"/>
+      <c r="AU27" s="26"/>
+      <c r="AV27" s="26"/>
+      <c r="AW27" s="26"/>
+      <c r="AX27" s="26"/>
+      <c r="AY27" s="26"/>
+      <c r="AZ27" s="26"/>
+      <c r="BA27" s="26"/>
+      <c r="BB27" s="26"/>
+      <c r="BC27" s="26"/>
+      <c r="BD27" s="26"/>
+      <c r="BE27" s="26"/>
+      <c r="BF27" s="26"/>
+      <c r="BG27" s="26"/>
+      <c r="BH27" s="26"/>
+      <c r="BI27" s="26"/>
+      <c r="BJ27" s="26"/>
+      <c r="BK27" s="26"/>
+      <c r="BL27" s="26"/>
+      <c r="BM27" s="26"/>
+      <c r="BN27" s="26"/>
+      <c r="BO27" s="26"/>
+      <c r="BP27" s="26"/>
+      <c r="BQ27" s="26"/>
+      <c r="BR27" s="26"/>
+      <c r="BS27" s="26"/>
+      <c r="BT27" s="26"/>
+      <c r="BU27" s="26"/>
+      <c r="BV27" s="26"/>
+      <c r="BW27" s="26"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3632,7 +3666,7 @@
     <row r="29" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="21">
         <f>SUM(E11:E18)/8</f>
-        <v>0.16875000000000001</v>
+        <v>0.19791666666666669</v>
       </c>
       <c r="AJ29" s="15"/>
       <c r="AK29" s="16" t="s">
@@ -3652,7 +3686,152 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="169">
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="E26:BW26"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="F27:S27"/>
@@ -3677,150 +3856,6 @@
     <mergeCell ref="BB2:BB7"/>
     <mergeCell ref="BC2:BC7"/>
     <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="E26:BW26"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T1:U1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3842,49 +3877,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="54" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="60" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="56" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="56"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -3930,7 +3965,7 @@
       </c>
       <c r="E6" s="18">
         <f>COUNTIF(cms!H12:Y12,0)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="18">
         <f>COUNTIF(cms!Z12:AY12,0)</f>
@@ -3958,7 +3993,7 @@
       </c>
       <c r="E7" s="18">
         <f>COUNTIF(cms!H13:Y13,0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7" s="18">
         <f>COUNTIF(cms!Z13:AY13,0)</f>
@@ -3986,7 +4021,7 @@
       </c>
       <c r="E8" s="18">
         <f>COUNTIF(cms!H14:Y14,0)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" s="18">
         <f>COUNTIF(cms!Z14:AY14,0)</f>
@@ -4014,7 +4049,7 @@
       </c>
       <c r="E9" s="18">
         <f>COUNTIF(cms!H15:Y15,0)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F9" s="18">
         <f>COUNTIF(cms!Z15:AY15,0)</f>
@@ -4042,7 +4077,7 @@
       </c>
       <c r="E10" s="18">
         <f>COUNTIF(cms!H16:Y16,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" s="18">
         <f>COUNTIF(cms!Z16:AY16,0)</f>
@@ -4070,7 +4105,7 @@
       </c>
       <c r="E11" s="18">
         <f>COUNTIF(cms!H17:Y17,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" s="18">
         <f>COUNTIF(cms!Z17:AY17,0)</f>
@@ -4098,7 +4133,7 @@
       </c>
       <c r="E12" s="18">
         <f>COUNTIF(cms!H18:Y18,0)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F12" s="18">
         <f>COUNTIF(cms!Z18:AY18,0)</f>

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -532,92 +532,92 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -877,16 +877,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="35"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
       <c r="F1" s="24">
         <v>7</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="51"/>
       <c r="H1" s="25"/>
       <c r="I1" s="23">
         <v>1</v>
@@ -923,8 +923,10 @@
         <v>2</v>
       </c>
       <c r="Y1" s="25"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
+      <c r="Z1" s="24">
+        <v>2</v>
+      </c>
+      <c r="AA1" s="25"/>
       <c r="AB1" s="22"/>
       <c r="AC1" s="22"/>
       <c r="AD1" s="22"/>
@@ -975,839 +977,843 @@
       <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="29">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="28">
         <v>46274</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="28">
         <v>46274</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="28">
         <v>46274</v>
       </c>
-      <c r="I2" s="29">
+      <c r="I2" s="28">
         <v>46276</v>
       </c>
-      <c r="J2" s="29">
+      <c r="J2" s="28">
         <v>46279</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="28">
         <v>46279</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="28">
         <v>46286</v>
       </c>
-      <c r="O2" s="29">
+      <c r="O2" s="28">
         <v>46286</v>
       </c>
-      <c r="P2" s="29">
+      <c r="P2" s="28">
         <v>46290</v>
       </c>
-      <c r="Q2" s="29">
+      <c r="Q2" s="28">
         <v>46290</v>
       </c>
-      <c r="R2" s="29">
+      <c r="R2" s="28">
         <v>46293</v>
       </c>
-      <c r="S2" s="29">
+      <c r="S2" s="28">
         <v>46293</v>
       </c>
-      <c r="T2" s="29">
+      <c r="T2" s="28">
         <v>46297</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="28">
         <v>46297</v>
       </c>
-      <c r="V2" s="31">
+      <c r="V2" s="52">
         <v>46300</v>
       </c>
-      <c r="W2" s="31">
+      <c r="W2" s="52">
         <v>46300</v>
       </c>
-      <c r="X2" s="29">
+      <c r="X2" s="28">
         <v>46304</v>
       </c>
-      <c r="Y2" s="29">
+      <c r="Y2" s="28">
         <v>46304</v>
       </c>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
-      <c r="BJ2" s="29"/>
-      <c r="BK2" s="29"/>
-      <c r="BL2" s="29"/>
-      <c r="BM2" s="29"/>
-      <c r="BN2" s="29"/>
-      <c r="BO2" s="29"/>
-      <c r="BP2" s="29"/>
-      <c r="BQ2" s="29"/>
-      <c r="BR2" s="29"/>
-      <c r="BS2" s="29"/>
-      <c r="BT2" s="29"/>
-      <c r="BU2" s="29"/>
-      <c r="BV2" s="29"/>
-      <c r="BW2" s="29"/>
+      <c r="Z2" s="28">
+        <v>46307</v>
+      </c>
+      <c r="AA2" s="28">
+        <v>46307</v>
+      </c>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="29"/>
-      <c r="BJ3" s="29"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="29"/>
-      <c r="BM3" s="29"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="29"/>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="29"/>
-      <c r="BT3" s="29"/>
-      <c r="BU3" s="29"/>
-      <c r="BV3" s="29"/>
-      <c r="BW3" s="29"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44" t="s">
+      <c r="A4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29"/>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="29"/>
-      <c r="AS4" s="29"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="29"/>
-      <c r="AV4" s="29"/>
-      <c r="AW4" s="29"/>
-      <c r="AX4" s="29"/>
-      <c r="AY4" s="29"/>
-      <c r="AZ4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="29"/>
-      <c r="BJ4" s="29"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="29"/>
-      <c r="BT4" s="29"/>
-      <c r="BU4" s="29"/>
-      <c r="BV4" s="29"/>
-      <c r="BW4" s="29"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="47">
+      <c r="B5" s="47"/>
+      <c r="C5" s="48">
         <v>60</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="31"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
-      <c r="BJ5" s="29"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="29"/>
-      <c r="BM5" s="29"/>
-      <c r="BN5" s="29"/>
-      <c r="BO5" s="29"/>
-      <c r="BP5" s="29"/>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="29"/>
-      <c r="BS5" s="29"/>
-      <c r="BT5" s="29"/>
-      <c r="BU5" s="29"/>
-      <c r="BV5" s="29"/>
-      <c r="BW5" s="29"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48">
         <v>4</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
-      <c r="AI6" s="29"/>
-      <c r="AJ6" s="29"/>
-      <c r="AK6" s="29"/>
-      <c r="AL6" s="29"/>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
-      <c r="AO6" s="29"/>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="29"/>
-      <c r="AS6" s="29"/>
-      <c r="AT6" s="29"/>
-      <c r="AU6" s="29"/>
-      <c r="AV6" s="29"/>
-      <c r="AW6" s="29"/>
-      <c r="AX6" s="29"/>
-      <c r="AY6" s="29"/>
-      <c r="AZ6" s="29"/>
-      <c r="BA6" s="29"/>
-      <c r="BB6" s="29"/>
-      <c r="BC6" s="29"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="29"/>
-      <c r="BG6" s="29"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="29"/>
-      <c r="BJ6" s="29"/>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="29"/>
-      <c r="BM6" s="29"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="29"/>
-      <c r="BP6" s="29"/>
-      <c r="BQ6" s="29"/>
-      <c r="BR6" s="29"/>
-      <c r="BS6" s="29"/>
-      <c r="BT6" s="29"/>
-      <c r="BU6" s="29"/>
-      <c r="BV6" s="29"/>
-      <c r="BW6" s="29"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="52"/>
+      <c r="W6" s="52"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
+      <c r="BM6" s="28"/>
+      <c r="BN6" s="28"/>
+      <c r="BO6" s="28"/>
+      <c r="BP6" s="28"/>
+      <c r="BQ6" s="28"/>
+      <c r="BR6" s="28"/>
+      <c r="BS6" s="28"/>
+      <c r="BT6" s="28"/>
+      <c r="BU6" s="28"/>
+      <c r="BV6" s="28"/>
+      <c r="BW6" s="28"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="47">
+      <c r="B7" s="50"/>
+      <c r="C7" s="48">
         <v>11</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="32"/>
-      <c r="W7" s="32"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="30"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="30"/>
-      <c r="AN7" s="30"/>
-      <c r="AO7" s="30"/>
-      <c r="AP7" s="30"/>
-      <c r="AQ7" s="30"/>
-      <c r="AR7" s="30"/>
-      <c r="AS7" s="30"/>
-      <c r="AT7" s="30"/>
-      <c r="AU7" s="30"/>
-      <c r="AV7" s="30"/>
-      <c r="AW7" s="30"/>
-      <c r="AX7" s="30"/>
-      <c r="AY7" s="30"/>
-      <c r="AZ7" s="30"/>
-      <c r="BA7" s="30"/>
-      <c r="BB7" s="30"/>
-      <c r="BC7" s="30"/>
-      <c r="BD7" s="30"/>
-      <c r="BE7" s="30"/>
-      <c r="BF7" s="30"/>
-      <c r="BG7" s="30"/>
-      <c r="BH7" s="30"/>
-      <c r="BI7" s="30"/>
-      <c r="BJ7" s="30"/>
-      <c r="BK7" s="30"/>
-      <c r="BL7" s="30"/>
-      <c r="BM7" s="30"/>
-      <c r="BN7" s="30"/>
-      <c r="BO7" s="30"/>
-      <c r="BP7" s="30"/>
-      <c r="BQ7" s="30"/>
-      <c r="BR7" s="30"/>
-      <c r="BS7" s="30"/>
-      <c r="BT7" s="30"/>
-      <c r="BU7" s="30"/>
-      <c r="BV7" s="30"/>
-      <c r="BW7" s="30"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52">
+      <c r="B8" s="32"/>
+      <c r="C8" s="30">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="45"/>
+      <c r="D8" s="33"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="27">
-        <v>1</v>
-      </c>
-      <c r="G8" s="27">
+      <c r="F8" s="26">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26">
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="26">
         <v>3</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="26">
         <v>4</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="26">
         <v>5</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="26">
         <v>6</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="26">
         <v>7</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="26">
         <v>8</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="26">
         <v>9</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="26">
         <v>10</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="26">
         <v>11</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="26">
         <v>12</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="26">
         <v>13</v>
       </c>
-      <c r="S8" s="27">
+      <c r="S8" s="26">
         <v>14</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="26">
         <v>15</v>
       </c>
-      <c r="U8" s="27">
+      <c r="U8" s="26">
         <v>16</v>
       </c>
-      <c r="V8" s="27">
+      <c r="V8" s="26">
         <v>17</v>
       </c>
-      <c r="W8" s="27">
+      <c r="W8" s="26">
         <v>18</v>
       </c>
-      <c r="X8" s="27">
+      <c r="X8" s="26">
         <v>19</v>
       </c>
-      <c r="Y8" s="27">
+      <c r="Y8" s="26">
         <v>20</v>
       </c>
-      <c r="Z8" s="27">
+      <c r="Z8" s="26">
         <v>21</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AA8" s="26">
         <v>22</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="26">
         <v>23</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AC8" s="26">
         <v>24</v>
       </c>
-      <c r="AD8" s="27">
+      <c r="AD8" s="26">
         <v>25</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AE8" s="26">
         <v>26</v>
       </c>
-      <c r="AF8" s="27">
+      <c r="AF8" s="26">
         <v>27</v>
       </c>
-      <c r="AG8" s="27">
+      <c r="AG8" s="26">
         <v>28</v>
       </c>
-      <c r="AH8" s="27">
+      <c r="AH8" s="26">
         <v>29</v>
       </c>
-      <c r="AI8" s="27">
+      <c r="AI8" s="26">
         <v>30</v>
       </c>
-      <c r="AJ8" s="27">
+      <c r="AJ8" s="26">
         <v>31</v>
       </c>
-      <c r="AK8" s="27">
+      <c r="AK8" s="26">
         <v>32</v>
       </c>
-      <c r="AL8" s="27">
+      <c r="AL8" s="26">
         <v>33</v>
       </c>
-      <c r="AM8" s="27">
+      <c r="AM8" s="26">
         <v>34</v>
       </c>
-      <c r="AN8" s="27">
+      <c r="AN8" s="26">
         <v>35</v>
       </c>
-      <c r="AO8" s="27">
+      <c r="AO8" s="26">
         <v>36</v>
       </c>
-      <c r="AP8" s="27">
+      <c r="AP8" s="26">
         <v>37</v>
       </c>
-      <c r="AQ8" s="27">
+      <c r="AQ8" s="26">
         <v>38</v>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="26">
         <v>39</v>
       </c>
-      <c r="AS8" s="27">
+      <c r="AS8" s="26">
         <v>40</v>
       </c>
-      <c r="AT8" s="27">
+      <c r="AT8" s="26">
         <v>41</v>
       </c>
-      <c r="AU8" s="27">
+      <c r="AU8" s="26">
         <v>42</v>
       </c>
-      <c r="AV8" s="27">
+      <c r="AV8" s="26">
         <v>43</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="AW8" s="26">
         <v>44</v>
       </c>
-      <c r="AX8" s="27">
+      <c r="AX8" s="26">
         <v>45</v>
       </c>
-      <c r="AY8" s="27">
+      <c r="AY8" s="26">
         <v>46</v>
       </c>
-      <c r="AZ8" s="27">
+      <c r="AZ8" s="26">
         <v>47</v>
       </c>
-      <c r="BA8" s="27">
+      <c r="BA8" s="26">
         <v>48</v>
       </c>
-      <c r="BB8" s="27">
+      <c r="BB8" s="26">
         <v>49</v>
       </c>
-      <c r="BC8" s="27">
+      <c r="BC8" s="26">
         <v>50</v>
       </c>
-      <c r="BD8" s="27">
+      <c r="BD8" s="26">
         <v>51</v>
       </c>
-      <c r="BE8" s="27">
+      <c r="BE8" s="26">
         <v>52</v>
       </c>
-      <c r="BF8" s="27">
+      <c r="BF8" s="26">
         <v>53</v>
       </c>
-      <c r="BG8" s="27">
+      <c r="BG8" s="26">
         <v>54</v>
       </c>
-      <c r="BH8" s="27">
+      <c r="BH8" s="26">
         <v>55</v>
       </c>
-      <c r="BI8" s="27">
+      <c r="BI8" s="26">
         <v>56</v>
       </c>
-      <c r="BJ8" s="27">
+      <c r="BJ8" s="26">
         <v>57</v>
       </c>
-      <c r="BK8" s="27">
+      <c r="BK8" s="26">
         <v>58</v>
       </c>
-      <c r="BL8" s="27">
+      <c r="BL8" s="26">
         <v>59</v>
       </c>
-      <c r="BM8" s="27">
+      <c r="BM8" s="26">
         <v>60</v>
       </c>
-      <c r="BN8" s="27">
+      <c r="BN8" s="26">
         <v>61</v>
       </c>
-      <c r="BO8" s="27">
+      <c r="BO8" s="26">
         <v>62</v>
       </c>
-      <c r="BP8" s="27">
+      <c r="BP8" s="26">
         <v>63</v>
       </c>
-      <c r="BQ8" s="27">
+      <c r="BQ8" s="26">
         <v>64</v>
       </c>
-      <c r="BR8" s="27">
+      <c r="BR8" s="26">
         <v>65</v>
       </c>
-      <c r="BS8" s="27">
+      <c r="BS8" s="26">
         <v>66</v>
       </c>
-      <c r="BT8" s="27">
+      <c r="BT8" s="26">
         <v>67</v>
       </c>
-      <c r="BU8" s="27">
+      <c r="BU8" s="26">
         <v>68</v>
       </c>
-      <c r="BV8" s="27">
+      <c r="BV8" s="26">
         <v>69</v>
       </c>
-      <c r="BW8" s="27">
+      <c r="BW8" s="26">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="53"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="28"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
-      <c r="AU9" s="28"/>
-      <c r="AV9" s="28"/>
-      <c r="AW9" s="28"/>
-      <c r="AX9" s="28"/>
-      <c r="AY9" s="28"/>
-      <c r="AZ9" s="28"/>
-      <c r="BA9" s="28"/>
-      <c r="BB9" s="28"/>
-      <c r="BC9" s="28"/>
-      <c r="BD9" s="28"/>
-      <c r="BE9" s="28"/>
-      <c r="BF9" s="28"/>
-      <c r="BG9" s="28"/>
-      <c r="BH9" s="28"/>
-      <c r="BI9" s="28"/>
-      <c r="BJ9" s="28"/>
-      <c r="BK9" s="28"/>
-      <c r="BL9" s="28"/>
-      <c r="BM9" s="28"/>
-      <c r="BN9" s="28"/>
-      <c r="BO9" s="28"/>
-      <c r="BP9" s="28"/>
-      <c r="BQ9" s="28"/>
-      <c r="BR9" s="28"/>
-      <c r="BS9" s="28"/>
-      <c r="BT9" s="28"/>
-      <c r="BU9" s="28"/>
-      <c r="BV9" s="28"/>
-      <c r="BW9" s="28"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="27"/>
+      <c r="X9" s="27"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27"/>
+      <c r="AB9" s="27"/>
+      <c r="AC9" s="27"/>
+      <c r="AD9" s="27"/>
+      <c r="AE9" s="27"/>
+      <c r="AF9" s="27"/>
+      <c r="AG9" s="27"/>
+      <c r="AH9" s="27"/>
+      <c r="AI9" s="27"/>
+      <c r="AJ9" s="27"/>
+      <c r="AK9" s="27"/>
+      <c r="AL9" s="27"/>
+      <c r="AM9" s="27"/>
+      <c r="AN9" s="27"/>
+      <c r="AO9" s="27"/>
+      <c r="AP9" s="27"/>
+      <c r="AQ9" s="27"/>
+      <c r="AR9" s="27"/>
+      <c r="AS9" s="27"/>
+      <c r="AT9" s="27"/>
+      <c r="AU9" s="27"/>
+      <c r="AV9" s="27"/>
+      <c r="AW9" s="27"/>
+      <c r="AX9" s="27"/>
+      <c r="AY9" s="27"/>
+      <c r="AZ9" s="27"/>
+      <c r="BA9" s="27"/>
+      <c r="BB9" s="27"/>
+      <c r="BC9" s="27"/>
+      <c r="BD9" s="27"/>
+      <c r="BE9" s="27"/>
+      <c r="BF9" s="27"/>
+      <c r="BG9" s="27"/>
+      <c r="BH9" s="27"/>
+      <c r="BI9" s="27"/>
+      <c r="BJ9" s="27"/>
+      <c r="BK9" s="27"/>
+      <c r="BL9" s="27"/>
+      <c r="BM9" s="27"/>
+      <c r="BN9" s="27"/>
+      <c r="BO9" s="27"/>
+      <c r="BP9" s="27"/>
+      <c r="BQ9" s="27"/>
+      <c r="BR9" s="27"/>
+      <c r="BS9" s="27"/>
+      <c r="BT9" s="27"/>
+      <c r="BU9" s="27"/>
+      <c r="BV9" s="27"/>
+      <c r="BW9" s="27"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42"/>
-      <c r="B10" s="53"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -3514,149 +3520,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="52"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="44"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="44"/>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44"/>
-      <c r="V26" s="44"/>
-      <c r="W26" s="44"/>
-      <c r="X26" s="44"/>
-      <c r="Y26" s="44"/>
-      <c r="Z26" s="44"/>
-      <c r="AA26" s="44"/>
-      <c r="AB26" s="44"/>
-      <c r="AC26" s="44"/>
-      <c r="AD26" s="44"/>
-      <c r="AE26" s="44"/>
-      <c r="AF26" s="44"/>
-      <c r="AG26" s="44"/>
-      <c r="AH26" s="44"/>
-      <c r="AI26" s="44"/>
-      <c r="AJ26" s="44"/>
-      <c r="AK26" s="44"/>
-      <c r="AL26" s="44"/>
-      <c r="AM26" s="44"/>
-      <c r="AN26" s="44"/>
-      <c r="AO26" s="44"/>
-      <c r="AP26" s="44"/>
-      <c r="AQ26" s="44"/>
-      <c r="AR26" s="44"/>
-      <c r="AS26" s="44"/>
-      <c r="AT26" s="44"/>
-      <c r="AU26" s="44"/>
-      <c r="AV26" s="44"/>
-      <c r="AW26" s="44"/>
-      <c r="AX26" s="44"/>
-      <c r="AY26" s="44"/>
-      <c r="AZ26" s="44"/>
-      <c r="BA26" s="44"/>
-      <c r="BB26" s="44"/>
-      <c r="BC26" s="44"/>
-      <c r="BD26" s="44"/>
-      <c r="BE26" s="44"/>
-      <c r="BF26" s="44"/>
-      <c r="BG26" s="44"/>
-      <c r="BH26" s="44"/>
-      <c r="BI26" s="44"/>
-      <c r="BJ26" s="44"/>
-      <c r="BK26" s="44"/>
-      <c r="BL26" s="44"/>
-      <c r="BM26" s="44"/>
-      <c r="BN26" s="44"/>
-      <c r="BO26" s="44"/>
-      <c r="BP26" s="44"/>
-      <c r="BQ26" s="44"/>
-      <c r="BR26" s="44"/>
-      <c r="BS26" s="44"/>
-      <c r="BT26" s="44"/>
-      <c r="BU26" s="44"/>
-      <c r="BV26" s="44"/>
-      <c r="BW26" s="44"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="31"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="31"/>
+      <c r="AL26" s="31"/>
+      <c r="AM26" s="31"/>
+      <c r="AN26" s="31"/>
+      <c r="AO26" s="31"/>
+      <c r="AP26" s="31"/>
+      <c r="AQ26" s="31"/>
+      <c r="AR26" s="31"/>
+      <c r="AS26" s="31"/>
+      <c r="AT26" s="31"/>
+      <c r="AU26" s="31"/>
+      <c r="AV26" s="31"/>
+      <c r="AW26" s="31"/>
+      <c r="AX26" s="31"/>
+      <c r="AY26" s="31"/>
+      <c r="AZ26" s="31"/>
+      <c r="BA26" s="31"/>
+      <c r="BB26" s="31"/>
+      <c r="BC26" s="31"/>
+      <c r="BD26" s="31"/>
+      <c r="BE26" s="31"/>
+      <c r="BF26" s="31"/>
+      <c r="BG26" s="31"/>
+      <c r="BH26" s="31"/>
+      <c r="BI26" s="31"/>
+      <c r="BJ26" s="31"/>
+      <c r="BK26" s="31"/>
+      <c r="BL26" s="31"/>
+      <c r="BM26" s="31"/>
+      <c r="BN26" s="31"/>
+      <c r="BO26" s="31"/>
+      <c r="BP26" s="31"/>
+      <c r="BQ26" s="31"/>
+      <c r="BR26" s="31"/>
+      <c r="BS26" s="31"/>
+      <c r="BT26" s="31"/>
+      <c r="BU26" s="31"/>
+      <c r="BV26" s="31"/>
+      <c r="BW26" s="31"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="26"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="26"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
-      <c r="AC27" s="26"/>
-      <c r="AD27" s="26"/>
-      <c r="AE27" s="26"/>
-      <c r="AF27" s="26"/>
-      <c r="AG27" s="26"/>
-      <c r="AH27" s="26"/>
-      <c r="AI27" s="26"/>
-      <c r="AJ27" s="26"/>
-      <c r="AK27" s="26"/>
-      <c r="AL27" s="26"/>
-      <c r="AM27" s="26"/>
-      <c r="AN27" s="26"/>
-      <c r="AO27" s="26"/>
-      <c r="AP27" s="26"/>
-      <c r="AQ27" s="26"/>
-      <c r="AR27" s="26"/>
-      <c r="AS27" s="26"/>
-      <c r="AT27" s="26"/>
-      <c r="AU27" s="26"/>
-      <c r="AV27" s="26"/>
-      <c r="AW27" s="26"/>
-      <c r="AX27" s="26"/>
-      <c r="AY27" s="26"/>
-      <c r="AZ27" s="26"/>
-      <c r="BA27" s="26"/>
-      <c r="BB27" s="26"/>
-      <c r="BC27" s="26"/>
-      <c r="BD27" s="26"/>
-      <c r="BE27" s="26"/>
-      <c r="BF27" s="26"/>
-      <c r="BG27" s="26"/>
-      <c r="BH27" s="26"/>
-      <c r="BI27" s="26"/>
-      <c r="BJ27" s="26"/>
-      <c r="BK27" s="26"/>
-      <c r="BL27" s="26"/>
-      <c r="BM27" s="26"/>
-      <c r="BN27" s="26"/>
-      <c r="BO27" s="26"/>
-      <c r="BP27" s="26"/>
-      <c r="BQ27" s="26"/>
-      <c r="BR27" s="26"/>
-      <c r="BS27" s="26"/>
-      <c r="BT27" s="26"/>
-      <c r="BU27" s="26"/>
-      <c r="BV27" s="26"/>
-      <c r="BW27" s="26"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="54"/>
+      <c r="R27" s="54"/>
+      <c r="S27" s="54"/>
+      <c r="T27" s="54"/>
+      <c r="U27" s="54"/>
+      <c r="V27" s="54"/>
+      <c r="W27" s="54"/>
+      <c r="X27" s="54"/>
+      <c r="Y27" s="54"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="54"/>
+      <c r="AB27" s="54"/>
+      <c r="AC27" s="54"/>
+      <c r="AD27" s="54"/>
+      <c r="AE27" s="54"/>
+      <c r="AF27" s="54"/>
+      <c r="AG27" s="54"/>
+      <c r="AH27" s="54"/>
+      <c r="AI27" s="54"/>
+      <c r="AJ27" s="54"/>
+      <c r="AK27" s="54"/>
+      <c r="AL27" s="54"/>
+      <c r="AM27" s="54"/>
+      <c r="AN27" s="54"/>
+      <c r="AO27" s="54"/>
+      <c r="AP27" s="54"/>
+      <c r="AQ27" s="54"/>
+      <c r="AR27" s="54"/>
+      <c r="AS27" s="54"/>
+      <c r="AT27" s="54"/>
+      <c r="AU27" s="54"/>
+      <c r="AV27" s="54"/>
+      <c r="AW27" s="54"/>
+      <c r="AX27" s="54"/>
+      <c r="AY27" s="54"/>
+      <c r="AZ27" s="54"/>
+      <c r="BA27" s="54"/>
+      <c r="BB27" s="54"/>
+      <c r="BC27" s="54"/>
+      <c r="BD27" s="54"/>
+      <c r="BE27" s="54"/>
+      <c r="BF27" s="54"/>
+      <c r="BG27" s="54"/>
+      <c r="BH27" s="54"/>
+      <c r="BI27" s="54"/>
+      <c r="BJ27" s="54"/>
+      <c r="BK27" s="54"/>
+      <c r="BL27" s="54"/>
+      <c r="BM27" s="54"/>
+      <c r="BN27" s="54"/>
+      <c r="BO27" s="54"/>
+      <c r="BP27" s="54"/>
+      <c r="BQ27" s="54"/>
+      <c r="BR27" s="54"/>
+      <c r="BS27" s="54"/>
+      <c r="BT27" s="54"/>
+      <c r="BU27" s="54"/>
+      <c r="BV27" s="54"/>
+      <c r="BW27" s="54"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3686,67 +3692,78 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="169">
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BQ2:BQ7"/>
+  <mergeCells count="170">
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:BW27"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E26:BW26"/>
     <mergeCell ref="BU8:BU9"/>
     <mergeCell ref="BV8:BV9"/>
@@ -3771,43 +3788,69 @@
     <mergeCell ref="AN8:AN9"/>
     <mergeCell ref="AO8:AO9"/>
     <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="M2:M7"/>
     <mergeCell ref="N2:N7"/>
     <mergeCell ref="O2:O7"/>
     <mergeCell ref="P2:P7"/>
@@ -3820,42 +3863,6 @@
     <mergeCell ref="V2:V7"/>
     <mergeCell ref="W2:W7"/>
     <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:BW27"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3888,7 +3895,7 @@
       <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="34" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="58" t="s">
@@ -3912,7 +3919,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="42"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="60"/>
       <c r="C4" s="61"/>
       <c r="D4" s="63"/>

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -473,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -532,6 +532,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -544,81 +547,78 @@
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -645,6 +645,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -877,16 +883,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="F1" s="24">
         <v>7</v>
       </c>
-      <c r="G1" s="51"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="25"/>
       <c r="I1" s="23">
         <v>1</v>
@@ -929,8 +935,10 @@
       <c r="AA1" s="25"/>
       <c r="AB1" s="22"/>
       <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
+      <c r="AD1" s="24">
+        <v>2</v>
+      </c>
+      <c r="AE1" s="25"/>
       <c r="AF1" s="22"/>
       <c r="AG1" s="22"/>
       <c r="AH1" s="22"/>
@@ -977,843 +985,851 @@
       <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="28">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="29">
         <v>46274</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="29">
         <v>46274</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="29">
         <v>46274</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="29">
         <v>46276</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="29">
         <v>46279</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="29">
         <v>46279</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="29">
         <v>46286</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="29">
         <v>46286</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="29">
         <v>46290</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="29">
         <v>46290</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="29">
         <v>46293</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="29">
         <v>46293</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="29">
         <v>46297</v>
       </c>
-      <c r="U2" s="28">
+      <c r="U2" s="29">
         <v>46297</v>
       </c>
-      <c r="V2" s="52">
+      <c r="V2" s="64">
         <v>46300</v>
       </c>
-      <c r="W2" s="52">
+      <c r="W2" s="64">
         <v>46300</v>
       </c>
-      <c r="X2" s="28">
+      <c r="X2" s="29">
         <v>46304</v>
       </c>
-      <c r="Y2" s="28">
+      <c r="Y2" s="29">
         <v>46304</v>
       </c>
-      <c r="Z2" s="28">
+      <c r="Z2" s="29">
         <v>46307</v>
       </c>
-      <c r="AA2" s="28">
+      <c r="AA2" s="29">
         <v>46307</v>
       </c>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
+      <c r="AB2" s="53">
+        <v>46311</v>
+      </c>
+      <c r="AC2" s="53">
+        <v>46311</v>
+      </c>
+      <c r="AD2" s="29">
+        <v>46314</v>
+      </c>
+      <c r="AE2" s="29">
+        <v>46314</v>
+      </c>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+      <c r="AT2" s="29"/>
+      <c r="AU2" s="29"/>
+      <c r="AV2" s="29"/>
+      <c r="AW2" s="29"/>
+      <c r="AX2" s="29"/>
+      <c r="AY2" s="29"/>
+      <c r="AZ2" s="29"/>
+      <c r="BA2" s="29"/>
+      <c r="BB2" s="29"/>
+      <c r="BC2" s="29"/>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="29"/>
+      <c r="BG2" s="29"/>
+      <c r="BH2" s="29"/>
+      <c r="BI2" s="29"/>
+      <c r="BJ2" s="29"/>
+      <c r="BK2" s="29"/>
+      <c r="BL2" s="29"/>
+      <c r="BM2" s="29"/>
+      <c r="BN2" s="29"/>
+      <c r="BO2" s="29"/>
+      <c r="BP2" s="29"/>
+      <c r="BQ2" s="29"/>
+      <c r="BR2" s="29"/>
+      <c r="BS2" s="29"/>
+      <c r="BT2" s="29"/>
+      <c r="BU2" s="29"/>
+      <c r="BV2" s="29"/>
+      <c r="BW2" s="29"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="28"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="28"/>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="28"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="28"/>
-      <c r="AZ3" s="28"/>
-      <c r="BA3" s="28"/>
-      <c r="BB3" s="28"/>
-      <c r="BC3" s="28"/>
-      <c r="BD3" s="28"/>
-      <c r="BE3" s="28"/>
-      <c r="BF3" s="28"/>
-      <c r="BG3" s="28"/>
-      <c r="BH3" s="28"/>
-      <c r="BI3" s="28"/>
-      <c r="BJ3" s="28"/>
-      <c r="BK3" s="28"/>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="28"/>
-      <c r="BN3" s="28"/>
-      <c r="BO3" s="28"/>
-      <c r="BP3" s="28"/>
-      <c r="BQ3" s="28"/>
-      <c r="BR3" s="28"/>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="28"/>
-      <c r="BU3" s="28"/>
-      <c r="BV3" s="28"/>
-      <c r="BW3" s="28"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="29"/>
+      <c r="AE3" s="29"/>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="29"/>
+      <c r="AH3" s="29"/>
+      <c r="AI3" s="29"/>
+      <c r="AJ3" s="29"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="29"/>
+      <c r="AN3" s="29"/>
+      <c r="AO3" s="29"/>
+      <c r="AP3" s="29"/>
+      <c r="AQ3" s="29"/>
+      <c r="AR3" s="29"/>
+      <c r="AS3" s="29"/>
+      <c r="AT3" s="29"/>
+      <c r="AU3" s="29"/>
+      <c r="AV3" s="29"/>
+      <c r="AW3" s="29"/>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+      <c r="AZ3" s="29"/>
+      <c r="BA3" s="29"/>
+      <c r="BB3" s="29"/>
+      <c r="BC3" s="29"/>
+      <c r="BD3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="29"/>
+      <c r="BG3" s="29"/>
+      <c r="BH3" s="29"/>
+      <c r="BI3" s="29"/>
+      <c r="BJ3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="29"/>
+      <c r="BO3" s="29"/>
+      <c r="BP3" s="29"/>
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="29"/>
+      <c r="BS3" s="29"/>
+      <c r="BT3" s="29"/>
+      <c r="BU3" s="29"/>
+      <c r="BV3" s="29"/>
+      <c r="BW3" s="29"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="31" t="s">
+      <c r="A4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
-      <c r="BJ4" s="28"/>
-      <c r="BK4" s="28"/>
-      <c r="BL4" s="28"/>
-      <c r="BM4" s="28"/>
-      <c r="BN4" s="28"/>
-      <c r="BO4" s="28"/>
-      <c r="BP4" s="28"/>
-      <c r="BQ4" s="28"/>
-      <c r="BR4" s="28"/>
-      <c r="BS4" s="28"/>
-      <c r="BT4" s="28"/>
-      <c r="BU4" s="28"/>
-      <c r="BV4" s="28"/>
-      <c r="BW4" s="28"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="53"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="29"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="29"/>
+      <c r="AX4" s="29"/>
+      <c r="AY4" s="29"/>
+      <c r="AZ4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+      <c r="BC4" s="29"/>
+      <c r="BD4" s="29"/>
+      <c r="BE4" s="29"/>
+      <c r="BF4" s="29"/>
+      <c r="BG4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="29"/>
+      <c r="BJ4" s="29"/>
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="29"/>
+      <c r="BM4" s="29"/>
+      <c r="BN4" s="29"/>
+      <c r="BO4" s="29"/>
+      <c r="BP4" s="29"/>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="29"/>
+      <c r="BS4" s="29"/>
+      <c r="BT4" s="29"/>
+      <c r="BU4" s="29"/>
+      <c r="BV4" s="29"/>
+      <c r="BW4" s="29"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45">
         <v>60</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="28"/>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="28"/>
-      <c r="BP5" s="28"/>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="28"/>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="28"/>
-      <c r="BU5" s="28"/>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="28"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="64"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="53"/>
+      <c r="AC5" s="53"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="29"/>
+      <c r="BS5" s="29"/>
+      <c r="BT5" s="29"/>
+      <c r="BU5" s="29"/>
+      <c r="BV5" s="29"/>
+      <c r="BW5" s="29"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45">
         <v>4</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="52"/>
-      <c r="W6" s="52"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="28"/>
-      <c r="AH6" s="28"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="28"/>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
-      <c r="BJ6" s="28"/>
-      <c r="BK6" s="28"/>
-      <c r="BL6" s="28"/>
-      <c r="BM6" s="28"/>
-      <c r="BN6" s="28"/>
-      <c r="BO6" s="28"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="28"/>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="28"/>
-      <c r="BU6" s="28"/>
-      <c r="BV6" s="28"/>
-      <c r="BW6" s="28"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="53"/>
+      <c r="AC6" s="53"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="29"/>
+      <c r="BD6" s="29"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BG6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="29"/>
+      <c r="BJ6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="29"/>
+      <c r="BM6" s="29"/>
+      <c r="BN6" s="29"/>
+      <c r="BO6" s="29"/>
+      <c r="BP6" s="29"/>
+      <c r="BQ6" s="29"/>
+      <c r="BR6" s="29"/>
+      <c r="BS6" s="29"/>
+      <c r="BT6" s="29"/>
+      <c r="BU6" s="29"/>
+      <c r="BV6" s="29"/>
+      <c r="BW6" s="29"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="48">
+      <c r="B7" s="47"/>
+      <c r="C7" s="45">
         <v>11</v>
       </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
-      <c r="AV7" s="29"/>
-      <c r="AW7" s="29"/>
-      <c r="AX7" s="29"/>
-      <c r="AY7" s="29"/>
-      <c r="AZ7" s="29"/>
-      <c r="BA7" s="29"/>
-      <c r="BB7" s="29"/>
-      <c r="BC7" s="29"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="29"/>
-      <c r="BG7" s="29"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="29"/>
-      <c r="BJ7" s="29"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="29"/>
-      <c r="BM7" s="29"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="29"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="29"/>
-      <c r="BS7" s="29"/>
-      <c r="BT7" s="29"/>
-      <c r="BU7" s="29"/>
-      <c r="BV7" s="29"/>
-      <c r="BW7" s="29"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="54"/>
+      <c r="AC7" s="54"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="30"/>
+      <c r="AU7" s="30"/>
+      <c r="AV7" s="30"/>
+      <c r="AW7" s="30"/>
+      <c r="AX7" s="30"/>
+      <c r="AY7" s="30"/>
+      <c r="AZ7" s="30"/>
+      <c r="BA7" s="30"/>
+      <c r="BB7" s="30"/>
+      <c r="BC7" s="30"/>
+      <c r="BD7" s="30"/>
+      <c r="BE7" s="30"/>
+      <c r="BF7" s="30"/>
+      <c r="BG7" s="30"/>
+      <c r="BH7" s="30"/>
+      <c r="BI7" s="30"/>
+      <c r="BJ7" s="30"/>
+      <c r="BK7" s="30"/>
+      <c r="BL7" s="30"/>
+      <c r="BM7" s="30"/>
+      <c r="BN7" s="30"/>
+      <c r="BO7" s="30"/>
+      <c r="BP7" s="30"/>
+      <c r="BQ7" s="30"/>
+      <c r="BR7" s="30"/>
+      <c r="BS7" s="30"/>
+      <c r="BT7" s="30"/>
+      <c r="BU7" s="30"/>
+      <c r="BV7" s="30"/>
+      <c r="BW7" s="30"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="30">
+      <c r="B8" s="49"/>
+      <c r="C8" s="50">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="26">
-        <v>1</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="F8" s="27">
+        <v>1</v>
+      </c>
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <v>3</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <v>5</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="27">
         <v>7</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="27">
         <v>8</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="27">
         <v>9</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="27">
         <v>10</v>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="27">
         <v>11</v>
       </c>
-      <c r="Q8" s="26">
+      <c r="Q8" s="27">
         <v>12</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="27">
         <v>13</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="27">
         <v>14</v>
       </c>
-      <c r="T8" s="26">
+      <c r="T8" s="27">
         <v>15</v>
       </c>
-      <c r="U8" s="26">
+      <c r="U8" s="27">
         <v>16</v>
       </c>
-      <c r="V8" s="26">
+      <c r="V8" s="27">
         <v>17</v>
       </c>
-      <c r="W8" s="26">
+      <c r="W8" s="27">
         <v>18</v>
       </c>
-      <c r="X8" s="26">
+      <c r="X8" s="27">
         <v>19</v>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="27">
         <v>20</v>
       </c>
-      <c r="Z8" s="26">
+      <c r="Z8" s="27">
         <v>21</v>
       </c>
-      <c r="AA8" s="26">
+      <c r="AA8" s="27">
         <v>22</v>
       </c>
-      <c r="AB8" s="26">
+      <c r="AB8" s="27">
         <v>23</v>
       </c>
-      <c r="AC8" s="26">
+      <c r="AC8" s="27">
         <v>24</v>
       </c>
-      <c r="AD8" s="26">
+      <c r="AD8" s="27">
         <v>25</v>
       </c>
-      <c r="AE8" s="26">
+      <c r="AE8" s="27">
         <v>26</v>
       </c>
-      <c r="AF8" s="26">
+      <c r="AF8" s="27">
         <v>27</v>
       </c>
-      <c r="AG8" s="26">
+      <c r="AG8" s="27">
         <v>28</v>
       </c>
-      <c r="AH8" s="26">
+      <c r="AH8" s="27">
         <v>29</v>
       </c>
-      <c r="AI8" s="26">
+      <c r="AI8" s="27">
         <v>30</v>
       </c>
-      <c r="AJ8" s="26">
+      <c r="AJ8" s="27">
         <v>31</v>
       </c>
-      <c r="AK8" s="26">
+      <c r="AK8" s="27">
         <v>32</v>
       </c>
-      <c r="AL8" s="26">
+      <c r="AL8" s="27">
         <v>33</v>
       </c>
-      <c r="AM8" s="26">
+      <c r="AM8" s="27">
         <v>34</v>
       </c>
-      <c r="AN8" s="26">
+      <c r="AN8" s="27">
         <v>35</v>
       </c>
-      <c r="AO8" s="26">
+      <c r="AO8" s="27">
         <v>36</v>
       </c>
-      <c r="AP8" s="26">
+      <c r="AP8" s="27">
         <v>37</v>
       </c>
-      <c r="AQ8" s="26">
+      <c r="AQ8" s="27">
         <v>38</v>
       </c>
-      <c r="AR8" s="26">
+      <c r="AR8" s="27">
         <v>39</v>
       </c>
-      <c r="AS8" s="26">
+      <c r="AS8" s="27">
         <v>40</v>
       </c>
-      <c r="AT8" s="26">
+      <c r="AT8" s="27">
         <v>41</v>
       </c>
-      <c r="AU8" s="26">
+      <c r="AU8" s="27">
         <v>42</v>
       </c>
-      <c r="AV8" s="26">
+      <c r="AV8" s="27">
         <v>43</v>
       </c>
-      <c r="AW8" s="26">
+      <c r="AW8" s="27">
         <v>44</v>
       </c>
-      <c r="AX8" s="26">
+      <c r="AX8" s="27">
         <v>45</v>
       </c>
-      <c r="AY8" s="26">
+      <c r="AY8" s="27">
         <v>46</v>
       </c>
-      <c r="AZ8" s="26">
+      <c r="AZ8" s="27">
         <v>47</v>
       </c>
-      <c r="BA8" s="26">
+      <c r="BA8" s="27">
         <v>48</v>
       </c>
-      <c r="BB8" s="26">
+      <c r="BB8" s="27">
         <v>49</v>
       </c>
-      <c r="BC8" s="26">
+      <c r="BC8" s="27">
         <v>50</v>
       </c>
-      <c r="BD8" s="26">
+      <c r="BD8" s="27">
         <v>51</v>
       </c>
-      <c r="BE8" s="26">
+      <c r="BE8" s="27">
         <v>52</v>
       </c>
-      <c r="BF8" s="26">
+      <c r="BF8" s="27">
         <v>53</v>
       </c>
-      <c r="BG8" s="26">
+      <c r="BG8" s="27">
         <v>54</v>
       </c>
-      <c r="BH8" s="26">
+      <c r="BH8" s="27">
         <v>55</v>
       </c>
-      <c r="BI8" s="26">
+      <c r="BI8" s="27">
         <v>56</v>
       </c>
-      <c r="BJ8" s="26">
+      <c r="BJ8" s="27">
         <v>57</v>
       </c>
-      <c r="BK8" s="26">
+      <c r="BK8" s="27">
         <v>58</v>
       </c>
-      <c r="BL8" s="26">
+      <c r="BL8" s="27">
         <v>59</v>
       </c>
-      <c r="BM8" s="26">
+      <c r="BM8" s="27">
         <v>60</v>
       </c>
-      <c r="BN8" s="26">
+      <c r="BN8" s="27">
         <v>61</v>
       </c>
-      <c r="BO8" s="26">
+      <c r="BO8" s="27">
         <v>62</v>
       </c>
-      <c r="BP8" s="26">
+      <c r="BP8" s="27">
         <v>63</v>
       </c>
-      <c r="BQ8" s="26">
+      <c r="BQ8" s="27">
         <v>64</v>
       </c>
-      <c r="BR8" s="26">
+      <c r="BR8" s="27">
         <v>65</v>
       </c>
-      <c r="BS8" s="26">
+      <c r="BS8" s="27">
         <v>66</v>
       </c>
-      <c r="BT8" s="26">
+      <c r="BT8" s="27">
         <v>67</v>
       </c>
-      <c r="BU8" s="26">
+      <c r="BU8" s="27">
         <v>68</v>
       </c>
-      <c r="BV8" s="26">
+      <c r="BV8" s="27">
         <v>69</v>
       </c>
-      <c r="BW8" s="26">
+      <c r="BW8" s="27">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="27"/>
-      <c r="AC9" s="27"/>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27"/>
-      <c r="AF9" s="27"/>
-      <c r="AG9" s="27"/>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27"/>
-      <c r="AJ9" s="27"/>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="27"/>
-      <c r="AN9" s="27"/>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="27"/>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="27"/>
-      <c r="AT9" s="27"/>
-      <c r="AU9" s="27"/>
-      <c r="AV9" s="27"/>
-      <c r="AW9" s="27"/>
-      <c r="AX9" s="27"/>
-      <c r="AY9" s="27"/>
-      <c r="AZ9" s="27"/>
-      <c r="BA9" s="27"/>
-      <c r="BB9" s="27"/>
-      <c r="BC9" s="27"/>
-      <c r="BD9" s="27"/>
-      <c r="BE9" s="27"/>
-      <c r="BF9" s="27"/>
-      <c r="BG9" s="27"/>
-      <c r="BH9" s="27"/>
-      <c r="BI9" s="27"/>
-      <c r="BJ9" s="27"/>
-      <c r="BK9" s="27"/>
-      <c r="BL9" s="27"/>
-      <c r="BM9" s="27"/>
-      <c r="BN9" s="27"/>
-      <c r="BO9" s="27"/>
-      <c r="BP9" s="27"/>
-      <c r="BQ9" s="27"/>
-      <c r="BR9" s="27"/>
-      <c r="BS9" s="27"/>
-      <c r="BT9" s="27"/>
-      <c r="BU9" s="27"/>
-      <c r="BV9" s="27"/>
-      <c r="BW9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
+      <c r="A10" s="40"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -3520,149 +3536,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="31"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
-      <c r="AL26" s="31"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="31"/>
-      <c r="AO26" s="31"/>
-      <c r="AP26" s="31"/>
-      <c r="AQ26" s="31"/>
-      <c r="AR26" s="31"/>
-      <c r="AS26" s="31"/>
-      <c r="AT26" s="31"/>
-      <c r="AU26" s="31"/>
-      <c r="AV26" s="31"/>
-      <c r="AW26" s="31"/>
-      <c r="AX26" s="31"/>
-      <c r="AY26" s="31"/>
-      <c r="AZ26" s="31"/>
-      <c r="BA26" s="31"/>
-      <c r="BB26" s="31"/>
-      <c r="BC26" s="31"/>
-      <c r="BD26" s="31"/>
-      <c r="BE26" s="31"/>
-      <c r="BF26" s="31"/>
-      <c r="BG26" s="31"/>
-      <c r="BH26" s="31"/>
-      <c r="BI26" s="31"/>
-      <c r="BJ26" s="31"/>
-      <c r="BK26" s="31"/>
-      <c r="BL26" s="31"/>
-      <c r="BM26" s="31"/>
-      <c r="BN26" s="31"/>
-      <c r="BO26" s="31"/>
-      <c r="BP26" s="31"/>
-      <c r="BQ26" s="31"/>
-      <c r="BR26" s="31"/>
-      <c r="BS26" s="31"/>
-      <c r="BT26" s="31"/>
-      <c r="BU26" s="31"/>
-      <c r="BV26" s="31"/>
-      <c r="BW26" s="31"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="42"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="42"/>
+      <c r="V26" s="42"/>
+      <c r="W26" s="42"/>
+      <c r="X26" s="42"/>
+      <c r="Y26" s="42"/>
+      <c r="Z26" s="42"/>
+      <c r="AA26" s="42"/>
+      <c r="AB26" s="42"/>
+      <c r="AC26" s="42"/>
+      <c r="AD26" s="42"/>
+      <c r="AE26" s="42"/>
+      <c r="AF26" s="42"/>
+      <c r="AG26" s="42"/>
+      <c r="AH26" s="42"/>
+      <c r="AI26" s="42"/>
+      <c r="AJ26" s="42"/>
+      <c r="AK26" s="42"/>
+      <c r="AL26" s="42"/>
+      <c r="AM26" s="42"/>
+      <c r="AN26" s="42"/>
+      <c r="AO26" s="42"/>
+      <c r="AP26" s="42"/>
+      <c r="AQ26" s="42"/>
+      <c r="AR26" s="42"/>
+      <c r="AS26" s="42"/>
+      <c r="AT26" s="42"/>
+      <c r="AU26" s="42"/>
+      <c r="AV26" s="42"/>
+      <c r="AW26" s="42"/>
+      <c r="AX26" s="42"/>
+      <c r="AY26" s="42"/>
+      <c r="AZ26" s="42"/>
+      <c r="BA26" s="42"/>
+      <c r="BB26" s="42"/>
+      <c r="BC26" s="42"/>
+      <c r="BD26" s="42"/>
+      <c r="BE26" s="42"/>
+      <c r="BF26" s="42"/>
+      <c r="BG26" s="42"/>
+      <c r="BH26" s="42"/>
+      <c r="BI26" s="42"/>
+      <c r="BJ26" s="42"/>
+      <c r="BK26" s="42"/>
+      <c r="BL26" s="42"/>
+      <c r="BM26" s="42"/>
+      <c r="BN26" s="42"/>
+      <c r="BO26" s="42"/>
+      <c r="BP26" s="42"/>
+      <c r="BQ26" s="42"/>
+      <c r="BR26" s="42"/>
+      <c r="BS26" s="42"/>
+      <c r="BT26" s="42"/>
+      <c r="BU26" s="42"/>
+      <c r="BV26" s="42"/>
+      <c r="BW26" s="42"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="54"/>
-      <c r="R27" s="54"/>
-      <c r="S27" s="54"/>
-      <c r="T27" s="54"/>
-      <c r="U27" s="54"/>
-      <c r="V27" s="54"/>
-      <c r="W27" s="54"/>
-      <c r="X27" s="54"/>
-      <c r="Y27" s="54"/>
-      <c r="Z27" s="54"/>
-      <c r="AA27" s="54"/>
-      <c r="AB27" s="54"/>
-      <c r="AC27" s="54"/>
-      <c r="AD27" s="54"/>
-      <c r="AE27" s="54"/>
-      <c r="AF27" s="54"/>
-      <c r="AG27" s="54"/>
-      <c r="AH27" s="54"/>
-      <c r="AI27" s="54"/>
-      <c r="AJ27" s="54"/>
-      <c r="AK27" s="54"/>
-      <c r="AL27" s="54"/>
-      <c r="AM27" s="54"/>
-      <c r="AN27" s="54"/>
-      <c r="AO27" s="54"/>
-      <c r="AP27" s="54"/>
-      <c r="AQ27" s="54"/>
-      <c r="AR27" s="54"/>
-      <c r="AS27" s="54"/>
-      <c r="AT27" s="54"/>
-      <c r="AU27" s="54"/>
-      <c r="AV27" s="54"/>
-      <c r="AW27" s="54"/>
-      <c r="AX27" s="54"/>
-      <c r="AY27" s="54"/>
-      <c r="AZ27" s="54"/>
-      <c r="BA27" s="54"/>
-      <c r="BB27" s="54"/>
-      <c r="BC27" s="54"/>
-      <c r="BD27" s="54"/>
-      <c r="BE27" s="54"/>
-      <c r="BF27" s="54"/>
-      <c r="BG27" s="54"/>
-      <c r="BH27" s="54"/>
-      <c r="BI27" s="54"/>
-      <c r="BJ27" s="54"/>
-      <c r="BK27" s="54"/>
-      <c r="BL27" s="54"/>
-      <c r="BM27" s="54"/>
-      <c r="BN27" s="54"/>
-      <c r="BO27" s="54"/>
-      <c r="BP27" s="54"/>
-      <c r="BQ27" s="54"/>
-      <c r="BR27" s="54"/>
-      <c r="BS27" s="54"/>
-      <c r="BT27" s="54"/>
-      <c r="BU27" s="54"/>
-      <c r="BV27" s="54"/>
-      <c r="BW27" s="54"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="26"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="26"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="26"/>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="26"/>
+      <c r="AC27" s="26"/>
+      <c r="AD27" s="26"/>
+      <c r="AE27" s="26"/>
+      <c r="AF27" s="26"/>
+      <c r="AG27" s="26"/>
+      <c r="AH27" s="26"/>
+      <c r="AI27" s="26"/>
+      <c r="AJ27" s="26"/>
+      <c r="AK27" s="26"/>
+      <c r="AL27" s="26"/>
+      <c r="AM27" s="26"/>
+      <c r="AN27" s="26"/>
+      <c r="AO27" s="26"/>
+      <c r="AP27" s="26"/>
+      <c r="AQ27" s="26"/>
+      <c r="AR27" s="26"/>
+      <c r="AS27" s="26"/>
+      <c r="AT27" s="26"/>
+      <c r="AU27" s="26"/>
+      <c r="AV27" s="26"/>
+      <c r="AW27" s="26"/>
+      <c r="AX27" s="26"/>
+      <c r="AY27" s="26"/>
+      <c r="AZ27" s="26"/>
+      <c r="BA27" s="26"/>
+      <c r="BB27" s="26"/>
+      <c r="BC27" s="26"/>
+      <c r="BD27" s="26"/>
+      <c r="BE27" s="26"/>
+      <c r="BF27" s="26"/>
+      <c r="BG27" s="26"/>
+      <c r="BH27" s="26"/>
+      <c r="BI27" s="26"/>
+      <c r="BJ27" s="26"/>
+      <c r="BK27" s="26"/>
+      <c r="BL27" s="26"/>
+      <c r="BM27" s="26"/>
+      <c r="BN27" s="26"/>
+      <c r="BO27" s="26"/>
+      <c r="BP27" s="26"/>
+      <c r="BQ27" s="26"/>
+      <c r="BR27" s="26"/>
+      <c r="BS27" s="26"/>
+      <c r="BT27" s="26"/>
+      <c r="BU27" s="26"/>
+      <c r="BV27" s="26"/>
+      <c r="BW27" s="26"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3692,7 +3708,154 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="170">
+  <mergeCells count="171">
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="E26:BW26"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
     <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="R1:S1"/>
@@ -3717,152 +3880,6 @@
     <mergeCell ref="BA2:BA7"/>
     <mergeCell ref="BB2:BB7"/>
     <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E26:BW26"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3895,7 +3912,7 @@
       <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="40" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="58" t="s">
@@ -3919,7 +3936,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="60"/>
       <c r="C4" s="61"/>
       <c r="D4" s="63"/>

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -532,93 +532,99 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -645,12 +651,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -883,16 +883,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
       <c r="F1" s="24">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="52"/>
       <c r="H1" s="25"/>
       <c r="I1" s="23">
         <v>1</v>
@@ -939,8 +939,10 @@
         <v>2</v>
       </c>
       <c r="AE1" s="25"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
+      <c r="AF1" s="24">
+        <v>2</v>
+      </c>
+      <c r="AG1" s="25"/>
       <c r="AH1" s="22"/>
       <c r="AI1" s="22"/>
       <c r="AJ1" s="22"/>
@@ -985,851 +987,855 @@
       <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="29">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="28">
         <v>46274</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="28">
         <v>46274</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="28">
         <v>46274</v>
       </c>
-      <c r="I2" s="29">
+      <c r="I2" s="28">
         <v>46276</v>
       </c>
-      <c r="J2" s="29">
+      <c r="J2" s="28">
         <v>46279</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="28">
         <v>46279</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="28">
         <v>46286</v>
       </c>
-      <c r="O2" s="29">
+      <c r="O2" s="28">
         <v>46286</v>
       </c>
-      <c r="P2" s="29">
+      <c r="P2" s="28">
         <v>46290</v>
       </c>
-      <c r="Q2" s="29">
+      <c r="Q2" s="28">
         <v>46290</v>
       </c>
-      <c r="R2" s="29">
+      <c r="R2" s="28">
         <v>46293</v>
       </c>
-      <c r="S2" s="29">
+      <c r="S2" s="28">
         <v>46293</v>
       </c>
-      <c r="T2" s="29">
+      <c r="T2" s="28">
         <v>46297</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="28">
         <v>46297</v>
       </c>
-      <c r="V2" s="64">
+      <c r="V2" s="30">
         <v>46300</v>
       </c>
-      <c r="W2" s="64">
+      <c r="W2" s="30">
         <v>46300</v>
       </c>
-      <c r="X2" s="29">
+      <c r="X2" s="28">
         <v>46304</v>
       </c>
-      <c r="Y2" s="29">
+      <c r="Y2" s="28">
         <v>46304</v>
       </c>
-      <c r="Z2" s="29">
+      <c r="Z2" s="28">
         <v>46307</v>
       </c>
-      <c r="AA2" s="29">
+      <c r="AA2" s="28">
         <v>46307</v>
       </c>
-      <c r="AB2" s="53">
+      <c r="AB2" s="54">
         <v>46311</v>
       </c>
-      <c r="AC2" s="53">
+      <c r="AC2" s="54">
         <v>46311</v>
       </c>
-      <c r="AD2" s="29">
+      <c r="AD2" s="28">
         <v>46314</v>
       </c>
-      <c r="AE2" s="29">
+      <c r="AE2" s="28">
         <v>46314</v>
       </c>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
-      <c r="BJ2" s="29"/>
-      <c r="BK2" s="29"/>
-      <c r="BL2" s="29"/>
-      <c r="BM2" s="29"/>
-      <c r="BN2" s="29"/>
-      <c r="BO2" s="29"/>
-      <c r="BP2" s="29"/>
-      <c r="BQ2" s="29"/>
-      <c r="BR2" s="29"/>
-      <c r="BS2" s="29"/>
-      <c r="BT2" s="29"/>
-      <c r="BU2" s="29"/>
-      <c r="BV2" s="29"/>
-      <c r="BW2" s="29"/>
+      <c r="AF2" s="28">
+        <v>46318</v>
+      </c>
+      <c r="AG2" s="28">
+        <v>46318</v>
+      </c>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="29"/>
-      <c r="BJ3" s="29"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="29"/>
-      <c r="BM3" s="29"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="29"/>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="29"/>
-      <c r="BT3" s="29"/>
-      <c r="BU3" s="29"/>
-      <c r="BV3" s="29"/>
-      <c r="BW3" s="29"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="54"/>
+      <c r="AC3" s="54"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="42" t="s">
+      <c r="A4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="53"/>
-      <c r="AC4" s="53"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29"/>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="29"/>
-      <c r="AS4" s="29"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="29"/>
-      <c r="AV4" s="29"/>
-      <c r="AW4" s="29"/>
-      <c r="AX4" s="29"/>
-      <c r="AY4" s="29"/>
-      <c r="AZ4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="29"/>
-      <c r="BJ4" s="29"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="29"/>
-      <c r="BT4" s="29"/>
-      <c r="BU4" s="29"/>
-      <c r="BV4" s="29"/>
-      <c r="BW4" s="29"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="54"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
         <v>60</v>
       </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="64"/>
-      <c r="W5" s="64"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="53"/>
-      <c r="AC5" s="53"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
-      <c r="BJ5" s="29"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="29"/>
-      <c r="BM5" s="29"/>
-      <c r="BN5" s="29"/>
-      <c r="BO5" s="29"/>
-      <c r="BP5" s="29"/>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="29"/>
-      <c r="BS5" s="29"/>
-      <c r="BT5" s="29"/>
-      <c r="BU5" s="29"/>
-      <c r="BV5" s="29"/>
-      <c r="BW5" s="29"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="54"/>
+      <c r="AC5" s="54"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
         <v>4</v>
       </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="64"/>
-      <c r="W6" s="64"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="53"/>
-      <c r="AC6" s="53"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
-      <c r="AI6" s="29"/>
-      <c r="AJ6" s="29"/>
-      <c r="AK6" s="29"/>
-      <c r="AL6" s="29"/>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
-      <c r="AO6" s="29"/>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="29"/>
-      <c r="AS6" s="29"/>
-      <c r="AT6" s="29"/>
-      <c r="AU6" s="29"/>
-      <c r="AV6" s="29"/>
-      <c r="AW6" s="29"/>
-      <c r="AX6" s="29"/>
-      <c r="AY6" s="29"/>
-      <c r="AZ6" s="29"/>
-      <c r="BA6" s="29"/>
-      <c r="BB6" s="29"/>
-      <c r="BC6" s="29"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="29"/>
-      <c r="BG6" s="29"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="29"/>
-      <c r="BJ6" s="29"/>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="29"/>
-      <c r="BM6" s="29"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="29"/>
-      <c r="BP6" s="29"/>
-      <c r="BQ6" s="29"/>
-      <c r="BR6" s="29"/>
-      <c r="BS6" s="29"/>
-      <c r="BT6" s="29"/>
-      <c r="BU6" s="29"/>
-      <c r="BV6" s="29"/>
-      <c r="BW6" s="29"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="54"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
+      <c r="BM6" s="28"/>
+      <c r="BN6" s="28"/>
+      <c r="BO6" s="28"/>
+      <c r="BP6" s="28"/>
+      <c r="BQ6" s="28"/>
+      <c r="BR6" s="28"/>
+      <c r="BS6" s="28"/>
+      <c r="BT6" s="28"/>
+      <c r="BU6" s="28"/>
+      <c r="BV6" s="28"/>
+      <c r="BW6" s="28"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="45">
+      <c r="B7" s="51"/>
+      <c r="C7" s="49">
         <v>11</v>
       </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="65"/>
-      <c r="W7" s="65"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="54"/>
-      <c r="AC7" s="54"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="30"/>
-      <c r="AN7" s="30"/>
-      <c r="AO7" s="30"/>
-      <c r="AP7" s="30"/>
-      <c r="AQ7" s="30"/>
-      <c r="AR7" s="30"/>
-      <c r="AS7" s="30"/>
-      <c r="AT7" s="30"/>
-      <c r="AU7" s="30"/>
-      <c r="AV7" s="30"/>
-      <c r="AW7" s="30"/>
-      <c r="AX7" s="30"/>
-      <c r="AY7" s="30"/>
-      <c r="AZ7" s="30"/>
-      <c r="BA7" s="30"/>
-      <c r="BB7" s="30"/>
-      <c r="BC7" s="30"/>
-      <c r="BD7" s="30"/>
-      <c r="BE7" s="30"/>
-      <c r="BF7" s="30"/>
-      <c r="BG7" s="30"/>
-      <c r="BH7" s="30"/>
-      <c r="BI7" s="30"/>
-      <c r="BJ7" s="30"/>
-      <c r="BK7" s="30"/>
-      <c r="BL7" s="30"/>
-      <c r="BM7" s="30"/>
-      <c r="BN7" s="30"/>
-      <c r="BO7" s="30"/>
-      <c r="BP7" s="30"/>
-      <c r="BQ7" s="30"/>
-      <c r="BR7" s="30"/>
-      <c r="BS7" s="30"/>
-      <c r="BT7" s="30"/>
-      <c r="BU7" s="30"/>
-      <c r="BV7" s="30"/>
-      <c r="BW7" s="30"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="55"/>
+      <c r="AC7" s="55"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50">
+      <c r="B8" s="53"/>
+      <c r="C8" s="32">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="43"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="27">
-        <v>1</v>
-      </c>
-      <c r="G8" s="27">
+      <c r="F8" s="26">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26">
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="26">
         <v>3</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="26">
         <v>4</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="26">
         <v>5</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="26">
         <v>6</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="26">
         <v>7</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="26">
         <v>8</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="26">
         <v>9</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="26">
         <v>10</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="26">
         <v>11</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="26">
         <v>12</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="26">
         <v>13</v>
       </c>
-      <c r="S8" s="27">
+      <c r="S8" s="26">
         <v>14</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="26">
         <v>15</v>
       </c>
-      <c r="U8" s="27">
+      <c r="U8" s="26">
         <v>16</v>
       </c>
-      <c r="V8" s="27">
+      <c r="V8" s="26">
         <v>17</v>
       </c>
-      <c r="W8" s="27">
+      <c r="W8" s="26">
         <v>18</v>
       </c>
-      <c r="X8" s="27">
+      <c r="X8" s="26">
         <v>19</v>
       </c>
-      <c r="Y8" s="27">
+      <c r="Y8" s="26">
         <v>20</v>
       </c>
-      <c r="Z8" s="27">
+      <c r="Z8" s="26">
         <v>21</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AA8" s="26">
         <v>22</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="26">
         <v>23</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AC8" s="26">
         <v>24</v>
       </c>
-      <c r="AD8" s="27">
+      <c r="AD8" s="26">
         <v>25</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AE8" s="26">
         <v>26</v>
       </c>
-      <c r="AF8" s="27">
+      <c r="AF8" s="26">
         <v>27</v>
       </c>
-      <c r="AG8" s="27">
+      <c r="AG8" s="26">
         <v>28</v>
       </c>
-      <c r="AH8" s="27">
+      <c r="AH8" s="26">
         <v>29</v>
       </c>
-      <c r="AI8" s="27">
+      <c r="AI8" s="26">
         <v>30</v>
       </c>
-      <c r="AJ8" s="27">
+      <c r="AJ8" s="26">
         <v>31</v>
       </c>
-      <c r="AK8" s="27">
+      <c r="AK8" s="26">
         <v>32</v>
       </c>
-      <c r="AL8" s="27">
+      <c r="AL8" s="26">
         <v>33</v>
       </c>
-      <c r="AM8" s="27">
+      <c r="AM8" s="26">
         <v>34</v>
       </c>
-      <c r="AN8" s="27">
+      <c r="AN8" s="26">
         <v>35</v>
       </c>
-      <c r="AO8" s="27">
+      <c r="AO8" s="26">
         <v>36</v>
       </c>
-      <c r="AP8" s="27">
+      <c r="AP8" s="26">
         <v>37</v>
       </c>
-      <c r="AQ8" s="27">
+      <c r="AQ8" s="26">
         <v>38</v>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="26">
         <v>39</v>
       </c>
-      <c r="AS8" s="27">
+      <c r="AS8" s="26">
         <v>40</v>
       </c>
-      <c r="AT8" s="27">
+      <c r="AT8" s="26">
         <v>41</v>
       </c>
-      <c r="AU8" s="27">
+      <c r="AU8" s="26">
         <v>42</v>
       </c>
-      <c r="AV8" s="27">
+      <c r="AV8" s="26">
         <v>43</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="AW8" s="26">
         <v>44</v>
       </c>
-      <c r="AX8" s="27">
+      <c r="AX8" s="26">
         <v>45</v>
       </c>
-      <c r="AY8" s="27">
+      <c r="AY8" s="26">
         <v>46</v>
       </c>
-      <c r="AZ8" s="27">
+      <c r="AZ8" s="26">
         <v>47</v>
       </c>
-      <c r="BA8" s="27">
+      <c r="BA8" s="26">
         <v>48</v>
       </c>
-      <c r="BB8" s="27">
+      <c r="BB8" s="26">
         <v>49</v>
       </c>
-      <c r="BC8" s="27">
+      <c r="BC8" s="26">
         <v>50</v>
       </c>
-      <c r="BD8" s="27">
+      <c r="BD8" s="26">
         <v>51</v>
       </c>
-      <c r="BE8" s="27">
+      <c r="BE8" s="26">
         <v>52</v>
       </c>
-      <c r="BF8" s="27">
+      <c r="BF8" s="26">
         <v>53</v>
       </c>
-      <c r="BG8" s="27">
+      <c r="BG8" s="26">
         <v>54</v>
       </c>
-      <c r="BH8" s="27">
+      <c r="BH8" s="26">
         <v>55</v>
       </c>
-      <c r="BI8" s="27">
+      <c r="BI8" s="26">
         <v>56</v>
       </c>
-      <c r="BJ8" s="27">
+      <c r="BJ8" s="26">
         <v>57</v>
       </c>
-      <c r="BK8" s="27">
+      <c r="BK8" s="26">
         <v>58</v>
       </c>
-      <c r="BL8" s="27">
+      <c r="BL8" s="26">
         <v>59</v>
       </c>
-      <c r="BM8" s="27">
+      <c r="BM8" s="26">
         <v>60</v>
       </c>
-      <c r="BN8" s="27">
+      <c r="BN8" s="26">
         <v>61</v>
       </c>
-      <c r="BO8" s="27">
+      <c r="BO8" s="26">
         <v>62</v>
       </c>
-      <c r="BP8" s="27">
+      <c r="BP8" s="26">
         <v>63</v>
       </c>
-      <c r="BQ8" s="27">
+      <c r="BQ8" s="26">
         <v>64</v>
       </c>
-      <c r="BR8" s="27">
+      <c r="BR8" s="26">
         <v>65</v>
       </c>
-      <c r="BS8" s="27">
+      <c r="BS8" s="26">
         <v>66</v>
       </c>
-      <c r="BT8" s="27">
+      <c r="BT8" s="26">
         <v>67</v>
       </c>
-      <c r="BU8" s="27">
+      <c r="BU8" s="26">
         <v>68</v>
       </c>
-      <c r="BV8" s="27">
+      <c r="BV8" s="26">
         <v>69</v>
       </c>
-      <c r="BW8" s="27">
+      <c r="BW8" s="26">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="28"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
-      <c r="AU9" s="28"/>
-      <c r="AV9" s="28"/>
-      <c r="AW9" s="28"/>
-      <c r="AX9" s="28"/>
-      <c r="AY9" s="28"/>
-      <c r="AZ9" s="28"/>
-      <c r="BA9" s="28"/>
-      <c r="BB9" s="28"/>
-      <c r="BC9" s="28"/>
-      <c r="BD9" s="28"/>
-      <c r="BE9" s="28"/>
-      <c r="BF9" s="28"/>
-      <c r="BG9" s="28"/>
-      <c r="BH9" s="28"/>
-      <c r="BI9" s="28"/>
-      <c r="BJ9" s="28"/>
-      <c r="BK9" s="28"/>
-      <c r="BL9" s="28"/>
-      <c r="BM9" s="28"/>
-      <c r="BN9" s="28"/>
-      <c r="BO9" s="28"/>
-      <c r="BP9" s="28"/>
-      <c r="BQ9" s="28"/>
-      <c r="BR9" s="28"/>
-      <c r="BS9" s="28"/>
-      <c r="BT9" s="28"/>
-      <c r="BU9" s="28"/>
-      <c r="BV9" s="28"/>
-      <c r="BW9" s="28"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="27"/>
+      <c r="X9" s="27"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27"/>
+      <c r="AB9" s="27"/>
+      <c r="AC9" s="27"/>
+      <c r="AD9" s="27"/>
+      <c r="AE9" s="27"/>
+      <c r="AF9" s="27"/>
+      <c r="AG9" s="27"/>
+      <c r="AH9" s="27"/>
+      <c r="AI9" s="27"/>
+      <c r="AJ9" s="27"/>
+      <c r="AK9" s="27"/>
+      <c r="AL9" s="27"/>
+      <c r="AM9" s="27"/>
+      <c r="AN9" s="27"/>
+      <c r="AO9" s="27"/>
+      <c r="AP9" s="27"/>
+      <c r="AQ9" s="27"/>
+      <c r="AR9" s="27"/>
+      <c r="AS9" s="27"/>
+      <c r="AT9" s="27"/>
+      <c r="AU9" s="27"/>
+      <c r="AV9" s="27"/>
+      <c r="AW9" s="27"/>
+      <c r="AX9" s="27"/>
+      <c r="AY9" s="27"/>
+      <c r="AZ9" s="27"/>
+      <c r="BA9" s="27"/>
+      <c r="BB9" s="27"/>
+      <c r="BC9" s="27"/>
+      <c r="BD9" s="27"/>
+      <c r="BE9" s="27"/>
+      <c r="BF9" s="27"/>
+      <c r="BG9" s="27"/>
+      <c r="BH9" s="27"/>
+      <c r="BI9" s="27"/>
+      <c r="BJ9" s="27"/>
+      <c r="BK9" s="27"/>
+      <c r="BL9" s="27"/>
+      <c r="BM9" s="27"/>
+      <c r="BN9" s="27"/>
+      <c r="BO9" s="27"/>
+      <c r="BP9" s="27"/>
+      <c r="BQ9" s="27"/>
+      <c r="BR9" s="27"/>
+      <c r="BS9" s="27"/>
+      <c r="BT9" s="27"/>
+      <c r="BU9" s="27"/>
+      <c r="BV9" s="27"/>
+      <c r="BW9" s="27"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="40"/>
-      <c r="B10" s="51"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -3536,149 +3542,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="50"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="42"/>
-      <c r="U26" s="42"/>
-      <c r="V26" s="42"/>
-      <c r="W26" s="42"/>
-      <c r="X26" s="42"/>
-      <c r="Y26" s="42"/>
-      <c r="Z26" s="42"/>
-      <c r="AA26" s="42"/>
-      <c r="AB26" s="42"/>
-      <c r="AC26" s="42"/>
-      <c r="AD26" s="42"/>
-      <c r="AE26" s="42"/>
-      <c r="AF26" s="42"/>
-      <c r="AG26" s="42"/>
-      <c r="AH26" s="42"/>
-      <c r="AI26" s="42"/>
-      <c r="AJ26" s="42"/>
-      <c r="AK26" s="42"/>
-      <c r="AL26" s="42"/>
-      <c r="AM26" s="42"/>
-      <c r="AN26" s="42"/>
-      <c r="AO26" s="42"/>
-      <c r="AP26" s="42"/>
-      <c r="AQ26" s="42"/>
-      <c r="AR26" s="42"/>
-      <c r="AS26" s="42"/>
-      <c r="AT26" s="42"/>
-      <c r="AU26" s="42"/>
-      <c r="AV26" s="42"/>
-      <c r="AW26" s="42"/>
-      <c r="AX26" s="42"/>
-      <c r="AY26" s="42"/>
-      <c r="AZ26" s="42"/>
-      <c r="BA26" s="42"/>
-      <c r="BB26" s="42"/>
-      <c r="BC26" s="42"/>
-      <c r="BD26" s="42"/>
-      <c r="BE26" s="42"/>
-      <c r="BF26" s="42"/>
-      <c r="BG26" s="42"/>
-      <c r="BH26" s="42"/>
-      <c r="BI26" s="42"/>
-      <c r="BJ26" s="42"/>
-      <c r="BK26" s="42"/>
-      <c r="BL26" s="42"/>
-      <c r="BM26" s="42"/>
-      <c r="BN26" s="42"/>
-      <c r="BO26" s="42"/>
-      <c r="BP26" s="42"/>
-      <c r="BQ26" s="42"/>
-      <c r="BR26" s="42"/>
-      <c r="BS26" s="42"/>
-      <c r="BT26" s="42"/>
-      <c r="BU26" s="42"/>
-      <c r="BV26" s="42"/>
-      <c r="BW26" s="42"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="33"/>
+      <c r="AB26" s="33"/>
+      <c r="AC26" s="33"/>
+      <c r="AD26" s="33"/>
+      <c r="AE26" s="33"/>
+      <c r="AF26" s="33"/>
+      <c r="AG26" s="33"/>
+      <c r="AH26" s="33"/>
+      <c r="AI26" s="33"/>
+      <c r="AJ26" s="33"/>
+      <c r="AK26" s="33"/>
+      <c r="AL26" s="33"/>
+      <c r="AM26" s="33"/>
+      <c r="AN26" s="33"/>
+      <c r="AO26" s="33"/>
+      <c r="AP26" s="33"/>
+      <c r="AQ26" s="33"/>
+      <c r="AR26" s="33"/>
+      <c r="AS26" s="33"/>
+      <c r="AT26" s="33"/>
+      <c r="AU26" s="33"/>
+      <c r="AV26" s="33"/>
+      <c r="AW26" s="33"/>
+      <c r="AX26" s="33"/>
+      <c r="AY26" s="33"/>
+      <c r="AZ26" s="33"/>
+      <c r="BA26" s="33"/>
+      <c r="BB26" s="33"/>
+      <c r="BC26" s="33"/>
+      <c r="BD26" s="33"/>
+      <c r="BE26" s="33"/>
+      <c r="BF26" s="33"/>
+      <c r="BG26" s="33"/>
+      <c r="BH26" s="33"/>
+      <c r="BI26" s="33"/>
+      <c r="BJ26" s="33"/>
+      <c r="BK26" s="33"/>
+      <c r="BL26" s="33"/>
+      <c r="BM26" s="33"/>
+      <c r="BN26" s="33"/>
+      <c r="BO26" s="33"/>
+      <c r="BP26" s="33"/>
+      <c r="BQ26" s="33"/>
+      <c r="BR26" s="33"/>
+      <c r="BS26" s="33"/>
+      <c r="BT26" s="33"/>
+      <c r="BU26" s="33"/>
+      <c r="BV26" s="33"/>
+      <c r="BW26" s="33"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="26"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="26"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
-      <c r="AC27" s="26"/>
-      <c r="AD27" s="26"/>
-      <c r="AE27" s="26"/>
-      <c r="AF27" s="26"/>
-      <c r="AG27" s="26"/>
-      <c r="AH27" s="26"/>
-      <c r="AI27" s="26"/>
-      <c r="AJ27" s="26"/>
-      <c r="AK27" s="26"/>
-      <c r="AL27" s="26"/>
-      <c r="AM27" s="26"/>
-      <c r="AN27" s="26"/>
-      <c r="AO27" s="26"/>
-      <c r="AP27" s="26"/>
-      <c r="AQ27" s="26"/>
-      <c r="AR27" s="26"/>
-      <c r="AS27" s="26"/>
-      <c r="AT27" s="26"/>
-      <c r="AU27" s="26"/>
-      <c r="AV27" s="26"/>
-      <c r="AW27" s="26"/>
-      <c r="AX27" s="26"/>
-      <c r="AY27" s="26"/>
-      <c r="AZ27" s="26"/>
-      <c r="BA27" s="26"/>
-      <c r="BB27" s="26"/>
-      <c r="BC27" s="26"/>
-      <c r="BD27" s="26"/>
-      <c r="BE27" s="26"/>
-      <c r="BF27" s="26"/>
-      <c r="BG27" s="26"/>
-      <c r="BH27" s="26"/>
-      <c r="BI27" s="26"/>
-      <c r="BJ27" s="26"/>
-      <c r="BK27" s="26"/>
-      <c r="BL27" s="26"/>
-      <c r="BM27" s="26"/>
-      <c r="BN27" s="26"/>
-      <c r="BO27" s="26"/>
-      <c r="BP27" s="26"/>
-      <c r="BQ27" s="26"/>
-      <c r="BR27" s="26"/>
-      <c r="BS27" s="26"/>
-      <c r="BT27" s="26"/>
-      <c r="BU27" s="26"/>
-      <c r="BV27" s="26"/>
-      <c r="BW27" s="26"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="56"/>
+      <c r="R27" s="56"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="56"/>
+      <c r="U27" s="56"/>
+      <c r="V27" s="56"/>
+      <c r="W27" s="56"/>
+      <c r="X27" s="56"/>
+      <c r="Y27" s="56"/>
+      <c r="Z27" s="56"/>
+      <c r="AA27" s="56"/>
+      <c r="AB27" s="56"/>
+      <c r="AC27" s="56"/>
+      <c r="AD27" s="56"/>
+      <c r="AE27" s="56"/>
+      <c r="AF27" s="56"/>
+      <c r="AG27" s="56"/>
+      <c r="AH27" s="56"/>
+      <c r="AI27" s="56"/>
+      <c r="AJ27" s="56"/>
+      <c r="AK27" s="56"/>
+      <c r="AL27" s="56"/>
+      <c r="AM27" s="56"/>
+      <c r="AN27" s="56"/>
+      <c r="AO27" s="56"/>
+      <c r="AP27" s="56"/>
+      <c r="AQ27" s="56"/>
+      <c r="AR27" s="56"/>
+      <c r="AS27" s="56"/>
+      <c r="AT27" s="56"/>
+      <c r="AU27" s="56"/>
+      <c r="AV27" s="56"/>
+      <c r="AW27" s="56"/>
+      <c r="AX27" s="56"/>
+      <c r="AY27" s="56"/>
+      <c r="AZ27" s="56"/>
+      <c r="BA27" s="56"/>
+      <c r="BB27" s="56"/>
+      <c r="BC27" s="56"/>
+      <c r="BD27" s="56"/>
+      <c r="BE27" s="56"/>
+      <c r="BF27" s="56"/>
+      <c r="BG27" s="56"/>
+      <c r="BH27" s="56"/>
+      <c r="BI27" s="56"/>
+      <c r="BJ27" s="56"/>
+      <c r="BK27" s="56"/>
+      <c r="BL27" s="56"/>
+      <c r="BM27" s="56"/>
+      <c r="BN27" s="56"/>
+      <c r="BO27" s="56"/>
+      <c r="BP27" s="56"/>
+      <c r="BQ27" s="56"/>
+      <c r="BR27" s="56"/>
+      <c r="BS27" s="56"/>
+      <c r="BT27" s="56"/>
+      <c r="BU27" s="56"/>
+      <c r="BV27" s="56"/>
+      <c r="BW27" s="56"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3708,32 +3714,115 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="171">
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
+  <mergeCells count="172">
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:BW27"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E26:BW26"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AP2:AP7"/>
     <mergeCell ref="AV8:AV9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
@@ -3758,93 +3847,22 @@
     <mergeCell ref="AB8:AB9"/>
     <mergeCell ref="AC8:AC9"/>
     <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="E26:BW26"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
     <mergeCell ref="Z2:Z7"/>
     <mergeCell ref="AA2:AA7"/>
     <mergeCell ref="AB2:AB7"/>
@@ -3853,33 +3871,22 @@
     <mergeCell ref="AE2:AE7"/>
     <mergeCell ref="AH2:AH7"/>
     <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
     <mergeCell ref="AJ2:AJ7"/>
     <mergeCell ref="AG2:AG7"/>
     <mergeCell ref="AF2:AF7"/>
     <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:BW27"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AF1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3901,49 +3908,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="56" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="62" t="s">
+      <c r="C3" s="61"/>
+      <c r="D3" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="58" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="56"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="58"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -526,23 +526,92 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -550,80 +619,11 @@
     <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -883,68 +883,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40"/>
-      <c r="F1" s="24">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="31"/>
+      <c r="F1" s="46">
         <v>7</v>
       </c>
-      <c r="G1" s="52"/>
-      <c r="H1" s="25"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
       <c r="I1" s="23">
         <v>1</v>
       </c>
-      <c r="J1" s="24">
+      <c r="J1" s="46">
         <v>2</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="24">
+      <c r="K1" s="48"/>
+      <c r="L1" s="46">
         <v>2</v>
       </c>
-      <c r="M1" s="25"/>
-      <c r="N1" s="24">
+      <c r="M1" s="48"/>
+      <c r="N1" s="46">
         <v>2</v>
       </c>
-      <c r="O1" s="25"/>
-      <c r="P1" s="24">
+      <c r="O1" s="48"/>
+      <c r="P1" s="46">
         <v>2</v>
       </c>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="24">
+      <c r="Q1" s="48"/>
+      <c r="R1" s="46">
         <v>2</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="24">
+      <c r="S1" s="48"/>
+      <c r="T1" s="46">
         <v>2</v>
       </c>
-      <c r="U1" s="25"/>
-      <c r="V1" s="24">
+      <c r="U1" s="48"/>
+      <c r="V1" s="46">
         <v>2</v>
       </c>
-      <c r="W1" s="25"/>
-      <c r="X1" s="24">
+      <c r="W1" s="48"/>
+      <c r="X1" s="46">
         <v>2</v>
       </c>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="24">
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="46">
         <v>2</v>
       </c>
-      <c r="AA1" s="25"/>
+      <c r="AA1" s="48"/>
       <c r="AB1" s="22"/>
       <c r="AC1" s="22"/>
-      <c r="AD1" s="24">
+      <c r="AD1" s="46">
         <v>2</v>
       </c>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="24">
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="46">
         <v>2</v>
       </c>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
+      <c r="AG1" s="48"/>
+      <c r="AH1" s="46">
+        <v>2</v>
+      </c>
+      <c r="AI1" s="48"/>
       <c r="AJ1" s="22"/>
       <c r="AK1" s="22"/>
       <c r="AL1" s="22"/>
@@ -987,855 +989,859 @@
       <c r="BW1" s="22"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="28">
+      <c r="A2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="27">
         <v>46274</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>46274</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <v>46274</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="27">
         <v>46276</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="27">
         <v>46279</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="27">
         <v>46279</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="27">
         <v>46286</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="27">
         <v>46286</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="27">
         <v>46290</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="27">
         <v>46290</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="27">
         <v>46293</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="27">
         <v>46293</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="27">
         <v>46297</v>
       </c>
-      <c r="U2" s="28">
+      <c r="U2" s="27">
         <v>46297</v>
       </c>
-      <c r="V2" s="30">
+      <c r="V2" s="53">
         <v>46300</v>
       </c>
-      <c r="W2" s="30">
+      <c r="W2" s="53">
         <v>46300</v>
       </c>
-      <c r="X2" s="28">
+      <c r="X2" s="27">
         <v>46304</v>
       </c>
-      <c r="Y2" s="28">
+      <c r="Y2" s="27">
         <v>46304</v>
       </c>
-      <c r="Z2" s="28">
+      <c r="Z2" s="27">
         <v>46307</v>
       </c>
-      <c r="AA2" s="28">
+      <c r="AA2" s="27">
         <v>46307</v>
       </c>
-      <c r="AB2" s="54">
+      <c r="AB2" s="55">
         <v>46311</v>
       </c>
-      <c r="AC2" s="54">
+      <c r="AC2" s="55">
         <v>46311</v>
       </c>
-      <c r="AD2" s="28">
+      <c r="AD2" s="27">
         <v>46314</v>
       </c>
-      <c r="AE2" s="28">
+      <c r="AE2" s="27">
         <v>46314</v>
       </c>
-      <c r="AF2" s="28">
+      <c r="AF2" s="27">
         <v>46318</v>
       </c>
-      <c r="AG2" s="28">
+      <c r="AG2" s="27">
         <v>46318</v>
       </c>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="28"/>
-      <c r="BK2" s="28"/>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="28"/>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="28"/>
-      <c r="BP2" s="28"/>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="28"/>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="28"/>
-      <c r="BU2" s="28"/>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="28"/>
+      <c r="AH2" s="27">
+        <v>46321</v>
+      </c>
+      <c r="AI2" s="27">
+        <v>46321</v>
+      </c>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="27"/>
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="27"/>
+      <c r="AU2" s="27"/>
+      <c r="AV2" s="27"/>
+      <c r="AW2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="27"/>
+      <c r="AZ2" s="27"/>
+      <c r="BA2" s="27"/>
+      <c r="BB2" s="27"/>
+      <c r="BC2" s="27"/>
+      <c r="BD2" s="27"/>
+      <c r="BE2" s="27"/>
+      <c r="BF2" s="27"/>
+      <c r="BG2" s="27"/>
+      <c r="BH2" s="27"/>
+      <c r="BI2" s="27"/>
+      <c r="BJ2" s="27"/>
+      <c r="BK2" s="27"/>
+      <c r="BL2" s="27"/>
+      <c r="BM2" s="27"/>
+      <c r="BN2" s="27"/>
+      <c r="BO2" s="27"/>
+      <c r="BP2" s="27"/>
+      <c r="BQ2" s="27"/>
+      <c r="BR2" s="27"/>
+      <c r="BS2" s="27"/>
+      <c r="BT2" s="27"/>
+      <c r="BU2" s="27"/>
+      <c r="BV2" s="27"/>
+      <c r="BW2" s="27"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="54"/>
-      <c r="AC3" s="54"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="28"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="28"/>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="28"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="28"/>
-      <c r="AZ3" s="28"/>
-      <c r="BA3" s="28"/>
-      <c r="BB3" s="28"/>
-      <c r="BC3" s="28"/>
-      <c r="BD3" s="28"/>
-      <c r="BE3" s="28"/>
-      <c r="BF3" s="28"/>
-      <c r="BG3" s="28"/>
-      <c r="BH3" s="28"/>
-      <c r="BI3" s="28"/>
-      <c r="BJ3" s="28"/>
-      <c r="BK3" s="28"/>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="28"/>
-      <c r="BN3" s="28"/>
-      <c r="BO3" s="28"/>
-      <c r="BP3" s="28"/>
-      <c r="BQ3" s="28"/>
-      <c r="BR3" s="28"/>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="28"/>
-      <c r="BU3" s="28"/>
-      <c r="BV3" s="28"/>
-      <c r="BW3" s="28"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27"/>
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="27"/>
+      <c r="AS3" s="27"/>
+      <c r="AT3" s="27"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="27"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27"/>
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="27"/>
+      <c r="BB3" s="27"/>
+      <c r="BC3" s="27"/>
+      <c r="BD3" s="27"/>
+      <c r="BE3" s="27"/>
+      <c r="BF3" s="27"/>
+      <c r="BG3" s="27"/>
+      <c r="BH3" s="27"/>
+      <c r="BI3" s="27"/>
+      <c r="BJ3" s="27"/>
+      <c r="BK3" s="27"/>
+      <c r="BL3" s="27"/>
+      <c r="BM3" s="27"/>
+      <c r="BN3" s="27"/>
+      <c r="BO3" s="27"/>
+      <c r="BP3" s="27"/>
+      <c r="BQ3" s="27"/>
+      <c r="BR3" s="27"/>
+      <c r="BS3" s="27"/>
+      <c r="BT3" s="27"/>
+      <c r="BU3" s="27"/>
+      <c r="BV3" s="27"/>
+      <c r="BW3" s="27"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="33" t="s">
+      <c r="A4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
-      <c r="BJ4" s="28"/>
-      <c r="BK4" s="28"/>
-      <c r="BL4" s="28"/>
-      <c r="BM4" s="28"/>
-      <c r="BN4" s="28"/>
-      <c r="BO4" s="28"/>
-      <c r="BP4" s="28"/>
-      <c r="BQ4" s="28"/>
-      <c r="BR4" s="28"/>
-      <c r="BS4" s="28"/>
-      <c r="BT4" s="28"/>
-      <c r="BU4" s="28"/>
-      <c r="BV4" s="28"/>
-      <c r="BW4" s="28"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="53"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="55"/>
+      <c r="AC4" s="55"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="27"/>
+      <c r="AW4" s="27"/>
+      <c r="AX4" s="27"/>
+      <c r="AY4" s="27"/>
+      <c r="AZ4" s="27"/>
+      <c r="BA4" s="27"/>
+      <c r="BB4" s="27"/>
+      <c r="BC4" s="27"/>
+      <c r="BD4" s="27"/>
+      <c r="BE4" s="27"/>
+      <c r="BF4" s="27"/>
+      <c r="BG4" s="27"/>
+      <c r="BH4" s="27"/>
+      <c r="BI4" s="27"/>
+      <c r="BJ4" s="27"/>
+      <c r="BK4" s="27"/>
+      <c r="BL4" s="27"/>
+      <c r="BM4" s="27"/>
+      <c r="BN4" s="27"/>
+      <c r="BO4" s="27"/>
+      <c r="BP4" s="27"/>
+      <c r="BQ4" s="27"/>
+      <c r="BR4" s="27"/>
+      <c r="BS4" s="27"/>
+      <c r="BT4" s="27"/>
+      <c r="BU4" s="27"/>
+      <c r="BV4" s="27"/>
+      <c r="BW4" s="27"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="42"/>
+      <c r="C5" s="43">
         <v>60</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="54"/>
-      <c r="AC5" s="54"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="28"/>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="28"/>
-      <c r="BP5" s="28"/>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="28"/>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="28"/>
-      <c r="BU5" s="28"/>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="28"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="55"/>
+      <c r="AC5" s="55"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="27"/>
+      <c r="AK5" s="27"/>
+      <c r="AL5" s="27"/>
+      <c r="AM5" s="27"/>
+      <c r="AN5" s="27"/>
+      <c r="AO5" s="27"/>
+      <c r="AP5" s="27"/>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="27"/>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="27"/>
+      <c r="AW5" s="27"/>
+      <c r="AX5" s="27"/>
+      <c r="AY5" s="27"/>
+      <c r="AZ5" s="27"/>
+      <c r="BA5" s="27"/>
+      <c r="BB5" s="27"/>
+      <c r="BC5" s="27"/>
+      <c r="BD5" s="27"/>
+      <c r="BE5" s="27"/>
+      <c r="BF5" s="27"/>
+      <c r="BG5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="27"/>
+      <c r="BJ5" s="27"/>
+      <c r="BK5" s="27"/>
+      <c r="BL5" s="27"/>
+      <c r="BM5" s="27"/>
+      <c r="BN5" s="27"/>
+      <c r="BO5" s="27"/>
+      <c r="BP5" s="27"/>
+      <c r="BQ5" s="27"/>
+      <c r="BR5" s="27"/>
+      <c r="BS5" s="27"/>
+      <c r="BT5" s="27"/>
+      <c r="BU5" s="27"/>
+      <c r="BV5" s="27"/>
+      <c r="BW5" s="27"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43">
         <v>4</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="54"/>
-      <c r="AC6" s="54"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="28"/>
-      <c r="AH6" s="28"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="28"/>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
-      <c r="BJ6" s="28"/>
-      <c r="BK6" s="28"/>
-      <c r="BL6" s="28"/>
-      <c r="BM6" s="28"/>
-      <c r="BN6" s="28"/>
-      <c r="BO6" s="28"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="28"/>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="28"/>
-      <c r="BU6" s="28"/>
-      <c r="BV6" s="28"/>
-      <c r="BW6" s="28"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="53"/>
+      <c r="W6" s="53"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="55"/>
+      <c r="AC6" s="55"/>
+      <c r="AD6" s="27"/>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="27"/>
+      <c r="AG6" s="27"/>
+      <c r="AH6" s="27"/>
+      <c r="AI6" s="27"/>
+      <c r="AJ6" s="27"/>
+      <c r="AK6" s="27"/>
+      <c r="AL6" s="27"/>
+      <c r="AM6" s="27"/>
+      <c r="AN6" s="27"/>
+      <c r="AO6" s="27"/>
+      <c r="AP6" s="27"/>
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="27"/>
+      <c r="AS6" s="27"/>
+      <c r="AT6" s="27"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="27"/>
+      <c r="AW6" s="27"/>
+      <c r="AX6" s="27"/>
+      <c r="AY6" s="27"/>
+      <c r="AZ6" s="27"/>
+      <c r="BA6" s="27"/>
+      <c r="BB6" s="27"/>
+      <c r="BC6" s="27"/>
+      <c r="BD6" s="27"/>
+      <c r="BE6" s="27"/>
+      <c r="BF6" s="27"/>
+      <c r="BG6" s="27"/>
+      <c r="BH6" s="27"/>
+      <c r="BI6" s="27"/>
+      <c r="BJ6" s="27"/>
+      <c r="BK6" s="27"/>
+      <c r="BL6" s="27"/>
+      <c r="BM6" s="27"/>
+      <c r="BN6" s="27"/>
+      <c r="BO6" s="27"/>
+      <c r="BP6" s="27"/>
+      <c r="BQ6" s="27"/>
+      <c r="BR6" s="27"/>
+      <c r="BS6" s="27"/>
+      <c r="BT6" s="27"/>
+      <c r="BU6" s="27"/>
+      <c r="BV6" s="27"/>
+      <c r="BW6" s="27"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="49">
+      <c r="B7" s="45"/>
+      <c r="C7" s="43">
         <v>11</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="55"/>
-      <c r="AC7" s="55"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="29"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
-      <c r="AV7" s="29"/>
-      <c r="AW7" s="29"/>
-      <c r="AX7" s="29"/>
-      <c r="AY7" s="29"/>
-      <c r="AZ7" s="29"/>
-      <c r="BA7" s="29"/>
-      <c r="BB7" s="29"/>
-      <c r="BC7" s="29"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="29"/>
-      <c r="BG7" s="29"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="29"/>
-      <c r="BJ7" s="29"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="29"/>
-      <c r="BM7" s="29"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="29"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="29"/>
-      <c r="BS7" s="29"/>
-      <c r="BT7" s="29"/>
-      <c r="BU7" s="29"/>
-      <c r="BV7" s="29"/>
-      <c r="BW7" s="29"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="56"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="28"/>
+      <c r="AH7" s="28"/>
+      <c r="AI7" s="28"/>
+      <c r="AJ7" s="28"/>
+      <c r="AK7" s="28"/>
+      <c r="AL7" s="28"/>
+      <c r="AM7" s="28"/>
+      <c r="AN7" s="28"/>
+      <c r="AO7" s="28"/>
+      <c r="AP7" s="28"/>
+      <c r="AQ7" s="28"/>
+      <c r="AR7" s="28"/>
+      <c r="AS7" s="28"/>
+      <c r="AT7" s="28"/>
+      <c r="AU7" s="28"/>
+      <c r="AV7" s="28"/>
+      <c r="AW7" s="28"/>
+      <c r="AX7" s="28"/>
+      <c r="AY7" s="28"/>
+      <c r="AZ7" s="28"/>
+      <c r="BA7" s="28"/>
+      <c r="BB7" s="28"/>
+      <c r="BC7" s="28"/>
+      <c r="BD7" s="28"/>
+      <c r="BE7" s="28"/>
+      <c r="BF7" s="28"/>
+      <c r="BG7" s="28"/>
+      <c r="BH7" s="28"/>
+      <c r="BI7" s="28"/>
+      <c r="BJ7" s="28"/>
+      <c r="BK7" s="28"/>
+      <c r="BL7" s="28"/>
+      <c r="BM7" s="28"/>
+      <c r="BN7" s="28"/>
+      <c r="BO7" s="28"/>
+      <c r="BP7" s="28"/>
+      <c r="BQ7" s="28"/>
+      <c r="BR7" s="28"/>
+      <c r="BS7" s="28"/>
+      <c r="BT7" s="28"/>
+      <c r="BU7" s="28"/>
+      <c r="BV7" s="28"/>
+      <c r="BW7" s="28"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="32">
+      <c r="B8" s="49"/>
+      <c r="C8" s="50">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="26">
-        <v>1</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="F8" s="25">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25">
         <v>2</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>3</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="25">
         <v>4</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="25">
         <v>5</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="25">
         <v>6</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="25">
         <v>7</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="25">
         <v>8</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="25">
         <v>9</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="25">
         <v>10</v>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="25">
         <v>11</v>
       </c>
-      <c r="Q8" s="26">
+      <c r="Q8" s="25">
         <v>12</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="25">
         <v>13</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="25">
         <v>14</v>
       </c>
-      <c r="T8" s="26">
+      <c r="T8" s="25">
         <v>15</v>
       </c>
-      <c r="U8" s="26">
+      <c r="U8" s="25">
         <v>16</v>
       </c>
-      <c r="V8" s="26">
+      <c r="V8" s="25">
         <v>17</v>
       </c>
-      <c r="W8" s="26">
+      <c r="W8" s="25">
         <v>18</v>
       </c>
-      <c r="X8" s="26">
+      <c r="X8" s="25">
         <v>19</v>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="25">
         <v>20</v>
       </c>
-      <c r="Z8" s="26">
+      <c r="Z8" s="25">
         <v>21</v>
       </c>
-      <c r="AA8" s="26">
+      <c r="AA8" s="25">
         <v>22</v>
       </c>
-      <c r="AB8" s="26">
+      <c r="AB8" s="25">
         <v>23</v>
       </c>
-      <c r="AC8" s="26">
+      <c r="AC8" s="25">
         <v>24</v>
       </c>
-      <c r="AD8" s="26">
+      <c r="AD8" s="25">
         <v>25</v>
       </c>
-      <c r="AE8" s="26">
+      <c r="AE8" s="25">
         <v>26</v>
       </c>
-      <c r="AF8" s="26">
+      <c r="AF8" s="25">
         <v>27</v>
       </c>
-      <c r="AG8" s="26">
+      <c r="AG8" s="25">
         <v>28</v>
       </c>
-      <c r="AH8" s="26">
+      <c r="AH8" s="25">
         <v>29</v>
       </c>
-      <c r="AI8" s="26">
+      <c r="AI8" s="25">
         <v>30</v>
       </c>
-      <c r="AJ8" s="26">
+      <c r="AJ8" s="25">
         <v>31</v>
       </c>
-      <c r="AK8" s="26">
+      <c r="AK8" s="25">
         <v>32</v>
       </c>
-      <c r="AL8" s="26">
+      <c r="AL8" s="25">
         <v>33</v>
       </c>
-      <c r="AM8" s="26">
+      <c r="AM8" s="25">
         <v>34</v>
       </c>
-      <c r="AN8" s="26">
+      <c r="AN8" s="25">
         <v>35</v>
       </c>
-      <c r="AO8" s="26">
+      <c r="AO8" s="25">
         <v>36</v>
       </c>
-      <c r="AP8" s="26">
+      <c r="AP8" s="25">
         <v>37</v>
       </c>
-      <c r="AQ8" s="26">
+      <c r="AQ8" s="25">
         <v>38</v>
       </c>
-      <c r="AR8" s="26">
+      <c r="AR8" s="25">
         <v>39</v>
       </c>
-      <c r="AS8" s="26">
+      <c r="AS8" s="25">
         <v>40</v>
       </c>
-      <c r="AT8" s="26">
+      <c r="AT8" s="25">
         <v>41</v>
       </c>
-      <c r="AU8" s="26">
+      <c r="AU8" s="25">
         <v>42</v>
       </c>
-      <c r="AV8" s="26">
+      <c r="AV8" s="25">
         <v>43</v>
       </c>
-      <c r="AW8" s="26">
+      <c r="AW8" s="25">
         <v>44</v>
       </c>
-      <c r="AX8" s="26">
+      <c r="AX8" s="25">
         <v>45</v>
       </c>
-      <c r="AY8" s="26">
+      <c r="AY8" s="25">
         <v>46</v>
       </c>
-      <c r="AZ8" s="26">
+      <c r="AZ8" s="25">
         <v>47</v>
       </c>
-      <c r="BA8" s="26">
+      <c r="BA8" s="25">
         <v>48</v>
       </c>
-      <c r="BB8" s="26">
+      <c r="BB8" s="25">
         <v>49</v>
       </c>
-      <c r="BC8" s="26">
+      <c r="BC8" s="25">
         <v>50</v>
       </c>
-      <c r="BD8" s="26">
+      <c r="BD8" s="25">
         <v>51</v>
       </c>
-      <c r="BE8" s="26">
+      <c r="BE8" s="25">
         <v>52</v>
       </c>
-      <c r="BF8" s="26">
+      <c r="BF8" s="25">
         <v>53</v>
       </c>
-      <c r="BG8" s="26">
+      <c r="BG8" s="25">
         <v>54</v>
       </c>
-      <c r="BH8" s="26">
+      <c r="BH8" s="25">
         <v>55</v>
       </c>
-      <c r="BI8" s="26">
+      <c r="BI8" s="25">
         <v>56</v>
       </c>
-      <c r="BJ8" s="26">
+      <c r="BJ8" s="25">
         <v>57</v>
       </c>
-      <c r="BK8" s="26">
+      <c r="BK8" s="25">
         <v>58</v>
       </c>
-      <c r="BL8" s="26">
+      <c r="BL8" s="25">
         <v>59</v>
       </c>
-      <c r="BM8" s="26">
+      <c r="BM8" s="25">
         <v>60</v>
       </c>
-      <c r="BN8" s="26">
+      <c r="BN8" s="25">
         <v>61</v>
       </c>
-      <c r="BO8" s="26">
+      <c r="BO8" s="25">
         <v>62</v>
       </c>
-      <c r="BP8" s="26">
+      <c r="BP8" s="25">
         <v>63</v>
       </c>
-      <c r="BQ8" s="26">
+      <c r="BQ8" s="25">
         <v>64</v>
       </c>
-      <c r="BR8" s="26">
+      <c r="BR8" s="25">
         <v>65</v>
       </c>
-      <c r="BS8" s="26">
+      <c r="BS8" s="25">
         <v>66</v>
       </c>
-      <c r="BT8" s="26">
+      <c r="BT8" s="25">
         <v>67</v>
       </c>
-      <c r="BU8" s="26">
+      <c r="BU8" s="25">
         <v>68</v>
       </c>
-      <c r="BV8" s="26">
+      <c r="BV8" s="25">
         <v>69</v>
       </c>
-      <c r="BW8" s="26">
+      <c r="BW8" s="25">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="27"/>
-      <c r="AC9" s="27"/>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27"/>
-      <c r="AF9" s="27"/>
-      <c r="AG9" s="27"/>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27"/>
-      <c r="AJ9" s="27"/>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="27"/>
-      <c r="AN9" s="27"/>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="27"/>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="27"/>
-      <c r="AT9" s="27"/>
-      <c r="AU9" s="27"/>
-      <c r="AV9" s="27"/>
-      <c r="AW9" s="27"/>
-      <c r="AX9" s="27"/>
-      <c r="AY9" s="27"/>
-      <c r="AZ9" s="27"/>
-      <c r="BA9" s="27"/>
-      <c r="BB9" s="27"/>
-      <c r="BC9" s="27"/>
-      <c r="BD9" s="27"/>
-      <c r="BE9" s="27"/>
-      <c r="BF9" s="27"/>
-      <c r="BG9" s="27"/>
-      <c r="BH9" s="27"/>
-      <c r="BI9" s="27"/>
-      <c r="BJ9" s="27"/>
-      <c r="BK9" s="27"/>
-      <c r="BL9" s="27"/>
-      <c r="BM9" s="27"/>
-      <c r="BN9" s="27"/>
-      <c r="BO9" s="27"/>
-      <c r="BP9" s="27"/>
-      <c r="BQ9" s="27"/>
-      <c r="BR9" s="27"/>
-      <c r="BS9" s="27"/>
-      <c r="BT9" s="27"/>
-      <c r="BU9" s="27"/>
-      <c r="BV9" s="27"/>
-      <c r="BW9" s="27"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="26"/>
+      <c r="AA9" s="26"/>
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26"/>
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26"/>
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="26"/>
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="26"/>
+      <c r="AN9" s="26"/>
+      <c r="AO9" s="26"/>
+      <c r="AP9" s="26"/>
+      <c r="AQ9" s="26"/>
+      <c r="AR9" s="26"/>
+      <c r="AS9" s="26"/>
+      <c r="AT9" s="26"/>
+      <c r="AU9" s="26"/>
+      <c r="AV9" s="26"/>
+      <c r="AW9" s="26"/>
+      <c r="AX9" s="26"/>
+      <c r="AY9" s="26"/>
+      <c r="AZ9" s="26"/>
+      <c r="BA9" s="26"/>
+      <c r="BB9" s="26"/>
+      <c r="BC9" s="26"/>
+      <c r="BD9" s="26"/>
+      <c r="BE9" s="26"/>
+      <c r="BF9" s="26"/>
+      <c r="BG9" s="26"/>
+      <c r="BH9" s="26"/>
+      <c r="BI9" s="26"/>
+      <c r="BJ9" s="26"/>
+      <c r="BK9" s="26"/>
+      <c r="BL9" s="26"/>
+      <c r="BM9" s="26"/>
+      <c r="BN9" s="26"/>
+      <c r="BO9" s="26"/>
+      <c r="BP9" s="26"/>
+      <c r="BQ9" s="26"/>
+      <c r="BR9" s="26"/>
+      <c r="BS9" s="26"/>
+      <c r="BT9" s="26"/>
+      <c r="BU9" s="26"/>
+      <c r="BV9" s="26"/>
+      <c r="BW9" s="26"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -3542,149 +3548,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
-      <c r="Y26" s="33"/>
-      <c r="Z26" s="33"/>
-      <c r="AA26" s="33"/>
-      <c r="AB26" s="33"/>
-      <c r="AC26" s="33"/>
-      <c r="AD26" s="33"/>
-      <c r="AE26" s="33"/>
-      <c r="AF26" s="33"/>
-      <c r="AG26" s="33"/>
-      <c r="AH26" s="33"/>
-      <c r="AI26" s="33"/>
-      <c r="AJ26" s="33"/>
-      <c r="AK26" s="33"/>
-      <c r="AL26" s="33"/>
-      <c r="AM26" s="33"/>
-      <c r="AN26" s="33"/>
-      <c r="AO26" s="33"/>
-      <c r="AP26" s="33"/>
-      <c r="AQ26" s="33"/>
-      <c r="AR26" s="33"/>
-      <c r="AS26" s="33"/>
-      <c r="AT26" s="33"/>
-      <c r="AU26" s="33"/>
-      <c r="AV26" s="33"/>
-      <c r="AW26" s="33"/>
-      <c r="AX26" s="33"/>
-      <c r="AY26" s="33"/>
-      <c r="AZ26" s="33"/>
-      <c r="BA26" s="33"/>
-      <c r="BB26" s="33"/>
-      <c r="BC26" s="33"/>
-      <c r="BD26" s="33"/>
-      <c r="BE26" s="33"/>
-      <c r="BF26" s="33"/>
-      <c r="BG26" s="33"/>
-      <c r="BH26" s="33"/>
-      <c r="BI26" s="33"/>
-      <c r="BJ26" s="33"/>
-      <c r="BK26" s="33"/>
-      <c r="BL26" s="33"/>
-      <c r="BM26" s="33"/>
-      <c r="BN26" s="33"/>
-      <c r="BO26" s="33"/>
-      <c r="BP26" s="33"/>
-      <c r="BQ26" s="33"/>
-      <c r="BR26" s="33"/>
-      <c r="BS26" s="33"/>
-      <c r="BT26" s="33"/>
-      <c r="BU26" s="33"/>
-      <c r="BV26" s="33"/>
-      <c r="BW26" s="33"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="40"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+      <c r="V26" s="40"/>
+      <c r="W26" s="40"/>
+      <c r="X26" s="40"/>
+      <c r="Y26" s="40"/>
+      <c r="Z26" s="40"/>
+      <c r="AA26" s="40"/>
+      <c r="AB26" s="40"/>
+      <c r="AC26" s="40"/>
+      <c r="AD26" s="40"/>
+      <c r="AE26" s="40"/>
+      <c r="AF26" s="40"/>
+      <c r="AG26" s="40"/>
+      <c r="AH26" s="40"/>
+      <c r="AI26" s="40"/>
+      <c r="AJ26" s="40"/>
+      <c r="AK26" s="40"/>
+      <c r="AL26" s="40"/>
+      <c r="AM26" s="40"/>
+      <c r="AN26" s="40"/>
+      <c r="AO26" s="40"/>
+      <c r="AP26" s="40"/>
+      <c r="AQ26" s="40"/>
+      <c r="AR26" s="40"/>
+      <c r="AS26" s="40"/>
+      <c r="AT26" s="40"/>
+      <c r="AU26" s="40"/>
+      <c r="AV26" s="40"/>
+      <c r="AW26" s="40"/>
+      <c r="AX26" s="40"/>
+      <c r="AY26" s="40"/>
+      <c r="AZ26" s="40"/>
+      <c r="BA26" s="40"/>
+      <c r="BB26" s="40"/>
+      <c r="BC26" s="40"/>
+      <c r="BD26" s="40"/>
+      <c r="BE26" s="40"/>
+      <c r="BF26" s="40"/>
+      <c r="BG26" s="40"/>
+      <c r="BH26" s="40"/>
+      <c r="BI26" s="40"/>
+      <c r="BJ26" s="40"/>
+      <c r="BK26" s="40"/>
+      <c r="BL26" s="40"/>
+      <c r="BM26" s="40"/>
+      <c r="BN26" s="40"/>
+      <c r="BO26" s="40"/>
+      <c r="BP26" s="40"/>
+      <c r="BQ26" s="40"/>
+      <c r="BR26" s="40"/>
+      <c r="BS26" s="40"/>
+      <c r="BT26" s="40"/>
+      <c r="BU26" s="40"/>
+      <c r="BV26" s="40"/>
+      <c r="BW26" s="40"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="56"/>
-      <c r="R27" s="56"/>
-      <c r="S27" s="56"/>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56"/>
-      <c r="Y27" s="56"/>
-      <c r="Z27" s="56"/>
-      <c r="AA27" s="56"/>
-      <c r="AB27" s="56"/>
-      <c r="AC27" s="56"/>
-      <c r="AD27" s="56"/>
-      <c r="AE27" s="56"/>
-      <c r="AF27" s="56"/>
-      <c r="AG27" s="56"/>
-      <c r="AH27" s="56"/>
-      <c r="AI27" s="56"/>
-      <c r="AJ27" s="56"/>
-      <c r="AK27" s="56"/>
-      <c r="AL27" s="56"/>
-      <c r="AM27" s="56"/>
-      <c r="AN27" s="56"/>
-      <c r="AO27" s="56"/>
-      <c r="AP27" s="56"/>
-      <c r="AQ27" s="56"/>
-      <c r="AR27" s="56"/>
-      <c r="AS27" s="56"/>
-      <c r="AT27" s="56"/>
-      <c r="AU27" s="56"/>
-      <c r="AV27" s="56"/>
-      <c r="AW27" s="56"/>
-      <c r="AX27" s="56"/>
-      <c r="AY27" s="56"/>
-      <c r="AZ27" s="56"/>
-      <c r="BA27" s="56"/>
-      <c r="BB27" s="56"/>
-      <c r="BC27" s="56"/>
-      <c r="BD27" s="56"/>
-      <c r="BE27" s="56"/>
-      <c r="BF27" s="56"/>
-      <c r="BG27" s="56"/>
-      <c r="BH27" s="56"/>
-      <c r="BI27" s="56"/>
-      <c r="BJ27" s="56"/>
-      <c r="BK27" s="56"/>
-      <c r="BL27" s="56"/>
-      <c r="BM27" s="56"/>
-      <c r="BN27" s="56"/>
-      <c r="BO27" s="56"/>
-      <c r="BP27" s="56"/>
-      <c r="BQ27" s="56"/>
-      <c r="BR27" s="56"/>
-      <c r="BS27" s="56"/>
-      <c r="BT27" s="56"/>
-      <c r="BU27" s="56"/>
-      <c r="BV27" s="56"/>
-      <c r="BW27" s="56"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="24"/>
+      <c r="T27" s="24"/>
+      <c r="U27" s="24"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="24"/>
+      <c r="X27" s="24"/>
+      <c r="Y27" s="24"/>
+      <c r="Z27" s="24"/>
+      <c r="AA27" s="24"/>
+      <c r="AB27" s="24"/>
+      <c r="AC27" s="24"/>
+      <c r="AD27" s="24"/>
+      <c r="AE27" s="24"/>
+      <c r="AF27" s="24"/>
+      <c r="AG27" s="24"/>
+      <c r="AH27" s="24"/>
+      <c r="AI27" s="24"/>
+      <c r="AJ27" s="24"/>
+      <c r="AK27" s="24"/>
+      <c r="AL27" s="24"/>
+      <c r="AM27" s="24"/>
+      <c r="AN27" s="24"/>
+      <c r="AO27" s="24"/>
+      <c r="AP27" s="24"/>
+      <c r="AQ27" s="24"/>
+      <c r="AR27" s="24"/>
+      <c r="AS27" s="24"/>
+      <c r="AT27" s="24"/>
+      <c r="AU27" s="24"/>
+      <c r="AV27" s="24"/>
+      <c r="AW27" s="24"/>
+      <c r="AX27" s="24"/>
+      <c r="AY27" s="24"/>
+      <c r="AZ27" s="24"/>
+      <c r="BA27" s="24"/>
+      <c r="BB27" s="24"/>
+      <c r="BC27" s="24"/>
+      <c r="BD27" s="24"/>
+      <c r="BE27" s="24"/>
+      <c r="BF27" s="24"/>
+      <c r="BG27" s="24"/>
+      <c r="BH27" s="24"/>
+      <c r="BI27" s="24"/>
+      <c r="BJ27" s="24"/>
+      <c r="BK27" s="24"/>
+      <c r="BL27" s="24"/>
+      <c r="BM27" s="24"/>
+      <c r="BN27" s="24"/>
+      <c r="BO27" s="24"/>
+      <c r="BP27" s="24"/>
+      <c r="BQ27" s="24"/>
+      <c r="BR27" s="24"/>
+      <c r="BS27" s="24"/>
+      <c r="BT27" s="24"/>
+      <c r="BU27" s="24"/>
+      <c r="BV27" s="24"/>
+      <c r="BW27" s="24"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3714,7 +3720,156 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="172">
+  <mergeCells count="173">
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M2:M7"/>
     <mergeCell ref="F27:S27"/>
     <mergeCell ref="T27:AW27"/>
     <mergeCell ref="AX27:BW27"/>
@@ -3737,156 +3892,8 @@
     <mergeCell ref="BB2:BB7"/>
     <mergeCell ref="BC2:BC7"/>
     <mergeCell ref="M8:M9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E26:BW26"/>
     <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="AF1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3919,7 +3926,7 @@
       <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="38" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="60" t="s">
@@ -3943,7 +3950,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
+      <c r="A4" s="38"/>
       <c r="B4" s="62"/>
       <c r="C4" s="63"/>
       <c r="D4" s="65"/>

--- a/Journals/bootstrap ჟურნალი.xlsx
+++ b/Journals/bootstrap ჟურნალი.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\Mermisi-main\Journals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\0 -Mermisi-main\Journals\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="cms" sheetId="1" r:id="rId1"/>
@@ -109,9 +109,6 @@
     <t>გავაცდინე ეს საათი</t>
   </si>
   <si>
-    <t>წინა მასწავლებელმა ჩაატარა</t>
-  </si>
-  <si>
     <t>მარტი</t>
   </si>
   <si>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t>18,09,2026</t>
+  </si>
+  <si>
+    <t>თვე დამთავრდა</t>
   </si>
 </sst>
 </file>
@@ -262,12 +262,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -287,6 +281,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -511,22 +511,30 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -535,123 +543,121 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -883,965 +889,971 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="31"/>
-      <c r="F1" s="46">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41"/>
+      <c r="F1" s="25">
         <v>7</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="23">
-        <v>1</v>
-      </c>
-      <c r="J1" s="46">
+      <c r="G1" s="54"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="22">
+        <v>1</v>
+      </c>
+      <c r="J1" s="25">
         <v>2</v>
       </c>
-      <c r="K1" s="48"/>
-      <c r="L1" s="46">
+      <c r="K1" s="26"/>
+      <c r="L1" s="25">
         <v>2</v>
       </c>
-      <c r="M1" s="48"/>
-      <c r="N1" s="46">
+      <c r="M1" s="26"/>
+      <c r="N1" s="25">
         <v>2</v>
       </c>
-      <c r="O1" s="48"/>
-      <c r="P1" s="46">
+      <c r="O1" s="26"/>
+      <c r="P1" s="25">
         <v>2</v>
       </c>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="46">
+      <c r="Q1" s="26"/>
+      <c r="R1" s="25">
         <v>2</v>
       </c>
-      <c r="S1" s="48"/>
-      <c r="T1" s="46">
+      <c r="S1" s="26"/>
+      <c r="T1" s="25">
         <v>2</v>
       </c>
-      <c r="U1" s="48"/>
-      <c r="V1" s="46">
+      <c r="U1" s="26"/>
+      <c r="V1" s="25">
         <v>2</v>
       </c>
-      <c r="W1" s="48"/>
-      <c r="X1" s="46">
+      <c r="W1" s="26"/>
+      <c r="X1" s="25">
         <v>2</v>
       </c>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="46">
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="25">
         <v>2</v>
       </c>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="46">
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="25">
         <v>2</v>
       </c>
-      <c r="AE1" s="48"/>
-      <c r="AF1" s="46">
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="25">
         <v>2</v>
       </c>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="46">
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="25">
         <v>2</v>
       </c>
-      <c r="AI1" s="48"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="22"/>
-      <c r="AM1" s="22"/>
-      <c r="AN1" s="22"/>
-      <c r="AO1" s="22"/>
-      <c r="AP1" s="22"/>
-      <c r="AQ1" s="22"/>
-      <c r="AR1" s="22"/>
-      <c r="AS1" s="22"/>
-      <c r="AT1" s="22"/>
-      <c r="AU1" s="22"/>
-      <c r="AV1" s="22"/>
-      <c r="AW1" s="22"/>
-      <c r="AX1" s="22"/>
-      <c r="AY1" s="22"/>
-      <c r="AZ1" s="22"/>
-      <c r="BA1" s="22"/>
-      <c r="BB1" s="22"/>
-      <c r="BC1" s="22"/>
-      <c r="BD1" s="22"/>
-      <c r="BE1" s="22"/>
-      <c r="BF1" s="22"/>
-      <c r="BG1" s="22"/>
-      <c r="BH1" s="22"/>
-      <c r="BI1" s="22"/>
-      <c r="BJ1" s="22"/>
-      <c r="BK1" s="22"/>
-      <c r="BL1" s="22"/>
-      <c r="BM1" s="22"/>
-      <c r="BN1" s="22"/>
-      <c r="BO1" s="22"/>
-      <c r="BP1" s="22"/>
-      <c r="BQ1" s="22"/>
-      <c r="BR1" s="22"/>
-      <c r="BS1" s="22"/>
-      <c r="BT1" s="22"/>
-      <c r="BU1" s="22"/>
-      <c r="BV1" s="22"/>
-      <c r="BW1" s="22"/>
+      <c r="AI1" s="26"/>
+      <c r="AJ1" s="25">
+        <v>2</v>
+      </c>
+      <c r="AK1" s="26"/>
+      <c r="AL1" s="21"/>
+      <c r="AM1" s="21"/>
+      <c r="AN1" s="21"/>
+      <c r="AO1" s="21"/>
+      <c r="AP1" s="21"/>
+      <c r="AQ1" s="21"/>
+      <c r="AR1" s="21"/>
+      <c r="AS1" s="21"/>
+      <c r="AT1" s="21"/>
+      <c r="AU1" s="21"/>
+      <c r="AV1" s="21"/>
+      <c r="AW1" s="21"/>
+      <c r="AX1" s="21"/>
+      <c r="AY1" s="21"/>
+      <c r="AZ1" s="21"/>
+      <c r="BA1" s="21"/>
+      <c r="BB1" s="21"/>
+      <c r="BC1" s="21"/>
+      <c r="BD1" s="21"/>
+      <c r="BE1" s="21"/>
+      <c r="BF1" s="21"/>
+      <c r="BG1" s="21"/>
+      <c r="BH1" s="21"/>
+      <c r="BI1" s="21"/>
+      <c r="BJ1" s="21"/>
+      <c r="BK1" s="21"/>
+      <c r="BL1" s="21"/>
+      <c r="BM1" s="21"/>
+      <c r="BN1" s="21"/>
+      <c r="BO1" s="21"/>
+      <c r="BP1" s="21"/>
+      <c r="BQ1" s="21"/>
+      <c r="BR1" s="21"/>
+      <c r="BS1" s="21"/>
+      <c r="BT1" s="21"/>
+      <c r="BU1" s="21"/>
+      <c r="BV1" s="21"/>
+      <c r="BW1" s="21"/>
       <c r="BX1" s="2">
         <f>SUM(F1:BW1)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="27">
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="23">
         <v>46274</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="23">
         <v>46274</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="23">
         <v>46274</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="23">
         <v>46276</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="23">
         <v>46279</v>
       </c>
-      <c r="K2" s="27">
+      <c r="K2" s="23">
         <v>46279</v>
       </c>
-      <c r="L2" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="27">
+      <c r="L2" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="23">
         <v>46286</v>
       </c>
-      <c r="O2" s="27">
+      <c r="O2" s="23">
         <v>46286</v>
       </c>
-      <c r="P2" s="27">
+      <c r="P2" s="23">
         <v>46290</v>
       </c>
-      <c r="Q2" s="27">
+      <c r="Q2" s="23">
         <v>46290</v>
       </c>
-      <c r="R2" s="27">
+      <c r="R2" s="65">
         <v>46293</v>
       </c>
-      <c r="S2" s="27">
+      <c r="S2" s="65">
         <v>46293</v>
       </c>
-      <c r="T2" s="27">
+      <c r="T2" s="23">
         <v>46297</v>
       </c>
-      <c r="U2" s="27">
+      <c r="U2" s="23">
         <v>46297</v>
       </c>
-      <c r="V2" s="53">
+      <c r="V2" s="29">
         <v>46300</v>
       </c>
-      <c r="W2" s="53">
+      <c r="W2" s="29">
         <v>46300</v>
       </c>
-      <c r="X2" s="27">
+      <c r="X2" s="23">
         <v>46304</v>
       </c>
-      <c r="Y2" s="27">
+      <c r="Y2" s="23">
         <v>46304</v>
       </c>
-      <c r="Z2" s="27">
+      <c r="Z2" s="23">
         <v>46307</v>
       </c>
-      <c r="AA2" s="27">
+      <c r="AA2" s="23">
         <v>46307</v>
       </c>
-      <c r="AB2" s="55">
+      <c r="AB2" s="31">
         <v>46311</v>
       </c>
-      <c r="AC2" s="55">
+      <c r="AC2" s="31">
         <v>46311</v>
       </c>
-      <c r="AD2" s="27">
+      <c r="AD2" s="23">
         <v>46314</v>
       </c>
-      <c r="AE2" s="27">
+      <c r="AE2" s="23">
         <v>46314</v>
       </c>
-      <c r="AF2" s="27">
+      <c r="AF2" s="23">
         <v>46318</v>
       </c>
-      <c r="AG2" s="27">
+      <c r="AG2" s="23">
         <v>46318</v>
       </c>
-      <c r="AH2" s="27">
+      <c r="AH2" s="23">
         <v>46321</v>
       </c>
-      <c r="AI2" s="27">
+      <c r="AI2" s="23">
         <v>46321</v>
       </c>
-      <c r="AJ2" s="27"/>
-      <c r="AK2" s="27"/>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="27"/>
-      <c r="AO2" s="27"/>
-      <c r="AP2" s="27"/>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="27"/>
-      <c r="AS2" s="27"/>
-      <c r="AT2" s="27"/>
-      <c r="AU2" s="27"/>
-      <c r="AV2" s="27"/>
-      <c r="AW2" s="27"/>
-      <c r="AX2" s="27"/>
-      <c r="AY2" s="27"/>
-      <c r="AZ2" s="27"/>
-      <c r="BA2" s="27"/>
-      <c r="BB2" s="27"/>
-      <c r="BC2" s="27"/>
-      <c r="BD2" s="27"/>
-      <c r="BE2" s="27"/>
-      <c r="BF2" s="27"/>
-      <c r="BG2" s="27"/>
-      <c r="BH2" s="27"/>
-      <c r="BI2" s="27"/>
-      <c r="BJ2" s="27"/>
-      <c r="BK2" s="27"/>
-      <c r="BL2" s="27"/>
-      <c r="BM2" s="27"/>
-      <c r="BN2" s="27"/>
-      <c r="BO2" s="27"/>
-      <c r="BP2" s="27"/>
-      <c r="BQ2" s="27"/>
-      <c r="BR2" s="27"/>
-      <c r="BS2" s="27"/>
-      <c r="BT2" s="27"/>
-      <c r="BU2" s="27"/>
-      <c r="BV2" s="27"/>
-      <c r="BW2" s="27"/>
+      <c r="AJ2" s="65">
+        <v>46325</v>
+      </c>
+      <c r="AK2" s="65">
+        <v>46325</v>
+      </c>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
+      <c r="AQ2" s="23"/>
+      <c r="AR2" s="23"/>
+      <c r="AS2" s="23"/>
+      <c r="AT2" s="23"/>
+      <c r="AU2" s="23"/>
+      <c r="AV2" s="23"/>
+      <c r="AW2" s="23"/>
+      <c r="AX2" s="23"/>
+      <c r="AY2" s="23"/>
+      <c r="AZ2" s="23"/>
+      <c r="BA2" s="23"/>
+      <c r="BB2" s="23"/>
+      <c r="BC2" s="23"/>
+      <c r="BD2" s="23"/>
+      <c r="BE2" s="23"/>
+      <c r="BF2" s="23"/>
+      <c r="BG2" s="23"/>
+      <c r="BH2" s="23"/>
+      <c r="BI2" s="23"/>
+      <c r="BJ2" s="23"/>
+      <c r="BK2" s="23"/>
+      <c r="BL2" s="23"/>
+      <c r="BM2" s="23"/>
+      <c r="BN2" s="23"/>
+      <c r="BO2" s="23"/>
+      <c r="BP2" s="23"/>
+      <c r="BQ2" s="23"/>
+      <c r="BR2" s="23"/>
+      <c r="BS2" s="23"/>
+      <c r="BT2" s="23"/>
+      <c r="BU2" s="23"/>
+      <c r="BV2" s="23"/>
+      <c r="BW2" s="23"/>
     </row>
     <row r="3" spans="1:76" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="55"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="27"/>
-      <c r="AN3" s="27"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="27"/>
-      <c r="AS3" s="27"/>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27"/>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="27"/>
-      <c r="BF3" s="27"/>
-      <c r="BG3" s="27"/>
-      <c r="BH3" s="27"/>
-      <c r="BI3" s="27"/>
-      <c r="BJ3" s="27"/>
-      <c r="BK3" s="27"/>
-      <c r="BL3" s="27"/>
-      <c r="BM3" s="27"/>
-      <c r="BN3" s="27"/>
-      <c r="BO3" s="27"/>
-      <c r="BP3" s="27"/>
-      <c r="BQ3" s="27"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27"/>
+      <c r="A3" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AG3" s="23"/>
+      <c r="AH3" s="23"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="65"/>
+      <c r="AK3" s="65"/>
+      <c r="AL3" s="23"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="23"/>
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="23"/>
+      <c r="AY3" s="23"/>
+      <c r="AZ3" s="23"/>
+      <c r="BA3" s="23"/>
+      <c r="BB3" s="23"/>
+      <c r="BC3" s="23"/>
+      <c r="BD3" s="23"/>
+      <c r="BE3" s="23"/>
+      <c r="BF3" s="23"/>
+      <c r="BG3" s="23"/>
+      <c r="BH3" s="23"/>
+      <c r="BI3" s="23"/>
+      <c r="BJ3" s="23"/>
+      <c r="BK3" s="23"/>
+      <c r="BL3" s="23"/>
+      <c r="BM3" s="23"/>
+      <c r="BN3" s="23"/>
+      <c r="BO3" s="23"/>
+      <c r="BP3" s="23"/>
+      <c r="BQ3" s="23"/>
+      <c r="BR3" s="23"/>
+      <c r="BS3" s="23"/>
+      <c r="BT3" s="23"/>
+      <c r="BU3" s="23"/>
+      <c r="BV3" s="23"/>
+      <c r="BW3" s="23"/>
     </row>
     <row r="4" spans="1:76" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40" t="s">
+      <c r="A4" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="53"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="55"/>
-      <c r="AC4" s="55"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="27"/>
-      <c r="AH4" s="27"/>
-      <c r="AI4" s="27"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="27"/>
-      <c r="AL4" s="27"/>
-      <c r="AM4" s="27"/>
-      <c r="AN4" s="27"/>
-      <c r="AO4" s="27"/>
-      <c r="AP4" s="27"/>
-      <c r="AQ4" s="27"/>
-      <c r="AR4" s="27"/>
-      <c r="AS4" s="27"/>
-      <c r="AT4" s="27"/>
-      <c r="AU4" s="27"/>
-      <c r="AV4" s="27"/>
-      <c r="AW4" s="27"/>
-      <c r="AX4" s="27"/>
-      <c r="AY4" s="27"/>
-      <c r="AZ4" s="27"/>
-      <c r="BA4" s="27"/>
-      <c r="BB4" s="27"/>
-      <c r="BC4" s="27"/>
-      <c r="BD4" s="27"/>
-      <c r="BE4" s="27"/>
-      <c r="BF4" s="27"/>
-      <c r="BG4" s="27"/>
-      <c r="BH4" s="27"/>
-      <c r="BI4" s="27"/>
-      <c r="BJ4" s="27"/>
-      <c r="BK4" s="27"/>
-      <c r="BL4" s="27"/>
-      <c r="BM4" s="27"/>
-      <c r="BN4" s="27"/>
-      <c r="BO4" s="27"/>
-      <c r="BP4" s="27"/>
-      <c r="BQ4" s="27"/>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="27"/>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="27"/>
-      <c r="BV4" s="27"/>
-      <c r="BW4" s="27"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="23"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="23"/>
+      <c r="AE4" s="23"/>
+      <c r="AF4" s="23"/>
+      <c r="AG4" s="23"/>
+      <c r="AH4" s="23"/>
+      <c r="AI4" s="23"/>
+      <c r="AJ4" s="65"/>
+      <c r="AK4" s="65"/>
+      <c r="AL4" s="23"/>
+      <c r="AM4" s="23"/>
+      <c r="AN4" s="23"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="23"/>
+      <c r="AS4" s="23"/>
+      <c r="AT4" s="23"/>
+      <c r="AU4" s="23"/>
+      <c r="AV4" s="23"/>
+      <c r="AW4" s="23"/>
+      <c r="AX4" s="23"/>
+      <c r="AY4" s="23"/>
+      <c r="AZ4" s="23"/>
+      <c r="BA4" s="23"/>
+      <c r="BB4" s="23"/>
+      <c r="BC4" s="23"/>
+      <c r="BD4" s="23"/>
+      <c r="BE4" s="23"/>
+      <c r="BF4" s="23"/>
+      <c r="BG4" s="23"/>
+      <c r="BH4" s="23"/>
+      <c r="BI4" s="23"/>
+      <c r="BJ4" s="23"/>
+      <c r="BK4" s="23"/>
+      <c r="BL4" s="23"/>
+      <c r="BM4" s="23"/>
+      <c r="BN4" s="23"/>
+      <c r="BO4" s="23"/>
+      <c r="BP4" s="23"/>
+      <c r="BQ4" s="23"/>
+      <c r="BR4" s="23"/>
+      <c r="BS4" s="23"/>
+      <c r="BT4" s="23"/>
+      <c r="BU4" s="23"/>
+      <c r="BV4" s="23"/>
+      <c r="BW4" s="23"/>
     </row>
     <row r="5" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="43">
+      <c r="B5" s="50"/>
+      <c r="C5" s="51">
         <v>60</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="53"/>
-      <c r="W5" s="53"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="55"/>
-      <c r="AC5" s="55"/>
-      <c r="AD5" s="27"/>
-      <c r="AE5" s="27"/>
-      <c r="AF5" s="27"/>
-      <c r="AG5" s="27"/>
-      <c r="AH5" s="27"/>
-      <c r="AI5" s="27"/>
-      <c r="AJ5" s="27"/>
-      <c r="AK5" s="27"/>
-      <c r="AL5" s="27"/>
-      <c r="AM5" s="27"/>
-      <c r="AN5" s="27"/>
-      <c r="AO5" s="27"/>
-      <c r="AP5" s="27"/>
-      <c r="AQ5" s="27"/>
-      <c r="AR5" s="27"/>
-      <c r="AS5" s="27"/>
-      <c r="AT5" s="27"/>
-      <c r="AU5" s="27"/>
-      <c r="AV5" s="27"/>
-      <c r="AW5" s="27"/>
-      <c r="AX5" s="27"/>
-      <c r="AY5" s="27"/>
-      <c r="AZ5" s="27"/>
-      <c r="BA5" s="27"/>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="27"/>
-      <c r="BD5" s="27"/>
-      <c r="BE5" s="27"/>
-      <c r="BF5" s="27"/>
-      <c r="BG5" s="27"/>
-      <c r="BH5" s="27"/>
-      <c r="BI5" s="27"/>
-      <c r="BJ5" s="27"/>
-      <c r="BK5" s="27"/>
-      <c r="BL5" s="27"/>
-      <c r="BM5" s="27"/>
-      <c r="BN5" s="27"/>
-      <c r="BO5" s="27"/>
-      <c r="BP5" s="27"/>
-      <c r="BQ5" s="27"/>
-      <c r="BR5" s="27"/>
-      <c r="BS5" s="27"/>
-      <c r="BT5" s="27"/>
-      <c r="BU5" s="27"/>
-      <c r="BV5" s="27"/>
-      <c r="BW5" s="27"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="23"/>
+      <c r="AG5" s="23"/>
+      <c r="AH5" s="23"/>
+      <c r="AI5" s="23"/>
+      <c r="AJ5" s="65"/>
+      <c r="AK5" s="65"/>
+      <c r="AL5" s="23"/>
+      <c r="AM5" s="23"/>
+      <c r="AN5" s="23"/>
+      <c r="AO5" s="23"/>
+      <c r="AP5" s="23"/>
+      <c r="AQ5" s="23"/>
+      <c r="AR5" s="23"/>
+      <c r="AS5" s="23"/>
+      <c r="AT5" s="23"/>
+      <c r="AU5" s="23"/>
+      <c r="AV5" s="23"/>
+      <c r="AW5" s="23"/>
+      <c r="AX5" s="23"/>
+      <c r="AY5" s="23"/>
+      <c r="AZ5" s="23"/>
+      <c r="BA5" s="23"/>
+      <c r="BB5" s="23"/>
+      <c r="BC5" s="23"/>
+      <c r="BD5" s="23"/>
+      <c r="BE5" s="23"/>
+      <c r="BF5" s="23"/>
+      <c r="BG5" s="23"/>
+      <c r="BH5" s="23"/>
+      <c r="BI5" s="23"/>
+      <c r="BJ5" s="23"/>
+      <c r="BK5" s="23"/>
+      <c r="BL5" s="23"/>
+      <c r="BM5" s="23"/>
+      <c r="BN5" s="23"/>
+      <c r="BO5" s="23"/>
+      <c r="BP5" s="23"/>
+      <c r="BQ5" s="23"/>
+      <c r="BR5" s="23"/>
+      <c r="BS5" s="23"/>
+      <c r="BT5" s="23"/>
+      <c r="BU5" s="23"/>
+      <c r="BV5" s="23"/>
+      <c r="BW5" s="23"/>
     </row>
     <row r="6" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43">
+      <c r="B6" s="50"/>
+      <c r="C6" s="51">
         <v>4</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="53"/>
-      <c r="W6" s="53"/>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="55"/>
-      <c r="AC6" s="55"/>
-      <c r="AD6" s="27"/>
-      <c r="AE6" s="27"/>
-      <c r="AF6" s="27"/>
-      <c r="AG6" s="27"/>
-      <c r="AH6" s="27"/>
-      <c r="AI6" s="27"/>
-      <c r="AJ6" s="27"/>
-      <c r="AK6" s="27"/>
-      <c r="AL6" s="27"/>
-      <c r="AM6" s="27"/>
-      <c r="AN6" s="27"/>
-      <c r="AO6" s="27"/>
-      <c r="AP6" s="27"/>
-      <c r="AQ6" s="27"/>
-      <c r="AR6" s="27"/>
-      <c r="AS6" s="27"/>
-      <c r="AT6" s="27"/>
-      <c r="AU6" s="27"/>
-      <c r="AV6" s="27"/>
-      <c r="AW6" s="27"/>
-      <c r="AX6" s="27"/>
-      <c r="AY6" s="27"/>
-      <c r="AZ6" s="27"/>
-      <c r="BA6" s="27"/>
-      <c r="BB6" s="27"/>
-      <c r="BC6" s="27"/>
-      <c r="BD6" s="27"/>
-      <c r="BE6" s="27"/>
-      <c r="BF6" s="27"/>
-      <c r="BG6" s="27"/>
-      <c r="BH6" s="27"/>
-      <c r="BI6" s="27"/>
-      <c r="BJ6" s="27"/>
-      <c r="BK6" s="27"/>
-      <c r="BL6" s="27"/>
-      <c r="BM6" s="27"/>
-      <c r="BN6" s="27"/>
-      <c r="BO6" s="27"/>
-      <c r="BP6" s="27"/>
-      <c r="BQ6" s="27"/>
-      <c r="BR6" s="27"/>
-      <c r="BS6" s="27"/>
-      <c r="BT6" s="27"/>
-      <c r="BU6" s="27"/>
-      <c r="BV6" s="27"/>
-      <c r="BW6" s="27"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="23"/>
+      <c r="Y6" s="23"/>
+      <c r="Z6" s="23"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="23"/>
+      <c r="AE6" s="23"/>
+      <c r="AF6" s="23"/>
+      <c r="AG6" s="23"/>
+      <c r="AH6" s="23"/>
+      <c r="AI6" s="23"/>
+      <c r="AJ6" s="65"/>
+      <c r="AK6" s="65"/>
+      <c r="AL6" s="23"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="23"/>
+      <c r="AP6" s="23"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="23"/>
+      <c r="AS6" s="23"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="23"/>
+      <c r="AV6" s="23"/>
+      <c r="AW6" s="23"/>
+      <c r="AX6" s="23"/>
+      <c r="AY6" s="23"/>
+      <c r="AZ6" s="23"/>
+      <c r="BA6" s="23"/>
+      <c r="BB6" s="23"/>
+      <c r="BC6" s="23"/>
+      <c r="BD6" s="23"/>
+      <c r="BE6" s="23"/>
+      <c r="BF6" s="23"/>
+      <c r="BG6" s="23"/>
+      <c r="BH6" s="23"/>
+      <c r="BI6" s="23"/>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="23"/>
+      <c r="BM6" s="23"/>
+      <c r="BN6" s="23"/>
+      <c r="BO6" s="23"/>
+      <c r="BP6" s="23"/>
+      <c r="BQ6" s="23"/>
+      <c r="BR6" s="23"/>
+      <c r="BS6" s="23"/>
+      <c r="BT6" s="23"/>
+      <c r="BU6" s="23"/>
+      <c r="BV6" s="23"/>
+      <c r="BW6" s="23"/>
     </row>
     <row r="7" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="43">
+      <c r="B7" s="53"/>
+      <c r="C7" s="51">
         <v>11</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="54"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="56"/>
-      <c r="AC7" s="56"/>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="28"/>
-      <c r="AH7" s="28"/>
-      <c r="AI7" s="28"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="28"/>
-      <c r="AL7" s="28"/>
-      <c r="AM7" s="28"/>
-      <c r="AN7" s="28"/>
-      <c r="AO7" s="28"/>
-      <c r="AP7" s="28"/>
-      <c r="AQ7" s="28"/>
-      <c r="AR7" s="28"/>
-      <c r="AS7" s="28"/>
-      <c r="AT7" s="28"/>
-      <c r="AU7" s="28"/>
-      <c r="AV7" s="28"/>
-      <c r="AW7" s="28"/>
-      <c r="AX7" s="28"/>
-      <c r="AY7" s="28"/>
-      <c r="AZ7" s="28"/>
-      <c r="BA7" s="28"/>
-      <c r="BB7" s="28"/>
-      <c r="BC7" s="28"/>
-      <c r="BD7" s="28"/>
-      <c r="BE7" s="28"/>
-      <c r="BF7" s="28"/>
-      <c r="BG7" s="28"/>
-      <c r="BH7" s="28"/>
-      <c r="BI7" s="28"/>
-      <c r="BJ7" s="28"/>
-      <c r="BK7" s="28"/>
-      <c r="BL7" s="28"/>
-      <c r="BM7" s="28"/>
-      <c r="BN7" s="28"/>
-      <c r="BO7" s="28"/>
-      <c r="BP7" s="28"/>
-      <c r="BQ7" s="28"/>
-      <c r="BR7" s="28"/>
-      <c r="BS7" s="28"/>
-      <c r="BT7" s="28"/>
-      <c r="BU7" s="28"/>
-      <c r="BV7" s="28"/>
-      <c r="BW7" s="28"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="66"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
+      <c r="AH7" s="24"/>
+      <c r="AI7" s="24"/>
+      <c r="AJ7" s="66"/>
+      <c r="AK7" s="66"/>
+      <c r="AL7" s="24"/>
+      <c r="AM7" s="24"/>
+      <c r="AN7" s="24"/>
+      <c r="AO7" s="24"/>
+      <c r="AP7" s="24"/>
+      <c r="AQ7" s="24"/>
+      <c r="AR7" s="24"/>
+      <c r="AS7" s="24"/>
+      <c r="AT7" s="24"/>
+      <c r="AU7" s="24"/>
+      <c r="AV7" s="24"/>
+      <c r="AW7" s="24"/>
+      <c r="AX7" s="24"/>
+      <c r="AY7" s="24"/>
+      <c r="AZ7" s="24"/>
+      <c r="BA7" s="24"/>
+      <c r="BB7" s="24"/>
+      <c r="BC7" s="24"/>
+      <c r="BD7" s="24"/>
+      <c r="BE7" s="24"/>
+      <c r="BF7" s="24"/>
+      <c r="BG7" s="24"/>
+      <c r="BH7" s="24"/>
+      <c r="BI7" s="24"/>
+      <c r="BJ7" s="24"/>
+      <c r="BK7" s="24"/>
+      <c r="BL7" s="24"/>
+      <c r="BM7" s="24"/>
+      <c r="BN7" s="24"/>
+      <c r="BO7" s="24"/>
+      <c r="BP7" s="24"/>
+      <c r="BQ7" s="24"/>
+      <c r="BR7" s="24"/>
+      <c r="BS7" s="24"/>
+      <c r="BT7" s="24"/>
+      <c r="BU7" s="24"/>
+      <c r="BV7" s="24"/>
+      <c r="BW7" s="24"/>
     </row>
     <row r="8" spans="1:76" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="41"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="25">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25">
+      <c r="F8" s="27">
+        <v>1</v>
+      </c>
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="27">
         <v>3</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="27">
         <v>5</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="27">
         <v>7</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="27">
         <v>8</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="27">
         <v>9</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="27">
         <v>10</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="27">
         <v>11</v>
       </c>
-      <c r="Q8" s="25">
+      <c r="Q8" s="27">
         <v>12</v>
       </c>
-      <c r="R8" s="25">
+      <c r="R8" s="27">
         <v>13</v>
       </c>
-      <c r="S8" s="25">
+      <c r="S8" s="27">
         <v>14</v>
       </c>
-      <c r="T8" s="25">
+      <c r="T8" s="27">
         <v>15</v>
       </c>
-      <c r="U8" s="25">
+      <c r="U8" s="27">
         <v>16</v>
       </c>
-      <c r="V8" s="25">
+      <c r="V8" s="27">
         <v>17</v>
       </c>
-      <c r="W8" s="25">
+      <c r="W8" s="27">
         <v>18</v>
       </c>
-      <c r="X8" s="25">
+      <c r="X8" s="27">
         <v>19</v>
       </c>
-      <c r="Y8" s="25">
+      <c r="Y8" s="27">
         <v>20</v>
       </c>
-      <c r="Z8" s="25">
+      <c r="Z8" s="27">
         <v>21</v>
       </c>
-      <c r="AA8" s="25">
+      <c r="AA8" s="27">
         <v>22</v>
       </c>
-      <c r="AB8" s="25">
+      <c r="AB8" s="27">
         <v>23</v>
       </c>
-      <c r="AC8" s="25">
+      <c r="AC8" s="27">
         <v>24</v>
       </c>
-      <c r="AD8" s="25">
+      <c r="AD8" s="27">
         <v>25</v>
       </c>
-      <c r="AE8" s="25">
+      <c r="AE8" s="27">
         <v>26</v>
       </c>
-      <c r="AF8" s="25">
+      <c r="AF8" s="27">
         <v>27</v>
       </c>
-      <c r="AG8" s="25">
+      <c r="AG8" s="27">
         <v>28</v>
       </c>
-      <c r="AH8" s="25">
+      <c r="AH8" s="27">
         <v>29</v>
       </c>
-      <c r="AI8" s="25">
+      <c r="AI8" s="27">
         <v>30</v>
       </c>
-      <c r="AJ8" s="25">
+      <c r="AJ8" s="27">
         <v>31</v>
       </c>
-      <c r="AK8" s="25">
+      <c r="AK8" s="27">
         <v>32</v>
       </c>
-      <c r="AL8" s="25">
+      <c r="AL8" s="27">
         <v>33</v>
       </c>
-      <c r="AM8" s="25">
+      <c r="AM8" s="27">
         <v>34</v>
       </c>
-      <c r="AN8" s="25">
+      <c r="AN8" s="27">
         <v>35</v>
       </c>
-      <c r="AO8" s="25">
+      <c r="AO8" s="27">
         <v>36</v>
       </c>
-      <c r="AP8" s="25">
+      <c r="AP8" s="27">
         <v>37</v>
       </c>
-      <c r="AQ8" s="25">
+      <c r="AQ8" s="27">
         <v>38</v>
       </c>
-      <c r="AR8" s="25">
+      <c r="AR8" s="27">
         <v>39</v>
       </c>
-      <c r="AS8" s="25">
+      <c r="AS8" s="27">
         <v>40</v>
       </c>
-      <c r="AT8" s="25">
+      <c r="AT8" s="27">
         <v>41</v>
       </c>
-      <c r="AU8" s="25">
+      <c r="AU8" s="27">
         <v>42</v>
       </c>
-      <c r="AV8" s="25">
+      <c r="AV8" s="27">
         <v>43</v>
       </c>
-      <c r="AW8" s="25">
+      <c r="AW8" s="27">
         <v>44</v>
       </c>
-      <c r="AX8" s="25">
+      <c r="AX8" s="27">
         <v>45</v>
       </c>
-      <c r="AY8" s="25">
+      <c r="AY8" s="27">
         <v>46</v>
       </c>
-      <c r="AZ8" s="25">
+      <c r="AZ8" s="27">
         <v>47</v>
       </c>
-      <c r="BA8" s="25">
+      <c r="BA8" s="27">
         <v>48</v>
       </c>
-      <c r="BB8" s="25">
+      <c r="BB8" s="27">
         <v>49</v>
       </c>
-      <c r="BC8" s="25">
+      <c r="BC8" s="27">
         <v>50</v>
       </c>
-      <c r="BD8" s="25">
+      <c r="BD8" s="27">
         <v>51</v>
       </c>
-      <c r="BE8" s="25">
+      <c r="BE8" s="27">
         <v>52</v>
       </c>
-      <c r="BF8" s="25">
+      <c r="BF8" s="27">
         <v>53</v>
       </c>
-      <c r="BG8" s="25">
+      <c r="BG8" s="27">
         <v>54</v>
       </c>
-      <c r="BH8" s="25">
+      <c r="BH8" s="27">
         <v>55</v>
       </c>
-      <c r="BI8" s="25">
+      <c r="BI8" s="27">
         <v>56</v>
       </c>
-      <c r="BJ8" s="25">
+      <c r="BJ8" s="27">
         <v>57</v>
       </c>
-      <c r="BK8" s="25">
+      <c r="BK8" s="27">
         <v>58</v>
       </c>
-      <c r="BL8" s="25">
+      <c r="BL8" s="27">
         <v>59</v>
       </c>
-      <c r="BM8" s="25">
+      <c r="BM8" s="27">
         <v>60</v>
       </c>
-      <c r="BN8" s="25">
+      <c r="BN8" s="27">
         <v>61</v>
       </c>
-      <c r="BO8" s="25">
+      <c r="BO8" s="27">
         <v>62</v>
       </c>
-      <c r="BP8" s="25">
+      <c r="BP8" s="27">
         <v>63</v>
       </c>
-      <c r="BQ8" s="25">
+      <c r="BQ8" s="27">
         <v>64</v>
       </c>
-      <c r="BR8" s="25">
+      <c r="BR8" s="27">
         <v>65</v>
       </c>
-      <c r="BS8" s="25">
+      <c r="BS8" s="27">
         <v>66</v>
       </c>
-      <c r="BT8" s="25">
+      <c r="BT8" s="27">
         <v>67</v>
       </c>
-      <c r="BU8" s="25">
+      <c r="BU8" s="27">
         <v>68</v>
       </c>
-      <c r="BV8" s="25">
+      <c r="BV8" s="27">
         <v>69</v>
       </c>
-      <c r="BW8" s="25">
+      <c r="BW8" s="27">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="26"/>
-      <c r="AD9" s="26"/>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="26"/>
-      <c r="AK9" s="26"/>
-      <c r="AL9" s="26"/>
-      <c r="AM9" s="26"/>
-      <c r="AN9" s="26"/>
-      <c r="AO9" s="26"/>
-      <c r="AP9" s="26"/>
-      <c r="AQ9" s="26"/>
-      <c r="AR9" s="26"/>
-      <c r="AS9" s="26"/>
-      <c r="AT9" s="26"/>
-      <c r="AU9" s="26"/>
-      <c r="AV9" s="26"/>
-      <c r="AW9" s="26"/>
-      <c r="AX9" s="26"/>
-      <c r="AY9" s="26"/>
-      <c r="AZ9" s="26"/>
-      <c r="BA9" s="26"/>
-      <c r="BB9" s="26"/>
-      <c r="BC9" s="26"/>
-      <c r="BD9" s="26"/>
-      <c r="BE9" s="26"/>
-      <c r="BF9" s="26"/>
-      <c r="BG9" s="26"/>
-      <c r="BH9" s="26"/>
-      <c r="BI9" s="26"/>
-      <c r="BJ9" s="26"/>
-      <c r="BK9" s="26"/>
-      <c r="BL9" s="26"/>
-      <c r="BM9" s="26"/>
-      <c r="BN9" s="26"/>
-      <c r="BO9" s="26"/>
-      <c r="BP9" s="26"/>
-      <c r="BQ9" s="26"/>
-      <c r="BR9" s="26"/>
-      <c r="BS9" s="26"/>
-      <c r="BT9" s="26"/>
-      <c r="BU9" s="26"/>
-      <c r="BV9" s="26"/>
-      <c r="BW9" s="26"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
     </row>
     <row r="10" spans="1:76" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38"/>
-      <c r="B10" s="51"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -2081,7 +2093,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
@@ -3548,149 +3560,149 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="50"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="40"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="40"/>
-      <c r="U26" s="40"/>
-      <c r="V26" s="40"/>
-      <c r="W26" s="40"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
-      <c r="AD26" s="40"/>
-      <c r="AE26" s="40"/>
-      <c r="AF26" s="40"/>
-      <c r="AG26" s="40"/>
-      <c r="AH26" s="40"/>
-      <c r="AI26" s="40"/>
-      <c r="AJ26" s="40"/>
-      <c r="AK26" s="40"/>
-      <c r="AL26" s="40"/>
-      <c r="AM26" s="40"/>
-      <c r="AN26" s="40"/>
-      <c r="AO26" s="40"/>
-      <c r="AP26" s="40"/>
-      <c r="AQ26" s="40"/>
-      <c r="AR26" s="40"/>
-      <c r="AS26" s="40"/>
-      <c r="AT26" s="40"/>
-      <c r="AU26" s="40"/>
-      <c r="AV26" s="40"/>
-      <c r="AW26" s="40"/>
-      <c r="AX26" s="40"/>
-      <c r="AY26" s="40"/>
-      <c r="AZ26" s="40"/>
-      <c r="BA26" s="40"/>
-      <c r="BB26" s="40"/>
-      <c r="BC26" s="40"/>
-      <c r="BD26" s="40"/>
-      <c r="BE26" s="40"/>
-      <c r="BF26" s="40"/>
-      <c r="BG26" s="40"/>
-      <c r="BH26" s="40"/>
-      <c r="BI26" s="40"/>
-      <c r="BJ26" s="40"/>
-      <c r="BK26" s="40"/>
-      <c r="BL26" s="40"/>
-      <c r="BM26" s="40"/>
-      <c r="BN26" s="40"/>
-      <c r="BO26" s="40"/>
-      <c r="BP26" s="40"/>
-      <c r="BQ26" s="40"/>
-      <c r="BR26" s="40"/>
-      <c r="BS26" s="40"/>
-      <c r="BT26" s="40"/>
-      <c r="BU26" s="40"/>
-      <c r="BV26" s="40"/>
-      <c r="BW26" s="40"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="49"/>
+      <c r="W26" s="49"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="49"/>
+      <c r="AA26" s="49"/>
+      <c r="AB26" s="49"/>
+      <c r="AC26" s="49"/>
+      <c r="AD26" s="49"/>
+      <c r="AE26" s="49"/>
+      <c r="AF26" s="49"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="49"/>
+      <c r="AI26" s="49"/>
+      <c r="AJ26" s="49"/>
+      <c r="AK26" s="49"/>
+      <c r="AL26" s="49"/>
+      <c r="AM26" s="49"/>
+      <c r="AN26" s="49"/>
+      <c r="AO26" s="49"/>
+      <c r="AP26" s="49"/>
+      <c r="AQ26" s="49"/>
+      <c r="AR26" s="49"/>
+      <c r="AS26" s="49"/>
+      <c r="AT26" s="49"/>
+      <c r="AU26" s="49"/>
+      <c r="AV26" s="49"/>
+      <c r="AW26" s="49"/>
+      <c r="AX26" s="49"/>
+      <c r="AY26" s="49"/>
+      <c r="AZ26" s="49"/>
+      <c r="BA26" s="49"/>
+      <c r="BB26" s="49"/>
+      <c r="BC26" s="49"/>
+      <c r="BD26" s="49"/>
+      <c r="BE26" s="49"/>
+      <c r="BF26" s="49"/>
+      <c r="BG26" s="49"/>
+      <c r="BH26" s="49"/>
+      <c r="BI26" s="49"/>
+      <c r="BJ26" s="49"/>
+      <c r="BK26" s="49"/>
+      <c r="BL26" s="49"/>
+      <c r="BM26" s="49"/>
+      <c r="BN26" s="49"/>
+      <c r="BO26" s="49"/>
+      <c r="BP26" s="49"/>
+      <c r="BQ26" s="49"/>
+      <c r="BR26" s="49"/>
+      <c r="BS26" s="49"/>
+      <c r="BT26" s="49"/>
+      <c r="BU26" s="49"/>
+      <c r="BV26" s="49"/>
+      <c r="BW26" s="49"/>
     </row>
     <row r="27" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
-      <c r="R27" s="24"/>
-      <c r="S27" s="24"/>
-      <c r="T27" s="24"/>
-      <c r="U27" s="24"/>
-      <c r="V27" s="24"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-      <c r="AA27" s="24"/>
-      <c r="AB27" s="24"/>
-      <c r="AC27" s="24"/>
-      <c r="AD27" s="24"/>
-      <c r="AE27" s="24"/>
-      <c r="AF27" s="24"/>
-      <c r="AG27" s="24"/>
-      <c r="AH27" s="24"/>
-      <c r="AI27" s="24"/>
-      <c r="AJ27" s="24"/>
-      <c r="AK27" s="24"/>
-      <c r="AL27" s="24"/>
-      <c r="AM27" s="24"/>
-      <c r="AN27" s="24"/>
-      <c r="AO27" s="24"/>
-      <c r="AP27" s="24"/>
-      <c r="AQ27" s="24"/>
-      <c r="AR27" s="24"/>
-      <c r="AS27" s="24"/>
-      <c r="AT27" s="24"/>
-      <c r="AU27" s="24"/>
-      <c r="AV27" s="24"/>
-      <c r="AW27" s="24"/>
-      <c r="AX27" s="24"/>
-      <c r="AY27" s="24"/>
-      <c r="AZ27" s="24"/>
-      <c r="BA27" s="24"/>
-      <c r="BB27" s="24"/>
-      <c r="BC27" s="24"/>
-      <c r="BD27" s="24"/>
-      <c r="BE27" s="24"/>
-      <c r="BF27" s="24"/>
-      <c r="BG27" s="24"/>
-      <c r="BH27" s="24"/>
-      <c r="BI27" s="24"/>
-      <c r="BJ27" s="24"/>
-      <c r="BK27" s="24"/>
-      <c r="BL27" s="24"/>
-      <c r="BM27" s="24"/>
-      <c r="BN27" s="24"/>
-      <c r="BO27" s="24"/>
-      <c r="BP27" s="24"/>
-      <c r="BQ27" s="24"/>
-      <c r="BR27" s="24"/>
-      <c r="BS27" s="24"/>
-      <c r="BT27" s="24"/>
-      <c r="BU27" s="24"/>
-      <c r="BV27" s="24"/>
-      <c r="BW27" s="24"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="55"/>
+      <c r="P27" s="55"/>
+      <c r="Q27" s="55"/>
+      <c r="R27" s="55"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="55"/>
+      <c r="U27" s="55"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="55"/>
+      <c r="X27" s="55"/>
+      <c r="Y27" s="55"/>
+      <c r="Z27" s="55"/>
+      <c r="AA27" s="55"/>
+      <c r="AB27" s="55"/>
+      <c r="AC27" s="55"/>
+      <c r="AD27" s="55"/>
+      <c r="AE27" s="55"/>
+      <c r="AF27" s="55"/>
+      <c r="AG27" s="55"/>
+      <c r="AH27" s="55"/>
+      <c r="AI27" s="55"/>
+      <c r="AJ27" s="55"/>
+      <c r="AK27" s="55"/>
+      <c r="AL27" s="55"/>
+      <c r="AM27" s="55"/>
+      <c r="AN27" s="55"/>
+      <c r="AO27" s="55"/>
+      <c r="AP27" s="55"/>
+      <c r="AQ27" s="55"/>
+      <c r="AR27" s="55"/>
+      <c r="AS27" s="55"/>
+      <c r="AT27" s="55"/>
+      <c r="AU27" s="55"/>
+      <c r="AV27" s="55"/>
+      <c r="AW27" s="55"/>
+      <c r="AX27" s="55"/>
+      <c r="AY27" s="55"/>
+      <c r="AZ27" s="55"/>
+      <c r="BA27" s="55"/>
+      <c r="BB27" s="55"/>
+      <c r="BC27" s="55"/>
+      <c r="BD27" s="55"/>
+      <c r="BE27" s="55"/>
+      <c r="BF27" s="55"/>
+      <c r="BG27" s="55"/>
+      <c r="BH27" s="55"/>
+      <c r="BI27" s="55"/>
+      <c r="BJ27" s="55"/>
+      <c r="BK27" s="55"/>
+      <c r="BL27" s="55"/>
+      <c r="BM27" s="55"/>
+      <c r="BN27" s="55"/>
+      <c r="BO27" s="55"/>
+      <c r="BP27" s="55"/>
+      <c r="BQ27" s="55"/>
+      <c r="BR27" s="55"/>
+      <c r="BS27" s="55"/>
+      <c r="BT27" s="55"/>
+      <c r="BU27" s="55"/>
+      <c r="BV27" s="55"/>
+      <c r="BW27" s="55"/>
     </row>
     <row r="28" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="1">
@@ -3698,7 +3710,7 @@
       </c>
     </row>
     <row r="29" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="21">
+      <c r="E29" s="20">
         <f>SUM(E11:E18)/8</f>
         <v>0.19791666666666669</v>
       </c>
@@ -3708,91 +3720,96 @@
       </c>
     </row>
     <row r="30" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AJ30" s="17"/>
-      <c r="AK30" s="16" t="s">
-        <v>29</v>
+      <c r="AJ30" s="19"/>
+      <c r="AK30" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:75" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AJ31" s="20"/>
+      <c r="AJ31" s="67"/>
       <c r="AK31" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="173">
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AP2:AP7"/>
+  <mergeCells count="174">
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:BW27"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="E26:BW26"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
     <mergeCell ref="AN8:AN9"/>
     <mergeCell ref="AO8:AO9"/>
     <mergeCell ref="AP8:AP9"/>
@@ -3817,83 +3834,79 @@
     <mergeCell ref="AR8:AR9"/>
     <mergeCell ref="AS8:AS9"/>
     <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:BW27"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="E26:BW26"/>
-    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3915,49 +3928,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="58" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="64" t="s">
+      <c r="C3" s="60"/>
+      <c r="D3" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="F3" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="57" t="s">
+      <c r="H3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="58" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="38"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="58"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="57"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -3969,23 +3982,23 @@
       <c r="C5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <f>COUNTIF(cms!F11:G11,0)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <f>COUNTIF(cms!H11:Y11,0)</f>
         <v>8</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <f>COUNTIF(cms!Z11:AY11,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="17">
         <f>COUNTIF(cms!AZ11:BU11,0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="19"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -3997,23 +4010,23 @@
       <c r="C6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <f>COUNTIF(cms!F12:G12,0)</f>
         <v>2</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <f>COUNTIF(cms!H12:Y12,0)</f>
         <v>13</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <f>COUNTIF(cms!Z12:AY12,0)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <f>COUNTIF(cms!AZ12:BU12,0)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -4025,23 +4038,23 @@
       <c r="C7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <f>COUNTIF(cms!F13:G13,0)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <f>COUNTIF(cms!H13:Y13,0)</f>
         <v>12</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <f>COUNTIF(cms!Z13:AY13,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <f>COUNTIF(cms!AZ13:BU13,0)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="19"/>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -4053,23 +4066,23 @@
       <c r="C8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <f>COUNTIF(cms!F14:G14,0)</f>
         <v>2</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <f>COUNTIF(cms!H14:Y14,0)</f>
         <v>13</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>COUNTIF(cms!Z14:AY14,0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <f>COUNTIF(cms!AZ14:BU14,0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -4081,23 +4094,23 @@
       <c r="C9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <f>COUNTIF(cms!F15:G15,0)</f>
         <v>2</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <f>COUNTIF(cms!H15:Y15,0)</f>
         <v>13</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <f>COUNTIF(cms!Z15:AY15,0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <f>COUNTIF(cms!AZ15:BU15,0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="19"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
@@ -4109,23 +4122,23 @@
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <f>COUNTIF(cms!F16:G16,0)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <f>COUNTIF(cms!H16:Y16,0)</f>
         <v>10</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <f>COUNTIF(cms!Z16:AY16,0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <f>COUNTIF(cms!AZ16:BU16,0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
@@ -4137,23 +4150,23 @@
       <c r="C11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <f>COUNTIF(cms!F17:G17,0)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <f>COUNTIF(cms!H17:Y17,0)</f>
         <v>5</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>COUNTIF(cms!Z17:AY17,0)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f>COUNTIF(cms!AZ17:BU17,0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="19"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
@@ -4165,23 +4178,23 @@
       <c r="C12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <f>COUNTIF(cms!F18:G18,0)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <f>COUNTIF(cms!H18:Y18,0)</f>
         <v>13</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>COUNTIF(cms!Z18:AY18,0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <f>COUNTIF(cms!AZ18:BU18,0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="19"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
@@ -4189,11 +4202,11 @@
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
@@ -4201,11 +4214,11 @@
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
@@ -4213,11 +4226,11 @@
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
@@ -4225,11 +4238,11 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -4237,11 +4250,11 @@
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
@@ -4249,11 +4262,11 @@
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
@@ -4261,11 +4274,11 @@
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
@@ -4273,11 +4286,11 @@
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="9">
